--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -1,31 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0921DAA7-4E37-4799-B0B3-E25650BDAFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="57480" yWindow="4965" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>##var</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +106,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +393,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:J1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0921DAA7-4E37-4799-B0B3-E25650BDAFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61921884-FE3D-4D34-9B4B-2110875A3D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="4965" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5840" yWindow="2060" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,7 +62,180 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Item</t>
+    <t>Remark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NameKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DescKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>白萝卜</t>
+  </si>
+  <si>
+    <t>嫩豆腐</t>
+  </si>
+  <si>
+    <t>IconSoftTofuName</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>IconPotatoName</t>
+  </si>
+  <si>
+    <t>青椒</t>
+  </si>
+  <si>
+    <t>IconGreenBellPepperName</t>
+  </si>
+  <si>
+    <t>大白菜</t>
+  </si>
+  <si>
+    <t>IconChineseCabbageName</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>IconTomatoName</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>IconEggName</t>
+  </si>
+  <si>
+    <t>五花肉</t>
+  </si>
+  <si>
+    <t>IconPorkBellyName</t>
+  </si>
+  <si>
+    <t>冬瓜</t>
+  </si>
+  <si>
+    <t>IconWinterMelonName</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>IconBroccoliName</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>IconEggplantName</t>
+  </si>
+  <si>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>IconChineseYamName</t>
+  </si>
+  <si>
+    <t>香菇</t>
+  </si>
+  <si>
+    <t>IconShiitakeMushroomName</t>
+  </si>
+  <si>
+    <t>芹菜</t>
+  </si>
+  <si>
+    <t>IconCeleryName</t>
+  </si>
+  <si>
+    <t>腐竹</t>
+  </si>
+  <si>
+    <t>IconDriedBeanCurdStickName</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>IconCarrotName</t>
+  </si>
+  <si>
+    <t>生菜</t>
+  </si>
+  <si>
+    <t>IconLettuceName</t>
+  </si>
+  <si>
+    <t>鸡胸肉</t>
+  </si>
+  <si>
+    <t>IconChickenBreastName</t>
+  </si>
+  <si>
+    <t>豆角</t>
+  </si>
+  <si>
+    <t>IconLongBeanName</t>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconWhiteRadishName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -70,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,16 +258,43 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2329"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -102,17 +302,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,50 +621,498 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="29.08203125" customWidth="1"/>
+    <col min="4" max="4" width="41.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>999</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>100001</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>999</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>100002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>999</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>100003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>100004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>999</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>100005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>999</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>100006</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>999</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>100007</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>999</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>100008</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>999</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>100009</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>100010</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>999</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>100011</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>999</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>100012</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>999</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>100013</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>999</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>100014</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>999</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>100015</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>999</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>100016</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>999</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>100017</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>999</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>100018</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>999</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C1:J1"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61921884-FE3D-4D34-9B4B-2110875A3D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4A7B3F-8D5C-42E2-BCD1-6B78F0483333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5840" yWindow="2060" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="2030" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,111 +111,57 @@
     <t>嫩豆腐</t>
   </si>
   <si>
-    <t>IconSoftTofuName</t>
-  </si>
-  <si>
     <t>土豆</t>
   </si>
   <si>
-    <t>IconPotatoName</t>
-  </si>
-  <si>
     <t>青椒</t>
   </si>
   <si>
-    <t>IconGreenBellPepperName</t>
-  </si>
-  <si>
     <t>大白菜</t>
   </si>
   <si>
-    <t>IconChineseCabbageName</t>
-  </si>
-  <si>
     <t>番茄</t>
   </si>
   <si>
-    <t>IconTomatoName</t>
-  </si>
-  <si>
     <t>鸡蛋</t>
   </si>
   <si>
-    <t>IconEggName</t>
-  </si>
-  <si>
     <t>五花肉</t>
   </si>
   <si>
-    <t>IconPorkBellyName</t>
-  </si>
-  <si>
     <t>冬瓜</t>
   </si>
   <si>
-    <t>IconWinterMelonName</t>
-  </si>
-  <si>
     <t>西兰花</t>
   </si>
   <si>
-    <t>IconBroccoliName</t>
-  </si>
-  <si>
     <t>茄子</t>
   </si>
   <si>
-    <t>IconEggplantName</t>
-  </si>
-  <si>
     <t>山药</t>
   </si>
   <si>
-    <t>IconChineseYamName</t>
-  </si>
-  <si>
     <t>香菇</t>
   </si>
   <si>
-    <t>IconShiitakeMushroomName</t>
-  </si>
-  <si>
     <t>芹菜</t>
   </si>
   <si>
-    <t>IconCeleryName</t>
-  </si>
-  <si>
     <t>腐竹</t>
   </si>
   <si>
-    <t>IconDriedBeanCurdStickName</t>
-  </si>
-  <si>
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>IconCarrotName</t>
-  </si>
-  <si>
     <t>生菜</t>
   </si>
   <si>
-    <t>IconLettuceName</t>
-  </si>
-  <si>
     <t>鸡胸肉</t>
   </si>
   <si>
-    <t>IconChickenBreastName</t>
-  </si>
-  <si>
     <t>豆角</t>
   </si>
   <si>
-    <t>IconLongBeanName</t>
-  </si>
-  <si>
     <t>TbLocalzationKeyData#sep=+</t>
   </si>
   <si>
@@ -236,6 +182,89 @@
   </si>
   <si>
     <t>InventoryItem+IconWhiteRadishName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconSoftTofuName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconPotatoName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconGreenBellPepperName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconChineseCabbageName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconTomatoName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconEggName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconPorkBellyName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconWinterMelonName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconBroccoliName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconEggplantName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconChineseYamName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconShiitakeMushroomName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconCeleryName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconDriedBeanCurdStickName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconCarrotName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconLettuceName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconChickenBreastName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconLongBeanName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconWhiteRadishDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconWhiteRadish</t>
+  </si>
+  <si>
+    <t>物品图标</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -625,9 +654,9 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="29.08203125" customWidth="1"/>
-    <col min="4" max="4" width="41.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="41.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.1640625" customWidth="1"/>
     <col min="9" max="9" width="16.08203125" customWidth="1"/>
   </cols>
@@ -643,13 +672,13 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>13</v>
@@ -671,14 +700,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>54</v>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
@@ -687,7 +716,7 @@
         <v>15</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -701,16 +730,19 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
@@ -720,10 +752,15 @@
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="2"/>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
@@ -741,10 +778,15 @@
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2"/>
+      <c r="D5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
@@ -760,12 +802,17 @@
         <v>100002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
@@ -781,12 +828,17 @@
         <v>100003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G7" s="6">
         <v>0</v>
       </c>
@@ -802,12 +854,17 @@
         <v>100004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
@@ -823,12 +880,17 @@
         <v>100005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
@@ -844,12 +906,17 @@
         <v>100006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
@@ -865,12 +932,17 @@
         <v>100007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G11" s="6">
         <v>0</v>
       </c>
@@ -886,12 +958,17 @@
         <v>100008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G12" s="6">
         <v>0</v>
       </c>
@@ -907,12 +984,17 @@
         <v>100009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G13" s="6">
         <v>0</v>
       </c>
@@ -928,12 +1010,17 @@
         <v>100010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G14" s="6">
         <v>0</v>
       </c>
@@ -949,12 +1036,17 @@
         <v>100011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G15" s="6">
         <v>0</v>
       </c>
@@ -970,12 +1062,17 @@
         <v>100012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G16" s="6">
         <v>0</v>
       </c>
@@ -991,12 +1088,17 @@
         <v>100013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G17" s="6">
         <v>0</v>
       </c>
@@ -1012,12 +1114,17 @@
         <v>100014</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G18" s="6">
         <v>0</v>
       </c>
@@ -1033,12 +1140,17 @@
         <v>100015</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G19" s="6">
         <v>0</v>
       </c>
@@ -1054,12 +1166,17 @@
         <v>100016</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G20" s="6">
         <v>0</v>
       </c>
@@ -1075,12 +1192,17 @@
         <v>100017</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G21" s="6">
         <v>0</v>
       </c>
@@ -1096,12 +1218,17 @@
         <v>100018</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G22" s="6">
         <v>0</v>
       </c>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4A7B3F-8D5C-42E2-BCD1-6B78F0483333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772168AF-07FC-4A90-B903-43DA5CA59E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="2030" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1530" yWindow="2460" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MaterialItemData" sheetId="1" r:id="rId1"/>
+    <sheet name="ConsumablesItemData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="74">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -265,6 +266,48 @@
   </si>
   <si>
     <t>物品图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品表ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄炒蛋</t>
+  </si>
+  <si>
+    <t>IconTomatoAndEggStirFryName</t>
+  </si>
+  <si>
+    <t>RewardItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000+50/10000+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryItem+IconTomatoAndEggStirFry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=/),TbRewardItemData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售价格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -272,7 +315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +344,30 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -350,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -369,6 +436,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="29.08203125" customWidth="1"/>
@@ -661,7 +746,7 @@
     <col min="9" max="9" width="16.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -689,8 +774,11 @@
       <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J1" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -718,8 +806,11 @@
       <c r="I2" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -744,8 +835,11 @@
       <c r="I3" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J3" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>100000</v>
       </c>
@@ -770,8 +864,11 @@
       <c r="I4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>100001</v>
       </c>
@@ -796,8 +893,11 @@
       <c r="I5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>100002</v>
       </c>
@@ -822,8 +922,11 @@
       <c r="I6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>100003</v>
       </c>
@@ -848,8 +951,11 @@
       <c r="I7" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>100004</v>
       </c>
@@ -874,8 +980,11 @@
       <c r="I8" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>100005</v>
       </c>
@@ -900,8 +1009,11 @@
       <c r="I9" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>100006</v>
       </c>
@@ -926,8 +1038,11 @@
       <c r="I10" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>100007</v>
       </c>
@@ -952,8 +1067,11 @@
       <c r="I11" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>100008</v>
       </c>
@@ -978,8 +1096,11 @@
       <c r="I12" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>100009</v>
       </c>
@@ -1004,8 +1125,11 @@
       <c r="I13" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>100010</v>
       </c>
@@ -1030,8 +1154,11 @@
       <c r="I14" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>100011</v>
       </c>
@@ -1056,8 +1183,11 @@
       <c r="I15" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>100012</v>
       </c>
@@ -1082,8 +1212,11 @@
       <c r="I16" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>100013</v>
       </c>
@@ -1108,8 +1241,11 @@
       <c r="I17" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>100014</v>
       </c>
@@ -1134,8 +1270,11 @@
       <c r="I18" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>100015</v>
       </c>
@@ -1160,8 +1299,11 @@
       <c r="I19" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>100016</v>
       </c>
@@ -1186,8 +1328,11 @@
       <c r="I20" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>100017</v>
       </c>
@@ -1212,8 +1357,11 @@
       <c r="I21" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>100018</v>
       </c>
@@ -1238,6 +1386,135 @@
       <c r="I22" s="5">
         <v>1</v>
       </c>
+      <c r="J22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="7">
+        <v>120006</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>999</v>
+      </c>
+      <c r="I23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>100</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51E28B37-8729-4856-8B3C-FB17AADDF4AC}">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" customWidth="1"/>
+    <col min="4" max="4" width="37.5" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.58203125" customWidth="1"/>
+    <col min="8" max="8" width="15.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="11">
+        <v>120006</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772168AF-07FC-4A90-B903-43DA5CA59E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA9D21D-9C43-4DB3-8F66-1C7E09D61CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1530" yWindow="2460" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4380" yWindow="1300" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialItemData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="95">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -308,6 +308,71 @@
   </si>
   <si>
     <t>出售价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+101</t>
+  </si>
+  <si>
+    <t>1+102</t>
+  </si>
+  <si>
+    <t>1+103</t>
+  </si>
+  <si>
+    <t>1+104</t>
+  </si>
+  <si>
+    <t>1+105</t>
+  </si>
+  <si>
+    <t>1+106</t>
+  </si>
+  <si>
+    <t>1+107</t>
+  </si>
+  <si>
+    <t>1+108</t>
+  </si>
+  <si>
+    <t>1+109</t>
+  </si>
+  <si>
+    <t>1+110</t>
+  </si>
+  <si>
+    <t>1+111</t>
+  </si>
+  <si>
+    <t>1+112</t>
+  </si>
+  <si>
+    <t>1+113</t>
+  </si>
+  <si>
+    <t>1+114</t>
+  </si>
+  <si>
+    <t>1+115</t>
+  </si>
+  <si>
+    <t>1+116</t>
+  </si>
+  <si>
+    <t>1+117</t>
+  </si>
+  <si>
+    <t>1+118</t>
+  </si>
+  <si>
+    <t>1+119</t>
+  </si>
+  <si>
+    <t>TbRewardPropData#sep=+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -370,7 +435,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,6 +451,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,8 +523,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,6 +815,7 @@
     <col min="6" max="6" width="42.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.1640625" customWidth="1"/>
     <col min="9" max="9" width="16.08203125" customWidth="1"/>
+    <col min="10" max="10" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
@@ -774,7 +846,7 @@
       <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -806,8 +878,8 @@
       <c r="I2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>15</v>
+      <c r="J2" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -864,8 +936,8 @@
       <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="1">
-        <v>100</v>
+      <c r="J4" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -893,8 +965,8 @@
       <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="1">
-        <v>100</v>
+      <c r="J5" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -922,8 +994,8 @@
       <c r="I6" s="5">
         <v>1</v>
       </c>
-      <c r="J6" s="1">
-        <v>100</v>
+      <c r="J6" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -951,8 +1023,8 @@
       <c r="I7" s="5">
         <v>1</v>
       </c>
-      <c r="J7" s="1">
-        <v>100</v>
+      <c r="J7" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -980,8 +1052,8 @@
       <c r="I8" s="5">
         <v>1</v>
       </c>
-      <c r="J8" s="1">
-        <v>100</v>
+      <c r="J8" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1009,8 +1081,8 @@
       <c r="I9" s="5">
         <v>1</v>
       </c>
-      <c r="J9" s="1">
-        <v>100</v>
+      <c r="J9" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1038,8 +1110,8 @@
       <c r="I10" s="5">
         <v>1</v>
       </c>
-      <c r="J10" s="1">
-        <v>100</v>
+      <c r="J10" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1067,8 +1139,8 @@
       <c r="I11" s="5">
         <v>1</v>
       </c>
-      <c r="J11" s="1">
-        <v>100</v>
+      <c r="J11" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1096,8 +1168,8 @@
       <c r="I12" s="5">
         <v>1</v>
       </c>
-      <c r="J12" s="1">
-        <v>100</v>
+      <c r="J12" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1125,8 +1197,8 @@
       <c r="I13" s="5">
         <v>1</v>
       </c>
-      <c r="J13" s="1">
-        <v>100</v>
+      <c r="J13" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1154,8 +1226,8 @@
       <c r="I14" s="5">
         <v>1</v>
       </c>
-      <c r="J14" s="1">
-        <v>100</v>
+      <c r="J14" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1183,8 +1255,8 @@
       <c r="I15" s="5">
         <v>1</v>
       </c>
-      <c r="J15" s="1">
-        <v>100</v>
+      <c r="J15" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1212,8 +1284,8 @@
       <c r="I16" s="5">
         <v>1</v>
       </c>
-      <c r="J16" s="1">
-        <v>100</v>
+      <c r="J16" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1241,8 +1313,8 @@
       <c r="I17" s="5">
         <v>1</v>
       </c>
-      <c r="J17" s="1">
-        <v>100</v>
+      <c r="J17" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1270,8 +1342,8 @@
       <c r="I18" s="5">
         <v>1</v>
       </c>
-      <c r="J18" s="1">
-        <v>100</v>
+      <c r="J18" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1299,8 +1371,8 @@
       <c r="I19" s="5">
         <v>1</v>
       </c>
-      <c r="J19" s="1">
-        <v>100</v>
+      <c r="J19" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1328,8 +1400,8 @@
       <c r="I20" s="5">
         <v>1</v>
       </c>
-      <c r="J20" s="1">
-        <v>100</v>
+      <c r="J20" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1357,8 +1429,8 @@
       <c r="I21" s="5">
         <v>1</v>
       </c>
-      <c r="J21" s="1">
-        <v>100</v>
+      <c r="J21" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1386,8 +1458,8 @@
       <c r="I22" s="5">
         <v>1</v>
       </c>
-      <c r="J22" s="1">
-        <v>100</v>
+      <c r="J22" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1407,7 +1479,7 @@
         <v>60</v>
       </c>
       <c r="G23" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3">
         <v>999</v>
@@ -1415,8 +1487,8 @@
       <c r="I23" s="5">
         <v>1</v>
       </c>
-      <c r="J23" s="1">
-        <v>100</v>
+      <c r="J23" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA9D21D-9C43-4DB3-8F66-1C7E09D61CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E85E645-BE12-4297-914C-8A896E86EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="1300" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialItemData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -262,9 +262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IconWhiteRadish</t>
-  </si>
-  <si>
     <t>物品图标</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,9 +277,6 @@
     <t>番茄炒蛋</t>
   </si>
   <si>
-    <t>IconTomatoAndEggStirFryName</t>
-  </si>
-  <si>
     <t>RewardItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -373,6 +367,34 @@
   </si>
   <si>
     <t>TbRewardPropData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardProp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=/),TbRewardPropData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardCharacterProp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=/),TbRewardCharacterPropData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励角色属性(角色ID+值)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_unit_unknown.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -810,7 +832,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="29.08203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.5" customWidth="1"/>
     <col min="5" max="5" width="41.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="42.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.1640625" customWidth="1"/>
@@ -847,7 +869,7 @@
         <v>16</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -879,7 +901,7 @@
         <v>37</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -893,7 +915,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -908,7 +930,7 @@
         <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -919,7 +941,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>41</v>
@@ -937,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -948,7 +970,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>42</v>
@@ -966,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -977,7 +999,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>43</v>
@@ -995,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1006,7 +1028,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>44</v>
@@ -1024,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1035,7 +1057,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>45</v>
@@ -1053,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1064,7 +1086,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>46</v>
@@ -1082,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1093,7 +1115,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>47</v>
@@ -1111,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1122,7 +1144,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>48</v>
@@ -1140,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1151,7 +1173,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -1169,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1180,7 +1202,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>50</v>
@@ -1198,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1209,7 +1231,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>51</v>
@@ -1227,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1238,7 +1260,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>52</v>
@@ -1256,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1267,7 +1289,7 @@
         <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>53</v>
@@ -1285,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1296,7 +1318,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>54</v>
@@ -1314,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1325,7 +1347,7 @@
         <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>55</v>
@@ -1343,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1354,7 +1376,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>56</v>
@@ -1372,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1383,7 +1405,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>57</v>
@@ -1401,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1412,7 +1434,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>58</v>
@@ -1430,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1441,7 +1463,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>59</v>
@@ -1459,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
@@ -1467,13 +1489,13 @@
         <v>120006</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>60</v>
@@ -1488,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="2"/>
@@ -1515,8 +1537,8 @@
     <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.08203125" customWidth="1"/>
     <col min="4" max="4" width="37.5" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="40.1640625" customWidth="1"/>
+    <col min="6" max="6" width="41.08203125" customWidth="1"/>
     <col min="7" max="7" width="19.58203125" customWidth="1"/>
     <col min="8" max="8" width="15.08203125" customWidth="1"/>
   </cols>
@@ -1526,13 +1548,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1546,7 +1574,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -1554,13 +1588,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.3">
@@ -1568,10 +1608,10 @@
         <v>120006</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E85E645-BE12-4297-914C-8A896E86EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885E75F2-653C-4763-AE10-0217E7997F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5610" yWindow="2070" windowWidth="30580" windowHeight="18810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialItemData" sheetId="1" r:id="rId1"/>
     <sheet name="ConsumablesItemData" sheetId="2" r:id="rId2"/>
+    <sheet name="RecipeItemData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="105">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -395,6 +396,24 @@
   </si>
   <si>
     <t>1_unit_unknown.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>TypeNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synthesis</t>
+  </si>
+  <si>
+    <t>合成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1632,4 +1651,88 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B320200-1424-465F-9A2D-74F4D970F5D5}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="20.08203125" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="11">
+        <v>120006</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="11">
+        <v>90</v>
+      </c>
+      <c r="E4" s="11">
+        <v>800001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940A7130-A94E-4444-9EF3-BBFB6B9D096F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F45BCA-3F30-4404-B4AE-77B4F2A8B138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="1470" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2200" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialItemData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="451">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,61 +95,19 @@
     <t>Quality</t>
   </si>
   <si>
-    <t>白萝卜</t>
-  </si>
-  <si>
-    <t>嫩豆腐</t>
-  </si>
-  <si>
     <t>土豆</t>
   </si>
   <si>
-    <t>青椒</t>
-  </si>
-  <si>
-    <t>大白菜</t>
-  </si>
-  <si>
     <t>番茄</t>
   </si>
   <si>
     <t>鸡蛋</t>
   </si>
   <si>
-    <t>五花肉</t>
-  </si>
-  <si>
-    <t>冬瓜</t>
-  </si>
-  <si>
-    <t>西兰花</t>
-  </si>
-  <si>
-    <t>茄子</t>
-  </si>
-  <si>
-    <t>山药</t>
-  </si>
-  <si>
     <t>香菇</t>
   </si>
   <si>
-    <t>芹菜</t>
-  </si>
-  <si>
-    <t>腐竹</t>
-  </si>
-  <si>
-    <t>胡萝卜</t>
-  </si>
-  <si>
     <t>生菜</t>
-  </si>
-  <si>
-    <t>鸡胸肉</t>
-  </si>
-  <si>
-    <t>豆角</t>
   </si>
   <si>
     <t>TbLocalzationKeyData#sep=+</t>
@@ -325,309 +283,15 @@
     <t>备注</t>
   </si>
   <si>
-    <t>金针菇</t>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>罗非鱼</t>
-  </si>
-  <si>
-    <t>小黄鱼</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>乌鳢</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>石斑鱼</t>
-  </si>
-  <si>
-    <t>大黄鱼</t>
-  </si>
-  <si>
-    <t>多宝鱼</t>
-  </si>
-  <si>
-    <t>东星斑</t>
-  </si>
-  <si>
-    <t>鳕鱼</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>鳜鱼</t>
-  </si>
-  <si>
-    <t>马鲛鱼</t>
-  </si>
-  <si>
-    <t>长江鲥鱼</t>
-  </si>
-  <si>
-    <t>蓝鳍金枪鱼</t>
-  </si>
-  <si>
-    <t>食用精盐</t>
-  </si>
-  <si>
     <t>白砂糖</t>
   </si>
   <si>
-    <t>酿造米醋</t>
-  </si>
-  <si>
-    <t>八角茴香</t>
-  </si>
-  <si>
-    <t>桂皮</t>
-  </si>
-  <si>
-    <t>白胡椒粉</t>
-  </si>
-  <si>
-    <t>藏红花丝</t>
-  </si>
-  <si>
-    <t>天然香草荚</t>
-  </si>
-  <si>
-    <t>野生松茸粉</t>
-  </si>
-  <si>
-    <t>陈年鱼露</t>
-  </si>
-  <si>
-    <t>清炒白萝卜配方</t>
-  </si>
-  <si>
-    <t>家常嫩豆腐汤配方</t>
-  </si>
-  <si>
-    <t>红烧土豆块配方</t>
-  </si>
-  <si>
-    <t>手撕青椒小炒配方</t>
-  </si>
-  <si>
-    <t>清炒大白菜配方</t>
-  </si>
-  <si>
-    <t>番茄炒蛋配方</t>
-  </si>
-  <si>
-    <t>五花肉烧冬瓜配方</t>
-  </si>
-  <si>
-    <t>白灼西兰花配方</t>
-  </si>
-  <si>
-    <t>红烧茄子配方</t>
-  </si>
-  <si>
-    <t>清炒山药片配方</t>
-  </si>
-  <si>
-    <t>香菇炒芹菜配方</t>
-  </si>
-  <si>
-    <t>红烧腐竹配方</t>
-  </si>
-  <si>
     <t>生菜鸡胸肉沙拉配方</t>
   </si>
   <si>
-    <t>干煸豆角配方</t>
-  </si>
-  <si>
-    <t>金针菇豆腐汤配方</t>
-  </si>
-  <si>
-    <t>鲫鱼鲜汤配方</t>
-  </si>
-  <si>
-    <t>草鱼水煮鱼片配方</t>
-  </si>
-  <si>
-    <t>糖醋鲤鱼配方</t>
-  </si>
-  <si>
-    <t>花鲢鱼头煲配方</t>
-  </si>
-  <si>
-    <t>香煎罗非鱼配方</t>
-  </si>
-  <si>
-    <t>红烧小黄鱼配方</t>
-  </si>
-  <si>
-    <t>清蒸鲈鱼配方</t>
-  </si>
-  <si>
-    <t>黑鱼酸菜鱼配方</t>
-  </si>
-  <si>
-    <t>香草煎鲳鱼配方</t>
-  </si>
-  <si>
-    <t>鱼露清蒸石斑鱼配方</t>
-  </si>
-  <si>
-    <t>松茸焖大黄鱼配方</t>
-  </si>
-  <si>
-    <t>米醋蒸多宝鱼配方</t>
-  </si>
-  <si>
-    <t>藏红花东星斑配方</t>
-  </si>
-  <si>
-    <t>香草烤鳕鱼配方</t>
-  </si>
-  <si>
-    <t>银鱼蛋羹配方</t>
-  </si>
-  <si>
-    <t>松鼠鳜鱼配方</t>
-  </si>
-  <si>
-    <t>香煎马鲛鱼配方</t>
-  </si>
-  <si>
-    <t>古法蒸长江鲥鱼配方</t>
-  </si>
-  <si>
-    <t>松茸金枪鱼刺身配方</t>
-  </si>
-  <si>
-    <t>白鲢鱼丸汤配方</t>
-  </si>
-  <si>
-    <t>拼好饭</t>
-  </si>
-  <si>
-    <t>清炒白萝卜</t>
-  </si>
-  <si>
-    <t>家常嫩豆腐汤</t>
-  </si>
-  <si>
-    <t>红烧土豆块</t>
-  </si>
-  <si>
-    <t>手撕青椒小炒</t>
-  </si>
-  <si>
-    <t>清炒大白菜</t>
-  </si>
-  <si>
-    <t>五花肉烧冬瓜</t>
-  </si>
-  <si>
-    <t>白灼西兰花</t>
-  </si>
-  <si>
-    <t>红烧茄子</t>
-  </si>
-  <si>
-    <t>清炒山药片</t>
-  </si>
-  <si>
-    <t>香菇炒芹菜</t>
-  </si>
-  <si>
-    <t>红烧腐竹</t>
-  </si>
-  <si>
     <t>生菜鸡胸肉沙拉</t>
   </si>
   <si>
-    <t>干煸豆角</t>
-  </si>
-  <si>
-    <t>金针菇豆腐汤</t>
-  </si>
-  <si>
-    <t>鲫鱼鲜汤</t>
-  </si>
-  <si>
-    <t>草鱼水煮鱼片</t>
-  </si>
-  <si>
-    <t>糖醋鲤鱼</t>
-  </si>
-  <si>
-    <t>花鲢鱼头煲</t>
-  </si>
-  <si>
-    <t>香煎罗非鱼</t>
-  </si>
-  <si>
-    <t>红烧小黄鱼</t>
-  </si>
-  <si>
-    <t>清蒸鲈鱼</t>
-  </si>
-  <si>
-    <t>黑鱼酸菜鱼</t>
-  </si>
-  <si>
-    <t>香草煎鲳鱼</t>
-  </si>
-  <si>
-    <t>鱼露清蒸石斑鱼</t>
-  </si>
-  <si>
-    <t>松茸焖大黄鱼</t>
-  </si>
-  <si>
-    <t>米醋蒸多宝鱼</t>
-  </si>
-  <si>
-    <t>藏红花东星斑</t>
-  </si>
-  <si>
-    <t>香草烤鳕鱼</t>
-  </si>
-  <si>
-    <t>银鱼蛋羹</t>
-  </si>
-  <si>
-    <t>松鼠鳜鱼</t>
-  </si>
-  <si>
-    <t>香煎马鲛鱼</t>
-  </si>
-  <si>
-    <t>古法蒸长江鲥鱼</t>
-  </si>
-  <si>
-    <t>松茸金枪鱼刺身</t>
-  </si>
-  <si>
-    <t>白鲢鱼丸汤</t>
-  </si>
-  <si>
     <t>星野休憩</t>
   </si>
   <si>
@@ -638,96 +302,6 @@
   </si>
   <si>
     <t>青空信约</t>
-  </si>
-  <si>
-    <t>樱花私语</t>
-  </si>
-  <si>
-    <t>星轨魔导</t>
-  </si>
-  <si>
-    <t>雾境魔女</t>
-  </si>
-  <si>
-    <t>月光咒印</t>
-  </si>
-  <si>
-    <t>冰晶灵使</t>
-  </si>
-  <si>
-    <t>云间神谕</t>
-  </si>
-  <si>
-    <t>课间碎光</t>
-  </si>
-  <si>
-    <t>校服晚风</t>
-  </si>
-  <si>
-    <t>操场落日</t>
-  </si>
-  <si>
-    <t>图书馆秘思</t>
-  </si>
-  <si>
-    <t>天台告白</t>
-  </si>
-  <si>
-    <t>月下青衫</t>
-  </si>
-  <si>
-    <t>桃枝执扇</t>
-  </si>
-  <si>
-    <t>山河辞赋</t>
-  </si>
-  <si>
-    <t>云袖清欢</t>
-  </si>
-  <si>
-    <t>灯影红笺</t>
-  </si>
-  <si>
-    <t>霓虹战姬</t>
-  </si>
-  <si>
-    <t>深空巡卫</t>
-  </si>
-  <si>
-    <t>机甲星旅</t>
-  </si>
-  <si>
-    <t>雨夜刃影</t>
-  </si>
-  <si>
-    <t>虚空战歌</t>
-  </si>
-  <si>
-    <t>猫屿午后</t>
-  </si>
-  <si>
-    <t>雪落狐踪</t>
-  </si>
-  <si>
-    <t>深海人鱼</t>
-  </si>
-  <si>
-    <t>林间萤火</t>
-  </si>
-  <si>
-    <t>浅海碎浪</t>
-  </si>
-  <si>
-    <t>勋章</t>
-  </si>
-  <si>
-    <t>画册</t>
-  </si>
-  <si>
-    <t>抱枕</t>
-  </si>
-  <si>
-    <t>毯子</t>
   </si>
   <si>
     <t>聚酯斜纹</t>
@@ -1210,13 +784,658 @@
   </si>
   <si>
     <t>物品图标</t>
+  </si>
+  <si>
+    <t>米饭</t>
+  </si>
+  <si>
+    <t>豆腐</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>猪肉</t>
+  </si>
+  <si>
+    <t>包菜</t>
+  </si>
+  <si>
+    <t>洋葱</t>
+  </si>
+  <si>
+    <t>鸡肉</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>面条</t>
+  </si>
+  <si>
+    <t>海苔</t>
+  </si>
+  <si>
+    <t>红豆</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+  </si>
+  <si>
+    <t>螃蟹</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>生蚝</t>
+  </si>
+  <si>
+    <t>扇贝</t>
+  </si>
+  <si>
+    <t>大虾</t>
+  </si>
+  <si>
+    <t>鰤鱼</t>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>河豚</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>安康鱼</t>
+  </si>
+  <si>
+    <t>海鲈鱼</t>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>秋刀鱼</t>
+  </si>
+  <si>
+    <t>青花鱼</t>
+  </si>
+  <si>
+    <t>鳗鱼</t>
+  </si>
+  <si>
+    <t>三文鱼</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>食用盐</t>
+  </si>
+  <si>
+    <t>芥末</t>
+  </si>
+  <si>
+    <t>高汤</t>
+  </si>
+  <si>
+    <t>牛奶</t>
+  </si>
+  <si>
+    <t>面粉</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>奶油</t>
+  </si>
+  <si>
+    <t>芝士</t>
+  </si>
+  <si>
+    <t>咖喱</t>
+  </si>
+  <si>
+    <t>变异章鱼</t>
+  </si>
+  <si>
+    <t>变异南瓜</t>
+  </si>
+  <si>
+    <t>变异蘑菇</t>
+  </si>
+  <si>
+    <t>变异鸡肉</t>
+  </si>
+  <si>
+    <t>变异牛奶</t>
+  </si>
+  <si>
+    <t>水果沙拉配方</t>
+  </si>
+  <si>
+    <t>蛋炒饭配方</t>
+  </si>
+  <si>
+    <t>八宝菜配方</t>
+  </si>
+  <si>
+    <t>饭团配方</t>
+  </si>
+  <si>
+    <t>海鲜饭团配方</t>
+  </si>
+  <si>
+    <t>海鲜寿司配方</t>
+  </si>
+  <si>
+    <t>刺身料理配方</t>
+  </si>
+  <si>
+    <t>香煎鱼配方</t>
+  </si>
+  <si>
+    <t>杂蔬海鲜天妇罗配方</t>
+  </si>
+  <si>
+    <t>大阪烧配方</t>
+  </si>
+  <si>
+    <t>章鱼小丸子配方</t>
+  </si>
+  <si>
+    <t>煎饺配方</t>
+  </si>
+  <si>
+    <t>芝士焗龙虾配方</t>
+  </si>
+  <si>
+    <t>海鲜炒面配方</t>
+  </si>
+  <si>
+    <t>煎牛排配方</t>
+  </si>
+  <si>
+    <t>豚骨拉面配方</t>
+  </si>
+  <si>
+    <t>乌冬面配方</t>
+  </si>
+  <si>
+    <t>味增汤配方</t>
+  </si>
+  <si>
+    <t>茶碗蒸配方</t>
+  </si>
+  <si>
+    <t>鳗鱼盖饭配方</t>
+  </si>
+  <si>
+    <t>烤生蚝配方</t>
+  </si>
+  <si>
+    <t>亲子丼配方</t>
+  </si>
+  <si>
+    <t>咖喱蛋包饭配方</t>
+  </si>
+  <si>
+    <t>可乐饼配方</t>
+  </si>
+  <si>
+    <t>明太子烤土豆配方</t>
+  </si>
+  <si>
+    <t>关东煮配方</t>
+  </si>
+  <si>
+    <t>寿喜烧配方</t>
+  </si>
+  <si>
+    <t>玉子烧配方</t>
+  </si>
+  <si>
+    <t>鲷鱼烧配方</t>
+  </si>
+  <si>
+    <t>可丽饼配方</t>
+  </si>
+  <si>
+    <t>蛋糕配方</t>
+  </si>
+  <si>
+    <t>布丁配方</t>
+  </si>
+  <si>
+    <t>冰淇淋配方</t>
+  </si>
+  <si>
+    <t>肉咖喱配方</t>
+  </si>
+  <si>
+    <t>变异章鱼触手意面 配方</t>
+  </si>
+  <si>
+    <t>变异杰克南瓜浓汤配方</t>
+  </si>
+  <si>
+    <t>变异水煮大蝎子与行走菇配方</t>
+  </si>
+  <si>
+    <t>变异奇怪的鸡蛋包饭配方</t>
+  </si>
+  <si>
+    <t>变异史莱姆牛奶雪糕配方</t>
+  </si>
+  <si>
+    <t>便当</t>
+  </si>
+  <si>
+    <t>水果沙拉</t>
+  </si>
+  <si>
+    <t>蛋炒饭</t>
+  </si>
+  <si>
+    <t>八宝菜</t>
+  </si>
+  <si>
+    <t>饭团</t>
+  </si>
+  <si>
+    <t>海鲜饭团</t>
+  </si>
+  <si>
+    <t>海鲜寿司</t>
+  </si>
+  <si>
+    <t>刺身料理</t>
+  </si>
+  <si>
+    <t>香煎鱼</t>
+  </si>
+  <si>
+    <t>杂蔬海鲜天妇罗</t>
+  </si>
+  <si>
+    <t>大阪烧</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>煎饺</t>
+  </si>
+  <si>
+    <t>芝士焗龙虾</t>
+  </si>
+  <si>
+    <t>海鲜炒面</t>
+  </si>
+  <si>
+    <t>煎牛排</t>
+  </si>
+  <si>
+    <t>豚骨拉面</t>
+  </si>
+  <si>
+    <t>乌冬面</t>
+  </si>
+  <si>
+    <t>味增汤</t>
+  </si>
+  <si>
+    <t>茶碗蒸</t>
+  </si>
+  <si>
+    <t>鳗鱼盖饭</t>
+  </si>
+  <si>
+    <t>烤生蚝</t>
+  </si>
+  <si>
+    <t>亲子丼</t>
+  </si>
+  <si>
+    <t>咖喱蛋包饭</t>
+  </si>
+  <si>
+    <t>可乐饼</t>
+  </si>
+  <si>
+    <t>明太子烤土豆</t>
+  </si>
+  <si>
+    <t>关东煮</t>
+  </si>
+  <si>
+    <t>寿喜烧</t>
+  </si>
+  <si>
+    <t>玉子烧</t>
+  </si>
+  <si>
+    <t>鲷鱼烧</t>
+  </si>
+  <si>
+    <t>可丽饼</t>
+  </si>
+  <si>
+    <t>蛋糕</t>
+  </si>
+  <si>
+    <t>布丁</t>
+  </si>
+  <si>
+    <t>冰淇淋</t>
+  </si>
+  <si>
+    <t>肉咖喱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">变异章鱼触手意面 </t>
+  </si>
+  <si>
+    <t>变异杰克南瓜浓汤</t>
+  </si>
+  <si>
+    <t>变异水煮大蝎子与行走菇</t>
+  </si>
+  <si>
+    <t>变异奇怪的鸡蛋包饭</t>
+  </si>
+  <si>
+    <t>变异史莱姆牛奶雪糕</t>
+  </si>
+  <si>
+    <t>挂轴</t>
+  </si>
+  <si>
+    <t>文件夹</t>
+  </si>
+  <si>
+    <t>帆布包</t>
+  </si>
+  <si>
+    <t>明信片</t>
+  </si>
+  <si>
+    <t>立牌</t>
+  </si>
+  <si>
+    <t>毯子_星织款</t>
+  </si>
+  <si>
+    <t>毯子_漫印款</t>
+  </si>
+  <si>
+    <t>毯子_夜织款</t>
+  </si>
+  <si>
+    <t>抱枕_软拥款</t>
+  </si>
+  <si>
+    <t>抱枕_双面款</t>
+  </si>
+  <si>
+    <t>抱枕_半身款</t>
+  </si>
+  <si>
+    <t>画册_原画款</t>
+  </si>
+  <si>
+    <t>画册_典藏款</t>
+  </si>
+  <si>
+    <t>画册_全彩款</t>
+  </si>
+  <si>
+    <t>徽章_亮闪款</t>
+  </si>
+  <si>
+    <t>徽章_哑光款</t>
+  </si>
+  <si>
+    <t>徽章_闪银款</t>
+  </si>
+  <si>
+    <t>海报</t>
+  </si>
+  <si>
+    <t>镭射票</t>
+  </si>
+  <si>
+    <t>手机壳</t>
+  </si>
+  <si>
+    <t>道具1</t>
+  </si>
+  <si>
+    <t>道具2</t>
+  </si>
+  <si>
+    <t>道具3</t>
+  </si>
+  <si>
+    <t>道具4</t>
+  </si>
+  <si>
+    <t>道具5</t>
+  </si>
+  <si>
+    <t>道具6</t>
+  </si>
+  <si>
+    <t>道具7</t>
+  </si>
+  <si>
+    <t>道具8</t>
+  </si>
+  <si>
+    <t>道具9</t>
+  </si>
+  <si>
+    <t>道具10</t>
+  </si>
+  <si>
+    <t>初级鱼饵</t>
+  </si>
+  <si>
+    <t>中级鱼饵</t>
+  </si>
+  <si>
+    <t>高级鱼饵</t>
+  </si>
+  <si>
+    <t>竹鱼竿</t>
+  </si>
+  <si>
+    <t>玻璃纤维竿</t>
+  </si>
+  <si>
+    <t>铱金鱼竿</t>
+  </si>
+  <si>
+    <t>高级铱金鱼竿</t>
+  </si>
+  <si>
+    <t>跳蛋</t>
+  </si>
+  <si>
+    <t>震动棒</t>
+  </si>
+  <si>
+    <t>飞机杯</t>
+  </si>
+  <si>
+    <t>肛塞</t>
+  </si>
+  <si>
+    <t>润滑剂</t>
+  </si>
+  <si>
+    <t>仿真阳具</t>
+  </si>
+  <si>
+    <t>转珠棒</t>
+  </si>
+  <si>
+    <t>情趣内衣</t>
+  </si>
+  <si>
+    <t>香水</t>
+  </si>
+  <si>
+    <t>精油</t>
+  </si>
+  <si>
+    <t>少年剑士</t>
+  </si>
+  <si>
+    <t>魔法少女</t>
+  </si>
+  <si>
+    <t>日常校服少女</t>
+  </si>
+  <si>
+    <t>棒球少年</t>
+  </si>
+  <si>
+    <t>电竞少年</t>
+  </si>
+  <si>
+    <t>居家少女</t>
+  </si>
+  <si>
+    <t>骑士侍从</t>
+  </si>
+  <si>
+    <t>见习法师</t>
+  </si>
+  <si>
+    <t>短跑运动员</t>
+  </si>
+  <si>
+    <t>露营少年</t>
+  </si>
+  <si>
+    <t>水手少女</t>
+  </si>
+  <si>
+    <t>机车少年</t>
+  </si>
+  <si>
+    <t>花店少女</t>
+  </si>
+  <si>
+    <t>面包师少年</t>
+  </si>
+  <si>
+    <t>图书馆少女</t>
+  </si>
+  <si>
+    <t>滑板少年</t>
+  </si>
+  <si>
+    <t>茶艺少女</t>
+  </si>
+  <si>
+    <t>汽修少年</t>
+  </si>
+  <si>
+    <t>摄影少女</t>
+  </si>
+  <si>
+    <t>骑行少年</t>
+  </si>
+  <si>
+    <t>暗夜忍者</t>
+  </si>
+  <si>
+    <t>圣辉修女</t>
+  </si>
+  <si>
+    <t>龙纹武士</t>
+  </si>
+  <si>
+    <t>星海歌姬</t>
+  </si>
+  <si>
+    <t>白虎猎手</t>
+  </si>
+  <si>
+    <t>狐妖巫女</t>
+  </si>
+  <si>
+    <t>重装卫士</t>
+  </si>
+  <si>
+    <t>月影刺客</t>
+  </si>
+  <si>
+    <t>蔷薇骑士</t>
+  </si>
+  <si>
+    <t>极光魔法师</t>
+  </si>
+  <si>
+    <t>耀光剑士</t>
+  </si>
+  <si>
+    <t>星落歌姬</t>
+  </si>
+  <si>
+    <t>绯夜忍者</t>
+  </si>
+  <si>
+    <t>鎏金龙武士</t>
+  </si>
+  <si>
+    <t>极昼修女</t>
+  </si>
+  <si>
+    <t>苍雷猎手</t>
+  </si>
+  <si>
+    <t>幻梦狐妖</t>
+  </si>
+  <si>
+    <t>破晓骑士</t>
+  </si>
+  <si>
+    <t>永夜法师</t>
+  </si>
+  <si>
+    <t>星痕卫士</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1276,37 +1495,13 @@
       <name val="等线"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1348,7 +1543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1362,7 +1557,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1380,41 +1575,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1696,7 +1873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S200"/>
+  <dimension ref="A1:S240"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="29.08203125" style="1" customWidth="1"/>
@@ -1712,14 +1889,14 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>81</v>
+      <c r="B1" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>375</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -1737,7 +1914,7 @@
         <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1745,19 +1922,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>376</v>
+        <v>234</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
@@ -1766,10 +1943,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.3">
@@ -1777,39 +1954,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>377</v>
+        <v>235</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="12">
+      <c r="B4" s="15">
         <v>100000</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>14</v>
+      <c r="C4" s="16" t="s">
+        <v>236</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>CONCATENATE(B:B,"Name.png")</f>
@@ -1833,15 +2010,15 @@
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="12">
+      <c r="B5" s="15">
         <v>100001</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>15</v>
+      <c r="C5" s="16" t="s">
+        <v>237</v>
       </c>
       <c r="D5" s="3" t="str">
         <f t="shared" ref="D5:D68" si="0">CONCATENATE(B:B,"Name.png")</f>
@@ -1865,15 +2042,15 @@
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="12">
+      <c r="B6" s="15">
         <v>100002</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>16</v>
+      <c r="C6" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1897,15 +2074,15 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="12">
+      <c r="B7" s="15">
         <v>100003</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>17</v>
+      <c r="C7" s="16" t="s">
+        <v>238</v>
       </c>
       <c r="D7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1929,15 +2106,15 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="12">
+      <c r="B8" s="15">
         <v>100004</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>18</v>
+      <c r="C8" s="16" t="s">
+        <v>239</v>
       </c>
       <c r="D8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1961,15 +2138,15 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="12">
+      <c r="B9" s="15">
         <v>100005</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>19</v>
+      <c r="C9" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1993,15 +2170,15 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="12">
+      <c r="B10" s="15">
         <v>100006</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>20</v>
+      <c r="C10" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2025,15 +2202,15 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="12">
+      <c r="B11" s="15">
         <v>100007</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>21</v>
+      <c r="C11" s="16" t="s">
+        <v>240</v>
       </c>
       <c r="D11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2057,15 +2234,15 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="12">
+      <c r="B12" s="15">
         <v>100008</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>22</v>
+      <c r="C12" s="16" t="s">
+        <v>241</v>
       </c>
       <c r="D12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2089,15 +2266,15 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="12">
+      <c r="B13" s="15">
         <v>100009</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>23</v>
+      <c r="C13" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2121,15 +2298,15 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="12">
+      <c r="B14" s="15">
         <v>100010</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>24</v>
+      <c r="C14" s="16" t="s">
+        <v>242</v>
       </c>
       <c r="D14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2153,15 +2330,15 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="12">
+      <c r="B15" s="15">
         <v>100011</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>25</v>
+      <c r="C15" s="16" t="s">
+        <v>243</v>
       </c>
       <c r="D15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2185,15 +2362,15 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="12">
+      <c r="B16" s="15">
         <v>100012</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>26</v>
+      <c r="C16" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2217,15 +2394,15 @@
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="12">
+      <c r="B17" s="15">
         <v>100013</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>27</v>
+      <c r="C17" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="D17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2249,15 +2426,15 @@
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="12">
+      <c r="B18" s="15">
         <v>100014</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>28</v>
+      <c r="C18" s="16" t="s">
+        <v>245</v>
       </c>
       <c r="D18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2281,15 +2458,15 @@
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="12">
+      <c r="B19" s="15">
         <v>100015</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>29</v>
+      <c r="C19" s="16" t="s">
+        <v>246</v>
       </c>
       <c r="D19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2313,15 +2490,15 @@
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="12">
+      <c r="B20" s="15">
         <v>100016</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="D20" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2345,15 +2522,15 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="12">
+      <c r="B21" s="15">
         <v>100017</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>31</v>
+      <c r="C21" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="D21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2377,15 +2554,15 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="12">
+      <c r="B22" s="15">
         <v>100018</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>32</v>
+      <c r="C22" s="16" t="s">
+        <v>249</v>
       </c>
       <c r="D22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2409,15 +2586,15 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="12">
+      <c r="B23" s="15">
         <v>100019</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>83</v>
+      <c r="C23" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="D23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2441,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="2"/>
@@ -2454,11 +2631,11 @@
       <c r="S23" s="8"/>
     </row>
     <row r="24" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="12">
+      <c r="B24" s="15">
         <v>100020</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>84</v>
+      <c r="C24" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="D24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2482,15 +2659,15 @@
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>229</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="12">
+      <c r="B25" s="15">
         <v>100021</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>85</v>
+      <c r="C25" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="D25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2514,15 +2691,15 @@
         <v>1</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="12">
+      <c r="B26" s="15">
         <v>100022</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>86</v>
+      <c r="C26" s="16" t="s">
+        <v>253</v>
       </c>
       <c r="D26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2546,15 +2723,15 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>231</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B27" s="12">
+      <c r="B27" s="15">
         <v>100023</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>87</v>
+      <c r="C27" s="16" t="s">
+        <v>254</v>
       </c>
       <c r="D27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2578,15 +2755,15 @@
         <v>1</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B28" s="12">
+      <c r="B28" s="15">
         <v>100024</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>88</v>
+      <c r="C28" s="16" t="s">
+        <v>255</v>
       </c>
       <c r="D28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2610,15 +2787,15 @@
         <v>1</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>233</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B29" s="12">
+      <c r="B29" s="15">
         <v>100025</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>89</v>
+      <c r="C29" s="16" t="s">
+        <v>256</v>
       </c>
       <c r="D29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2642,15 +2819,15 @@
         <v>1</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>234</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B30" s="12">
+      <c r="B30" s="15">
         <v>100026</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>90</v>
+      <c r="C30" s="16" t="s">
+        <v>257</v>
       </c>
       <c r="D30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2674,15 +2851,15 @@
         <v>1</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="12">
+      <c r="B31" s="15">
         <v>100027</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>91</v>
+      <c r="C31" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="D31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2706,15 +2883,15 @@
         <v>1</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>236</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="2:19" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B32" s="12">
+      <c r="B32" s="15">
         <v>100028</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>92</v>
+      <c r="C32" s="16" t="s">
+        <v>259</v>
       </c>
       <c r="D32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2738,15 +2915,15 @@
         <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="12">
+      <c r="B33" s="15">
         <v>100029</v>
       </c>
-      <c r="C33" s="18" t="s">
-        <v>93</v>
+      <c r="C33" s="16" t="s">
+        <v>260</v>
       </c>
       <c r="D33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2770,15 +2947,15 @@
         <v>1</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>238</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="12">
+      <c r="B34" s="15">
         <v>100030</v>
       </c>
-      <c r="C34" s="18" t="s">
-        <v>94</v>
+      <c r="C34" s="16" t="s">
+        <v>261</v>
       </c>
       <c r="D34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2802,15 +2979,15 @@
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="12">
+      <c r="B35" s="15">
         <v>100031</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>95</v>
+      <c r="C35" s="16" t="s">
+        <v>262</v>
       </c>
       <c r="D35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2834,15 +3011,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>240</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B36" s="12">
+      <c r="B36" s="15">
         <v>100032</v>
       </c>
-      <c r="C36" s="18" t="s">
-        <v>96</v>
+      <c r="C36" s="16" t="s">
+        <v>263</v>
       </c>
       <c r="D36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2866,15 +3043,15 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>241</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B37" s="12">
+      <c r="B37" s="15">
         <v>100033</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>97</v>
+      <c r="C37" s="16" t="s">
+        <v>264</v>
       </c>
       <c r="D37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2898,15 +3075,15 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>242</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="12">
+      <c r="B38" s="15">
         <v>100034</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>98</v>
+      <c r="C38" s="16" t="s">
+        <v>265</v>
       </c>
       <c r="D38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2930,15 +3107,15 @@
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>243</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B39" s="12">
+      <c r="B39" s="15">
         <v>100035</v>
       </c>
-      <c r="C39" s="18" t="s">
-        <v>99</v>
+      <c r="C39" s="16" t="s">
+        <v>266</v>
       </c>
       <c r="D39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2962,15 +3139,15 @@
         <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>244</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="12">
+      <c r="B40" s="15">
         <v>100036</v>
       </c>
-      <c r="C40" s="18" t="s">
-        <v>100</v>
+      <c r="C40" s="16" t="s">
+        <v>267</v>
       </c>
       <c r="D40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2994,15 +3171,15 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>245</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="12">
+      <c r="B41" s="15">
         <v>100037</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>101</v>
+      <c r="C41" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="D41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3026,15 +3203,15 @@
         <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>246</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B42" s="12">
+      <c r="B42" s="15">
         <v>100038</v>
       </c>
-      <c r="C42" s="18" t="s">
-        <v>102</v>
+      <c r="C42" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="D42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3058,15 +3235,15 @@
         <v>1</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>247</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B43" s="12">
+      <c r="B43" s="15">
         <v>100039</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>103</v>
+      <c r="C43" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="D43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3090,15 +3267,15 @@
         <v>1</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>248</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="12">
+      <c r="B44" s="15">
         <v>100040</v>
       </c>
-      <c r="C44" s="19" t="s">
-        <v>104</v>
+      <c r="C44" s="16" t="s">
+        <v>271</v>
       </c>
       <c r="D44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3122,15 +3299,15 @@
         <v>1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>249</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B45" s="12">
+      <c r="B45" s="15">
         <v>100041</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>105</v>
+      <c r="C45" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="D45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3154,15 +3331,15 @@
         <v>1</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="12">
+      <c r="B46" s="15">
         <v>100042</v>
       </c>
-      <c r="C46" s="19" t="s">
-        <v>106</v>
+      <c r="C46" s="16" t="s">
+        <v>272</v>
       </c>
       <c r="D46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3186,15 +3363,15 @@
         <v>1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>251</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="12">
+      <c r="B47" s="15">
         <v>100043</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>107</v>
+      <c r="C47" s="16" t="s">
+        <v>273</v>
       </c>
       <c r="D47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3218,15 +3395,15 @@
         <v>1</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>252</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B48" s="12">
+      <c r="B48" s="15">
         <v>100044</v>
       </c>
-      <c r="C48" s="19" t="s">
-        <v>108</v>
+      <c r="C48" s="16" t="s">
+        <v>274</v>
       </c>
       <c r="D48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3250,15 +3427,15 @@
         <v>1</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>253</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B49" s="12">
+      <c r="B49" s="15">
         <v>100045</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>109</v>
+      <c r="C49" s="16" t="s">
+        <v>275</v>
       </c>
       <c r="D49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3282,15 +3459,15 @@
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>254</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="12">
+      <c r="B50" s="15">
         <v>100046</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>110</v>
+      <c r="C50" s="16" t="s">
+        <v>276</v>
       </c>
       <c r="D50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3314,15 +3491,15 @@
         <v>1</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>255</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B51" s="12">
+      <c r="B51" s="15">
         <v>100047</v>
       </c>
-      <c r="C51" s="19" t="s">
-        <v>111</v>
+      <c r="C51" s="16" t="s">
+        <v>277</v>
       </c>
       <c r="D51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3346,15 +3523,15 @@
         <v>1</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>256</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B52" s="12">
+      <c r="B52" s="15">
         <v>100048</v>
       </c>
-      <c r="C52" s="19" t="s">
-        <v>112</v>
+      <c r="C52" s="16" t="s">
+        <v>278</v>
       </c>
       <c r="D52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3378,15 +3555,15 @@
         <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>257</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B53" s="12">
+      <c r="B53" s="15">
         <v>100049</v>
       </c>
-      <c r="C53" s="19" t="s">
-        <v>113</v>
+      <c r="C53" s="16" t="s">
+        <v>279</v>
       </c>
       <c r="D53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3410,27 +3587,27 @@
         <v>1</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B54" s="12">
-        <v>110000</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>114</v>
+      <c r="B54" s="15">
+        <v>100051</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>280</v>
       </c>
       <c r="D54" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110000Name.png</v>
+        <v>100051Name.png</v>
       </c>
       <c r="E54" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110000Name</v>
+        <v>InventoryItem+100051Name</v>
       </c>
       <c r="F54" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110000Text</v>
+        <v>InventoryItem+100051Text</v>
       </c>
       <c r="G54" s="5">
         <v>0</v>
@@ -3442,27 +3619,27 @@
         <v>1</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>259</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B55" s="13">
-        <v>110001</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>115</v>
+      <c r="B55" s="15">
+        <v>100052</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>281</v>
       </c>
       <c r="D55" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110001Name.png</v>
+        <v>100052Name.png</v>
       </c>
       <c r="E55" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110001Name</v>
+        <v>InventoryItem+100052Name</v>
       </c>
       <c r="F55" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110001Text</v>
+        <v>InventoryItem+100052Text</v>
       </c>
       <c r="G55" s="5">
         <v>0</v>
@@ -3474,27 +3651,27 @@
         <v>1</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>260</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="12">
-        <v>110002</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>116</v>
+      <c r="B56" s="15">
+        <v>100053</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>282</v>
       </c>
       <c r="D56" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110002Name.png</v>
+        <v>100053Name.png</v>
       </c>
       <c r="E56" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110002Name</v>
+        <v>InventoryItem+100053Name</v>
       </c>
       <c r="F56" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110002Text</v>
+        <v>InventoryItem+100053Text</v>
       </c>
       <c r="G56" s="5">
         <v>0</v>
@@ -3506,27 +3683,27 @@
         <v>1</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>261</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="13">
-        <v>110003</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>117</v>
+      <c r="B57" s="15">
+        <v>100054</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>283</v>
       </c>
       <c r="D57" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110003Name.png</v>
+        <v>100054Name.png</v>
       </c>
       <c r="E57" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110003Name</v>
+        <v>InventoryItem+100054Name</v>
       </c>
       <c r="F57" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110003Text</v>
+        <v>InventoryItem+100054Text</v>
       </c>
       <c r="G57" s="5">
         <v>0</v>
@@ -3538,27 +3715,27 @@
         <v>1</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>262</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B58" s="12">
-        <v>110004</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>118</v>
+      <c r="B58" s="15">
+        <v>100055</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>284</v>
       </c>
       <c r="D58" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110004Name.png</v>
+        <v>100055Name.png</v>
       </c>
       <c r="E58" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110004Name</v>
+        <v>InventoryItem+100055Name</v>
       </c>
       <c r="F58" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110004Text</v>
+        <v>InventoryItem+100055Text</v>
       </c>
       <c r="G58" s="5">
         <v>0</v>
@@ -3570,27 +3747,27 @@
         <v>1</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>263</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B59" s="13">
-        <v>110005</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>119</v>
+      <c r="B59" s="15">
+        <v>110000</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>285</v>
       </c>
       <c r="D59" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110005Name.png</v>
+        <v>110000Name.png</v>
       </c>
       <c r="E59" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110005Name</v>
+        <v>InventoryItem+110000Name</v>
       </c>
       <c r="F59" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110005Text</v>
+        <v>InventoryItem+110000Text</v>
       </c>
       <c r="G59" s="5">
         <v>0</v>
@@ -3602,27 +3779,27 @@
         <v>1</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B60" s="12">
-        <v>110006</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>120</v>
+      <c r="B60" s="15">
+        <v>110001</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="D60" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110006Name.png</v>
+        <v>110001Name.png</v>
       </c>
       <c r="E60" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110006Name</v>
+        <v>InventoryItem+110001Name</v>
       </c>
       <c r="F60" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110006Text</v>
+        <v>InventoryItem+110001Text</v>
       </c>
       <c r="G60" s="5">
         <v>0</v>
@@ -3634,27 +3811,27 @@
         <v>1</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B61" s="13">
-        <v>110007</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>121</v>
+      <c r="B61" s="15">
+        <v>110002</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="D61" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110007Name.png</v>
+        <v>110002Name.png</v>
       </c>
       <c r="E61" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110007Name</v>
+        <v>InventoryItem+110002Name</v>
       </c>
       <c r="F61" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110007Text</v>
+        <v>InventoryItem+110002Text</v>
       </c>
       <c r="G61" s="5">
         <v>0</v>
@@ -3666,27 +3843,27 @@
         <v>1</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>266</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B62" s="12">
-        <v>110008</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>122</v>
+      <c r="B62" s="15">
+        <v>110003</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>288</v>
       </c>
       <c r="D62" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110008Name.png</v>
+        <v>110003Name.png</v>
       </c>
       <c r="E62" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110008Name</v>
+        <v>InventoryItem+110003Name</v>
       </c>
       <c r="F62" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110008Text</v>
+        <v>InventoryItem+110003Text</v>
       </c>
       <c r="G62" s="5">
         <v>0</v>
@@ -3698,27 +3875,27 @@
         <v>1</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>267</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B63" s="13">
-        <v>110009</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>123</v>
+      <c r="B63" s="15">
+        <v>110004</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>289</v>
       </c>
       <c r="D63" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110009Name.png</v>
+        <v>110004Name.png</v>
       </c>
       <c r="E63" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110009Name</v>
+        <v>InventoryItem+110004Name</v>
       </c>
       <c r="F63" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110009Text</v>
+        <v>InventoryItem+110004Text</v>
       </c>
       <c r="G63" s="5">
         <v>0</v>
@@ -3730,27 +3907,27 @@
         <v>1</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>268</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B64" s="12">
-        <v>110010</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>124</v>
+      <c r="B64" s="15">
+        <v>110005</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>290</v>
       </c>
       <c r="D64" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110010Name.png</v>
+        <v>110005Name.png</v>
       </c>
       <c r="E64" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110010Name</v>
+        <v>InventoryItem+110005Name</v>
       </c>
       <c r="F64" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110010Text</v>
+        <v>InventoryItem+110005Text</v>
       </c>
       <c r="G64" s="5">
         <v>0</v>
@@ -3762,27 +3939,27 @@
         <v>1</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>269</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B65" s="13">
-        <v>110011</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>125</v>
+      <c r="B65" s="15">
+        <v>110006</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="D65" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110011Name.png</v>
+        <v>110006Name.png</v>
       </c>
       <c r="E65" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110011Name</v>
+        <v>InventoryItem+110006Name</v>
       </c>
       <c r="F65" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110011Text</v>
+        <v>InventoryItem+110006Text</v>
       </c>
       <c r="G65" s="5">
         <v>0</v>
@@ -3794,27 +3971,27 @@
         <v>1</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>270</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B66" s="12">
-        <v>110012</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>126</v>
+      <c r="B66" s="15">
+        <v>110007</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>292</v>
       </c>
       <c r="D66" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110012Name.png</v>
+        <v>110007Name.png</v>
       </c>
       <c r="E66" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110012Name</v>
+        <v>InventoryItem+110007Name</v>
       </c>
       <c r="F66" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110012Text</v>
+        <v>InventoryItem+110007Text</v>
       </c>
       <c r="G66" s="5">
         <v>0</v>
@@ -3826,27 +4003,27 @@
         <v>1</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>271</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B67" s="13">
-        <v>110013</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>127</v>
+      <c r="B67" s="15">
+        <v>110008</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>293</v>
       </c>
       <c r="D67" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110013Name.png</v>
+        <v>110008Name.png</v>
       </c>
       <c r="E67" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110013Name</v>
+        <v>InventoryItem+110008Name</v>
       </c>
       <c r="F67" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110013Text</v>
+        <v>InventoryItem+110008Text</v>
       </c>
       <c r="G67" s="5">
         <v>0</v>
@@ -3858,27 +4035,27 @@
         <v>1</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>272</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B68" s="12">
-        <v>110014</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>128</v>
+      <c r="B68" s="15">
+        <v>110009</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>294</v>
       </c>
       <c r="D68" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>110014Name.png</v>
+        <v>110009Name.png</v>
       </c>
       <c r="E68" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>InventoryItem+110014Name</v>
+        <v>InventoryItem+110009Name</v>
       </c>
       <c r="F68" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>InventoryItem+110014Text</v>
+        <v>InventoryItem+110009Text</v>
       </c>
       <c r="G68" s="5">
         <v>0</v>
@@ -3890,27 +4067,27 @@
         <v>1</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>273</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B69" s="13">
-        <v>110015</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>129</v>
+      <c r="B69" s="15">
+        <v>110010</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>295</v>
       </c>
       <c r="D69" s="3" t="str">
         <f t="shared" ref="D69:D132" si="3">CONCATENATE(B:B,"Name.png")</f>
-        <v>110015Name.png</v>
+        <v>110010Name.png</v>
       </c>
       <c r="E69" s="3" t="str">
         <f t="shared" ref="E69:E132" si="4">CONCATENATE("InventoryItem+",B:B,"Name")</f>
-        <v>InventoryItem+110015Name</v>
+        <v>InventoryItem+110010Name</v>
       </c>
       <c r="F69" s="2" t="str">
         <f t="shared" ref="F69:F132" si="5">CONCATENATE("InventoryItem+",B:B,"Text")</f>
-        <v>InventoryItem+110015Text</v>
+        <v>InventoryItem+110010Text</v>
       </c>
       <c r="G69" s="5">
         <v>0</v>
@@ -3922,27 +4099,27 @@
         <v>1</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>274</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B70" s="12">
-        <v>110016</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>130</v>
+      <c r="B70" s="15">
+        <v>110011</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>296</v>
       </c>
       <c r="D70" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110016Name.png</v>
+        <v>110011Name.png</v>
       </c>
       <c r="E70" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110016Name</v>
+        <v>InventoryItem+110011Name</v>
       </c>
       <c r="F70" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110016Text</v>
+        <v>InventoryItem+110011Text</v>
       </c>
       <c r="G70" s="5">
         <v>0</v>
@@ -3954,27 +4131,27 @@
         <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>275</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B71" s="13">
-        <v>110017</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>131</v>
+      <c r="B71" s="15">
+        <v>110012</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="D71" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110017Name.png</v>
+        <v>110012Name.png</v>
       </c>
       <c r="E71" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110017Name</v>
+        <v>InventoryItem+110012Name</v>
       </c>
       <c r="F71" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110017Text</v>
+        <v>InventoryItem+110012Text</v>
       </c>
       <c r="G71" s="5">
         <v>0</v>
@@ -3986,27 +4163,27 @@
         <v>1</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>276</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B72" s="12">
-        <v>110018</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>132</v>
+      <c r="B72" s="15">
+        <v>110013</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>297</v>
       </c>
       <c r="D72" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110018Name.png</v>
+        <v>110013Name.png</v>
       </c>
       <c r="E72" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110018Name</v>
+        <v>InventoryItem+110013Name</v>
       </c>
       <c r="F72" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110018Text</v>
+        <v>InventoryItem+110013Text</v>
       </c>
       <c r="G72" s="5">
         <v>0</v>
@@ -4018,27 +4195,27 @@
         <v>1</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B73" s="13">
-        <v>110019</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>133</v>
+      <c r="B73" s="15">
+        <v>110014</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>298</v>
       </c>
       <c r="D73" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110019Name.png</v>
+        <v>110014Name.png</v>
       </c>
       <c r="E73" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110019Name</v>
+        <v>InventoryItem+110014Name</v>
       </c>
       <c r="F73" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110019Text</v>
+        <v>InventoryItem+110014Text</v>
       </c>
       <c r="G73" s="5">
         <v>0</v>
@@ -4050,27 +4227,27 @@
         <v>1</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>278</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B74" s="12">
-        <v>110020</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>134</v>
+      <c r="B74" s="15">
+        <v>110015</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>299</v>
       </c>
       <c r="D74" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110020Name.png</v>
+        <v>110015Name.png</v>
       </c>
       <c r="E74" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110020Name</v>
+        <v>InventoryItem+110015Name</v>
       </c>
       <c r="F74" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110020Text</v>
+        <v>InventoryItem+110015Text</v>
       </c>
       <c r="G74" s="5">
         <v>0</v>
@@ -4082,27 +4259,27 @@
         <v>1</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>279</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B75" s="13">
-        <v>110021</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>135</v>
+      <c r="B75" s="15">
+        <v>110016</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>300</v>
       </c>
       <c r="D75" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110021Name.png</v>
+        <v>110016Name.png</v>
       </c>
       <c r="E75" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110021Name</v>
+        <v>InventoryItem+110016Name</v>
       </c>
       <c r="F75" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110021Text</v>
+        <v>InventoryItem+110016Text</v>
       </c>
       <c r="G75" s="5">
         <v>0</v>
@@ -4114,27 +4291,27 @@
         <v>1</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>280</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B76" s="12">
-        <v>110022</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>136</v>
+      <c r="B76" s="15">
+        <v>110017</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>301</v>
       </c>
       <c r="D76" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110022Name.png</v>
+        <v>110017Name.png</v>
       </c>
       <c r="E76" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110022Name</v>
+        <v>InventoryItem+110017Name</v>
       </c>
       <c r="F76" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110022Text</v>
+        <v>InventoryItem+110017Text</v>
       </c>
       <c r="G76" s="5">
         <v>0</v>
@@ -4146,27 +4323,27 @@
         <v>1</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>281</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B77" s="13">
-        <v>110023</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>137</v>
+      <c r="B77" s="15">
+        <v>110018</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>302</v>
       </c>
       <c r="D77" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110023Name.png</v>
+        <v>110018Name.png</v>
       </c>
       <c r="E77" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110023Name</v>
+        <v>InventoryItem+110018Name</v>
       </c>
       <c r="F77" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110023Text</v>
+        <v>InventoryItem+110018Text</v>
       </c>
       <c r="G77" s="5">
         <v>0</v>
@@ -4178,27 +4355,27 @@
         <v>1</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>282</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B78" s="12">
-        <v>110024</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>138</v>
+      <c r="B78" s="15">
+        <v>110019</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="D78" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110024Name.png</v>
+        <v>110019Name.png</v>
       </c>
       <c r="E78" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110024Name</v>
+        <v>InventoryItem+110019Name</v>
       </c>
       <c r="F78" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110024Text</v>
+        <v>InventoryItem+110019Text</v>
       </c>
       <c r="G78" s="5">
         <v>0</v>
@@ -4210,27 +4387,27 @@
         <v>1</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>283</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B79" s="13">
-        <v>110025</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>139</v>
+      <c r="B79" s="15">
+        <v>110020</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>304</v>
       </c>
       <c r="D79" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110025Name.png</v>
+        <v>110020Name.png</v>
       </c>
       <c r="E79" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110025Name</v>
+        <v>InventoryItem+110020Name</v>
       </c>
       <c r="F79" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110025Text</v>
+        <v>InventoryItem+110020Text</v>
       </c>
       <c r="G79" s="5">
         <v>0</v>
@@ -4242,27 +4419,27 @@
         <v>1</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>284</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B80" s="12">
-        <v>110026</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>140</v>
+      <c r="B80" s="15">
+        <v>110021</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>305</v>
       </c>
       <c r="D80" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110026Name.png</v>
+        <v>110021Name.png</v>
       </c>
       <c r="E80" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110026Name</v>
+        <v>InventoryItem+110021Name</v>
       </c>
       <c r="F80" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110026Text</v>
+        <v>InventoryItem+110021Text</v>
       </c>
       <c r="G80" s="5">
         <v>0</v>
@@ -4274,27 +4451,27 @@
         <v>1</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>285</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B81" s="13">
-        <v>110027</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>141</v>
+      <c r="B81" s="15">
+        <v>110022</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>306</v>
       </c>
       <c r="D81" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110027Name.png</v>
+        <v>110022Name.png</v>
       </c>
       <c r="E81" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110027Name</v>
+        <v>InventoryItem+110022Name</v>
       </c>
       <c r="F81" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110027Text</v>
+        <v>InventoryItem+110022Text</v>
       </c>
       <c r="G81" s="5">
         <v>0</v>
@@ -4306,27 +4483,27 @@
         <v>1</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>286</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B82" s="12">
-        <v>110028</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>142</v>
+      <c r="B82" s="15">
+        <v>110023</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>307</v>
       </c>
       <c r="D82" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110028Name.png</v>
+        <v>110023Name.png</v>
       </c>
       <c r="E82" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110028Name</v>
+        <v>InventoryItem+110023Name</v>
       </c>
       <c r="F82" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110028Text</v>
+        <v>InventoryItem+110023Text</v>
       </c>
       <c r="G82" s="5">
         <v>0</v>
@@ -4338,27 +4515,27 @@
         <v>1</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>287</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B83" s="13">
-        <v>110029</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>143</v>
+      <c r="B83" s="15">
+        <v>110024</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>308</v>
       </c>
       <c r="D83" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110029Name.png</v>
+        <v>110024Name.png</v>
       </c>
       <c r="E83" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110029Name</v>
+        <v>InventoryItem+110024Name</v>
       </c>
       <c r="F83" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110029Text</v>
+        <v>InventoryItem+110024Text</v>
       </c>
       <c r="G83" s="5">
         <v>0</v>
@@ -4370,27 +4547,27 @@
         <v>1</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>288</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B84" s="12">
-        <v>110030</v>
-      </c>
-      <c r="C84" s="19" t="s">
-        <v>144</v>
+      <c r="B84" s="15">
+        <v>110025</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>309</v>
       </c>
       <c r="D84" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110030Name.png</v>
+        <v>110025Name.png</v>
       </c>
       <c r="E84" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110030Name</v>
+        <v>InventoryItem+110025Name</v>
       </c>
       <c r="F84" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110030Text</v>
+        <v>InventoryItem+110025Text</v>
       </c>
       <c r="G84" s="5">
         <v>0</v>
@@ -4402,27 +4579,27 @@
         <v>1</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>289</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="13">
-        <v>110031</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>145</v>
+      <c r="B85" s="15">
+        <v>110026</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>310</v>
       </c>
       <c r="D85" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110031Name.png</v>
+        <v>110026Name.png</v>
       </c>
       <c r="E85" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110031Name</v>
+        <v>InventoryItem+110026Name</v>
       </c>
       <c r="F85" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110031Text</v>
+        <v>InventoryItem+110026Text</v>
       </c>
       <c r="G85" s="5">
         <v>0</v>
@@ -4434,27 +4611,27 @@
         <v>1</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>290</v>
+        <v>148</v>
       </c>
     </row>
     <row r="86" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B86" s="12">
-        <v>110032</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>146</v>
+      <c r="B86" s="15">
+        <v>110027</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>311</v>
       </c>
       <c r="D86" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110032Name.png</v>
+        <v>110027Name.png</v>
       </c>
       <c r="E86" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110032Name</v>
+        <v>InventoryItem+110027Name</v>
       </c>
       <c r="F86" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110032Text</v>
+        <v>InventoryItem+110027Text</v>
       </c>
       <c r="G86" s="5">
         <v>0</v>
@@ -4466,27 +4643,27 @@
         <v>1</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>291</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B87" s="13">
-        <v>110033</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>147</v>
+      <c r="B87" s="15">
+        <v>110028</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>312</v>
       </c>
       <c r="D87" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110033Name.png</v>
+        <v>110028Name.png</v>
       </c>
       <c r="E87" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110033Name</v>
+        <v>InventoryItem+110028Name</v>
       </c>
       <c r="F87" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110033Text</v>
+        <v>InventoryItem+110028Text</v>
       </c>
       <c r="G87" s="5">
         <v>0</v>
@@ -4498,27 +4675,27 @@
         <v>1</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B88" s="12">
-        <v>110034</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>148</v>
+      <c r="B88" s="15">
+        <v>110029</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>313</v>
       </c>
       <c r="D88" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>110034Name.png</v>
+        <v>110029Name.png</v>
       </c>
       <c r="E88" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+110034Name</v>
+        <v>InventoryItem+110029Name</v>
       </c>
       <c r="F88" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+110034Text</v>
+        <v>InventoryItem+110029Text</v>
       </c>
       <c r="G88" s="5">
         <v>0</v>
@@ -4530,27 +4707,27 @@
         <v>1</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>293</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B89" s="13">
-        <v>120000</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>149</v>
+      <c r="B89" s="15">
+        <v>110030</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="D89" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120000Name.png</v>
+        <v>110030Name.png</v>
       </c>
       <c r="E89" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120000Name</v>
+        <v>InventoryItem+110030Name</v>
       </c>
       <c r="F89" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120000Text</v>
+        <v>InventoryItem+110030Text</v>
       </c>
       <c r="G89" s="5">
         <v>0</v>
@@ -4562,27 +4739,27 @@
         <v>1</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>294</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B90" s="13">
-        <v>120001</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>150</v>
+      <c r="B90" s="15">
+        <v>110031</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>315</v>
       </c>
       <c r="D90" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120001Name.png</v>
+        <v>110031Name.png</v>
       </c>
       <c r="E90" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120001Name</v>
+        <v>InventoryItem+110031Name</v>
       </c>
       <c r="F90" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120001Text</v>
+        <v>InventoryItem+110031Text</v>
       </c>
       <c r="G90" s="5">
         <v>0</v>
@@ -4594,27 +4771,27 @@
         <v>1</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>295</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="13">
-        <v>120002</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>151</v>
+      <c r="B91" s="15">
+        <v>110032</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>316</v>
       </c>
       <c r="D91" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120002Name.png</v>
+        <v>110032Name.png</v>
       </c>
       <c r="E91" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120002Name</v>
+        <v>InventoryItem+110032Name</v>
       </c>
       <c r="F91" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120002Text</v>
+        <v>InventoryItem+110032Text</v>
       </c>
       <c r="G91" s="5">
         <v>0</v>
@@ -4626,27 +4803,27 @@
         <v>1</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>296</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B92" s="13">
-        <v>120003</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>152</v>
+      <c r="B92" s="15">
+        <v>110033</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>317</v>
       </c>
       <c r="D92" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120003Name.png</v>
+        <v>110033Name.png</v>
       </c>
       <c r="E92" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120003Name</v>
+        <v>InventoryItem+110033Name</v>
       </c>
       <c r="F92" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120003Text</v>
+        <v>InventoryItem+110033Text</v>
       </c>
       <c r="G92" s="5">
         <v>0</v>
@@ -4658,27 +4835,27 @@
         <v>1</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>297</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="13">
-        <v>120004</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>153</v>
+      <c r="B93" s="15">
+        <v>110034</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="D93" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120004Name.png</v>
+        <v>110034Name.png</v>
       </c>
       <c r="E93" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120004Name</v>
+        <v>InventoryItem+110034Name</v>
       </c>
       <c r="F93" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120004Text</v>
+        <v>InventoryItem+110034Text</v>
       </c>
       <c r="G93" s="5">
         <v>0</v>
@@ -4690,27 +4867,27 @@
         <v>1</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>298</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="13">
-        <v>120005</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>154</v>
+      <c r="B94" s="15">
+        <v>110035</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>319</v>
       </c>
       <c r="D94" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120005Name.png</v>
+        <v>110035Name.png</v>
       </c>
       <c r="E94" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120005Name</v>
+        <v>InventoryItem+110035Name</v>
       </c>
       <c r="F94" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120005Text</v>
+        <v>InventoryItem+110035Text</v>
       </c>
       <c r="G94" s="5">
         <v>0</v>
@@ -4722,27 +4899,27 @@
         <v>1</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
     </row>
     <row r="95" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="13">
-        <v>120007</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>40</v>
+      <c r="B95" s="15">
+        <v>110036</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>320</v>
       </c>
       <c r="D95" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120007Name.png</v>
+        <v>110036Name.png</v>
       </c>
       <c r="E95" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120007Name</v>
+        <v>InventoryItem+110036Name</v>
       </c>
       <c r="F95" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120007Text</v>
+        <v>InventoryItem+110036Text</v>
       </c>
       <c r="G95" s="5">
         <v>0</v>
@@ -4754,27 +4931,27 @@
         <v>1</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>300</v>
+        <v>158</v>
       </c>
     </row>
     <row r="96" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B96" s="13">
-        <v>120008</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>155</v>
+      <c r="B96" s="15">
+        <v>110037</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>321</v>
       </c>
       <c r="D96" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120008Name.png</v>
+        <v>110037Name.png</v>
       </c>
       <c r="E96" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120008Name</v>
+        <v>InventoryItem+110037Name</v>
       </c>
       <c r="F96" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120008Text</v>
+        <v>InventoryItem+110037Text</v>
       </c>
       <c r="G96" s="5">
         <v>0</v>
@@ -4786,27 +4963,27 @@
         <v>1</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>301</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B97" s="13">
-        <v>120009</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>156</v>
+      <c r="B97" s="15">
+        <v>110038</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="D97" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120009Name.png</v>
+        <v>110038Name.png</v>
       </c>
       <c r="E97" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120009Name</v>
+        <v>InventoryItem+110038Name</v>
       </c>
       <c r="F97" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120009Text</v>
+        <v>InventoryItem+110038Text</v>
       </c>
       <c r="G97" s="5">
         <v>0</v>
@@ -4818,27 +4995,27 @@
         <v>1</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>302</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B98" s="13">
-        <v>120010</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>157</v>
+      <c r="B98" s="15">
+        <v>110039</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>323</v>
       </c>
       <c r="D98" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120010Name.png</v>
+        <v>110039Name.png</v>
       </c>
       <c r="E98" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120010Name</v>
+        <v>InventoryItem+110039Name</v>
       </c>
       <c r="F98" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120010Text</v>
+        <v>InventoryItem+110039Text</v>
       </c>
       <c r="G98" s="5">
         <v>0</v>
@@ -4850,27 +5027,27 @@
         <v>1</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>303</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="13">
-        <v>120011</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>158</v>
+      <c r="B99" s="15">
+        <v>120000</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>324</v>
       </c>
       <c r="D99" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120011Name.png</v>
+        <v>120000Name.png</v>
       </c>
       <c r="E99" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120011Name</v>
+        <v>InventoryItem+120000Name</v>
       </c>
       <c r="F99" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120011Text</v>
+        <v>InventoryItem+120000Text</v>
       </c>
       <c r="G99" s="5">
         <v>0</v>
@@ -4882,27 +5059,27 @@
         <v>1</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>304</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B100" s="13">
-        <v>120012</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>159</v>
+      <c r="B100" s="15">
+        <v>120001</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>325</v>
       </c>
       <c r="D100" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120012Name.png</v>
+        <v>120001Name.png</v>
       </c>
       <c r="E100" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120012Name</v>
+        <v>InventoryItem+120001Name</v>
       </c>
       <c r="F100" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120012Text</v>
+        <v>InventoryItem+120001Text</v>
       </c>
       <c r="G100" s="5">
         <v>0</v>
@@ -4914,27 +5091,27 @@
         <v>1</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>305</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="13">
-        <v>120013</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>160</v>
+      <c r="B101" s="15">
+        <v>120002</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>326</v>
       </c>
       <c r="D101" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120013Name.png</v>
+        <v>120002Name.png</v>
       </c>
       <c r="E101" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120013Name</v>
+        <v>InventoryItem+120002Name</v>
       </c>
       <c r="F101" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120013Text</v>
+        <v>InventoryItem+120002Text</v>
       </c>
       <c r="G101" s="5">
         <v>0</v>
@@ -4946,27 +5123,27 @@
         <v>1</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>306</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B102" s="13">
-        <v>120014</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>161</v>
+      <c r="B102" s="15">
+        <v>120003</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>327</v>
       </c>
       <c r="D102" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120014Name.png</v>
+        <v>120003Name.png</v>
       </c>
       <c r="E102" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120014Name</v>
+        <v>InventoryItem+120003Name</v>
       </c>
       <c r="F102" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120014Text</v>
+        <v>InventoryItem+120003Text</v>
       </c>
       <c r="G102" s="5">
         <v>0</v>
@@ -4978,27 +5155,27 @@
         <v>1</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>307</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B103" s="13">
-        <v>120015</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>162</v>
+      <c r="B103" s="15">
+        <v>120004</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="D103" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120015Name.png</v>
+        <v>120004Name.png</v>
       </c>
       <c r="E103" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120015Name</v>
+        <v>InventoryItem+120004Name</v>
       </c>
       <c r="F103" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120015Text</v>
+        <v>InventoryItem+120004Text</v>
       </c>
       <c r="G103" s="5">
         <v>0</v>
@@ -5010,27 +5187,27 @@
         <v>1</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B104" s="13">
-        <v>120016</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>163</v>
+      <c r="B104" s="15">
+        <v>120005</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>329</v>
       </c>
       <c r="D104" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120016Name.png</v>
+        <v>120005Name.png</v>
       </c>
       <c r="E104" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120016Name</v>
+        <v>InventoryItem+120005Name</v>
       </c>
       <c r="F104" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120016Text</v>
+        <v>InventoryItem+120005Text</v>
       </c>
       <c r="G104" s="5">
         <v>0</v>
@@ -5042,27 +5219,27 @@
         <v>1</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>309</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B105" s="13">
-        <v>120017</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>164</v>
+      <c r="B105" s="15">
+        <v>120006</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>330</v>
       </c>
       <c r="D105" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120017Name.png</v>
+        <v>120006Name.png</v>
       </c>
       <c r="E105" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120017Name</v>
+        <v>InventoryItem+120006Name</v>
       </c>
       <c r="F105" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120017Text</v>
+        <v>InventoryItem+120006Text</v>
       </c>
       <c r="G105" s="5">
         <v>0</v>
@@ -5074,27 +5251,27 @@
         <v>1</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>310</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B106" s="13">
-        <v>120018</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>165</v>
+      <c r="B106" s="15">
+        <v>120007</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>331</v>
       </c>
       <c r="D106" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120018Name.png</v>
+        <v>120007Name.png</v>
       </c>
       <c r="E106" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120018Name</v>
+        <v>InventoryItem+120007Name</v>
       </c>
       <c r="F106" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120018Text</v>
+        <v>InventoryItem+120007Text</v>
       </c>
       <c r="G106" s="5">
         <v>0</v>
@@ -5106,27 +5283,27 @@
         <v>1</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>311</v>
+        <v>169</v>
       </c>
     </row>
     <row r="107" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B107" s="13">
-        <v>120019</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>166</v>
+      <c r="B107" s="15">
+        <v>120008</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>332</v>
       </c>
       <c r="D107" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120019Name.png</v>
+        <v>120008Name.png</v>
       </c>
       <c r="E107" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120019Name</v>
+        <v>InventoryItem+120008Name</v>
       </c>
       <c r="F107" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120019Text</v>
+        <v>InventoryItem+120008Text</v>
       </c>
       <c r="G107" s="5">
         <v>0</v>
@@ -5138,27 +5315,27 @@
         <v>1</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B108" s="13">
-        <v>120020</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>167</v>
+      <c r="B108" s="15">
+        <v>120009</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>333</v>
       </c>
       <c r="D108" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120020Name.png</v>
+        <v>120009Name.png</v>
       </c>
       <c r="E108" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120020Name</v>
+        <v>InventoryItem+120009Name</v>
       </c>
       <c r="F108" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120020Text</v>
+        <v>InventoryItem+120009Text</v>
       </c>
       <c r="G108" s="5">
         <v>0</v>
@@ -5170,27 +5347,27 @@
         <v>1</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>313</v>
+        <v>171</v>
       </c>
     </row>
     <row r="109" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B109" s="13">
-        <v>120021</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>168</v>
+      <c r="B109" s="15">
+        <v>120010</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>334</v>
       </c>
       <c r="D109" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120021Name.png</v>
+        <v>120010Name.png</v>
       </c>
       <c r="E109" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120021Name</v>
+        <v>InventoryItem+120010Name</v>
       </c>
       <c r="F109" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120021Text</v>
+        <v>InventoryItem+120010Text</v>
       </c>
       <c r="G109" s="5">
         <v>0</v>
@@ -5202,27 +5379,27 @@
         <v>1</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>314</v>
+        <v>172</v>
       </c>
     </row>
     <row r="110" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B110" s="13">
-        <v>120022</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>169</v>
+      <c r="B110" s="15">
+        <v>120011</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>335</v>
       </c>
       <c r="D110" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120022Name.png</v>
+        <v>120011Name.png</v>
       </c>
       <c r="E110" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120022Name</v>
+        <v>InventoryItem+120011Name</v>
       </c>
       <c r="F110" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120022Text</v>
+        <v>InventoryItem+120011Text</v>
       </c>
       <c r="G110" s="5">
         <v>0</v>
@@ -5234,27 +5411,27 @@
         <v>1</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>315</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B111" s="13">
-        <v>120023</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>170</v>
+      <c r="B111" s="15">
+        <v>120012</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="D111" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120023Name.png</v>
+        <v>120012Name.png</v>
       </c>
       <c r="E111" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120023Name</v>
+        <v>InventoryItem+120012Name</v>
       </c>
       <c r="F111" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120023Text</v>
+        <v>InventoryItem+120012Text</v>
       </c>
       <c r="G111" s="5">
         <v>0</v>
@@ -5266,27 +5443,27 @@
         <v>1</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>316</v>
+        <v>174</v>
       </c>
     </row>
     <row r="112" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B112" s="13">
-        <v>120024</v>
-      </c>
-      <c r="C112" s="19" t="s">
-        <v>171</v>
+      <c r="B112" s="15">
+        <v>120013</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="D112" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120024Name.png</v>
+        <v>120013Name.png</v>
       </c>
       <c r="E112" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120024Name</v>
+        <v>InventoryItem+120013Name</v>
       </c>
       <c r="F112" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120024Text</v>
+        <v>InventoryItem+120013Text</v>
       </c>
       <c r="G112" s="5">
         <v>0</v>
@@ -5298,27 +5475,27 @@
         <v>1</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>317</v>
+        <v>175</v>
       </c>
     </row>
     <row r="113" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B113" s="13">
-        <v>120025</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>172</v>
+      <c r="B113" s="15">
+        <v>120014</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>337</v>
       </c>
       <c r="D113" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120025Name.png</v>
+        <v>120014Name.png</v>
       </c>
       <c r="E113" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120025Name</v>
+        <v>InventoryItem+120014Name</v>
       </c>
       <c r="F113" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120025Text</v>
+        <v>InventoryItem+120014Text</v>
       </c>
       <c r="G113" s="5">
         <v>0</v>
@@ -5330,27 +5507,27 @@
         <v>1</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>318</v>
+        <v>176</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="13">
-        <v>120026</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>173</v>
+      <c r="B114" s="15">
+        <v>120015</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>338</v>
       </c>
       <c r="D114" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120026Name.png</v>
+        <v>120015Name.png</v>
       </c>
       <c r="E114" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120026Name</v>
+        <v>InventoryItem+120015Name</v>
       </c>
       <c r="F114" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120026Text</v>
+        <v>InventoryItem+120015Text</v>
       </c>
       <c r="G114" s="5">
         <v>0</v>
@@ -5362,27 +5539,27 @@
         <v>1</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>319</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B115" s="13">
-        <v>120027</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>174</v>
+      <c r="B115" s="15">
+        <v>120016</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>339</v>
       </c>
       <c r="D115" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120027Name.png</v>
+        <v>120016Name.png</v>
       </c>
       <c r="E115" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120027Name</v>
+        <v>InventoryItem+120016Name</v>
       </c>
       <c r="F115" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120027Text</v>
+        <v>InventoryItem+120016Text</v>
       </c>
       <c r="G115" s="5">
         <v>0</v>
@@ -5394,27 +5571,27 @@
         <v>1</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>320</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B116" s="13">
-        <v>120028</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>175</v>
+      <c r="B116" s="15">
+        <v>120017</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>340</v>
       </c>
       <c r="D116" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120028Name.png</v>
+        <v>120017Name.png</v>
       </c>
       <c r="E116" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120028Name</v>
+        <v>InventoryItem+120017Name</v>
       </c>
       <c r="F116" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120028Text</v>
+        <v>InventoryItem+120017Text</v>
       </c>
       <c r="G116" s="5">
         <v>0</v>
@@ -5426,27 +5603,27 @@
         <v>1</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>321</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B117" s="13">
-        <v>120029</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>176</v>
+      <c r="B117" s="15">
+        <v>120018</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>341</v>
       </c>
       <c r="D117" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120029Name.png</v>
+        <v>120018Name.png</v>
       </c>
       <c r="E117" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120029Name</v>
+        <v>InventoryItem+120018Name</v>
       </c>
       <c r="F117" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120029Text</v>
+        <v>InventoryItem+120018Text</v>
       </c>
       <c r="G117" s="5">
         <v>0</v>
@@ -5458,27 +5635,27 @@
         <v>1</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>322</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B118" s="13">
-        <v>120030</v>
-      </c>
-      <c r="C118" s="19" t="s">
-        <v>177</v>
+      <c r="B118" s="15">
+        <v>120019</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>342</v>
       </c>
       <c r="D118" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120030Name.png</v>
+        <v>120019Name.png</v>
       </c>
       <c r="E118" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120030Name</v>
+        <v>InventoryItem+120019Name</v>
       </c>
       <c r="F118" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120030Text</v>
+        <v>InventoryItem+120019Text</v>
       </c>
       <c r="G118" s="5">
         <v>0</v>
@@ -5490,27 +5667,27 @@
         <v>1</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>323</v>
+        <v>181</v>
       </c>
     </row>
     <row r="119" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B119" s="13">
-        <v>120031</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>178</v>
+      <c r="B119" s="15">
+        <v>120020</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>343</v>
       </c>
       <c r="D119" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120031Name.png</v>
+        <v>120020Name.png</v>
       </c>
       <c r="E119" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120031Name</v>
+        <v>InventoryItem+120020Name</v>
       </c>
       <c r="F119" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120031Text</v>
+        <v>InventoryItem+120020Text</v>
       </c>
       <c r="G119" s="5">
         <v>0</v>
@@ -5522,27 +5699,27 @@
         <v>1</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>324</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="13">
-        <v>120032</v>
-      </c>
-      <c r="C120" s="19" t="s">
-        <v>179</v>
+      <c r="B120" s="15">
+        <v>120021</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="D120" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120032Name.png</v>
+        <v>120021Name.png</v>
       </c>
       <c r="E120" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120032Name</v>
+        <v>InventoryItem+120021Name</v>
       </c>
       <c r="F120" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120032Text</v>
+        <v>InventoryItem+120021Text</v>
       </c>
       <c r="G120" s="5">
         <v>0</v>
@@ -5554,27 +5731,27 @@
         <v>1</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>325</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="13">
-        <v>120033</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>180</v>
+      <c r="B121" s="15">
+        <v>120022</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>345</v>
       </c>
       <c r="D121" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120033Name.png</v>
+        <v>120022Name.png</v>
       </c>
       <c r="E121" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120033Name</v>
+        <v>InventoryItem+120022Name</v>
       </c>
       <c r="F121" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120033Text</v>
+        <v>InventoryItem+120022Text</v>
       </c>
       <c r="G121" s="5">
         <v>0</v>
@@ -5586,27 +5763,27 @@
         <v>1</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>326</v>
+        <v>184</v>
       </c>
     </row>
     <row r="122" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="13">
-        <v>120034</v>
-      </c>
-      <c r="C122" s="19" t="s">
-        <v>181</v>
+      <c r="B122" s="15">
+        <v>120023</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>346</v>
       </c>
       <c r="D122" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120034Name.png</v>
+        <v>120023Name.png</v>
       </c>
       <c r="E122" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120034Name</v>
+        <v>InventoryItem+120023Name</v>
       </c>
       <c r="F122" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120034Text</v>
+        <v>InventoryItem+120023Text</v>
       </c>
       <c r="G122" s="5">
         <v>0</v>
@@ -5618,27 +5795,27 @@
         <v>1</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>327</v>
+        <v>185</v>
       </c>
     </row>
     <row r="123" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="13">
-        <v>120035</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>182</v>
+      <c r="B123" s="15">
+        <v>120024</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="D123" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>120035Name.png</v>
+        <v>120024Name.png</v>
       </c>
       <c r="E123" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+120035Name</v>
+        <v>InventoryItem+120024Name</v>
       </c>
       <c r="F123" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+120035Text</v>
+        <v>InventoryItem+120024Text</v>
       </c>
       <c r="G123" s="5">
         <v>0</v>
@@ -5650,27 +5827,27 @@
         <v>1</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>328</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="13">
-        <v>200000</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>183</v>
+      <c r="B124" s="15">
+        <v>120025</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>348</v>
       </c>
       <c r="D124" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200000Name.png</v>
+        <v>120025Name.png</v>
       </c>
       <c r="E124" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200000Name</v>
+        <v>InventoryItem+120025Name</v>
       </c>
       <c r="F124" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200000Text</v>
+        <v>InventoryItem+120025Text</v>
       </c>
       <c r="G124" s="5">
         <v>0</v>
@@ -5682,27 +5859,27 @@
         <v>1</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>329</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B125" s="13">
-        <v>200001</v>
-      </c>
-      <c r="C125" s="18" t="s">
-        <v>184</v>
+      <c r="B125" s="15">
+        <v>120026</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>349</v>
       </c>
       <c r="D125" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200001Name.png</v>
+        <v>120026Name.png</v>
       </c>
       <c r="E125" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200001Name</v>
+        <v>InventoryItem+120026Name</v>
       </c>
       <c r="F125" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200001Text</v>
+        <v>InventoryItem+120026Text</v>
       </c>
       <c r="G125" s="5">
         <v>0</v>
@@ -5714,27 +5891,27 @@
         <v>1</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
     </row>
     <row r="126" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="13">
-        <v>200002</v>
-      </c>
-      <c r="C126" s="18" t="s">
-        <v>185</v>
+      <c r="B126" s="15">
+        <v>120027</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>350</v>
       </c>
       <c r="D126" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200002Name.png</v>
+        <v>120027Name.png</v>
       </c>
       <c r="E126" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200002Name</v>
+        <v>InventoryItem+120027Name</v>
       </c>
       <c r="F126" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200002Text</v>
+        <v>InventoryItem+120027Text</v>
       </c>
       <c r="G126" s="5">
         <v>0</v>
@@ -5746,27 +5923,27 @@
         <v>1</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>331</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B127" s="13">
-        <v>200003</v>
-      </c>
-      <c r="C127" s="18" t="s">
-        <v>186</v>
+      <c r="B127" s="15">
+        <v>120028</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>351</v>
       </c>
       <c r="D127" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200003Name.png</v>
+        <v>120028Name.png</v>
       </c>
       <c r="E127" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200003Name</v>
+        <v>InventoryItem+120028Name</v>
       </c>
       <c r="F127" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200003Text</v>
+        <v>InventoryItem+120028Text</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
@@ -5778,27 +5955,27 @@
         <v>1</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>332</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B128" s="13">
-        <v>200004</v>
-      </c>
-      <c r="C128" s="18" t="s">
-        <v>187</v>
+      <c r="B128" s="15">
+        <v>120029</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>352</v>
       </c>
       <c r="D128" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200004Name.png</v>
+        <v>120029Name.png</v>
       </c>
       <c r="E128" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200004Name</v>
+        <v>InventoryItem+120029Name</v>
       </c>
       <c r="F128" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200004Text</v>
+        <v>InventoryItem+120029Text</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
@@ -5810,27 +5987,27 @@
         <v>1</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>333</v>
+        <v>191</v>
       </c>
     </row>
     <row r="129" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B129" s="13">
-        <v>200005</v>
-      </c>
-      <c r="C129" s="18" t="s">
-        <v>188</v>
+      <c r="B129" s="15">
+        <v>120030</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>353</v>
       </c>
       <c r="D129" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200005Name.png</v>
+        <v>120030Name.png</v>
       </c>
       <c r="E129" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200005Name</v>
+        <v>InventoryItem+120030Name</v>
       </c>
       <c r="F129" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200005Text</v>
+        <v>InventoryItem+120030Text</v>
       </c>
       <c r="G129" s="5">
         <v>0</v>
@@ -5842,27 +6019,27 @@
         <v>1</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>334</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B130" s="13">
-        <v>200006</v>
-      </c>
-      <c r="C130" s="18" t="s">
-        <v>189</v>
+      <c r="B130" s="15">
+        <v>120031</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>354</v>
       </c>
       <c r="D130" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200006Name.png</v>
+        <v>120031Name.png</v>
       </c>
       <c r="E130" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200006Name</v>
+        <v>InventoryItem+120031Name</v>
       </c>
       <c r="F130" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200006Text</v>
+        <v>InventoryItem+120031Text</v>
       </c>
       <c r="G130" s="5">
         <v>0</v>
@@ -5874,27 +6051,27 @@
         <v>1</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>335</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B131" s="13">
-        <v>200007</v>
-      </c>
-      <c r="C131" s="18" t="s">
-        <v>190</v>
+      <c r="B131" s="15">
+        <v>120032</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>355</v>
       </c>
       <c r="D131" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200007Name.png</v>
+        <v>120032Name.png</v>
       </c>
       <c r="E131" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200007Name</v>
+        <v>InventoryItem+120032Name</v>
       </c>
       <c r="F131" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200007Text</v>
+        <v>InventoryItem+120032Text</v>
       </c>
       <c r="G131" s="5">
         <v>0</v>
@@ -5906,27 +6083,27 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>336</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B132" s="13">
-        <v>200008</v>
-      </c>
-      <c r="C132" s="18" t="s">
-        <v>191</v>
+      <c r="B132" s="15">
+        <v>120033</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>356</v>
       </c>
       <c r="D132" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>200008Name.png</v>
+        <v>120033Name.png</v>
       </c>
       <c r="E132" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>InventoryItem+200008Name</v>
+        <v>InventoryItem+120033Name</v>
       </c>
       <c r="F132" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>InventoryItem+200008Text</v>
+        <v>InventoryItem+120033Text</v>
       </c>
       <c r="G132" s="5">
         <v>0</v>
@@ -5938,27 +6115,27 @@
         <v>1</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>337</v>
+        <v>195</v>
       </c>
     </row>
     <row r="133" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B133" s="13">
-        <v>200009</v>
-      </c>
-      <c r="C133" s="18" t="s">
-        <v>192</v>
+      <c r="B133" s="15">
+        <v>120034</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>357</v>
       </c>
       <c r="D133" s="3" t="str">
-        <f t="shared" ref="D133:D168" si="6">CONCATENATE(B:B,"Name.png")</f>
-        <v>200009Name.png</v>
+        <f t="shared" ref="D133:D196" si="6">CONCATENATE(B:B,"Name.png")</f>
+        <v>120034Name.png</v>
       </c>
       <c r="E133" s="3" t="str">
-        <f t="shared" ref="E133:E168" si="7">CONCATENATE("InventoryItem+",B:B,"Name")</f>
-        <v>InventoryItem+200009Name</v>
+        <f t="shared" ref="E133:E196" si="7">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+120034Name</v>
       </c>
       <c r="F133" s="2" t="str">
-        <f t="shared" ref="F133:F168" si="8">CONCATENATE("InventoryItem+",B:B,"Text")</f>
-        <v>InventoryItem+200009Text</v>
+        <f t="shared" ref="F133:F196" si="8">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+120034Text</v>
       </c>
       <c r="G133" s="5">
         <v>0</v>
@@ -5970,27 +6147,27 @@
         <v>1</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>338</v>
+        <v>196</v>
       </c>
     </row>
     <row r="134" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B134" s="13">
-        <v>200010</v>
-      </c>
-      <c r="C134" s="18" t="s">
-        <v>193</v>
+      <c r="B134" s="15">
+        <v>120035</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>358</v>
       </c>
       <c r="D134" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200010Name.png</v>
+        <v>120035Name.png</v>
       </c>
       <c r="E134" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200010Name</v>
+        <v>InventoryItem+120035Name</v>
       </c>
       <c r="F134" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200010Text</v>
+        <v>InventoryItem+120035Text</v>
       </c>
       <c r="G134" s="5">
         <v>0</v>
@@ -6002,27 +6179,27 @@
         <v>1</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>339</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B135" s="13">
-        <v>200011</v>
-      </c>
-      <c r="C135" s="18" t="s">
-        <v>194</v>
+      <c r="B135" s="15">
+        <v>120036</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>359</v>
       </c>
       <c r="D135" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200011Name.png</v>
+        <v>120036Name.png</v>
       </c>
       <c r="E135" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200011Name</v>
+        <v>InventoryItem+120036Name</v>
       </c>
       <c r="F135" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200011Text</v>
+        <v>InventoryItem+120036Text</v>
       </c>
       <c r="G135" s="5">
         <v>0</v>
@@ -6034,27 +6211,27 @@
         <v>1</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B136" s="13">
-        <v>200012</v>
-      </c>
-      <c r="C136" s="18" t="s">
-        <v>195</v>
+      <c r="B136" s="15">
+        <v>120037</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>360</v>
       </c>
       <c r="D136" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200012Name.png</v>
+        <v>120037Name.png</v>
       </c>
       <c r="E136" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200012Name</v>
+        <v>InventoryItem+120037Name</v>
       </c>
       <c r="F136" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200012Text</v>
+        <v>InventoryItem+120037Text</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
@@ -6066,27 +6243,27 @@
         <v>1</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>341</v>
+        <v>199</v>
       </c>
     </row>
     <row r="137" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B137" s="13">
-        <v>200013</v>
-      </c>
-      <c r="C137" s="18" t="s">
-        <v>196</v>
+      <c r="B137" s="15">
+        <v>120038</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>361</v>
       </c>
       <c r="D137" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200013Name.png</v>
+        <v>120038Name.png</v>
       </c>
       <c r="E137" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200013Name</v>
+        <v>InventoryItem+120038Name</v>
       </c>
       <c r="F137" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200013Text</v>
+        <v>InventoryItem+120038Text</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
@@ -6098,27 +6275,27 @@
         <v>1</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>342</v>
+        <v>200</v>
       </c>
     </row>
     <row r="138" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B138" s="13">
-        <v>200014</v>
-      </c>
-      <c r="C138" s="18" t="s">
-        <v>197</v>
+      <c r="B138" s="15">
+        <v>120039</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>362</v>
       </c>
       <c r="D138" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200014Name.png</v>
+        <v>120039Name.png</v>
       </c>
       <c r="E138" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200014Name</v>
+        <v>InventoryItem+120039Name</v>
       </c>
       <c r="F138" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200014Text</v>
+        <v>InventoryItem+120039Text</v>
       </c>
       <c r="G138" s="5">
         <v>0</v>
@@ -6130,27 +6307,27 @@
         <v>1</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>343</v>
+        <v>201</v>
       </c>
     </row>
     <row r="139" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B139" s="13">
-        <v>200015</v>
-      </c>
-      <c r="C139" s="18" t="s">
-        <v>198</v>
+      <c r="B139" s="15">
+        <v>120040</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>363</v>
       </c>
       <c r="D139" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200015Name.png</v>
+        <v>120040Name.png</v>
       </c>
       <c r="E139" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200015Name</v>
+        <v>InventoryItem+120040Name</v>
       </c>
       <c r="F139" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200015Text</v>
+        <v>InventoryItem+120040Text</v>
       </c>
       <c r="G139" s="5">
         <v>0</v>
@@ -6162,27 +6339,27 @@
         <v>1</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>344</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B140" s="13">
-        <v>200016</v>
-      </c>
-      <c r="C140" s="18" t="s">
-        <v>199</v>
+      <c r="B140" s="15">
+        <v>200000</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="D140" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200016Name.png</v>
+        <v>200000Name.png</v>
       </c>
       <c r="E140" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200016Name</v>
+        <v>InventoryItem+200000Name</v>
       </c>
       <c r="F140" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200016Text</v>
+        <v>InventoryItem+200000Text</v>
       </c>
       <c r="G140" s="5">
         <v>0</v>
@@ -6194,27 +6371,27 @@
         <v>1</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>345</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B141" s="13">
-        <v>200017</v>
-      </c>
-      <c r="C141" s="18" t="s">
-        <v>200</v>
+      <c r="B141" s="15">
+        <v>200001</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D141" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200017Name.png</v>
+        <v>200001Name.png</v>
       </c>
       <c r="E141" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200017Name</v>
+        <v>InventoryItem+200001Name</v>
       </c>
       <c r="F141" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200017Text</v>
+        <v>InventoryItem+200001Text</v>
       </c>
       <c r="G141" s="5">
         <v>0</v>
@@ -6226,27 +6403,27 @@
         <v>1</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>346</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B142" s="13">
-        <v>200018</v>
-      </c>
-      <c r="C142" s="18" t="s">
-        <v>201</v>
+      <c r="B142" s="15">
+        <v>200002</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="D142" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200018Name.png</v>
+        <v>200002Name.png</v>
       </c>
       <c r="E142" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200018Name</v>
+        <v>InventoryItem+200002Name</v>
       </c>
       <c r="F142" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200018Text</v>
+        <v>InventoryItem+200002Text</v>
       </c>
       <c r="G142" s="5">
         <v>0</v>
@@ -6258,27 +6435,27 @@
         <v>1</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>347</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B143" s="13">
-        <v>200019</v>
-      </c>
-      <c r="C143" s="18" t="s">
-        <v>202</v>
+      <c r="B143" s="15">
+        <v>200003</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="D143" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200019Name.png</v>
+        <v>200003Name.png</v>
       </c>
       <c r="E143" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200019Name</v>
+        <v>InventoryItem+200003Name</v>
       </c>
       <c r="F143" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200019Text</v>
+        <v>InventoryItem+200003Text</v>
       </c>
       <c r="G143" s="5">
         <v>0</v>
@@ -6290,27 +6467,27 @@
         <v>1</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B144" s="13">
-        <v>200020</v>
-      </c>
-      <c r="C144" s="18" t="s">
-        <v>203</v>
+      <c r="B144" s="15">
+        <v>210000</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>364</v>
       </c>
       <c r="D144" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200020Name.png</v>
+        <v>210000Name.png</v>
       </c>
       <c r="E144" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200020Name</v>
+        <v>InventoryItem+210000Name</v>
       </c>
       <c r="F144" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200020Text</v>
+        <v>InventoryItem+210000Text</v>
       </c>
       <c r="G144" s="5">
         <v>0</v>
@@ -6322,27 +6499,27 @@
         <v>1</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>349</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B145" s="13">
-        <v>200021</v>
-      </c>
-      <c r="C145" s="18" t="s">
-        <v>204</v>
+      <c r="B145" s="15">
+        <v>210001</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>365</v>
       </c>
       <c r="D145" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200021Name.png</v>
+        <v>210001Name.png</v>
       </c>
       <c r="E145" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200021Name</v>
+        <v>InventoryItem+210001Name</v>
       </c>
       <c r="F145" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200021Text</v>
+        <v>InventoryItem+210001Text</v>
       </c>
       <c r="G145" s="5">
         <v>0</v>
@@ -6354,27 +6531,27 @@
         <v>1</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>350</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B146" s="13">
-        <v>200022</v>
-      </c>
-      <c r="C146" s="18" t="s">
-        <v>205</v>
+      <c r="B146" s="15">
+        <v>210002</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>366</v>
       </c>
       <c r="D146" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200022Name.png</v>
+        <v>210002Name.png</v>
       </c>
       <c r="E146" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200022Name</v>
+        <v>InventoryItem+210002Name</v>
       </c>
       <c r="F146" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200022Text</v>
+        <v>InventoryItem+210002Text</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
@@ -6386,27 +6563,27 @@
         <v>1</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>351</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B147" s="13">
-        <v>200023</v>
-      </c>
-      <c r="C147" s="18" t="s">
-        <v>206</v>
+      <c r="B147" s="15">
+        <v>210003</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>367</v>
       </c>
       <c r="D147" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200023Name.png</v>
+        <v>210003Name.png</v>
       </c>
       <c r="E147" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200023Name</v>
+        <v>InventoryItem+210003Name</v>
       </c>
       <c r="F147" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200023Text</v>
+        <v>InventoryItem+210003Text</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
@@ -6418,27 +6595,27 @@
         <v>1</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>352</v>
+        <v>210</v>
       </c>
     </row>
     <row r="148" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B148" s="13">
-        <v>200024</v>
-      </c>
-      <c r="C148" s="18" t="s">
-        <v>207</v>
+      <c r="B148" s="15">
+        <v>210004</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>368</v>
       </c>
       <c r="D148" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200024Name.png</v>
+        <v>210004Name.png</v>
       </c>
       <c r="E148" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200024Name</v>
+        <v>InventoryItem+210004Name</v>
       </c>
       <c r="F148" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200024Text</v>
+        <v>InventoryItem+210004Text</v>
       </c>
       <c r="G148" s="5">
         <v>0</v>
@@ -6450,27 +6627,27 @@
         <v>1</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>353</v>
+        <v>211</v>
       </c>
     </row>
     <row r="149" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B149" s="13">
-        <v>200025</v>
-      </c>
-      <c r="C149" s="18" t="s">
-        <v>208</v>
+      <c r="B149" s="15">
+        <v>210005</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>369</v>
       </c>
       <c r="D149" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200025Name.png</v>
+        <v>210005Name.png</v>
       </c>
       <c r="E149" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200025Name</v>
+        <v>InventoryItem+210005Name</v>
       </c>
       <c r="F149" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200025Text</v>
+        <v>InventoryItem+210005Text</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
@@ -6482,27 +6659,27 @@
         <v>1</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>354</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B150" s="13">
-        <v>200026</v>
-      </c>
-      <c r="C150" s="18" t="s">
-        <v>209</v>
+      <c r="B150" s="15">
+        <v>210006</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>370</v>
       </c>
       <c r="D150" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200026Name.png</v>
+        <v>210006Name.png</v>
       </c>
       <c r="E150" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200026Name</v>
+        <v>InventoryItem+210006Name</v>
       </c>
       <c r="F150" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200026Text</v>
+        <v>InventoryItem+210006Text</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
@@ -6514,27 +6691,27 @@
         <v>1</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>355</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B151" s="13">
-        <v>200027</v>
-      </c>
-      <c r="C151" s="18" t="s">
-        <v>210</v>
+      <c r="B151" s="15">
+        <v>210007</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>371</v>
       </c>
       <c r="D151" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200027Name.png</v>
+        <v>210007Name.png</v>
       </c>
       <c r="E151" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200027Name</v>
+        <v>InventoryItem+210007Name</v>
       </c>
       <c r="F151" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200027Text</v>
+        <v>InventoryItem+210007Text</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
@@ -6546,27 +6723,27 @@
         <v>1</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>356</v>
+        <v>214</v>
       </c>
     </row>
     <row r="152" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B152" s="13">
-        <v>200028</v>
-      </c>
-      <c r="C152" s="18" t="s">
-        <v>211</v>
+      <c r="B152" s="15">
+        <v>210008</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>372</v>
       </c>
       <c r="D152" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200028Name.png</v>
+        <v>210008Name.png</v>
       </c>
       <c r="E152" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200028Name</v>
+        <v>InventoryItem+210008Name</v>
       </c>
       <c r="F152" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200028Text</v>
+        <v>InventoryItem+210008Text</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
@@ -6578,27 +6755,27 @@
         <v>1</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>357</v>
+        <v>215</v>
       </c>
     </row>
     <row r="153" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B153" s="13">
-        <v>200029</v>
-      </c>
-      <c r="C153" s="18" t="s">
-        <v>212</v>
+      <c r="B153" s="15">
+        <v>210009</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>373</v>
       </c>
       <c r="D153" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>200029Name.png</v>
+        <v>210009Name.png</v>
       </c>
       <c r="E153" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+200029Name</v>
+        <v>InventoryItem+210009Name</v>
       </c>
       <c r="F153" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+200029Text</v>
+        <v>InventoryItem+210009Text</v>
       </c>
       <c r="G153" s="5">
         <v>0</v>
@@ -6610,27 +6787,27 @@
         <v>1</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
     </row>
     <row r="154" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B154" s="13">
-        <v>210000</v>
-      </c>
-      <c r="C154" s="18" t="s">
-        <v>213</v>
+      <c r="B154" s="15">
+        <v>210010</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>374</v>
       </c>
       <c r="D154" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>210000Name.png</v>
+        <v>210010Name.png</v>
       </c>
       <c r="E154" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+210000Name</v>
+        <v>InventoryItem+210010Name</v>
       </c>
       <c r="F154" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+210000Text</v>
+        <v>InventoryItem+210010Text</v>
       </c>
       <c r="G154" s="5">
         <v>0</v>
@@ -6642,27 +6819,27 @@
         <v>1</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>359</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B155" s="13">
-        <v>210001</v>
-      </c>
-      <c r="C155" s="18" t="s">
-        <v>214</v>
+      <c r="B155" s="15">
+        <v>210011</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>375</v>
       </c>
       <c r="D155" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>210001Name.png</v>
+        <v>210011Name.png</v>
       </c>
       <c r="E155" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+210001Name</v>
+        <v>InventoryItem+210011Name</v>
       </c>
       <c r="F155" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+210001Text</v>
+        <v>InventoryItem+210011Text</v>
       </c>
       <c r="G155" s="5">
         <v>0</v>
@@ -6674,27 +6851,27 @@
         <v>1</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>360</v>
+        <v>218</v>
       </c>
     </row>
     <row r="156" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B156" s="13">
-        <v>210002</v>
-      </c>
-      <c r="C156" s="18" t="s">
-        <v>215</v>
+      <c r="B156" s="15">
+        <v>210012</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>376</v>
       </c>
       <c r="D156" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>210002Name.png</v>
+        <v>210012Name.png</v>
       </c>
       <c r="E156" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+210002Name</v>
+        <v>InventoryItem+210012Name</v>
       </c>
       <c r="F156" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+210002Text</v>
+        <v>InventoryItem+210012Text</v>
       </c>
       <c r="G156" s="5">
         <v>0</v>
@@ -6706,27 +6883,27 @@
         <v>1</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>361</v>
+        <v>219</v>
       </c>
     </row>
     <row r="157" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B157" s="13">
-        <v>210003</v>
-      </c>
-      <c r="C157" s="18" t="s">
-        <v>216</v>
+      <c r="B157" s="15">
+        <v>210013</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>377</v>
       </c>
       <c r="D157" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>210003Name.png</v>
+        <v>210013Name.png</v>
       </c>
       <c r="E157" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+210003Name</v>
+        <v>InventoryItem+210013Name</v>
       </c>
       <c r="F157" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+210003Text</v>
+        <v>InventoryItem+210013Text</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
@@ -6738,27 +6915,27 @@
         <v>1</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>362</v>
+        <v>220</v>
       </c>
     </row>
     <row r="158" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B158" s="13">
-        <v>220000</v>
-      </c>
-      <c r="C158" s="18" t="s">
-        <v>217</v>
+      <c r="B158" s="15">
+        <v>210014</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>378</v>
       </c>
       <c r="D158" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220000Name.png</v>
+        <v>210014Name.png</v>
       </c>
       <c r="E158" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220000Name</v>
+        <v>InventoryItem+210014Name</v>
       </c>
       <c r="F158" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220000Text</v>
+        <v>InventoryItem+210014Text</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
@@ -6770,27 +6947,27 @@
         <v>1</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>363</v>
+        <v>221</v>
       </c>
     </row>
     <row r="159" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B159" s="13">
-        <v>220001</v>
-      </c>
-      <c r="C159" s="17" t="s">
-        <v>218</v>
+      <c r="B159" s="15">
+        <v>210015</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>379</v>
       </c>
       <c r="D159" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220001Name.png</v>
+        <v>210015Name.png</v>
       </c>
       <c r="E159" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220001Name</v>
+        <v>InventoryItem+210015Name</v>
       </c>
       <c r="F159" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220001Text</v>
+        <v>InventoryItem+210015Text</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
@@ -6802,27 +6979,27 @@
         <v>1</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>364</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B160" s="13">
-        <v>220002</v>
-      </c>
-      <c r="C160" s="17" t="s">
-        <v>219</v>
+      <c r="B160" s="15">
+        <v>210016</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>380</v>
       </c>
       <c r="D160" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220002Name.png</v>
+        <v>210016Name.png</v>
       </c>
       <c r="E160" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220002Name</v>
+        <v>InventoryItem+210016Name</v>
       </c>
       <c r="F160" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220002Text</v>
+        <v>InventoryItem+210016Text</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
@@ -6834,27 +7011,27 @@
         <v>1</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B161" s="13">
-        <v>220003</v>
-      </c>
-      <c r="C161" s="20" t="s">
-        <v>220</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B161" s="15">
+        <v>210017</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>381</v>
       </c>
       <c r="D161" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220003Name.png</v>
+        <v>210017Name.png</v>
       </c>
       <c r="E161" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220003Name</v>
+        <v>InventoryItem+210017Name</v>
       </c>
       <c r="F161" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220003Text</v>
+        <v>InventoryItem+210017Text</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
@@ -6866,27 +7043,27 @@
         <v>1</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B162" s="13">
-        <v>220004</v>
-      </c>
-      <c r="C162" s="20" t="s">
-        <v>221</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B162" s="15">
+        <v>210018</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>382</v>
       </c>
       <c r="D162" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220004Name.png</v>
+        <v>210018Name.png</v>
       </c>
       <c r="E162" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220004Name</v>
+        <v>InventoryItem+210018Name</v>
       </c>
       <c r="F162" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220004Text</v>
+        <v>InventoryItem+210018Text</v>
       </c>
       <c r="G162" s="5">
         <v>0</v>
@@ -6898,27 +7075,27 @@
         <v>1</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>367</v>
+        <v>225</v>
       </c>
     </row>
     <row r="163" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B163" s="13">
-        <v>220005</v>
-      </c>
-      <c r="C163" s="17" t="s">
-        <v>222</v>
+      <c r="B163" s="15">
+        <v>210019</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>383</v>
       </c>
       <c r="D163" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220005Name.png</v>
+        <v>210019Name.png</v>
       </c>
       <c r="E163" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220005Name</v>
+        <v>InventoryItem+210019Name</v>
       </c>
       <c r="F163" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220005Text</v>
+        <v>InventoryItem+210019Text</v>
       </c>
       <c r="G163" s="5">
         <v>0</v>
@@ -6930,27 +7107,27 @@
         <v>1</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B164" s="13">
-        <v>220006</v>
-      </c>
-      <c r="C164" s="20" t="s">
-        <v>223</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B164" s="15">
+        <v>220000</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="D164" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220006Name.png</v>
+        <v>220000Name.png</v>
       </c>
       <c r="E164" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220006Name</v>
+        <v>InventoryItem+220000Name</v>
       </c>
       <c r="F164" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220006Text</v>
+        <v>InventoryItem+220000Text</v>
       </c>
       <c r="G164" s="5">
         <v>0</v>
@@ -6962,27 +7139,27 @@
         <v>1</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="165" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B165" s="13">
-        <v>220007</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>224</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B165" s="15">
+        <v>220001</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="D165" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220007Name.png</v>
+        <v>220001Name.png</v>
       </c>
       <c r="E165" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220007Name</v>
+        <v>InventoryItem+220001Name</v>
       </c>
       <c r="F165" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220007Text</v>
+        <v>InventoryItem+220001Text</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
@@ -6994,27 +7171,27 @@
         <v>1</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="166" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B166" s="13">
-        <v>220008</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>225</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B166" s="15">
+        <v>220002</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="D166" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220008Name.png</v>
+        <v>220002Name.png</v>
       </c>
       <c r="E166" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220008Name</v>
+        <v>InventoryItem+220002Name</v>
       </c>
       <c r="F166" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220008Text</v>
+        <v>InventoryItem+220002Text</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
@@ -7026,27 +7203,27 @@
         <v>1</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="167" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B167" s="13">
-        <v>220009</v>
-      </c>
-      <c r="C167" s="20" t="s">
-        <v>226</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B167" s="15">
+        <v>220003</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D167" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220009Name.png</v>
+        <v>220003Name.png</v>
       </c>
       <c r="E167" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220009Name</v>
+        <v>InventoryItem+220003Name</v>
       </c>
       <c r="F167" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220009Text</v>
+        <v>InventoryItem+220003Text</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
@@ -7058,27 +7235,27 @@
         <v>1</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B168" s="14">
-        <v>220010</v>
-      </c>
-      <c r="C168" s="20" t="s">
-        <v>227</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B168" s="15">
+        <v>220004</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>80</v>
       </c>
       <c r="D168" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>220010Name.png</v>
+        <v>220004Name.png</v>
       </c>
       <c r="E168" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>InventoryItem+220010Name</v>
+        <v>InventoryItem+220004Name</v>
       </c>
       <c r="F168" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>InventoryItem+220010Text</v>
+        <v>InventoryItem+220004Text</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
@@ -7090,135 +7267,2312 @@
         <v>1</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B169" s="14"/>
-      <c r="C169" s="21"/>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B170" s="14"/>
-      <c r="C170" s="21"/>
-    </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B171" s="14"/>
-      <c r="C171" s="21"/>
-    </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B172" s="14"/>
-      <c r="C172" s="21"/>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B173" s="14"/>
-      <c r="C173" s="21"/>
-    </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B174" s="14"/>
-      <c r="C174" s="21"/>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B175" s="14"/>
-      <c r="C175" s="21"/>
-    </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B176" s="14"/>
-      <c r="C176" s="21"/>
-    </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177" s="14"/>
-      <c r="C177" s="21"/>
-    </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B178" s="14"/>
-      <c r="C178" s="21"/>
-    </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B179" s="14"/>
-      <c r="C179" s="21"/>
-    </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B180" s="14"/>
-      <c r="C180" s="21"/>
-    </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B181" s="14"/>
-      <c r="C181" s="21"/>
-    </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B182" s="14"/>
-      <c r="C182" s="21"/>
-    </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B183" s="14"/>
-      <c r="C183" s="21"/>
-    </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B184" s="14"/>
-      <c r="C184" s="21"/>
-    </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B185" s="14"/>
-      <c r="C185" s="21"/>
-    </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B186" s="14"/>
-      <c r="C186" s="21"/>
-    </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B187" s="14"/>
-      <c r="C187" s="21"/>
-    </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188" s="14"/>
-      <c r="C188" s="21"/>
-    </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B189" s="14"/>
-      <c r="C189" s="21"/>
-    </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B190" s="14"/>
-      <c r="C190" s="21"/>
-    </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B191" s="14"/>
-      <c r="C191" s="21"/>
-    </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B192" s="14"/>
-      <c r="C192" s="21"/>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B193" s="14"/>
-      <c r="C193" s="21"/>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194" s="14"/>
-      <c r="C194" s="21"/>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B195" s="14"/>
-      <c r="C195" s="21"/>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B196" s="14"/>
-      <c r="C196" s="21"/>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B197" s="14"/>
-      <c r="C197" s="21"/>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B198" s="14"/>
-      <c r="C198" s="21"/>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B199" s="14"/>
-      <c r="C199" s="21"/>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C200" s="21"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B169" s="15">
+        <v>220005</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D169" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>220005Name.png</v>
+      </c>
+      <c r="E169" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+220005Name</v>
+      </c>
+      <c r="F169" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+220005Text</v>
+      </c>
+      <c r="G169" s="5">
+        <v>0</v>
+      </c>
+      <c r="H169" s="3">
+        <v>999</v>
+      </c>
+      <c r="I169" s="4">
+        <v>1</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B170" s="15">
+        <v>220006</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D170" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>220006Name.png</v>
+      </c>
+      <c r="E170" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+220006Name</v>
+      </c>
+      <c r="F170" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+220006Text</v>
+      </c>
+      <c r="G170" s="5">
+        <v>0</v>
+      </c>
+      <c r="H170" s="3">
+        <v>999</v>
+      </c>
+      <c r="I170" s="4">
+        <v>1</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B171" s="15">
+        <v>220007</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D171" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>220007Name.png</v>
+      </c>
+      <c r="E171" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+220007Name</v>
+      </c>
+      <c r="F171" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+220007Text</v>
+      </c>
+      <c r="G171" s="5">
+        <v>0</v>
+      </c>
+      <c r="H171" s="3">
+        <v>999</v>
+      </c>
+      <c r="I171" s="4">
+        <v>1</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B172" s="15">
+        <v>220008</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D172" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>220008Name.png</v>
+      </c>
+      <c r="E172" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+220008Name</v>
+      </c>
+      <c r="F172" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+220008Text</v>
+      </c>
+      <c r="G172" s="5">
+        <v>0</v>
+      </c>
+      <c r="H172" s="3">
+        <v>999</v>
+      </c>
+      <c r="I172" s="4">
+        <v>1</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B173" s="15">
+        <v>220009</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D173" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>220009Name.png</v>
+      </c>
+      <c r="E173" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+220009Name</v>
+      </c>
+      <c r="F173" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+220009Text</v>
+      </c>
+      <c r="G173" s="5">
+        <v>0</v>
+      </c>
+      <c r="H173" s="3">
+        <v>999</v>
+      </c>
+      <c r="I173" s="4">
+        <v>1</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B174" s="15">
+        <v>300000</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="D174" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300000Name.png</v>
+      </c>
+      <c r="E174" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300000Name</v>
+      </c>
+      <c r="F174" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300000Text</v>
+      </c>
+      <c r="G174" s="5">
+        <v>0</v>
+      </c>
+      <c r="H174" s="3">
+        <v>999</v>
+      </c>
+      <c r="I174" s="4">
+        <v>1</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B175" s="15">
+        <v>300001</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D175" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300001Name.png</v>
+      </c>
+      <c r="E175" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300001Name</v>
+      </c>
+      <c r="F175" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300001Text</v>
+      </c>
+      <c r="G175" s="5">
+        <v>0</v>
+      </c>
+      <c r="H175" s="3">
+        <v>999</v>
+      </c>
+      <c r="I175" s="4">
+        <v>1</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B176" s="15">
+        <v>300002</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="D176" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300002Name.png</v>
+      </c>
+      <c r="E176" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300002Name</v>
+      </c>
+      <c r="F176" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300002Text</v>
+      </c>
+      <c r="G176" s="5">
+        <v>0</v>
+      </c>
+      <c r="H176" s="3">
+        <v>999</v>
+      </c>
+      <c r="I176" s="4">
+        <v>1</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="177" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B177" s="15">
+        <v>300003</v>
+      </c>
+      <c r="C177" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="D177" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300003Name.png</v>
+      </c>
+      <c r="E177" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300003Name</v>
+      </c>
+      <c r="F177" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300003Text</v>
+      </c>
+      <c r="G177" s="5">
+        <v>0</v>
+      </c>
+      <c r="H177" s="3">
+        <v>999</v>
+      </c>
+      <c r="I177" s="4">
+        <v>1</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B178" s="15">
+        <v>300004</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="D178" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300004Name.png</v>
+      </c>
+      <c r="E178" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300004Name</v>
+      </c>
+      <c r="F178" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300004Text</v>
+      </c>
+      <c r="G178" s="5">
+        <v>0</v>
+      </c>
+      <c r="H178" s="3">
+        <v>999</v>
+      </c>
+      <c r="I178" s="4">
+        <v>1</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B179" s="15">
+        <v>300005</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="D179" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300005Name.png</v>
+      </c>
+      <c r="E179" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300005Name</v>
+      </c>
+      <c r="F179" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300005Text</v>
+      </c>
+      <c r="G179" s="5">
+        <v>0</v>
+      </c>
+      <c r="H179" s="3">
+        <v>999</v>
+      </c>
+      <c r="I179" s="4">
+        <v>1</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B180" s="15">
+        <v>300006</v>
+      </c>
+      <c r="C180" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="D180" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300006Name.png</v>
+      </c>
+      <c r="E180" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300006Name</v>
+      </c>
+      <c r="F180" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300006Text</v>
+      </c>
+      <c r="G180" s="5">
+        <v>0</v>
+      </c>
+      <c r="H180" s="3">
+        <v>999</v>
+      </c>
+      <c r="I180" s="4">
+        <v>1</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B181" s="15">
+        <v>300007</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="D181" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300007Name.png</v>
+      </c>
+      <c r="E181" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300007Name</v>
+      </c>
+      <c r="F181" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300007Text</v>
+      </c>
+      <c r="G181" s="5">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3">
+        <v>999</v>
+      </c>
+      <c r="I181" s="4">
+        <v>1</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B182" s="15">
+        <v>300008</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D182" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300008Name.png</v>
+      </c>
+      <c r="E182" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300008Name</v>
+      </c>
+      <c r="F182" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300008Text</v>
+      </c>
+      <c r="G182" s="5">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3">
+        <v>999</v>
+      </c>
+      <c r="I182" s="4">
+        <v>1</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B183" s="15">
+        <v>300009</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="D183" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>300009Name.png</v>
+      </c>
+      <c r="E183" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+300009Name</v>
+      </c>
+      <c r="F183" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+300009Text</v>
+      </c>
+      <c r="G183" s="5">
+        <v>0</v>
+      </c>
+      <c r="H183" s="3">
+        <v>999</v>
+      </c>
+      <c r="I183" s="4">
+        <v>1</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B184" s="15">
+        <v>130000</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="D184" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>130000Name.png</v>
+      </c>
+      <c r="E184" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+130000Name</v>
+      </c>
+      <c r="F184" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+130000Text</v>
+      </c>
+      <c r="G184" s="5">
+        <v>0</v>
+      </c>
+      <c r="H184" s="3">
+        <v>999</v>
+      </c>
+      <c r="I184" s="4">
+        <v>1</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B185" s="15">
+        <v>130001</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="D185" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>130001Name.png</v>
+      </c>
+      <c r="E185" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+130001Name</v>
+      </c>
+      <c r="F185" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+130001Text</v>
+      </c>
+      <c r="G185" s="5">
+        <v>0</v>
+      </c>
+      <c r="H185" s="3">
+        <v>999</v>
+      </c>
+      <c r="I185" s="4">
+        <v>1</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B186" s="15">
+        <v>130002</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="D186" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>130002Name.png</v>
+      </c>
+      <c r="E186" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+130002Name</v>
+      </c>
+      <c r="F186" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+130002Text</v>
+      </c>
+      <c r="G186" s="5">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3">
+        <v>999</v>
+      </c>
+      <c r="I186" s="4">
+        <v>1</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B187" s="15">
+        <v>140000</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D187" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>140000Name.png</v>
+      </c>
+      <c r="E187" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+140000Name</v>
+      </c>
+      <c r="F187" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+140000Text</v>
+      </c>
+      <c r="G187" s="5">
+        <v>0</v>
+      </c>
+      <c r="H187" s="3">
+        <v>999</v>
+      </c>
+      <c r="I187" s="4">
+        <v>1</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B188" s="15">
+        <v>140001</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="D188" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>140001Name.png</v>
+      </c>
+      <c r="E188" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+140001Name</v>
+      </c>
+      <c r="F188" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+140001Text</v>
+      </c>
+      <c r="G188" s="5">
+        <v>0</v>
+      </c>
+      <c r="H188" s="3">
+        <v>999</v>
+      </c>
+      <c r="I188" s="4">
+        <v>1</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B189" s="15">
+        <v>140002</v>
+      </c>
+      <c r="C189" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="D189" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>140002Name.png</v>
+      </c>
+      <c r="E189" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+140002Name</v>
+      </c>
+      <c r="F189" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+140002Text</v>
+      </c>
+      <c r="G189" s="5">
+        <v>0</v>
+      </c>
+      <c r="H189" s="3">
+        <v>999</v>
+      </c>
+      <c r="I189" s="4">
+        <v>1</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B190" s="15">
+        <v>140003</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="D190" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>140003Name.png</v>
+      </c>
+      <c r="E190" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+140003Name</v>
+      </c>
+      <c r="F190" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+140003Text</v>
+      </c>
+      <c r="G190" s="5">
+        <v>0</v>
+      </c>
+      <c r="H190" s="3">
+        <v>999</v>
+      </c>
+      <c r="I190" s="4">
+        <v>1</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B191" s="15">
+        <v>150000</v>
+      </c>
+      <c r="C191" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="D191" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150000Name.png</v>
+      </c>
+      <c r="E191" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150000Name</v>
+      </c>
+      <c r="F191" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150000Text</v>
+      </c>
+      <c r="G191" s="5">
+        <v>0</v>
+      </c>
+      <c r="H191" s="3">
+        <v>999</v>
+      </c>
+      <c r="I191" s="4">
+        <v>1</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B192" s="15">
+        <v>150001</v>
+      </c>
+      <c r="C192" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="D192" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150001Name.png</v>
+      </c>
+      <c r="E192" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150001Name</v>
+      </c>
+      <c r="F192" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150001Text</v>
+      </c>
+      <c r="G192" s="5">
+        <v>0</v>
+      </c>
+      <c r="H192" s="3">
+        <v>999</v>
+      </c>
+      <c r="I192" s="4">
+        <v>1</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B193" s="15">
+        <v>150002</v>
+      </c>
+      <c r="C193" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="D193" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150002Name.png</v>
+      </c>
+      <c r="E193" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150002Name</v>
+      </c>
+      <c r="F193" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150002Text</v>
+      </c>
+      <c r="G193" s="5">
+        <v>0</v>
+      </c>
+      <c r="H193" s="3">
+        <v>999</v>
+      </c>
+      <c r="I193" s="4">
+        <v>1</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B194" s="15">
+        <v>150003</v>
+      </c>
+      <c r="C194" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="D194" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150003Name.png</v>
+      </c>
+      <c r="E194" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150003Name</v>
+      </c>
+      <c r="F194" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150003Text</v>
+      </c>
+      <c r="G194" s="5">
+        <v>0</v>
+      </c>
+      <c r="H194" s="3">
+        <v>999</v>
+      </c>
+      <c r="I194" s="4">
+        <v>1</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B195" s="15">
+        <v>150004</v>
+      </c>
+      <c r="C195" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D195" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150004Name.png</v>
+      </c>
+      <c r="E195" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150004Name</v>
+      </c>
+      <c r="F195" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150004Text</v>
+      </c>
+      <c r="G195" s="5">
+        <v>0</v>
+      </c>
+      <c r="H195" s="3">
+        <v>999</v>
+      </c>
+      <c r="I195" s="4">
+        <v>1</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B196" s="15">
+        <v>150005</v>
+      </c>
+      <c r="C196" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D196" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>150005Name.png</v>
+      </c>
+      <c r="E196" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>InventoryItem+150005Name</v>
+      </c>
+      <c r="F196" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v>InventoryItem+150005Text</v>
+      </c>
+      <c r="G196" s="5">
+        <v>0</v>
+      </c>
+      <c r="H196" s="3">
+        <v>999</v>
+      </c>
+      <c r="I196" s="4">
+        <v>1</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B197" s="15">
+        <v>150006</v>
+      </c>
+      <c r="C197" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="D197" s="3" t="str">
+        <f t="shared" ref="D197:D240" si="9">CONCATENATE(B:B,"Name.png")</f>
+        <v>150006Name.png</v>
+      </c>
+      <c r="E197" s="3" t="str">
+        <f t="shared" ref="E197:E240" si="10">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150006Name</v>
+      </c>
+      <c r="F197" s="2" t="str">
+        <f t="shared" ref="F197:F240" si="11">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150006Text</v>
+      </c>
+      <c r="G197" s="5">
+        <v>0</v>
+      </c>
+      <c r="H197" s="3">
+        <v>999</v>
+      </c>
+      <c r="I197" s="4">
+        <v>1</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B198" s="15">
+        <v>150007</v>
+      </c>
+      <c r="C198" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="D198" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>150007Name.png</v>
+      </c>
+      <c r="E198" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+150007Name</v>
+      </c>
+      <c r="F198" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+150007Text</v>
+      </c>
+      <c r="G198" s="5">
+        <v>0</v>
+      </c>
+      <c r="H198" s="3">
+        <v>999</v>
+      </c>
+      <c r="I198" s="4">
+        <v>1</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B199" s="15">
+        <v>150008</v>
+      </c>
+      <c r="C199" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="D199" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>150008Name.png</v>
+      </c>
+      <c r="E199" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+150008Name</v>
+      </c>
+      <c r="F199" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+150008Text</v>
+      </c>
+      <c r="G199" s="5">
+        <v>0</v>
+      </c>
+      <c r="H199" s="3">
+        <v>999</v>
+      </c>
+      <c r="I199" s="4">
+        <v>1</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B200" s="15">
+        <v>150009</v>
+      </c>
+      <c r="C200" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="D200" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>150009Name.png</v>
+      </c>
+      <c r="E200" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+150009Name</v>
+      </c>
+      <c r="F200" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+150009Text</v>
+      </c>
+      <c r="G200" s="5">
+        <v>0</v>
+      </c>
+      <c r="H200" s="3">
+        <v>999</v>
+      </c>
+      <c r="I200" s="4">
+        <v>1</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B201" s="15">
+        <v>310000</v>
+      </c>
+      <c r="C201" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="D201" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310000Name.png</v>
+      </c>
+      <c r="E201" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310000Name</v>
+      </c>
+      <c r="F201" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310000Text</v>
+      </c>
+      <c r="G201" s="5">
+        <v>0</v>
+      </c>
+      <c r="H201" s="3">
+        <v>999</v>
+      </c>
+      <c r="I201" s="4">
+        <v>1</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B202" s="15">
+        <v>310001</v>
+      </c>
+      <c r="C202" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D202" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310001Name.png</v>
+      </c>
+      <c r="E202" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310001Name</v>
+      </c>
+      <c r="F202" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310001Text</v>
+      </c>
+      <c r="G202" s="5">
+        <v>0</v>
+      </c>
+      <c r="H202" s="3">
+        <v>999</v>
+      </c>
+      <c r="I202" s="4">
+        <v>1</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B203" s="15">
+        <v>310002</v>
+      </c>
+      <c r="C203" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="D203" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310002Name.png</v>
+      </c>
+      <c r="E203" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310002Name</v>
+      </c>
+      <c r="F203" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310002Text</v>
+      </c>
+      <c r="G203" s="5">
+        <v>0</v>
+      </c>
+      <c r="H203" s="3">
+        <v>999</v>
+      </c>
+      <c r="I203" s="4">
+        <v>1</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B204" s="15">
+        <v>310003</v>
+      </c>
+      <c r="C204" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D204" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310003Name.png</v>
+      </c>
+      <c r="E204" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310003Name</v>
+      </c>
+      <c r="F204" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310003Text</v>
+      </c>
+      <c r="G204" s="5">
+        <v>0</v>
+      </c>
+      <c r="H204" s="3">
+        <v>999</v>
+      </c>
+      <c r="I204" s="4">
+        <v>1</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B205" s="15">
+        <v>310004</v>
+      </c>
+      <c r="C205" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="D205" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310004Name.png</v>
+      </c>
+      <c r="E205" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310004Name</v>
+      </c>
+      <c r="F205" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310004Text</v>
+      </c>
+      <c r="G205" s="5">
+        <v>0</v>
+      </c>
+      <c r="H205" s="3">
+        <v>999</v>
+      </c>
+      <c r="I205" s="4">
+        <v>1</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B206" s="15">
+        <v>310005</v>
+      </c>
+      <c r="C206" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="D206" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310005Name.png</v>
+      </c>
+      <c r="E206" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310005Name</v>
+      </c>
+      <c r="F206" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310005Text</v>
+      </c>
+      <c r="G206" s="5">
+        <v>0</v>
+      </c>
+      <c r="H206" s="3">
+        <v>999</v>
+      </c>
+      <c r="I206" s="4">
+        <v>1</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B207" s="15">
+        <v>310006</v>
+      </c>
+      <c r="C207" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D207" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310006Name.png</v>
+      </c>
+      <c r="E207" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310006Name</v>
+      </c>
+      <c r="F207" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310006Text</v>
+      </c>
+      <c r="G207" s="5">
+        <v>0</v>
+      </c>
+      <c r="H207" s="3">
+        <v>999</v>
+      </c>
+      <c r="I207" s="4">
+        <v>1</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B208" s="15">
+        <v>310007</v>
+      </c>
+      <c r="C208" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="D208" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310007Name.png</v>
+      </c>
+      <c r="E208" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310007Name</v>
+      </c>
+      <c r="F208" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310007Text</v>
+      </c>
+      <c r="G208" s="5">
+        <v>0</v>
+      </c>
+      <c r="H208" s="3">
+        <v>999</v>
+      </c>
+      <c r="I208" s="4">
+        <v>1</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B209" s="15">
+        <v>310008</v>
+      </c>
+      <c r="C209" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="D209" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310008Name.png</v>
+      </c>
+      <c r="E209" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310008Name</v>
+      </c>
+      <c r="F209" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310008Text</v>
+      </c>
+      <c r="G209" s="5">
+        <v>0</v>
+      </c>
+      <c r="H209" s="3">
+        <v>999</v>
+      </c>
+      <c r="I209" s="4">
+        <v>1</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B210" s="15">
+        <v>310009</v>
+      </c>
+      <c r="C210" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="D210" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310009Name.png</v>
+      </c>
+      <c r="E210" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310009Name</v>
+      </c>
+      <c r="F210" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310009Text</v>
+      </c>
+      <c r="G210" s="5">
+        <v>0</v>
+      </c>
+      <c r="H210" s="3">
+        <v>999</v>
+      </c>
+      <c r="I210" s="4">
+        <v>1</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B211" s="15">
+        <v>310010</v>
+      </c>
+      <c r="C211" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="D211" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310010Name.png</v>
+      </c>
+      <c r="E211" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310010Name</v>
+      </c>
+      <c r="F211" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310010Text</v>
+      </c>
+      <c r="G211" s="5">
+        <v>0</v>
+      </c>
+      <c r="H211" s="3">
+        <v>999</v>
+      </c>
+      <c r="I211" s="4">
+        <v>1</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B212" s="15">
+        <v>310011</v>
+      </c>
+      <c r="C212" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="D212" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310011Name.png</v>
+      </c>
+      <c r="E212" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310011Name</v>
+      </c>
+      <c r="F212" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310011Text</v>
+      </c>
+      <c r="G212" s="5">
+        <v>0</v>
+      </c>
+      <c r="H212" s="3">
+        <v>999</v>
+      </c>
+      <c r="I212" s="4">
+        <v>1</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B213" s="15">
+        <v>310012</v>
+      </c>
+      <c r="C213" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="D213" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310012Name.png</v>
+      </c>
+      <c r="E213" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310012Name</v>
+      </c>
+      <c r="F213" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310012Text</v>
+      </c>
+      <c r="G213" s="5">
+        <v>0</v>
+      </c>
+      <c r="H213" s="3">
+        <v>999</v>
+      </c>
+      <c r="I213" s="4">
+        <v>1</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B214" s="15">
+        <v>310013</v>
+      </c>
+      <c r="C214" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="D214" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310013Name.png</v>
+      </c>
+      <c r="E214" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310013Name</v>
+      </c>
+      <c r="F214" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310013Text</v>
+      </c>
+      <c r="G214" s="5">
+        <v>0</v>
+      </c>
+      <c r="H214" s="3">
+        <v>999</v>
+      </c>
+      <c r="I214" s="4">
+        <v>1</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B215" s="15">
+        <v>310014</v>
+      </c>
+      <c r="C215" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="D215" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310014Name.png</v>
+      </c>
+      <c r="E215" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310014Name</v>
+      </c>
+      <c r="F215" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310014Text</v>
+      </c>
+      <c r="G215" s="5">
+        <v>0</v>
+      </c>
+      <c r="H215" s="3">
+        <v>999</v>
+      </c>
+      <c r="I215" s="4">
+        <v>1</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B216" s="15">
+        <v>310015</v>
+      </c>
+      <c r="C216" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="D216" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310015Name.png</v>
+      </c>
+      <c r="E216" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310015Name</v>
+      </c>
+      <c r="F216" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310015Text</v>
+      </c>
+      <c r="G216" s="5">
+        <v>0</v>
+      </c>
+      <c r="H216" s="3">
+        <v>999</v>
+      </c>
+      <c r="I216" s="4">
+        <v>1</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B217" s="15">
+        <v>310016</v>
+      </c>
+      <c r="C217" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D217" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310016Name.png</v>
+      </c>
+      <c r="E217" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310016Name</v>
+      </c>
+      <c r="F217" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310016Text</v>
+      </c>
+      <c r="G217" s="5">
+        <v>0</v>
+      </c>
+      <c r="H217" s="3">
+        <v>999</v>
+      </c>
+      <c r="I217" s="4">
+        <v>1</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B218" s="15">
+        <v>310017</v>
+      </c>
+      <c r="C218" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="D218" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310017Name.png</v>
+      </c>
+      <c r="E218" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310017Name</v>
+      </c>
+      <c r="F218" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310017Text</v>
+      </c>
+      <c r="G218" s="5">
+        <v>0</v>
+      </c>
+      <c r="H218" s="3">
+        <v>999</v>
+      </c>
+      <c r="I218" s="4">
+        <v>1</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B219" s="15">
+        <v>310018</v>
+      </c>
+      <c r="C219" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="D219" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310018Name.png</v>
+      </c>
+      <c r="E219" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310018Name</v>
+      </c>
+      <c r="F219" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310018Text</v>
+      </c>
+      <c r="G219" s="5">
+        <v>0</v>
+      </c>
+      <c r="H219" s="3">
+        <v>999</v>
+      </c>
+      <c r="I219" s="4">
+        <v>1</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B220" s="15">
+        <v>310019</v>
+      </c>
+      <c r="C220" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="D220" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310019Name.png</v>
+      </c>
+      <c r="E220" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310019Name</v>
+      </c>
+      <c r="F220" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310019Text</v>
+      </c>
+      <c r="G220" s="5">
+        <v>0</v>
+      </c>
+      <c r="H220" s="3">
+        <v>999</v>
+      </c>
+      <c r="I220" s="4">
+        <v>1</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B221" s="15">
+        <v>310020</v>
+      </c>
+      <c r="C221" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="D221" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310020Name.png</v>
+      </c>
+      <c r="E221" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310020Name</v>
+      </c>
+      <c r="F221" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310020Text</v>
+      </c>
+      <c r="G221" s="5">
+        <v>0</v>
+      </c>
+      <c r="H221" s="3">
+        <v>999</v>
+      </c>
+      <c r="I221" s="4">
+        <v>1</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B222" s="15">
+        <v>310021</v>
+      </c>
+      <c r="C222" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="D222" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310021Name.png</v>
+      </c>
+      <c r="E222" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310021Name</v>
+      </c>
+      <c r="F222" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310021Text</v>
+      </c>
+      <c r="G222" s="5">
+        <v>0</v>
+      </c>
+      <c r="H222" s="3">
+        <v>999</v>
+      </c>
+      <c r="I222" s="4">
+        <v>1</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="223" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B223" s="15">
+        <v>310022</v>
+      </c>
+      <c r="C223" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D223" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310022Name.png</v>
+      </c>
+      <c r="E223" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310022Name</v>
+      </c>
+      <c r="F223" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310022Text</v>
+      </c>
+      <c r="G223" s="5">
+        <v>0</v>
+      </c>
+      <c r="H223" s="3">
+        <v>999</v>
+      </c>
+      <c r="I223" s="4">
+        <v>1</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="224" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B224" s="15">
+        <v>310023</v>
+      </c>
+      <c r="C224" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="D224" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310023Name.png</v>
+      </c>
+      <c r="E224" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310023Name</v>
+      </c>
+      <c r="F224" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310023Text</v>
+      </c>
+      <c r="G224" s="5">
+        <v>0</v>
+      </c>
+      <c r="H224" s="3">
+        <v>999</v>
+      </c>
+      <c r="I224" s="4">
+        <v>1</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="225" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B225" s="15">
+        <v>310024</v>
+      </c>
+      <c r="C225" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D225" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310024Name.png</v>
+      </c>
+      <c r="E225" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310024Name</v>
+      </c>
+      <c r="F225" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310024Text</v>
+      </c>
+      <c r="G225" s="5">
+        <v>0</v>
+      </c>
+      <c r="H225" s="3">
+        <v>999</v>
+      </c>
+      <c r="I225" s="4">
+        <v>1</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B226" s="15">
+        <v>310025</v>
+      </c>
+      <c r="C226" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D226" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310025Name.png</v>
+      </c>
+      <c r="E226" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310025Name</v>
+      </c>
+      <c r="F226" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310025Text</v>
+      </c>
+      <c r="G226" s="5">
+        <v>0</v>
+      </c>
+      <c r="H226" s="3">
+        <v>999</v>
+      </c>
+      <c r="I226" s="4">
+        <v>1</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="227" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B227" s="15">
+        <v>310026</v>
+      </c>
+      <c r="C227" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D227" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310026Name.png</v>
+      </c>
+      <c r="E227" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310026Name</v>
+      </c>
+      <c r="F227" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310026Text</v>
+      </c>
+      <c r="G227" s="5">
+        <v>0</v>
+      </c>
+      <c r="H227" s="3">
+        <v>999</v>
+      </c>
+      <c r="I227" s="4">
+        <v>1</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B228" s="15">
+        <v>310027</v>
+      </c>
+      <c r="C228" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="D228" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310027Name.png</v>
+      </c>
+      <c r="E228" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310027Name</v>
+      </c>
+      <c r="F228" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310027Text</v>
+      </c>
+      <c r="G228" s="5">
+        <v>0</v>
+      </c>
+      <c r="H228" s="3">
+        <v>999</v>
+      </c>
+      <c r="I228" s="4">
+        <v>1</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B229" s="15">
+        <v>310028</v>
+      </c>
+      <c r="C229" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="D229" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310028Name.png</v>
+      </c>
+      <c r="E229" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310028Name</v>
+      </c>
+      <c r="F229" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310028Text</v>
+      </c>
+      <c r="G229" s="5">
+        <v>0</v>
+      </c>
+      <c r="H229" s="3">
+        <v>999</v>
+      </c>
+      <c r="I229" s="4">
+        <v>1</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B230" s="15">
+        <v>310029</v>
+      </c>
+      <c r="C230" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="D230" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310029Name.png</v>
+      </c>
+      <c r="E230" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310029Name</v>
+      </c>
+      <c r="F230" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310029Text</v>
+      </c>
+      <c r="G230" s="5">
+        <v>0</v>
+      </c>
+      <c r="H230" s="3">
+        <v>999</v>
+      </c>
+      <c r="I230" s="4">
+        <v>1</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="231" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B231" s="15">
+        <v>310030</v>
+      </c>
+      <c r="C231" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="D231" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310030Name.png</v>
+      </c>
+      <c r="E231" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310030Name</v>
+      </c>
+      <c r="F231" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310030Text</v>
+      </c>
+      <c r="G231" s="5">
+        <v>0</v>
+      </c>
+      <c r="H231" s="3">
+        <v>999</v>
+      </c>
+      <c r="I231" s="4">
+        <v>1</v>
+      </c>
+      <c r="J231" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="232" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B232" s="15">
+        <v>310031</v>
+      </c>
+      <c r="C232" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D232" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310031Name.png</v>
+      </c>
+      <c r="E232" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310031Name</v>
+      </c>
+      <c r="F232" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310031Text</v>
+      </c>
+      <c r="G232" s="5">
+        <v>0</v>
+      </c>
+      <c r="H232" s="3">
+        <v>999</v>
+      </c>
+      <c r="I232" s="4">
+        <v>1</v>
+      </c>
+      <c r="J232" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B233" s="15">
+        <v>310032</v>
+      </c>
+      <c r="C233" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="D233" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310032Name.png</v>
+      </c>
+      <c r="E233" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310032Name</v>
+      </c>
+      <c r="F233" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310032Text</v>
+      </c>
+      <c r="G233" s="5">
+        <v>0</v>
+      </c>
+      <c r="H233" s="3">
+        <v>999</v>
+      </c>
+      <c r="I233" s="4">
+        <v>1</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B234" s="15">
+        <v>310033</v>
+      </c>
+      <c r="C234" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="D234" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310033Name.png</v>
+      </c>
+      <c r="E234" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310033Name</v>
+      </c>
+      <c r="F234" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310033Text</v>
+      </c>
+      <c r="G234" s="5">
+        <v>0</v>
+      </c>
+      <c r="H234" s="3">
+        <v>999</v>
+      </c>
+      <c r="I234" s="4">
+        <v>1</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B235" s="15">
+        <v>310034</v>
+      </c>
+      <c r="C235" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D235" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310034Name.png</v>
+      </c>
+      <c r="E235" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310034Name</v>
+      </c>
+      <c r="F235" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310034Text</v>
+      </c>
+      <c r="G235" s="5">
+        <v>0</v>
+      </c>
+      <c r="H235" s="3">
+        <v>999</v>
+      </c>
+      <c r="I235" s="4">
+        <v>1</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B236" s="15">
+        <v>310035</v>
+      </c>
+      <c r="C236" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="D236" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310035Name.png</v>
+      </c>
+      <c r="E236" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310035Name</v>
+      </c>
+      <c r="F236" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310035Text</v>
+      </c>
+      <c r="G236" s="5">
+        <v>0</v>
+      </c>
+      <c r="H236" s="3">
+        <v>999</v>
+      </c>
+      <c r="I236" s="4">
+        <v>1</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="237" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B237" s="15">
+        <v>310036</v>
+      </c>
+      <c r="C237" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="D237" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310036Name.png</v>
+      </c>
+      <c r="E237" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310036Name</v>
+      </c>
+      <c r="F237" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310036Text</v>
+      </c>
+      <c r="G237" s="5">
+        <v>0</v>
+      </c>
+      <c r="H237" s="3">
+        <v>999</v>
+      </c>
+      <c r="I237" s="4">
+        <v>1</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="238" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B238" s="15">
+        <v>310037</v>
+      </c>
+      <c r="C238" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="D238" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310037Name.png</v>
+      </c>
+      <c r="E238" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310037Name</v>
+      </c>
+      <c r="F238" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310037Text</v>
+      </c>
+      <c r="G238" s="5">
+        <v>0</v>
+      </c>
+      <c r="H238" s="3">
+        <v>999</v>
+      </c>
+      <c r="I238" s="4">
+        <v>1</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="239" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B239" s="15">
+        <v>310038</v>
+      </c>
+      <c r="C239" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="D239" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310038Name.png</v>
+      </c>
+      <c r="E239" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310038Name</v>
+      </c>
+      <c r="F239" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310038Text</v>
+      </c>
+      <c r="G239" s="5">
+        <v>0</v>
+      </c>
+      <c r="H239" s="3">
+        <v>999</v>
+      </c>
+      <c r="I239" s="4">
+        <v>1</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="240" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B240" s="15">
+        <v>310039</v>
+      </c>
+      <c r="C240" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="D240" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>310039Name.png</v>
+      </c>
+      <c r="E240" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>InventoryItem+310039Name</v>
+      </c>
+      <c r="F240" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>InventoryItem+310039Text</v>
+      </c>
+      <c r="G240" s="5">
+        <v>0</v>
+      </c>
+      <c r="H240" s="3">
+        <v>999</v>
+      </c>
+      <c r="I240" s="4">
+        <v>1</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7246,19 +9600,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -7272,13 +9626,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -7286,19 +9640,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.3">
@@ -7306,10 +9660,10 @@
         <v>120006</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="6"/>
@@ -7346,16 +9700,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -7369,7 +9723,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -7380,16 +9734,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
@@ -7397,7 +9751,7 @@
         <v>120006</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D4" s="10">
         <v>90</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6B67E7-9E93-4457-9B06-51384FC397BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" activeTab="3"/>
+    <workbookView xWindow="10190" yWindow="1780" windowWidth="30580" windowHeight="18680" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="357">
   <si>
     <t>##var</t>
   </si>
@@ -1084,7 +1090,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Item</t>
     </r>
@@ -1092,7 +1098,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>MaterialType</t>
     </r>
@@ -1114,19 +1120,17 @@
   </si>
   <si>
     <t>Ingredient</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1137,146 +1141,33 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1289,188 +1180,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BC2E6"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE3D5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CAAB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4AF82"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBEBEB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7C7C7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CA"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD964"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4C6E7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8EA9DB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1EFD8"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5DFB3"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8D08C"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1493,253 +1204,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF5B9BD5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF5B9BD5"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF5B9BD5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1747,10 +1216,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1775,61 +1241,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2082,25 +1504,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R240"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="29.0833333333333" style="10" customWidth="1"/>
-    <col min="4" max="4" width="33.5" style="10" customWidth="1"/>
-    <col min="5" max="5" width="58.75" style="10" customWidth="1"/>
-    <col min="6" max="6" width="42.3333333333333" style="10" customWidth="1"/>
-    <col min="7" max="7" width="21.1666666666667" customWidth="1"/>
-    <col min="9" max="9" width="16.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="33.5" style="9" customWidth="1"/>
+    <col min="5" max="5" width="58.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" customWidth="1"/>
     <col min="10" max="10" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2132,7 +1554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2164,7 +1586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -2196,7 +1618,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>100000</v>
@@ -2229,7 +1651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>100001</v>
@@ -2262,7 +1684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>100002</v>
@@ -2295,7 +1717,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>100003</v>
@@ -2328,7 +1750,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>100004</v>
@@ -2361,7 +1783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>100005</v>
@@ -2394,7 +1816,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>100006</v>
@@ -2427,7 +1849,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>100007</v>
@@ -2460,7 +1882,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>100008</v>
@@ -2493,7 +1915,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>100009</v>
@@ -2526,7 +1948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>100010</v>
@@ -2559,7 +1981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>100011</v>
@@ -2592,7 +2014,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>100012</v>
@@ -2625,7 +2047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:18">
+    <row r="17" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>100013</v>
@@ -2658,7 +2080,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:18">
+    <row r="18" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>100014</v>
@@ -2691,7 +2113,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:18">
+    <row r="19" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>100015</v>
@@ -2724,7 +2146,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:18">
+    <row r="20" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>100016</v>
@@ -2757,7 +2179,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:18">
+    <row r="21" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>100017</v>
@@ -2790,7 +2212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:18">
+    <row r="22" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>100018</v>
@@ -2823,7 +2245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:18">
+    <row r="23" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>100019</v>
@@ -2855,12 +2277,12 @@
       <c r="J23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:18">
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+    </row>
+    <row r="24" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>100020</v>
@@ -2893,7 +2315,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:18">
+    <row r="25" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>100021</v>
@@ -2926,7 +2348,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:18">
+    <row r="26" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>100022</v>
@@ -2959,7 +2381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:18">
+    <row r="27" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>100023</v>
@@ -2992,7 +2414,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:18">
+    <row r="28" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>100024</v>
@@ -3025,7 +2447,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:18">
+    <row r="29" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>100025</v>
@@ -3058,7 +2480,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:18">
+    <row r="30" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>100026</v>
@@ -3091,7 +2513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:18">
+    <row r="31" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>100027</v>
@@ -3124,7 +2546,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:18">
+    <row r="32" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>100028</v>
@@ -3157,7 +2579,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:10">
+    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>100029</v>
@@ -3190,7 +2612,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:10">
+    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>100030</v>
@@ -3223,7 +2645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:10">
+    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>100031</v>
@@ -3256,7 +2678,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:10">
+    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>100032</v>
@@ -3289,7 +2711,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="1:10">
+    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>100033</v>
@@ -3322,7 +2744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" ht="16.5" spans="1:10">
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>100034</v>
@@ -3355,7 +2777,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:10">
+    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>100035</v>
@@ -3388,7 +2810,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" ht="16.5" spans="1:10">
+    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>100036</v>
@@ -3421,7 +2843,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" ht="16.5" spans="1:10">
+    <row r="41" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>100037</v>
@@ -3454,7 +2876,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" ht="16.5" spans="1:10">
+    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>100038</v>
@@ -3487,7 +2909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" ht="16.5" spans="1:10">
+    <row r="43" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>100039</v>
@@ -3520,7 +2942,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:10">
+    <row r="44" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>100040</v>
@@ -3553,7 +2975,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:10">
+    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>100041</v>
@@ -3586,7 +3008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:10">
+    <row r="46" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>100042</v>
@@ -3619,7 +3041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:10">
+    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>100043</v>
@@ -3652,7 +3074,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:10">
+    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>100044</v>
@@ -3685,7 +3107,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:10">
+    <row r="49" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>100045</v>
@@ -3718,7 +3140,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:10">
+    <row r="50" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>100046</v>
@@ -3751,7 +3173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:10">
+    <row r="51" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>100047</v>
@@ -3784,7 +3206,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:10">
+    <row r="52" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>100048</v>
@@ -3817,7 +3239,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:10">
+    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>100049</v>
@@ -3850,7 +3272,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:10">
+    <row r="54" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>100051</v>
@@ -3883,7 +3305,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:10">
+    <row r="55" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>100052</v>
@@ -3916,7 +3338,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:10">
+    <row r="56" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>100053</v>
@@ -3949,7 +3371,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:10">
+    <row r="57" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>100054</v>
@@ -3982,7 +3404,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:10">
+    <row r="58" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>100055</v>
@@ -4015,7 +3437,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:10">
+    <row r="59" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>110000</v>
@@ -4048,7 +3470,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:10">
+    <row r="60" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>110001</v>
@@ -4081,7 +3503,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:10">
+    <row r="61" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>110002</v>
@@ -4114,7 +3536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:10">
+    <row r="62" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>110003</v>
@@ -4147,7 +3569,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:10">
+    <row r="63" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>110004</v>
@@ -4180,7 +3602,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:10">
+    <row r="64" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>110005</v>
@@ -4213,7 +3635,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:10">
+    <row r="65" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>110006</v>
@@ -4246,7 +3668,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:10">
+    <row r="66" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>110007</v>
@@ -4279,7 +3701,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:10">
+    <row r="67" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>110008</v>
@@ -4312,7 +3734,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" ht="16.5" spans="1:10">
+    <row r="68" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>110009</v>
@@ -4345,7 +3767,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:10">
+    <row r="69" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>110010</v>
@@ -4378,7 +3800,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" ht="16.5" spans="1:10">
+    <row r="70" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>110011</v>
@@ -4411,7 +3833,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" ht="16.5" spans="1:10">
+    <row r="71" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>110012</v>
@@ -4444,7 +3866,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" ht="16.5" spans="1:10">
+    <row r="72" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>110013</v>
@@ -4477,7 +3899,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" ht="16.5" spans="1:10">
+    <row r="73" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>110014</v>
@@ -4510,7 +3932,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" ht="16.5" spans="1:10">
+    <row r="74" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>110015</v>
@@ -4543,7 +3965,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:10">
+    <row r="75" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>110016</v>
@@ -4576,7 +3998,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" ht="16.5" spans="1:10">
+    <row r="76" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>110017</v>
@@ -4609,7 +4031,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" ht="16.5" spans="1:10">
+    <row r="77" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>110018</v>
@@ -4642,7 +4064,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:10">
+    <row r="78" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>110019</v>
@@ -4675,7 +4097,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:10">
+    <row r="79" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>110020</v>
@@ -4708,7 +4130,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:10">
+    <row r="80" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>110021</v>
@@ -4741,7 +4163,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" ht="16.5" spans="1:10">
+    <row r="81" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>110022</v>
@@ -4774,7 +4196,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" ht="16.5" spans="1:10">
+    <row r="82" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>110023</v>
@@ -4807,7 +4229,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" ht="16.5" spans="1:10">
+    <row r="83" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>110024</v>
@@ -4840,7 +4262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" ht="16.5" spans="1:10">
+    <row r="84" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>110025</v>
@@ -4873,7 +4295,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" ht="16.5" spans="1:10">
+    <row r="85" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>110026</v>
@@ -4906,7 +4328,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="86" ht="16.5" spans="1:10">
+    <row r="86" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>110027</v>
@@ -4939,7 +4361,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="87" ht="16.5" spans="1:10">
+    <row r="87" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>110028</v>
@@ -4972,7 +4394,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" ht="16.5" spans="1:10">
+    <row r="88" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>110029</v>
@@ -5005,7 +4427,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" ht="16.5" spans="1:10">
+    <row r="89" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>110030</v>
@@ -5038,7 +4460,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="90" ht="16.5" spans="1:10">
+    <row r="90" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>110031</v>
@@ -5071,7 +4493,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" ht="16.5" spans="1:10">
+    <row r="91" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>110032</v>
@@ -5104,7 +4526,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="92" ht="16.5" spans="1:10">
+    <row r="92" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>110033</v>
@@ -5137,7 +4559,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" ht="16.5" spans="1:10">
+    <row r="93" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>110034</v>
@@ -5170,7 +4592,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="94" ht="16.5" spans="1:10">
+    <row r="94" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>110035</v>
@@ -5203,7 +4625,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="95" ht="16.5" spans="1:10">
+    <row r="95" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>110036</v>
@@ -5236,7 +4658,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="96" ht="16.5" spans="1:10">
+    <row r="96" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>110037</v>
@@ -5269,7 +4691,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="97" ht="16.5" spans="1:10">
+    <row r="97" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>110038</v>
@@ -5302,7 +4724,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="98" ht="16.5" spans="1:10">
+    <row r="98" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>110039</v>
@@ -5335,7 +4757,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="99" ht="16.5" spans="1:10">
+    <row r="99" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>120000</v>
@@ -5368,7 +4790,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" ht="16.5" spans="1:10">
+    <row r="100" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>120001</v>
@@ -5401,7 +4823,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="101" ht="16.5" spans="1:10">
+    <row r="101" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>120002</v>
@@ -5434,7 +4856,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="102" ht="16.5" spans="1:10">
+    <row r="102" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>120003</v>
@@ -5467,7 +4889,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:10">
+    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>120004</v>
@@ -5500,7 +4922,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:10">
+    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>120005</v>
@@ -5533,7 +4955,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:10">
+    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>120006</v>
@@ -5566,7 +4988,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:10">
+    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>120007</v>
@@ -5599,7 +5021,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:10">
+    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>120008</v>
@@ -5632,7 +5054,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:10">
+    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
         <v>120009</v>
@@ -5665,7 +5087,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:10">
+    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
         <v>120010</v>
@@ -5698,7 +5120,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="110" ht="16.5" spans="1:10">
+    <row r="110" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
         <v>120011</v>
@@ -5731,7 +5153,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="111" ht="16.5" spans="1:10">
+    <row r="111" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
         <v>120012</v>
@@ -5764,7 +5186,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="112" ht="16.5" spans="1:10">
+    <row r="112" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
         <v>120013</v>
@@ -5797,7 +5219,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="113" ht="16.5" spans="1:10">
+    <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
         <v>120014</v>
@@ -5830,7 +5252,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="114" ht="16.5" spans="1:10">
+    <row r="114" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
         <v>120015</v>
@@ -5863,7 +5285,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" ht="16.5" spans="1:10">
+    <row r="115" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
         <v>120016</v>
@@ -5896,7 +5318,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="116" ht="16.5" spans="1:10">
+    <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
         <v>120017</v>
@@ -5929,7 +5351,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="117" ht="16.5" spans="1:10">
+    <row r="117" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
         <v>120018</v>
@@ -5962,7 +5384,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="118" ht="16.5" spans="1:10">
+    <row r="118" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
         <v>120019</v>
@@ -5995,7 +5417,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="119" ht="16.5" spans="1:10">
+    <row r="119" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
         <v>120020</v>
@@ -6028,7 +5450,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="120" ht="16.5" spans="1:10">
+    <row r="120" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
         <v>120021</v>
@@ -6061,7 +5483,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="121" ht="16.5" spans="1:10">
+    <row r="121" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
         <v>120022</v>
@@ -6094,7 +5516,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="122" ht="16.5" spans="1:10">
+    <row r="122" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
         <v>120023</v>
@@ -6127,7 +5549,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="123" ht="16.5" spans="1:10">
+    <row r="123" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
         <v>120024</v>
@@ -6160,7 +5582,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="124" ht="16.5" spans="1:10">
+    <row r="124" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
         <v>120025</v>
@@ -6193,7 +5615,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="125" ht="16.5" spans="1:10">
+    <row r="125" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
         <v>120026</v>
@@ -6226,7 +5648,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="126" ht="16.5" spans="1:10">
+    <row r="126" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
         <v>120027</v>
@@ -6259,7 +5681,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="127" ht="16.5" spans="1:10">
+    <row r="127" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
         <v>120028</v>
@@ -6292,7 +5714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="128" ht="16.5" spans="1:10">
+    <row r="128" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
         <v>120029</v>
@@ -6325,7 +5747,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="129" ht="16.5" spans="1:10">
+    <row r="129" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
         <v>120030</v>
@@ -6358,7 +5780,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="130" ht="16.5" spans="1:10">
+    <row r="130" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
         <v>120031</v>
@@ -6391,7 +5813,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" ht="16.5" spans="1:10">
+    <row r="131" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
         <v>120032</v>
@@ -6424,7 +5846,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="132" ht="16.5" spans="1:10">
+    <row r="132" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
         <v>120033</v>
@@ -6457,7 +5879,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="133" ht="16.5" spans="1:10">
+    <row r="133" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
         <v>120034</v>
@@ -6490,7 +5912,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="134" ht="16.5" spans="1:10">
+    <row r="134" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
         <v>120035</v>
@@ -6523,7 +5945,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="135" ht="16.5" spans="1:10">
+    <row r="135" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
         <v>120036</v>
@@ -6556,7 +5978,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="136" ht="16.5" spans="1:10">
+    <row r="136" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
         <v>120037</v>
@@ -6589,7 +6011,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" ht="16.5" spans="1:10">
+    <row r="137" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
         <v>120038</v>
@@ -6622,7 +6044,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="138" ht="16.5" spans="1:10">
+    <row r="138" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
         <v>120039</v>
@@ -6655,7 +6077,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" ht="16.5" spans="1:10">
+    <row r="139" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
         <v>120040</v>
@@ -6688,7 +6110,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" ht="16.5" spans="1:10">
+    <row r="140" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
         <v>200000</v>
@@ -6721,7 +6143,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="141" ht="16.5" spans="1:10">
+    <row r="141" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
         <v>200001</v>
@@ -6754,7 +6176,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="142" ht="16.5" spans="1:10">
+    <row r="142" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
         <v>200002</v>
@@ -6787,7 +6209,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" ht="16.5" spans="1:10">
+    <row r="143" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
         <v>200003</v>
@@ -6820,7 +6242,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" ht="16.5" spans="1:10">
+    <row r="144" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
         <v>210000</v>
@@ -6853,7 +6275,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" ht="16.5" spans="1:10">
+    <row r="145" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
         <v>210001</v>
@@ -6886,7 +6308,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="146" ht="16.5" spans="1:10">
+    <row r="146" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
         <v>210002</v>
@@ -6919,7 +6341,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="147" ht="16.5" spans="1:10">
+    <row r="147" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
         <v>210003</v>
@@ -6952,7 +6374,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="148" ht="16.5" spans="1:10">
+    <row r="148" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
         <v>210004</v>
@@ -6985,7 +6407,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="149" ht="16.5" spans="1:10">
+    <row r="149" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
         <v>210005</v>
@@ -7018,7 +6440,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" ht="16.5" spans="1:10">
+    <row r="150" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
         <v>210006</v>
@@ -7051,7 +6473,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="151" ht="16.5" spans="1:10">
+    <row r="151" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
         <v>210007</v>
@@ -7084,7 +6506,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="152" ht="16.5" spans="1:10">
+    <row r="152" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
         <v>210008</v>
@@ -7117,7 +6539,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="153" ht="16.5" spans="1:10">
+    <row r="153" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
         <v>210009</v>
@@ -7150,7 +6572,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" ht="16.5" spans="1:10">
+    <row r="154" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
         <v>210010</v>
@@ -7183,7 +6605,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" ht="16.5" spans="1:10">
+    <row r="155" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
         <v>210011</v>
@@ -7216,7 +6638,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" ht="16.5" spans="1:10">
+    <row r="156" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
         <v>210012</v>
@@ -7249,7 +6671,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="157" ht="16.5" spans="1:10">
+    <row r="157" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
         <v>210013</v>
@@ -7282,7 +6704,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="158" ht="16.5" spans="1:10">
+    <row r="158" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
         <v>210014</v>
@@ -7315,7 +6737,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="159" ht="16.5" spans="1:10">
+    <row r="159" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
         <v>210015</v>
@@ -7348,7 +6770,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="160" ht="16.5" spans="1:10">
+    <row r="160" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
         <v>210016</v>
@@ -7381,7 +6803,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" ht="16.5" spans="1:10">
+    <row r="161" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
         <v>210017</v>
@@ -7414,7 +6836,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" ht="16.5" spans="1:10">
+    <row r="162" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
         <v>210018</v>
@@ -7447,7 +6869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" ht="16.5" spans="1:10">
+    <row r="163" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
         <v>210019</v>
@@ -7480,7 +6902,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" ht="16.5" spans="1:10">
+    <row r="164" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
         <v>220000</v>
@@ -7513,7 +6935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" ht="16.5" spans="1:10">
+    <row r="165" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
         <v>220001</v>
@@ -7546,7 +6968,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166" ht="16.5" spans="1:10">
+    <row r="166" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
         <v>220002</v>
@@ -7579,7 +7001,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="167" ht="16.5" spans="1:10">
+    <row r="167" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
         <v>220003</v>
@@ -7612,7 +7034,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="168" ht="16.5" spans="1:10">
+    <row r="168" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
         <v>220004</v>
@@ -7645,7 +7067,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="169" ht="16.5" spans="1:10">
+    <row r="169" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
         <v>220005</v>
@@ -7678,7 +7100,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" ht="16.5" spans="1:10">
+    <row r="170" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
         <v>220006</v>
@@ -7711,7 +7133,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="171" ht="16.5" spans="1:10">
+    <row r="171" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
         <v>220007</v>
@@ -7744,7 +7166,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="172" ht="16.5" spans="1:10">
+    <row r="172" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
         <v>220008</v>
@@ -7777,7 +7199,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="173" ht="16.5" spans="1:10">
+    <row r="173" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
         <v>220009</v>
@@ -7810,7 +7232,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="174" ht="16.5" spans="1:10">
+    <row r="174" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
         <v>300000</v>
@@ -7843,7 +7265,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175" ht="16.5" spans="1:10">
+    <row r="175" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
         <v>300001</v>
@@ -7876,7 +7298,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" ht="16.5" spans="1:10">
+    <row r="176" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
         <v>300002</v>
@@ -7909,7 +7331,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="177" ht="16.5" spans="1:10">
+    <row r="177" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
         <v>300003</v>
@@ -7942,7 +7364,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="178" ht="16.5" spans="1:10">
+    <row r="178" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
         <v>300004</v>
@@ -7975,7 +7397,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="179" ht="16.5" spans="1:10">
+    <row r="179" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
         <v>300005</v>
@@ -8008,7 +7430,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="180" ht="16.5" spans="1:10">
+    <row r="180" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
         <v>300006</v>
@@ -8041,7 +7463,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="181" ht="16.5" spans="1:10">
+    <row r="181" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
         <v>300007</v>
@@ -8074,7 +7496,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="182" ht="16.5" spans="1:10">
+    <row r="182" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
         <v>300008</v>
@@ -8107,7 +7529,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="183" ht="16.5" spans="1:10">
+    <row r="183" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
         <v>300009</v>
@@ -8140,7 +7562,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="184" ht="16.5" spans="1:10">
+    <row r="184" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
         <v>130000</v>
@@ -8173,7 +7595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="185" ht="16.5" spans="1:10">
+    <row r="185" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
         <v>130001</v>
@@ -8206,7 +7628,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="186" ht="16.5" spans="1:10">
+    <row r="186" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
         <v>130002</v>
@@ -8239,7 +7661,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="187" ht="16.5" spans="1:10">
+    <row r="187" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
         <v>140000</v>
@@ -8272,7 +7694,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" ht="16.5" spans="1:10">
+    <row r="188" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
         <v>140001</v>
@@ -8305,7 +7727,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="189" ht="16.5" spans="1:10">
+    <row r="189" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
         <v>140002</v>
@@ -8338,7 +7760,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="190" ht="16.5" spans="1:10">
+    <row r="190" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
         <v>140003</v>
@@ -8371,7 +7793,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="191" ht="16.5" spans="1:10">
+    <row r="191" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
         <v>150000</v>
@@ -8404,7 +7826,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="192" ht="16.5" spans="1:10">
+    <row r="192" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
         <v>150001</v>
@@ -8437,7 +7859,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="193" ht="16.5" spans="1:10">
+    <row r="193" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
         <v>150002</v>
@@ -8470,7 +7892,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="194" ht="16.5" spans="1:10">
+    <row r="194" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
         <v>150003</v>
@@ -8503,7 +7925,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="195" ht="16.5" spans="1:10">
+    <row r="195" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
         <v>150004</v>
@@ -8536,7 +7958,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="196" ht="16.5" spans="1:10">
+    <row r="196" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
         <v>150005</v>
@@ -8569,7 +7991,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="197" ht="16.5" spans="1:10">
+    <row r="197" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
         <v>150006</v>
@@ -8602,7 +8024,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="198" ht="16.5" spans="1:10">
+    <row r="198" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
         <v>150007</v>
@@ -8635,7 +8057,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="199" ht="16.5" spans="1:10">
+    <row r="199" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
         <v>150008</v>
@@ -8668,7 +8090,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="200" ht="16.5" spans="1:10">
+    <row r="200" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
         <v>150009</v>
@@ -8701,7 +8123,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" ht="16.5" spans="1:10">
+    <row r="201" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
         <v>310000</v>
@@ -8734,7 +8156,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="202" ht="16.5" spans="1:10">
+    <row r="202" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
         <v>310001</v>
@@ -8767,7 +8189,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="203" ht="16.5" spans="1:10">
+    <row r="203" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
         <v>310002</v>
@@ -8800,7 +8222,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="204" ht="16.5" spans="1:10">
+    <row r="204" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
         <v>310003</v>
@@ -8833,7 +8255,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="205" ht="16.5" spans="1:10">
+    <row r="205" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
         <v>310004</v>
@@ -8866,7 +8288,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="206" ht="16.5" spans="1:10">
+    <row r="206" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
         <v>310005</v>
@@ -8899,7 +8321,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" ht="16.5" spans="1:10">
+    <row r="207" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
         <v>310006</v>
@@ -8932,7 +8354,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="208" ht="16.5" spans="1:10">
+    <row r="208" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
         <v>310007</v>
@@ -8965,7 +8387,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="209" ht="16.5" spans="1:10">
+    <row r="209" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
         <v>310008</v>
@@ -8998,7 +8420,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="210" ht="16.5" spans="1:10">
+    <row r="210" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
         <v>310009</v>
@@ -9031,7 +8453,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="211" ht="16.5" spans="1:10">
+    <row r="211" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
         <v>310010</v>
@@ -9064,7 +8486,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="212" ht="16.5" spans="1:10">
+    <row r="212" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
         <v>310011</v>
@@ -9097,7 +8519,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="213" ht="16.5" spans="1:10">
+    <row r="213" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
         <v>310012</v>
@@ -9130,7 +8552,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="214" ht="16.5" spans="1:10">
+    <row r="214" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
         <v>310013</v>
@@ -9163,7 +8585,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="215" ht="16.5" spans="1:10">
+    <row r="215" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
         <v>310014</v>
@@ -9196,7 +8618,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" ht="16.5" spans="1:10">
+    <row r="216" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
         <v>310015</v>
@@ -9229,7 +8651,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="217" ht="16.5" spans="1:10">
+    <row r="217" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
         <v>310016</v>
@@ -9262,7 +8684,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="218" ht="16.5" spans="1:10">
+    <row r="218" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
         <v>310017</v>
@@ -9295,7 +8717,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="219" ht="16.5" spans="1:10">
+    <row r="219" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
         <v>310018</v>
@@ -9328,7 +8750,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="220" ht="16.5" spans="1:10">
+    <row r="220" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
         <v>310019</v>
@@ -9361,7 +8783,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="221" ht="16.5" spans="1:10">
+    <row r="221" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
         <v>310020</v>
@@ -9394,7 +8816,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="222" ht="16.5" spans="1:10">
+    <row r="222" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
         <v>310021</v>
@@ -9427,7 +8849,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="223" ht="16.5" spans="1:10">
+    <row r="223" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
         <v>310022</v>
@@ -9460,7 +8882,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="224" ht="16.5" spans="1:10">
+    <row r="224" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
         <v>310023</v>
@@ -9493,7 +8915,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="225" ht="16.5" spans="1:10">
+    <row r="225" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
         <v>310024</v>
@@ -9526,7 +8948,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="226" ht="16.5" spans="1:10">
+    <row r="226" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
         <v>310025</v>
@@ -9559,7 +8981,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="227" ht="16.5" spans="1:10">
+    <row r="227" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
         <v>310026</v>
@@ -9592,7 +9014,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="228" ht="16.5" spans="1:10">
+    <row r="228" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
         <v>310027</v>
@@ -9625,7 +9047,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="229" ht="16.5" spans="1:10">
+    <row r="229" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
         <v>310028</v>
@@ -9658,7 +9080,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="230" ht="16.5" spans="1:10">
+    <row r="230" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
         <v>310029</v>
@@ -9691,7 +9113,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="231" ht="16.5" spans="1:10">
+    <row r="231" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
         <v>310030</v>
@@ -9724,7 +9146,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" ht="16.5" spans="1:10">
+    <row r="232" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
         <v>310031</v>
@@ -9757,7 +9179,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" ht="16.5" spans="1:10">
+    <row r="233" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
         <v>310032</v>
@@ -9790,7 +9212,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="234" ht="16.5" spans="1:10">
+    <row r="234" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
         <v>310033</v>
@@ -9823,7 +9245,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" ht="16.5" spans="1:10">
+    <row r="235" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
         <v>310034</v>
@@ -9856,7 +9278,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" ht="16.5" spans="1:10">
+    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
         <v>310035</v>
@@ -9889,7 +9311,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" ht="16.5" spans="1:10">
+    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
         <v>310036</v>
@@ -9922,7 +9344,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" ht="16.5" spans="1:10">
+    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
         <v>310037</v>
@@ -9955,7 +9377,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="239" ht="16.5" spans="1:10">
+    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
         <v>310038</v>
@@ -9988,7 +9410,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="240" ht="16.5" spans="1:10">
+    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
         <v>310039</v>
@@ -10022,30 +9444,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="12.5833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.0833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.1666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.0833333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.5833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.08203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.08203125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10064,11 +9485,11 @@
       <c r="F1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -10091,7 +9512,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -10114,928 +9535,927 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="B4" s="6">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="B4" s="5">
         <v>120000</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B5" s="2">
         <v>120001</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B6" s="2">
         <v>120002</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B7" s="2">
         <v>120003</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B8" s="2">
         <v>120004</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B9" s="2">
         <v>120005</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>120006</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B11" s="2">
         <v>120007</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B12" s="2">
         <v>120008</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>120009</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <v>120010</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>120011</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>120012</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <v>120013</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>120014</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="2:8">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <v>120015</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="2:8">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <v>120016</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="2:8">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="2">
         <v>120017</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="2:8">
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="2">
         <v>120018</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="2:8">
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="2">
         <v>120019</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="2">
         <v>120020</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="2">
         <v>120021</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="2">
         <v>120022</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="2:8">
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <v>120023</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="2:8">
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B28" s="2">
         <v>120024</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="2:8">
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2">
         <v>120025</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="2:8">
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B30" s="2">
         <v>120026</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B31" s="2">
         <v>120027</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="2:8">
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B32" s="2">
         <v>120028</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="2:8">
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B33" s="2">
         <v>120029</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" s="2">
         <v>120030</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="2">
         <v>120031</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="2">
         <v>120032</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="2:8">
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B37" s="2">
         <v>120033</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="2:8">
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B38" s="2">
         <v>120034</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="2:8">
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B39" s="2">
         <v>120035</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="2:8">
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B40" s="2">
         <v>120036</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="2:8">
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B41" s="2">
         <v>120037</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B42" s="2">
         <v>120038</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="2:8">
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B43" s="2">
         <v>120039</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="2:8">
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B44" s="2">
         <v>120040</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="2:8">
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B45"/>
       <c r="C45"/>
       <c r="G45"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B46"/>
       <c r="C46"/>
       <c r="G46"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B47"/>
       <c r="C47"/>
       <c r="G47"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B48"/>
       <c r="C48"/>
       <c r="G48"/>
     </row>
-    <row r="49" spans="2:7">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B49"/>
       <c r="C49"/>
       <c r="G49"/>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B50"/>
       <c r="C50"/>
       <c r="G50"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B51"/>
       <c r="C51"/>
       <c r="G51"/>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B52"/>
       <c r="C52"/>
       <c r="G52"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B53"/>
       <c r="C53"/>
       <c r="G53"/>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B54"/>
       <c r="C54"/>
       <c r="G54"/>
     </row>
-    <row r="55" spans="2:7">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B55"/>
       <c r="C55"/>
       <c r="G55"/>
     </row>
-    <row r="56" spans="2:7">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B56"/>
       <c r="C56"/>
       <c r="G56"/>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B57"/>
       <c r="C57"/>
       <c r="G57"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B58"/>
       <c r="C58"/>
       <c r="G58"/>
     </row>
-    <row r="59" spans="2:7">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B59"/>
       <c r="C59"/>
       <c r="G59"/>
     </row>
-    <row r="60" spans="2:7">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B60"/>
       <c r="C60"/>
       <c r="G60"/>
     </row>
-    <row r="61" spans="2:7">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B61"/>
       <c r="C61"/>
       <c r="G61"/>
     </row>
-    <row r="62" spans="2:7">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B62"/>
       <c r="C62"/>
       <c r="G62"/>
     </row>
-    <row r="63" spans="2:7">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B63"/>
       <c r="C63"/>
       <c r="G63"/>
     </row>
-    <row r="64" spans="2:7">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B64"/>
       <c r="C64"/>
       <c r="G64"/>
     </row>
-    <row r="65" spans="2:7">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B65"/>
       <c r="C65"/>
       <c r="G65"/>
     </row>
-    <row r="66" spans="2:7">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B66"/>
       <c r="C66"/>
       <c r="G66"/>
     </row>
-    <row r="67" spans="2:7">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B67"/>
       <c r="C67"/>
       <c r="G67"/>
     </row>
-    <row r="68" spans="2:7">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B68"/>
       <c r="C68"/>
       <c r="G68"/>
     </row>
-    <row r="69" spans="2:7">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B69"/>
       <c r="C69"/>
       <c r="G69"/>
     </row>
-    <row r="70" spans="2:7">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B70"/>
       <c r="C70"/>
       <c r="G70"/>
     </row>
-    <row r="71" spans="2:7">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B71"/>
       <c r="C71"/>
       <c r="G71"/>
     </row>
-    <row r="72" spans="2:7">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B72"/>
       <c r="C72"/>
       <c r="G72"/>
     </row>
-    <row r="73" spans="2:7">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B73"/>
       <c r="C73"/>
       <c r="G73"/>
     </row>
-    <row r="74" spans="2:7">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B74"/>
       <c r="C74"/>
       <c r="G74"/>
     </row>
-    <row r="75" spans="2:7">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B75"/>
       <c r="C75"/>
       <c r="G75"/>
     </row>
-    <row r="76" spans="2:7">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B76"/>
       <c r="C76"/>
       <c r="G76"/>
     </row>
-    <row r="77" spans="2:7">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B77"/>
       <c r="C77"/>
       <c r="G77"/>
     </row>
-    <row r="78" spans="2:7">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B78"/>
       <c r="C78"/>
       <c r="G78"/>
     </row>
-    <row r="79" spans="2:7">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B79"/>
       <c r="C79"/>
       <c r="G79"/>
     </row>
-    <row r="80" spans="2:7">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B80"/>
       <c r="C80"/>
       <c r="G80"/>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B81"/>
       <c r="C81"/>
       <c r="G81"/>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B82"/>
       <c r="C82"/>
       <c r="G82"/>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B83"/>
       <c r="C83"/>
       <c r="G83"/>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B84"/>
       <c r="C84"/>
       <c r="G84"/>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B85"/>
       <c r="C85"/>
       <c r="G85"/>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B86"/>
       <c r="C86"/>
       <c r="G86"/>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B87"/>
       <c r="C87"/>
       <c r="G87"/>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B88"/>
       <c r="C88"/>
       <c r="G88"/>
     </row>
-    <row r="89" spans="2:7">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B89"/>
       <c r="C89"/>
       <c r="G89"/>
     </row>
-    <row r="90" spans="2:7">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B90"/>
       <c r="C90"/>
       <c r="G90"/>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B91"/>
       <c r="C91"/>
       <c r="G91"/>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B92"/>
       <c r="C92"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="2:7">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B93"/>
       <c r="C93"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B94"/>
       <c r="C94"/>
       <c r="G94"/>
     </row>
-    <row r="95" spans="2:7">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B95"/>
       <c r="C95"/>
       <c r="G95"/>
     </row>
-    <row r="96" spans="2:7">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B96"/>
       <c r="C96"/>
       <c r="G96"/>
     </row>
-    <row r="97" spans="2:7">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B97"/>
       <c r="C97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="2:7">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B98"/>
       <c r="C98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="2:7">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B99"/>
       <c r="C99"/>
       <c r="G99"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="29.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.9166666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.9140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11052,7 +10472,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -11069,7 +10489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -11086,7 +10506,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2">
         <v>110000</v>
       </c>
@@ -11100,7 +10520,7 @@
         <v>120001</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B5" s="2">
         <v>110001</v>
       </c>
@@ -11114,7 +10534,7 @@
         <v>120002</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2">
         <v>110002</v>
       </c>
@@ -11128,7 +10548,7 @@
         <v>120003</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B7" s="2">
         <v>110003</v>
       </c>
@@ -11142,7 +10562,7 @@
         <v>120004</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B8" s="2">
         <v>110004</v>
       </c>
@@ -11156,7 +10576,7 @@
         <v>120005</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B9" s="2">
         <v>110005</v>
       </c>
@@ -11170,7 +10590,7 @@
         <v>120006</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>110006</v>
       </c>
@@ -11184,7 +10604,7 @@
         <v>120007</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B11" s="2">
         <v>110007</v>
       </c>
@@ -11198,7 +10618,7 @@
         <v>120008</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B12" s="2">
         <v>110008</v>
       </c>
@@ -11212,7 +10632,7 @@
         <v>120009</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>110009</v>
       </c>
@@ -11226,7 +10646,7 @@
         <v>120010</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <v>110010</v>
       </c>
@@ -11240,7 +10660,7 @@
         <v>120011</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>110011</v>
       </c>
@@ -11254,7 +10674,7 @@
         <v>120012</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>110012</v>
       </c>
@@ -11268,7 +10688,7 @@
         <v>120013</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <v>110013</v>
       </c>
@@ -11282,7 +10702,7 @@
         <v>120014</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>110014</v>
       </c>
@@ -11296,7 +10716,7 @@
         <v>120015</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <v>110015</v>
       </c>
@@ -11310,7 +10730,7 @@
         <v>120016</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <v>110016</v>
       </c>
@@ -11324,7 +10744,7 @@
         <v>120017</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="2">
         <v>110017</v>
       </c>
@@ -11338,7 +10758,7 @@
         <v>120018</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="2">
         <v>110018</v>
       </c>
@@ -11352,7 +10772,7 @@
         <v>120019</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="2">
         <v>110019</v>
       </c>
@@ -11366,7 +10786,7 @@
         <v>120020</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="2">
         <v>110020</v>
       </c>
@@ -11380,7 +10800,7 @@
         <v>120021</v>
       </c>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="2">
         <v>110021</v>
       </c>
@@ -11394,7 +10814,7 @@
         <v>120022</v>
       </c>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="2">
         <v>110022</v>
       </c>
@@ -11408,7 +10828,7 @@
         <v>120023</v>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <v>110023</v>
       </c>
@@ -11422,7 +10842,7 @@
         <v>120024</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="2">
         <v>110024</v>
       </c>
@@ -11436,7 +10856,7 @@
         <v>120025</v>
       </c>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="2">
         <v>110025</v>
       </c>
@@ -11450,7 +10870,7 @@
         <v>120026</v>
       </c>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="2">
         <v>110026</v>
       </c>
@@ -11464,7 +10884,7 @@
         <v>120027</v>
       </c>
     </row>
-    <row r="31" spans="2:5">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="2">
         <v>110027</v>
       </c>
@@ -11478,7 +10898,7 @@
         <v>120028</v>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="2">
         <v>110028</v>
       </c>
@@ -11492,7 +10912,7 @@
         <v>120029</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="2">
         <v>110029</v>
       </c>
@@ -11506,7 +10926,7 @@
         <v>120030</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B34" s="2">
         <v>110030</v>
       </c>
@@ -11520,7 +10940,7 @@
         <v>120031</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B35" s="2">
         <v>110031</v>
       </c>
@@ -11534,7 +10954,7 @@
         <v>120032</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B36" s="2">
         <v>110032</v>
       </c>
@@ -11548,7 +10968,7 @@
         <v>120033</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B37" s="2">
         <v>110033</v>
       </c>
@@ -11562,7 +10982,7 @@
         <v>120034</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B38" s="2">
         <v>110034</v>
       </c>
@@ -11576,7 +10996,7 @@
         <v>120035</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B39" s="2">
         <v>110035</v>
       </c>
@@ -11590,7 +11010,7 @@
         <v>120036</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B40" s="2">
         <v>110036</v>
       </c>
@@ -11604,7 +11024,7 @@
         <v>120037</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B41" s="2">
         <v>110037</v>
       </c>
@@ -11618,7 +11038,7 @@
         <v>120038</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B42" s="2">
         <v>110038</v>
       </c>
@@ -11632,7 +11052,7 @@
         <v>120039</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B43" s="2">
         <v>110039</v>
       </c>
@@ -11647,26 +11067,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L162"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L261"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.05" customWidth="1"/>
-    <col min="3" max="3" width="29.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="35.5166666666667" customWidth="1"/>
-    <col min="6" max="6" width="28.6166666666667" customWidth="1"/>
-    <col min="7" max="7" width="32.325" customWidth="1"/>
+    <col min="2" max="2" width="19.08203125" customWidth="1"/>
+    <col min="3" max="3" width="29.9140625" customWidth="1"/>
+    <col min="4" max="4" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="28.58203125" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11687,7 +11106,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" ht="16.5" spans="1:12">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -11708,7 +11127,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:12">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -11729,7 +11148,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" ht="16.5" spans="1:12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>110000</v>
@@ -11737,11 +11156,11 @@
       <c r="C4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>110001</v>
@@ -11749,11 +11168,11 @@
       <c r="C5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>110002</v>
@@ -11761,11 +11180,11 @@
       <c r="C6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>110003</v>
@@ -11773,11 +11192,11 @@
       <c r="C7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>110004</v>
@@ -11785,11 +11204,11 @@
       <c r="C8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>110005</v>
@@ -11797,11 +11216,11 @@
       <c r="C9" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>110006</v>
@@ -11809,11 +11228,11 @@
       <c r="C10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>110007</v>
@@ -11821,11 +11240,11 @@
       <c r="C11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>110008</v>
@@ -11833,11 +11252,11 @@
       <c r="C12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>110009</v>
@@ -11845,11 +11264,11 @@
       <c r="C13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:12">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>110010</v>
@@ -11857,11 +11276,11 @@
       <c r="C14" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:12">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>110011</v>
@@ -11869,11 +11288,11 @@
       <c r="C15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:12">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>110012</v>
@@ -11881,11 +11300,11 @@
       <c r="C16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:4">
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>110013</v>
@@ -11893,11 +11312,11 @@
       <c r="C17" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:4">
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>110014</v>
@@ -11905,11 +11324,11 @@
       <c r="C18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:4">
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>110015</v>
@@ -11917,11 +11336,11 @@
       <c r="C19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:4">
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>110016</v>
@@ -11929,11 +11348,11 @@
       <c r="C20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:4">
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>110017</v>
@@ -11941,11 +11360,11 @@
       <c r="C21" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:4">
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>110018</v>
@@ -11953,11 +11372,11 @@
       <c r="C22" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:4">
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>110019</v>
@@ -11965,11 +11384,11 @@
       <c r="C23" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="24" ht="16.5" spans="1:4">
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>110020</v>
@@ -11977,11 +11396,11 @@
       <c r="C24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:4">
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>110021</v>
@@ -11989,11 +11408,11 @@
       <c r="C25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:4">
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>110022</v>
@@ -12001,11 +11420,11 @@
       <c r="C26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:4">
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>110023</v>
@@ -12013,11 +11432,11 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:4">
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>110024</v>
@@ -12025,11 +11444,11 @@
       <c r="C28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:4">
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>110025</v>
@@ -12037,11 +11456,11 @@
       <c r="C29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:4">
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>110026</v>
@@ -12049,11 +11468,11 @@
       <c r="C30" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:4">
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>110027</v>
@@ -12061,11 +11480,11 @@
       <c r="C31" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:4">
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>110028</v>
@@ -12073,11 +11492,11 @@
       <c r="C32" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:4">
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>110029</v>
@@ -12085,11 +11504,11 @@
       <c r="C33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:4">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>110030</v>
@@ -12097,11 +11516,11 @@
       <c r="C34" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:4">
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>110031</v>
@@ -12109,11 +11528,11 @@
       <c r="C35" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:4">
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>110032</v>
@@ -12121,11 +11540,11 @@
       <c r="C36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="1:4">
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>110033</v>
@@ -12133,11 +11552,11 @@
       <c r="C37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="38" ht="16.5" spans="1:4">
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>110034</v>
@@ -12145,11 +11564,11 @@
       <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:4">
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>110035</v>
@@ -12157,11 +11576,11 @@
       <c r="C39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="40" ht="16.5" spans="1:4">
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>110036</v>
@@ -12169,11 +11588,11 @@
       <c r="C40" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="41" ht="16.5" spans="1:4">
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>110037</v>
@@ -12181,11 +11600,11 @@
       <c r="C41" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="42" ht="16.5" spans="1:4">
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>110038</v>
@@ -12193,11 +11612,11 @@
       <c r="C42" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="43" ht="16.5" spans="1:4">
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>110039</v>
@@ -12205,11 +11624,11 @@
       <c r="C43" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:4">
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>210000</v>
@@ -12217,11 +11636,11 @@
       <c r="C44" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:4">
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>210001</v>
@@ -12229,11 +11648,11 @@
       <c r="C45" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:4">
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>210002</v>
@@ -12241,11 +11660,11 @@
       <c r="C46" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:4">
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>210003</v>
@@ -12253,11 +11672,11 @@
       <c r="C47" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:4">
+    <row r="48" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>210004</v>
@@ -12265,11 +11684,11 @@
       <c r="C48" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:4">
+    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>210005</v>
@@ -12277,11 +11696,11 @@
       <c r="C49" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:4">
+    <row r="50" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>210006</v>
@@ -12289,11 +11708,11 @@
       <c r="C50" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:4">
+    <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>210007</v>
@@ -12301,11 +11720,11 @@
       <c r="C51" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:4">
+    <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>210008</v>
@@ -12313,11 +11732,11 @@
       <c r="C52" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:4">
+    <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>210009</v>
@@ -12325,11 +11744,11 @@
       <c r="C53" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:4">
+    <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>210010</v>
@@ -12337,11 +11756,11 @@
       <c r="C54" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:4">
+    <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>210011</v>
@@ -12349,11 +11768,11 @@
       <c r="C55" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:4">
+    <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>210012</v>
@@ -12361,11 +11780,11 @@
       <c r="C56" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:4">
+    <row r="57" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>210013</v>
@@ -12373,11 +11792,11 @@
       <c r="C57" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:4">
+    <row r="58" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>210014</v>
@@ -12385,11 +11804,11 @@
       <c r="C58" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:4">
+    <row r="59" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>210015</v>
@@ -12397,11 +11816,11 @@
       <c r="C59" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:4">
+    <row r="60" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>210016</v>
@@ -12409,11 +11828,11 @@
       <c r="C60" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:4">
+    <row r="61" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>210017</v>
@@ -12421,11 +11840,11 @@
       <c r="C61" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:4">
+    <row r="62" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>210018</v>
@@ -12433,11 +11852,11 @@
       <c r="C62" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:4">
+    <row r="63" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>210019</v>
@@ -12445,11 +11864,11 @@
       <c r="C63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:4">
+    <row r="64" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>200000</v>
@@ -12457,11 +11876,11 @@
       <c r="C64" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:4">
+    <row r="65" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>200001</v>
@@ -12469,11 +11888,11 @@
       <c r="C65" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:4">
+    <row r="66" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>200002</v>
@@ -12481,11 +11900,11 @@
       <c r="C66" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:4">
+    <row r="67" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>200003</v>
@@ -12493,11 +11912,11 @@
       <c r="C67" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="68" ht="16.5" spans="1:4">
+    <row r="68" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>310000</v>
@@ -12505,11 +11924,11 @@
       <c r="C68" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:4">
+    <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>310001</v>
@@ -12517,11 +11936,11 @@
       <c r="C69" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="70" ht="16.5" spans="1:4">
+    <row r="70" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>310002</v>
@@ -12529,11 +11948,11 @@
       <c r="C70" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="71" ht="16.5" spans="1:4">
+    <row r="71" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>310003</v>
@@ -12541,11 +11960,11 @@
       <c r="C71" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="72" ht="16.5" spans="1:4">
+    <row r="72" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>310004</v>
@@ -12553,11 +11972,11 @@
       <c r="C72" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="73" ht="16.5" spans="1:4">
+    <row r="73" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>310005</v>
@@ -12565,11 +11984,11 @@
       <c r="C73" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="74" ht="16.5" spans="1:4">
+    <row r="74" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>310006</v>
@@ -12577,11 +11996,11 @@
       <c r="C74" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:4">
+    <row r="75" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>310007</v>
@@ -12589,11 +12008,11 @@
       <c r="C75" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="76" ht="16.5" spans="1:4">
+    <row r="76" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>310008</v>
@@ -12601,11 +12020,11 @@
       <c r="C76" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="77" ht="16.5" spans="1:4">
+    <row r="77" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>310009</v>
@@ -12613,11 +12032,11 @@
       <c r="C77" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:4">
+    <row r="78" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>310010</v>
@@ -12625,11 +12044,11 @@
       <c r="C78" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:4">
+    <row r="79" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>310011</v>
@@ -12637,11 +12056,11 @@
       <c r="C79" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:4">
+    <row r="80" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>310012</v>
@@ -12649,11 +12068,11 @@
       <c r="C80" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="81" ht="16.5" spans="1:4">
+    <row r="81" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>310013</v>
@@ -12661,11 +12080,11 @@
       <c r="C81" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="82" ht="16.5" spans="1:4">
+    <row r="82" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>310014</v>
@@ -12673,11 +12092,11 @@
       <c r="C82" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="83" ht="16.5" spans="1:4">
+    <row r="83" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>310015</v>
@@ -12685,11 +12104,11 @@
       <c r="C83" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="84" ht="16.5" spans="1:4">
+    <row r="84" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>310016</v>
@@ -12697,11 +12116,11 @@
       <c r="C84" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="85" ht="16.5" spans="1:4">
+    <row r="85" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>310017</v>
@@ -12709,11 +12128,11 @@
       <c r="C85" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="86" ht="16.5" spans="1:4">
+    <row r="86" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>310018</v>
@@ -12721,11 +12140,11 @@
       <c r="C86" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="87" ht="16.5" spans="1:4">
+    <row r="87" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>310019</v>
@@ -12733,11 +12152,11 @@
       <c r="C87" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="88" ht="16.5" spans="1:4">
+    <row r="88" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>310020</v>
@@ -12745,11 +12164,11 @@
       <c r="C88" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="89" ht="16.5" spans="1:4">
+    <row r="89" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>310021</v>
@@ -12757,11 +12176,11 @@
       <c r="C89" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="90" ht="16.5" spans="1:4">
+    <row r="90" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>310022</v>
@@ -12769,11 +12188,11 @@
       <c r="C90" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="91" ht="16.5" spans="1:4">
+    <row r="91" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>310023</v>
@@ -12781,11 +12200,11 @@
       <c r="C91" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="92" ht="16.5" spans="1:4">
+    <row r="92" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>310024</v>
@@ -12793,11 +12212,11 @@
       <c r="C92" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="93" ht="16.5" spans="1:4">
+    <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>310025</v>
@@ -12805,11 +12224,11 @@
       <c r="C93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="94" ht="16.5" spans="1:4">
+    <row r="94" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>310026</v>
@@ -12817,11 +12236,11 @@
       <c r="C94" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="95" ht="16.5" spans="1:4">
+    <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>310027</v>
@@ -12829,11 +12248,11 @@
       <c r="C95" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="96" ht="16.5" spans="1:4">
+    <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>310028</v>
@@ -12841,11 +12260,11 @@
       <c r="C96" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="97" ht="16.5" spans="1:4">
+    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>310029</v>
@@ -12853,11 +12272,11 @@
       <c r="C97" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="98" ht="16.5" spans="1:4">
+    <row r="98" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>310030</v>
@@ -12865,11 +12284,11 @@
       <c r="C98" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="99" ht="16.5" spans="1:4">
+    <row r="99" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>310031</v>
@@ -12877,11 +12296,11 @@
       <c r="C99" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="100" ht="16.5" spans="1:4">
+    <row r="100" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>310032</v>
@@ -12889,11 +12308,11 @@
       <c r="C100" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="101" ht="16.5" spans="1:4">
+    <row r="101" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>310033</v>
@@ -12901,11 +12320,11 @@
       <c r="C101" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="102" ht="16.5" spans="1:4">
+    <row r="102" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>310034</v>
@@ -12913,11 +12332,11 @@
       <c r="C102" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:4">
+    <row r="103" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>310035</v>
@@ -12925,11 +12344,11 @@
       <c r="C103" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:4">
+    <row r="104" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>310036</v>
@@ -12937,11 +12356,11 @@
       <c r="C104" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:4">
+    <row r="105" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>310037</v>
@@ -12949,11 +12368,11 @@
       <c r="C105" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:4">
+    <row r="106" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>310038</v>
@@ -12961,11 +12380,11 @@
       <c r="C106" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:4">
+    <row r="107" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>310039</v>
@@ -12973,618 +12392,1301 @@
       <c r="C107" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:4">
+    <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
         <v>100000</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:4">
+    <row r="109" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
         <v>100001</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="110" ht="16.5" spans="1:4">
+    <row r="110" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
         <v>100002</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="111" ht="16.5" spans="1:4">
+    <row r="111" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
         <v>100003</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="112" ht="16.5" spans="1:4">
+    <row r="112" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
         <v>100004</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="113" ht="16.5" spans="2:4">
+    <row r="113" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
         <v>100005</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="114" ht="16.5" spans="2:4">
+    <row r="114" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
         <v>100006</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="115" ht="16.5" spans="2:4">
+    <row r="115" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
         <v>100007</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="116" ht="16.5" spans="2:4">
+    <row r="116" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
         <v>100008</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="117" ht="16.5" spans="2:4">
+    <row r="117" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
         <v>100009</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="118" ht="16.5" spans="2:4">
+    <row r="118" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
         <v>100010</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="119" ht="16.5" spans="2:4">
+    <row r="119" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
         <v>100011</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="120" ht="16.5" spans="2:4">
+    <row r="120" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
         <v>100012</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="121" ht="16.5" spans="2:4">
+    <row r="121" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B121" s="1">
         <v>100013</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="122" ht="16.5" spans="2:4">
+    <row r="122" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
         <v>100014</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D122" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="123" ht="16.5" spans="2:4">
+    <row r="123" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B123" s="1">
         <v>100015</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="124" ht="16.5" spans="2:4">
+    <row r="124" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B124" s="1">
         <v>100016</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="125" ht="16.5" spans="2:4">
+    <row r="125" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
         <v>100017</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="126" ht="16.5" spans="2:4">
+    <row r="126" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
         <v>100018</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="127" ht="16.5" spans="2:4">
+    <row r="127" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B127" s="1">
         <v>100019</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="128" ht="16.5" spans="2:4">
+    <row r="128" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
         <v>100020</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="129" ht="16.5" spans="2:4">
+    <row r="129" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>100021</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="130" ht="16.5" spans="2:4">
+    <row r="130" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B130" s="1">
         <v>100022</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="131" ht="16.5" spans="2:4">
+    <row r="131" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B131" s="1">
         <v>100023</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="132" ht="16.5" spans="2:4">
+    <row r="132" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B132" s="1">
         <v>100024</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="133" ht="16.5" spans="2:4">
+    <row r="133" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B133" s="1">
         <v>100025</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="134" ht="16.5" spans="2:4">
+    <row r="134" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B134" s="1">
         <v>100026</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="D134" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="135" ht="16.5" spans="2:4">
+    <row r="135" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B135" s="1">
         <v>100027</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D135" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="136" ht="16.5" spans="2:4">
+    <row r="136" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B136" s="1">
         <v>100028</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D136" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="137" ht="16.5" spans="2:4">
+    <row r="137" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B137" s="1">
         <v>100029</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="138" ht="16.5" spans="2:4">
+    <row r="138" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B138" s="1">
         <v>100030</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="139" ht="16.5" spans="2:4">
+    <row r="139" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B139" s="1">
         <v>100031</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="140" ht="16.5" spans="2:4">
+    <row r="140" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B140" s="1">
         <v>100032</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="141" ht="16.5" spans="2:4">
+    <row r="141" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B141" s="1">
         <v>100033</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="142" ht="16.5" spans="2:4">
+    <row r="142" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B142" s="1">
         <v>100034</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D142" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="143" ht="16.5" spans="2:4">
+    <row r="143" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B143" s="1">
         <v>100035</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="144" ht="16.5" spans="2:4">
+    <row r="144" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B144" s="1">
         <v>100036</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="D144" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="145" ht="16.5" spans="2:4">
+    <row r="145" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B145" s="1">
         <v>100037</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D145" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="146" ht="16.5" spans="2:4">
+    <row r="146" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B146" s="1">
         <v>100038</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D146" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="147" ht="16.5" spans="2:4">
+    <row r="147" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B147" s="1">
         <v>100039</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="D147" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="148" ht="16.5" spans="2:4">
+    <row r="148" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B148" s="1">
         <v>100040</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="149" ht="16.5" spans="2:4">
+    <row r="149" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B149" s="1">
         <v>100041</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="150" ht="16.5" spans="2:4">
+    <row r="150" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B150" s="1">
         <v>100042</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="151" ht="16.5" spans="2:4">
+    <row r="151" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B151" s="1">
         <v>100043</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D151" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="152" ht="16.5" spans="2:4">
+    <row r="152" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B152" s="1">
         <v>100044</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D152" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="153" ht="16.5" spans="2:4">
+    <row r="153" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B153" s="1">
         <v>100045</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="154" ht="16.5" spans="2:4">
+    <row r="154" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B154" s="1">
         <v>100046</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="155" ht="16.5" spans="2:4">
+    <row r="155" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B155" s="1">
         <v>100047</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D155" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="156" ht="16.5" spans="2:4">
+    <row r="156" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B156" s="1">
         <v>100048</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="157" ht="16.5" spans="2:4">
+    <row r="157" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B157" s="1">
         <v>100049</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="158" ht="16.5" spans="2:4">
+    <row r="158" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B158" s="1">
         <v>100051</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="159" ht="16.5" spans="2:4">
+    <row r="159" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B159" s="1">
         <v>100052</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="160" ht="16.5" spans="2:4">
+    <row r="160" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B160" s="1">
         <v>100053</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="161" ht="16.5" spans="2:4">
+    <row r="161" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B161" s="1">
         <v>100054</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="162" ht="16.5" spans="2:4">
+    <row r="162" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B162" s="1">
         <v>100055</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" s="1" t="s">
         <v>355</v>
       </c>
     </row>
+    <row r="163" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B163" s="1">
+        <v>220006</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B164" s="1">
+        <v>220007</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B165" s="1">
+        <v>220008</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B166" s="1">
+        <v>220009</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B167" s="1">
+        <v>300000</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B168" s="1">
+        <v>300001</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B169" s="1">
+        <v>300002</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B170" s="1">
+        <v>300003</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B171" s="1">
+        <v>300004</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B172" s="1">
+        <v>300005</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B173" s="1">
+        <v>300006</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B174" s="1">
+        <v>300007</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B175" s="1">
+        <v>300008</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B176" s="1">
+        <v>300009</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B177" s="1">
+        <v>130000</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B178" s="1">
+        <v>130001</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B179" s="1">
+        <v>130002</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B180" s="1">
+        <v>140000</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B181" s="1">
+        <v>140001</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B182" s="1">
+        <v>140002</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B183" s="1">
+        <v>140003</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B184" s="1">
+        <v>150000</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B185" s="1">
+        <v>150001</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B186" s="1">
+        <v>150002</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B187" s="1">
+        <v>150003</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B188" s="1">
+        <v>150004</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B189" s="1">
+        <v>150005</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B190" s="1">
+        <v>150006</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B191" s="1">
+        <v>150007</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B192" s="1">
+        <v>150008</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B193" s="1">
+        <v>150009</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+    </row>
+    <row r="195" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+    </row>
+    <row r="196" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+    </row>
+    <row r="197" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+    </row>
+    <row r="198" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+    </row>
+    <row r="199" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+    </row>
+    <row r="200" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+    </row>
+    <row r="201" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+    </row>
+    <row r="202" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+    </row>
+    <row r="203" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+    </row>
+    <row r="204" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+    </row>
+    <row r="206" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+    </row>
+    <row r="207" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+    </row>
+    <row r="208" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+    </row>
+    <row r="209" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+    </row>
+    <row r="210" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+    </row>
+    <row r="211" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+    </row>
+    <row r="212" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+    </row>
+    <row r="213" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+    </row>
+    <row r="214" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+    </row>
+    <row r="215" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+    </row>
+    <row r="216" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+    </row>
+    <row r="217" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+    </row>
+    <row r="218" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+    </row>
+    <row r="219" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+    </row>
+    <row r="220" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+    </row>
+    <row r="221" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+    </row>
+    <row r="222" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+    </row>
+    <row r="223" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+    </row>
+    <row r="224" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+    </row>
+    <row r="225" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+    </row>
+    <row r="226" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+    </row>
+    <row r="227" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+    </row>
+    <row r="228" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+    </row>
+    <row r="229" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+    </row>
+    <row r="230" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+    </row>
+    <row r="231" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+    </row>
+    <row r="232" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+    </row>
+    <row r="233" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+    </row>
+    <row r="234" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+    </row>
+    <row r="235" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+    </row>
+    <row r="236" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+    </row>
+    <row r="237" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+    </row>
+    <row r="238" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+    </row>
+    <row r="239" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+    </row>
+    <row r="240" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+    </row>
+    <row r="241" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+    </row>
+    <row r="242" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+    </row>
+    <row r="243" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+    </row>
+    <row r="244" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+    </row>
+    <row r="245" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+    </row>
+    <row r="246" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+    </row>
+    <row r="247" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+    </row>
+    <row r="248" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+    </row>
+    <row r="249" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+    </row>
+    <row r="250" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+    </row>
+    <row r="251" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+    </row>
+    <row r="252" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+    </row>
+    <row r="253" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+    </row>
+    <row r="254" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+    </row>
+    <row r="255" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+    </row>
+    <row r="256" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+    </row>
+    <row r="257" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+    </row>
+    <row r="258" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+    </row>
+    <row r="259" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B259" s="1">
+        <v>310039</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C260" s="9"/>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C261" s="9"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.39375" footer="0.39375"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.78749999999999998" header="0.39374999999999999" footer="0.39374999999999999"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6B67E7-9E93-4457-9B06-51384FC397BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10190" yWindow="1780" windowWidth="30580" windowHeight="18680" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="360">
   <si>
     <t>##var</t>
   </si>
@@ -1090,7 +1084,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Item</t>
     </r>
@@ -1098,7 +1092,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="微软雅黑"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>MaterialType</t>
     </r>
@@ -1122,15 +1116,29 @@
     <t>Ingredient</t>
   </si>
   <si>
-    <t>None</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>Cloth</t>
+  </si>
+  <si>
+    <t>FishingBait</t>
+  </si>
+  <si>
+    <t>FishingGear</t>
+  </si>
+  <si>
+    <t>AdultProduct</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1141,33 +1149,178 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1180,8 +1333,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1204,11 +1543,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1218,6 +1799,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1234,24 +1821,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1504,25 +2132,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R240"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="29.08203125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="33.5" style="9" customWidth="1"/>
-    <col min="5" max="5" width="58.75" style="9" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" customWidth="1"/>
-    <col min="9" max="9" width="16.08203125" customWidth="1"/>
+    <col min="3" max="3" width="29.0833333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="33.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="58.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="42.3333333333333" style="5" customWidth="1"/>
+    <col min="7" max="7" width="21.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="16.0833333333333" customWidth="1"/>
     <col min="10" max="10" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +2182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1586,7 +2214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1618,7 +2246,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>100000</v>
@@ -1651,7 +2279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>100001</v>
@@ -1684,7 +2312,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>100002</v>
@@ -1717,7 +2345,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>100003</v>
@@ -1750,7 +2378,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>100004</v>
@@ -1783,7 +2411,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>100005</v>
@@ -1816,7 +2444,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>100006</v>
@@ -1849,7 +2477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>100007</v>
@@ -1882,7 +2510,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>100008</v>
@@ -1915,7 +2543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" ht="16.5" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>100009</v>
@@ -1948,7 +2576,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" ht="16.5" spans="1:10">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>100010</v>
@@ -1981,7 +2609,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" ht="16.5" spans="1:10">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>100011</v>
@@ -2014,7 +2642,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" ht="16.5" spans="1:10">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>100012</v>
@@ -2047,7 +2675,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" ht="16.5" spans="1:18">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>100013</v>
@@ -2080,7 +2708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" ht="16.5" spans="1:18">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>100014</v>
@@ -2113,7 +2741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" ht="16.5" spans="1:18">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>100015</v>
@@ -2146,7 +2774,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" ht="16.5" spans="1:18">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>100016</v>
@@ -2179,7 +2807,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" ht="16.5" spans="1:18">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>100017</v>
@@ -2212,7 +2840,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" ht="16.5" spans="1:18">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>100018</v>
@@ -2245,7 +2873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" ht="16.5" spans="1:18">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>100019</v>
@@ -2277,12 +2905,12 @@
       <c r="J23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-    </row>
-    <row r="24" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:18">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>100020</v>
@@ -2315,7 +2943,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" ht="16.5" spans="1:18">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>100021</v>
@@ -2348,7 +2976,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" ht="16.5" spans="1:18">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>100022</v>
@@ -2381,7 +3009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" ht="16.5" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>100023</v>
@@ -2414,7 +3042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" ht="16.5" spans="1:18">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>100024</v>
@@ -2447,7 +3075,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" ht="16.5" spans="1:18">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>100025</v>
@@ -2480,7 +3108,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" ht="16.5" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>100026</v>
@@ -2513,7 +3141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" ht="16.5" spans="1:18">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>100027</v>
@@ -2546,7 +3174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" ht="16.5" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>100028</v>
@@ -2579,7 +3207,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" ht="16.5" spans="1:10">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>100029</v>
@@ -2612,7 +3240,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" ht="16.5" spans="1:10">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>100030</v>
@@ -2645,7 +3273,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" ht="16.5" spans="1:10">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>100031</v>
@@ -2678,7 +3306,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" ht="16.5" spans="1:10">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>100032</v>
@@ -2711,7 +3339,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" ht="16.5" spans="1:10">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>100033</v>
@@ -2744,7 +3372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" ht="16.5" spans="1:10">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>100034</v>
@@ -2777,7 +3405,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" ht="16.5" spans="1:10">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>100035</v>
@@ -2810,7 +3438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" ht="16.5" spans="1:10">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>100036</v>
@@ -2843,7 +3471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" ht="16.5" spans="1:10">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>100037</v>
@@ -2876,7 +3504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="42" ht="16.5" spans="1:10">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>100038</v>
@@ -2909,7 +3537,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="43" ht="16.5" spans="1:10">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>100039</v>
@@ -2942,7 +3570,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" ht="16.5" spans="1:10">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>100040</v>
@@ -2975,7 +3603,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="45" ht="16.5" spans="1:10">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>100041</v>
@@ -3008,7 +3636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" ht="16.5" spans="1:10">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>100042</v>
@@ -3041,7 +3669,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" ht="16.5" spans="1:10">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>100043</v>
@@ -3074,7 +3702,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" ht="16.5" spans="1:10">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>100044</v>
@@ -3107,7 +3735,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" ht="16.5" spans="1:10">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>100045</v>
@@ -3140,7 +3768,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" ht="16.5" spans="1:10">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>100046</v>
@@ -3173,7 +3801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" ht="16.5" spans="1:10">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>100047</v>
@@ -3206,7 +3834,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" ht="16.5" spans="1:10">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>100048</v>
@@ -3239,7 +3867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" ht="16.5" spans="1:10">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>100049</v>
@@ -3272,7 +3900,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" ht="16.5" spans="1:10">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>100051</v>
@@ -3305,7 +3933,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" ht="16.5" spans="1:10">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>100052</v>
@@ -3338,7 +3966,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" ht="16.5" spans="1:10">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>100053</v>
@@ -3371,7 +3999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" ht="16.5" spans="1:10">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>100054</v>
@@ -3404,7 +4032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" ht="16.5" spans="1:10">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>100055</v>
@@ -3437,7 +4065,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" ht="16.5" spans="1:10">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>110000</v>
@@ -3470,7 +4098,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" ht="16.5" spans="1:10">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>110001</v>
@@ -3503,7 +4131,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" ht="16.5" spans="1:10">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>110002</v>
@@ -3536,7 +4164,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" ht="16.5" spans="1:10">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>110003</v>
@@ -3569,7 +4197,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" ht="16.5" spans="1:10">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>110004</v>
@@ -3602,7 +4230,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" ht="16.5" spans="1:10">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>110005</v>
@@ -3635,7 +4263,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="65" ht="16.5" spans="1:10">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>110006</v>
@@ -3668,7 +4296,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="66" ht="16.5" spans="1:10">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>110007</v>
@@ -3701,7 +4329,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="67" ht="16.5" spans="1:10">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>110008</v>
@@ -3734,7 +4362,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" ht="16.5" spans="1:10">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>110009</v>
@@ -3767,7 +4395,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="69" ht="16.5" spans="1:10">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>110010</v>
@@ -3800,7 +4428,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="70" ht="16.5" spans="1:10">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>110011</v>
@@ -3833,7 +4461,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" ht="16.5" spans="1:10">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>110012</v>
@@ -3866,7 +4494,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="72" ht="16.5" spans="1:10">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>110013</v>
@@ -3899,7 +4527,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="73" ht="16.5" spans="1:10">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>110014</v>
@@ -3932,7 +4560,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="74" ht="16.5" spans="1:10">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>110015</v>
@@ -3965,7 +4593,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="75" ht="16.5" spans="1:10">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>110016</v>
@@ -3998,7 +4626,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="76" ht="16.5" spans="1:10">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>110017</v>
@@ -4031,7 +4659,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="77" ht="16.5" spans="1:10">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>110018</v>
@@ -4064,7 +4692,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="78" ht="16.5" spans="1:10">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>110019</v>
@@ -4097,7 +4725,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="79" ht="16.5" spans="1:10">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>110020</v>
@@ -4130,7 +4758,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="80" ht="16.5" spans="1:10">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>110021</v>
@@ -4163,7 +4791,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="81" ht="16.5" spans="1:10">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>110022</v>
@@ -4196,7 +4824,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="82" ht="16.5" spans="1:10">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>110023</v>
@@ -4229,7 +4857,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="83" ht="16.5" spans="1:10">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>110024</v>
@@ -4262,7 +4890,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="84" ht="16.5" spans="1:10">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>110025</v>
@@ -4295,7 +4923,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="85" ht="16.5" spans="1:10">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>110026</v>
@@ -4328,7 +4956,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="86" ht="16.5" spans="1:10">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>110027</v>
@@ -4361,7 +4989,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="87" ht="16.5" spans="1:10">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>110028</v>
@@ -4394,7 +5022,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="88" ht="16.5" spans="1:10">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>110029</v>
@@ -4427,7 +5055,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="89" ht="16.5" spans="1:10">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>110030</v>
@@ -4460,7 +5088,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="90" ht="16.5" spans="1:10">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>110031</v>
@@ -4493,7 +5121,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="91" ht="16.5" spans="1:10">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>110032</v>
@@ -4526,7 +5154,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="92" ht="16.5" spans="1:10">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>110033</v>
@@ -4559,7 +5187,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="93" ht="16.5" spans="1:10">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>110034</v>
@@ -4592,7 +5220,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="94" ht="16.5" spans="1:10">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>110035</v>
@@ -4625,7 +5253,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="95" ht="16.5" spans="1:10">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>110036</v>
@@ -4658,7 +5286,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="96" ht="16.5" spans="1:10">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>110037</v>
@@ -4691,7 +5319,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="97" ht="16.5" spans="1:10">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>110038</v>
@@ -4724,7 +5352,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="98" ht="16.5" spans="1:10">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>110039</v>
@@ -4757,7 +5385,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="99" ht="16.5" spans="1:10">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>120000</v>
@@ -4790,7 +5418,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="100" ht="16.5" spans="1:10">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>120001</v>
@@ -4823,7 +5451,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="101" ht="16.5" spans="1:10">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>120002</v>
@@ -4856,7 +5484,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="102" ht="16.5" spans="1:10">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>120003</v>
@@ -4889,7 +5517,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="103" ht="16.5" spans="1:10">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>120004</v>
@@ -4922,7 +5550,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="104" ht="16.5" spans="1:10">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>120005</v>
@@ -4955,7 +5583,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="105" ht="16.5" spans="1:10">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>120006</v>
@@ -4988,7 +5616,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="106" ht="16.5" spans="1:10">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>120007</v>
@@ -5021,7 +5649,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="107" ht="16.5" spans="1:10">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>120008</v>
@@ -5054,7 +5682,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="108" ht="16.5" spans="1:10">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
         <v>120009</v>
@@ -5087,7 +5715,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="109" ht="16.5" spans="1:10">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
         <v>120010</v>
@@ -5120,7 +5748,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="110" ht="16.5" spans="1:10">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
         <v>120011</v>
@@ -5153,7 +5781,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="111" ht="16.5" spans="1:10">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
         <v>120012</v>
@@ -5186,7 +5814,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="112" ht="16.5" spans="1:10">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
         <v>120013</v>
@@ -5219,7 +5847,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="113" ht="16.5" spans="1:10">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
         <v>120014</v>
@@ -5252,7 +5880,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="114" ht="16.5" spans="1:10">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
         <v>120015</v>
@@ -5285,7 +5913,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="115" ht="16.5" spans="1:10">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
         <v>120016</v>
@@ -5318,7 +5946,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="116" ht="16.5" spans="1:10">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
         <v>120017</v>
@@ -5351,7 +5979,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="117" ht="16.5" spans="1:10">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
         <v>120018</v>
@@ -5384,7 +6012,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="118" ht="16.5" spans="1:10">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
         <v>120019</v>
@@ -5417,7 +6045,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="119" ht="16.5" spans="1:10">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
         <v>120020</v>
@@ -5450,7 +6078,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="120" ht="16.5" spans="1:10">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
         <v>120021</v>
@@ -5483,7 +6111,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="121" ht="16.5" spans="1:10">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
         <v>120022</v>
@@ -5516,7 +6144,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="122" ht="16.5" spans="1:10">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
         <v>120023</v>
@@ -5549,7 +6177,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="123" ht="16.5" spans="1:10">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
         <v>120024</v>
@@ -5582,7 +6210,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="124" ht="16.5" spans="1:10">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
         <v>120025</v>
@@ -5615,7 +6243,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="125" ht="16.5" spans="1:10">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
         <v>120026</v>
@@ -5648,7 +6276,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="126" ht="16.5" spans="1:10">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
         <v>120027</v>
@@ -5681,7 +6309,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="127" ht="16.5" spans="1:10">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
         <v>120028</v>
@@ -5714,7 +6342,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="128" ht="16.5" spans="1:10">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
         <v>120029</v>
@@ -5747,7 +6375,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="129" ht="16.5" spans="1:10">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
         <v>120030</v>
@@ -5780,7 +6408,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="130" ht="16.5" spans="1:10">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
         <v>120031</v>
@@ -5813,7 +6441,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="131" ht="16.5" spans="1:10">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
         <v>120032</v>
@@ -5846,7 +6474,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" ht="16.5" spans="1:10">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
         <v>120033</v>
@@ -5879,7 +6507,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" ht="16.5" spans="1:10">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
         <v>120034</v>
@@ -5912,7 +6540,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="134" ht="16.5" spans="1:10">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
         <v>120035</v>
@@ -5945,7 +6573,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" ht="16.5" spans="1:10">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
         <v>120036</v>
@@ -5978,7 +6606,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" ht="16.5" spans="1:10">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
         <v>120037</v>
@@ -6011,7 +6639,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" ht="16.5" spans="1:10">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
         <v>120038</v>
@@ -6044,7 +6672,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="138" ht="16.5" spans="1:10">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
         <v>120039</v>
@@ -6077,7 +6705,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" ht="16.5" spans="1:10">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
         <v>120040</v>
@@ -6110,7 +6738,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" ht="16.5" spans="1:10">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
         <v>200000</v>
@@ -6143,7 +6771,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="141" ht="16.5" spans="1:10">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
         <v>200001</v>
@@ -6176,7 +6804,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="142" ht="16.5" spans="1:10">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
         <v>200002</v>
@@ -6209,7 +6837,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="143" ht="16.5" spans="1:10">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
         <v>200003</v>
@@ -6242,7 +6870,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="144" ht="16.5" spans="1:10">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
         <v>210000</v>
@@ -6275,7 +6903,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="145" ht="16.5" spans="1:10">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
         <v>210001</v>
@@ -6308,7 +6936,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="146" ht="16.5" spans="1:10">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
         <v>210002</v>
@@ -6341,7 +6969,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="147" ht="16.5" spans="1:10">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
         <v>210003</v>
@@ -6374,7 +7002,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="148" ht="16.5" spans="1:10">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
         <v>210004</v>
@@ -6407,7 +7035,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="149" ht="16.5" spans="1:10">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
         <v>210005</v>
@@ -6440,7 +7068,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="150" ht="16.5" spans="1:10">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
         <v>210006</v>
@@ -6473,7 +7101,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="151" ht="16.5" spans="1:10">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
         <v>210007</v>
@@ -6506,7 +7134,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="152" ht="16.5" spans="1:10">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
         <v>210008</v>
@@ -6539,7 +7167,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="153" ht="16.5" spans="1:10">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
         <v>210009</v>
@@ -6572,7 +7200,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="154" ht="16.5" spans="1:10">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
         <v>210010</v>
@@ -6605,7 +7233,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="155" ht="16.5" spans="1:10">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
         <v>210011</v>
@@ -6638,7 +7266,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="156" ht="16.5" spans="1:10">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
         <v>210012</v>
@@ -6671,7 +7299,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="157" ht="16.5" spans="1:10">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
         <v>210013</v>
@@ -6704,7 +7332,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="158" ht="16.5" spans="1:10">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
         <v>210014</v>
@@ -6737,7 +7365,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="159" ht="16.5" spans="1:10">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
         <v>210015</v>
@@ -6770,7 +7398,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="160" ht="16.5" spans="1:10">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
         <v>210016</v>
@@ -6803,7 +7431,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="161" ht="16.5" spans="1:10">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
         <v>210017</v>
@@ -6836,7 +7464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="162" ht="16.5" spans="1:10">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
         <v>210018</v>
@@ -6869,7 +7497,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="163" ht="16.5" spans="1:10">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
         <v>210019</v>
@@ -6902,7 +7530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="164" ht="16.5" spans="1:10">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
         <v>220000</v>
@@ -6935,7 +7563,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="165" ht="16.5" spans="1:10">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
         <v>220001</v>
@@ -6968,7 +7596,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="166" ht="16.5" spans="1:10">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
         <v>220002</v>
@@ -7001,7 +7629,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="167" ht="16.5" spans="1:10">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
         <v>220003</v>
@@ -7034,7 +7662,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="168" ht="16.5" spans="1:10">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
         <v>220004</v>
@@ -7067,7 +7695,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="169" ht="16.5" spans="1:10">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
         <v>220005</v>
@@ -7100,7 +7728,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="170" ht="16.5" spans="1:10">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
         <v>220006</v>
@@ -7133,7 +7761,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="171" ht="16.5" spans="1:10">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
         <v>220007</v>
@@ -7166,7 +7794,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="172" ht="16.5" spans="1:10">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
         <v>220008</v>
@@ -7199,7 +7827,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="173" ht="16.5" spans="1:10">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
         <v>220009</v>
@@ -7232,7 +7860,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="174" ht="16.5" spans="1:10">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
         <v>300000</v>
@@ -7265,7 +7893,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="175" ht="16.5" spans="1:10">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
         <v>300001</v>
@@ -7298,7 +7926,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="176" ht="16.5" spans="1:10">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
         <v>300002</v>
@@ -7331,7 +7959,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="177" ht="16.5" spans="1:10">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
         <v>300003</v>
@@ -7364,7 +7992,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="178" ht="16.5" spans="1:10">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
         <v>300004</v>
@@ -7397,7 +8025,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="179" ht="16.5" spans="1:10">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
         <v>300005</v>
@@ -7430,7 +8058,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="180" ht="16.5" spans="1:10">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
         <v>300006</v>
@@ -7463,7 +8091,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="181" ht="16.5" spans="1:10">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
         <v>300007</v>
@@ -7496,7 +8124,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="182" ht="16.5" spans="1:10">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
         <v>300008</v>
@@ -7529,7 +8157,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="183" ht="16.5" spans="1:10">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
         <v>300009</v>
@@ -7562,7 +8190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="184" ht="16.5" spans="1:10">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
         <v>130000</v>
@@ -7595,7 +8223,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="185" ht="16.5" spans="1:10">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
         <v>130001</v>
@@ -7628,7 +8256,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="186" ht="16.5" spans="1:10">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
         <v>130002</v>
@@ -7661,7 +8289,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="187" ht="16.5" spans="1:10">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
         <v>140000</v>
@@ -7694,7 +8322,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="188" ht="16.5" spans="1:10">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
         <v>140001</v>
@@ -7727,7 +8355,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="189" ht="16.5" spans="1:10">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
         <v>140002</v>
@@ -7760,7 +8388,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="190" ht="16.5" spans="1:10">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
         <v>140003</v>
@@ -7793,7 +8421,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="191" ht="16.5" spans="1:10">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
         <v>150000</v>
@@ -7826,7 +8454,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="192" ht="16.5" spans="1:10">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
         <v>150001</v>
@@ -7859,7 +8487,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="193" ht="16.5" spans="1:10">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
         <v>150002</v>
@@ -7892,7 +8520,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="194" ht="16.5" spans="1:10">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
         <v>150003</v>
@@ -7925,7 +8553,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="195" ht="16.5" spans="1:10">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
         <v>150004</v>
@@ -7958,7 +8586,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="196" ht="16.5" spans="1:10">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
         <v>150005</v>
@@ -7991,7 +8619,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="197" ht="16.5" spans="1:10">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
         <v>150006</v>
@@ -8024,7 +8652,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="198" ht="16.5" spans="1:10">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
         <v>150007</v>
@@ -8057,7 +8685,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="199" ht="16.5" spans="1:10">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
         <v>150008</v>
@@ -8090,7 +8718,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="200" ht="16.5" spans="1:10">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
         <v>150009</v>
@@ -8123,7 +8751,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="201" ht="16.5" spans="1:10">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
         <v>310000</v>
@@ -8156,7 +8784,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="202" ht="16.5" spans="1:10">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
         <v>310001</v>
@@ -8189,7 +8817,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="203" ht="16.5" spans="1:10">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
         <v>310002</v>
@@ -8222,7 +8850,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="204" ht="16.5" spans="1:10">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
         <v>310003</v>
@@ -8255,7 +8883,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="205" ht="16.5" spans="1:10">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
         <v>310004</v>
@@ -8288,7 +8916,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="206" ht="16.5" spans="1:10">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
         <v>310005</v>
@@ -8321,7 +8949,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="207" ht="16.5" spans="1:10">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
         <v>310006</v>
@@ -8354,7 +8982,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="208" ht="16.5" spans="1:10">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
         <v>310007</v>
@@ -8387,7 +9015,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="209" ht="16.5" spans="1:10">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
         <v>310008</v>
@@ -8420,7 +9048,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="210" ht="16.5" spans="1:10">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
         <v>310009</v>
@@ -8453,7 +9081,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="211" ht="16.5" spans="1:10">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
         <v>310010</v>
@@ -8486,7 +9114,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="212" ht="16.5" spans="1:10">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
         <v>310011</v>
@@ -8519,7 +9147,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="213" ht="16.5" spans="1:10">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
         <v>310012</v>
@@ -8552,7 +9180,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="214" ht="16.5" spans="1:10">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
         <v>310013</v>
@@ -8585,7 +9213,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="215" ht="16.5" spans="1:10">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
         <v>310014</v>
@@ -8618,7 +9246,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="216" ht="16.5" spans="1:10">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
         <v>310015</v>
@@ -8651,7 +9279,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="217" ht="16.5" spans="1:10">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
         <v>310016</v>
@@ -8684,7 +9312,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="218" ht="16.5" spans="1:10">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
         <v>310017</v>
@@ -8717,7 +9345,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="219" ht="16.5" spans="1:10">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
         <v>310018</v>
@@ -8750,7 +9378,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="220" ht="16.5" spans="1:10">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
         <v>310019</v>
@@ -8783,7 +9411,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="221" ht="16.5" spans="1:10">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
         <v>310020</v>
@@ -8816,7 +9444,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="222" ht="16.5" spans="1:10">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
         <v>310021</v>
@@ -8849,7 +9477,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="223" ht="16.5" spans="1:10">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
         <v>310022</v>
@@ -8882,7 +9510,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="224" ht="16.5" spans="1:10">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
         <v>310023</v>
@@ -8915,7 +9543,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="225" ht="16.5" spans="1:10">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
         <v>310024</v>
@@ -8948,7 +9576,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="226" ht="16.5" spans="1:10">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
         <v>310025</v>
@@ -8981,7 +9609,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="227" ht="16.5" spans="1:10">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
         <v>310026</v>
@@ -9014,7 +9642,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="228" ht="16.5" spans="1:10">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
         <v>310027</v>
@@ -9047,7 +9675,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="229" ht="16.5" spans="1:10">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
         <v>310028</v>
@@ -9080,7 +9708,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="230" ht="16.5" spans="1:10">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
         <v>310029</v>
@@ -9113,7 +9741,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="231" ht="16.5" spans="1:10">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
         <v>310030</v>
@@ -9146,7 +9774,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="232" ht="16.5" spans="1:10">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
         <v>310031</v>
@@ -9179,7 +9807,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="233" ht="16.5" spans="1:10">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
         <v>310032</v>
@@ -9212,7 +9840,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="234" ht="16.5" spans="1:10">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
         <v>310033</v>
@@ -9245,7 +9873,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="235" ht="16.5" spans="1:10">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
         <v>310034</v>
@@ -9278,7 +9906,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="236" ht="16.5" spans="1:10">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
         <v>310035</v>
@@ -9311,7 +9939,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="237" ht="16.5" spans="1:10">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
         <v>310036</v>
@@ -9344,7 +9972,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="238" ht="16.5" spans="1:10">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
         <v>310037</v>
@@ -9377,7 +10005,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="239" ht="16.5" spans="1:10">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
         <v>310038</v>
@@ -9410,7 +10038,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="240" ht="16.5" spans="1:10">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
         <v>310039</v>
@@ -9444,29 +10072,30 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="12.58203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.5833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.0833333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.1640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.08203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.58203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.08203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.0833333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.5833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.0833333333333" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9485,11 +10114,11 @@
       <c r="F1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -9512,7 +10141,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -9535,37 +10164,37 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="B4" s="5">
+    <row r="4" spans="1:18">
+      <c r="B4" s="7">
         <v>120000</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
         <v>297</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5" s="2">
         <v>120001</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -9574,13 +10203,13 @@
       <c r="G5" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="B6" s="2">
         <v>120002</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -9589,13 +10218,13 @@
       <c r="G6" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7" s="2">
         <v>120003</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -9604,13 +10233,13 @@
       <c r="G7" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8" s="2">
         <v>120004</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -9619,13 +10248,13 @@
       <c r="G8" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9" s="2">
         <v>120005</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -9634,13 +10263,13 @@
       <c r="G9" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:18">
       <c r="B10" s="2">
         <v>120006</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -9649,13 +10278,13 @@
       <c r="G10" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11" s="2">
         <v>120007</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -9664,13 +10293,13 @@
       <c r="G11" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12" s="2">
         <v>120008</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -9679,13 +10308,13 @@
       <c r="G12" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13" s="2">
         <v>120009</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -9694,13 +10323,13 @@
       <c r="G13" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:18">
       <c r="B14" s="2">
         <v>120010</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -9709,13 +10338,13 @@
       <c r="G14" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:18">
       <c r="B15" s="2">
         <v>120011</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -9724,13 +10353,13 @@
       <c r="G15" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:18">
       <c r="B16" s="2">
         <v>120012</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -9739,13 +10368,13 @@
       <c r="G16" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17" s="2">
         <v>120013</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -9754,13 +10383,13 @@
       <c r="G17" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="2:8">
       <c r="B18" s="2">
         <v>120014</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -9769,13 +10398,13 @@
       <c r="G18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="2:8">
       <c r="B19" s="2">
         <v>120015</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -9784,13 +10413,13 @@
       <c r="G19" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="2:8">
       <c r="B20" s="2">
         <v>120016</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -9799,13 +10428,13 @@
       <c r="G20" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="2:8">
       <c r="B21" s="2">
         <v>120017</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="8" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -9814,13 +10443,13 @@
       <c r="G21" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="2:8">
       <c r="B22" s="2">
         <v>120018</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -9829,13 +10458,13 @@
       <c r="G22" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="2:8">
       <c r="B23" s="2">
         <v>120019</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="8" t="s">
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -9844,13 +10473,13 @@
       <c r="G23" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24" s="2">
         <v>120020</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="8" t="s">
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -9859,13 +10488,13 @@
       <c r="G24" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="2:8">
       <c r="B25" s="2">
         <v>120021</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="8" t="s">
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -9874,13 +10503,13 @@
       <c r="G25" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="2:8">
       <c r="B26" s="2">
         <v>120022</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="8" t="s">
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -9889,13 +10518,13 @@
       <c r="G26" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="2">
         <v>120023</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="8" t="s">
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -9904,13 +10533,13 @@
       <c r="G27" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="2:8">
       <c r="B28" s="2">
         <v>120024</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="8" t="s">
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -9919,13 +10548,13 @@
       <c r="G28" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="2:8">
       <c r="B29" s="2">
         <v>120025</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="8" t="s">
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -9934,13 +10563,13 @@
       <c r="G29" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="2:8">
       <c r="B30" s="2">
         <v>120026</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="8" t="s">
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -9949,13 +10578,13 @@
       <c r="G30" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="2:8">
       <c r="B31" s="2">
         <v>120027</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="8" t="s">
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -9964,13 +10593,13 @@
       <c r="G31" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="2:8">
       <c r="B32" s="2">
         <v>120028</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="8" t="s">
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -9979,13 +10608,13 @@
       <c r="G32" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="2">
         <v>120029</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="8" t="s">
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -9994,13 +10623,13 @@
       <c r="G33" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="2">
         <v>120030</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="8" t="s">
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -10009,13 +10638,13 @@
       <c r="G34" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="2:8">
       <c r="B35" s="2">
         <v>120031</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="8" t="s">
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -10024,13 +10653,13 @@
       <c r="G35" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="2:8">
       <c r="B36" s="2">
         <v>120032</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="8" t="s">
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -10039,13 +10668,13 @@
       <c r="G36" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H36" s="7"/>
+    </row>
+    <row r="37" spans="2:8">
       <c r="B37" s="2">
         <v>120033</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="8" t="s">
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -10054,13 +10683,13 @@
       <c r="G37" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="2:8">
       <c r="B38" s="2">
         <v>120034</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="8" t="s">
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -10069,13 +10698,13 @@
       <c r="G38" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="2:8">
       <c r="B39" s="2">
         <v>120035</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="8" t="s">
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -10084,13 +10713,13 @@
       <c r="G39" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="2:8">
       <c r="B40" s="2">
         <v>120036</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="8" t="s">
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -10099,13 +10728,13 @@
       <c r="G40" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H40" s="5"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="2:8">
       <c r="B41" s="2">
         <v>120037</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="8" t="s">
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -10114,13 +10743,13 @@
       <c r="G41" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="2:8">
       <c r="B42" s="2">
         <v>120038</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="8" t="s">
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -10129,13 +10758,13 @@
       <c r="G42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="2:8">
       <c r="B43" s="2">
         <v>120039</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="8" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -10144,13 +10773,13 @@
       <c r="G43" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="2:8">
       <c r="B44" s="2">
         <v>120040</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="8" t="s">
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -10159,303 +10788,304 @@
       <c r="G44" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="2:8">
       <c r="B45"/>
       <c r="C45"/>
       <c r="G45"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:8">
       <c r="B46"/>
       <c r="C46"/>
       <c r="G46"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:8">
       <c r="B47"/>
       <c r="C47"/>
       <c r="G47"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:8">
       <c r="B48"/>
       <c r="C48"/>
       <c r="G48"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:7">
       <c r="B49"/>
       <c r="C49"/>
       <c r="G49"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:7">
       <c r="B50"/>
       <c r="C50"/>
       <c r="G50"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:7">
       <c r="B51"/>
       <c r="C51"/>
       <c r="G51"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:7">
       <c r="B52"/>
       <c r="C52"/>
       <c r="G52"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:7">
       <c r="B53"/>
       <c r="C53"/>
       <c r="G53"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:7">
       <c r="B54"/>
       <c r="C54"/>
       <c r="G54"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:7">
       <c r="B55"/>
       <c r="C55"/>
       <c r="G55"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:7">
       <c r="B56"/>
       <c r="C56"/>
       <c r="G56"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:7">
       <c r="B57"/>
       <c r="C57"/>
       <c r="G57"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:7">
       <c r="B58"/>
       <c r="C58"/>
       <c r="G58"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:7">
       <c r="B59"/>
       <c r="C59"/>
       <c r="G59"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:7">
       <c r="B60"/>
       <c r="C60"/>
       <c r="G60"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:7">
       <c r="B61"/>
       <c r="C61"/>
       <c r="G61"/>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:7">
       <c r="B62"/>
       <c r="C62"/>
       <c r="G62"/>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:7">
       <c r="B63"/>
       <c r="C63"/>
       <c r="G63"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:7">
       <c r="B64"/>
       <c r="C64"/>
       <c r="G64"/>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:7">
       <c r="B65"/>
       <c r="C65"/>
       <c r="G65"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:7">
       <c r="B66"/>
       <c r="C66"/>
       <c r="G66"/>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:7">
       <c r="B67"/>
       <c r="C67"/>
       <c r="G67"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:7">
       <c r="B68"/>
       <c r="C68"/>
       <c r="G68"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:7">
       <c r="B69"/>
       <c r="C69"/>
       <c r="G69"/>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:7">
       <c r="B70"/>
       <c r="C70"/>
       <c r="G70"/>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:7">
       <c r="B71"/>
       <c r="C71"/>
       <c r="G71"/>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:7">
       <c r="B72"/>
       <c r="C72"/>
       <c r="G72"/>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:7">
       <c r="B73"/>
       <c r="C73"/>
       <c r="G73"/>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:7">
       <c r="B74"/>
       <c r="C74"/>
       <c r="G74"/>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:7">
       <c r="B75"/>
       <c r="C75"/>
       <c r="G75"/>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:7">
       <c r="B76"/>
       <c r="C76"/>
       <c r="G76"/>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:7">
       <c r="B77"/>
       <c r="C77"/>
       <c r="G77"/>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:7">
       <c r="B78"/>
       <c r="C78"/>
       <c r="G78"/>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:7">
       <c r="B79"/>
       <c r="C79"/>
       <c r="G79"/>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:7">
       <c r="B80"/>
       <c r="C80"/>
       <c r="G80"/>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:7">
       <c r="B81"/>
       <c r="C81"/>
       <c r="G81"/>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:7">
       <c r="B82"/>
       <c r="C82"/>
       <c r="G82"/>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:7">
       <c r="B83"/>
       <c r="C83"/>
       <c r="G83"/>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:7">
       <c r="B84"/>
       <c r="C84"/>
       <c r="G84"/>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:7">
       <c r="B85"/>
       <c r="C85"/>
       <c r="G85"/>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:7">
       <c r="B86"/>
       <c r="C86"/>
       <c r="G86"/>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:7">
       <c r="B87"/>
       <c r="C87"/>
       <c r="G87"/>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:7">
       <c r="B88"/>
       <c r="C88"/>
       <c r="G88"/>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:7">
       <c r="B89"/>
       <c r="C89"/>
       <c r="G89"/>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:7">
       <c r="B90"/>
       <c r="C90"/>
       <c r="G90"/>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:7">
       <c r="B91"/>
       <c r="C91"/>
       <c r="G91"/>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:7">
       <c r="B92"/>
       <c r="C92"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:7">
       <c r="B93"/>
       <c r="C93"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:7">
       <c r="B94"/>
       <c r="C94"/>
       <c r="G94"/>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:7">
       <c r="B95"/>
       <c r="C95"/>
       <c r="G95"/>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:7">
       <c r="B96"/>
       <c r="C96"/>
       <c r="G96"/>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:7">
       <c r="B97"/>
       <c r="C97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:7">
       <c r="B98"/>
       <c r="C98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:7">
       <c r="B99"/>
       <c r="C99"/>
       <c r="G99"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.9140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.9166666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10472,7 +11102,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -10489,7 +11119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -10506,7 +11136,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="B4" s="2">
         <v>110000</v>
       </c>
@@ -10520,7 +11150,7 @@
         <v>120001</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="B5" s="2">
         <v>110001</v>
       </c>
@@ -10534,7 +11164,7 @@
         <v>120002</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="B6" s="2">
         <v>110002</v>
       </c>
@@ -10548,7 +11178,7 @@
         <v>120003</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5">
       <c r="B7" s="2">
         <v>110003</v>
       </c>
@@ -10562,7 +11192,7 @@
         <v>120004</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5">
       <c r="B8" s="2">
         <v>110004</v>
       </c>
@@ -10576,7 +11206,7 @@
         <v>120005</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5">
       <c r="B9" s="2">
         <v>110005</v>
       </c>
@@ -10590,7 +11220,7 @@
         <v>120006</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5">
       <c r="B10" s="2">
         <v>110006</v>
       </c>
@@ -10604,7 +11234,7 @@
         <v>120007</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5">
       <c r="B11" s="2">
         <v>110007</v>
       </c>
@@ -10618,7 +11248,7 @@
         <v>120008</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5">
       <c r="B12" s="2">
         <v>110008</v>
       </c>
@@ -10632,7 +11262,7 @@
         <v>120009</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5">
       <c r="B13" s="2">
         <v>110009</v>
       </c>
@@ -10646,7 +11276,7 @@
         <v>120010</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5">
       <c r="B14" s="2">
         <v>110010</v>
       </c>
@@ -10660,7 +11290,7 @@
         <v>120011</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5">
       <c r="B15" s="2">
         <v>110011</v>
       </c>
@@ -10674,7 +11304,7 @@
         <v>120012</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5">
       <c r="B16" s="2">
         <v>110012</v>
       </c>
@@ -10688,7 +11318,7 @@
         <v>120013</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5">
       <c r="B17" s="2">
         <v>110013</v>
       </c>
@@ -10702,7 +11332,7 @@
         <v>120014</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5">
       <c r="B18" s="2">
         <v>110014</v>
       </c>
@@ -10716,7 +11346,7 @@
         <v>120015</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5">
       <c r="B19" s="2">
         <v>110015</v>
       </c>
@@ -10730,7 +11360,7 @@
         <v>120016</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5">
       <c r="B20" s="2">
         <v>110016</v>
       </c>
@@ -10744,7 +11374,7 @@
         <v>120017</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5">
       <c r="B21" s="2">
         <v>110017</v>
       </c>
@@ -10758,7 +11388,7 @@
         <v>120018</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5">
       <c r="B22" s="2">
         <v>110018</v>
       </c>
@@ -10772,7 +11402,7 @@
         <v>120019</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5">
       <c r="B23" s="2">
         <v>110019</v>
       </c>
@@ -10786,7 +11416,7 @@
         <v>120020</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5">
       <c r="B24" s="2">
         <v>110020</v>
       </c>
@@ -10800,7 +11430,7 @@
         <v>120021</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5">
       <c r="B25" s="2">
         <v>110021</v>
       </c>
@@ -10814,7 +11444,7 @@
         <v>120022</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5">
       <c r="B26" s="2">
         <v>110022</v>
       </c>
@@ -10828,7 +11458,7 @@
         <v>120023</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5">
       <c r="B27" s="2">
         <v>110023</v>
       </c>
@@ -10842,7 +11472,7 @@
         <v>120024</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5">
       <c r="B28" s="2">
         <v>110024</v>
       </c>
@@ -10856,7 +11486,7 @@
         <v>120025</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5">
       <c r="B29" s="2">
         <v>110025</v>
       </c>
@@ -10870,7 +11500,7 @@
         <v>120026</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5">
       <c r="B30" s="2">
         <v>110026</v>
       </c>
@@ -10884,7 +11514,7 @@
         <v>120027</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5">
       <c r="B31" s="2">
         <v>110027</v>
       </c>
@@ -10898,7 +11528,7 @@
         <v>120028</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5">
       <c r="B32" s="2">
         <v>110028</v>
       </c>
@@ -10912,7 +11542,7 @@
         <v>120029</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5">
       <c r="B33" s="2">
         <v>110029</v>
       </c>
@@ -10926,7 +11556,7 @@
         <v>120030</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5">
       <c r="B34" s="2">
         <v>110030</v>
       </c>
@@ -10940,7 +11570,7 @@
         <v>120031</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5">
       <c r="B35" s="2">
         <v>110031</v>
       </c>
@@ -10954,7 +11584,7 @@
         <v>120032</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5">
       <c r="B36" s="2">
         <v>110032</v>
       </c>
@@ -10968,7 +11598,7 @@
         <v>120033</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5">
       <c r="B37" s="2">
         <v>110033</v>
       </c>
@@ -10982,7 +11612,7 @@
         <v>120034</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5">
       <c r="B38" s="2">
         <v>110034</v>
       </c>
@@ -10996,7 +11626,7 @@
         <v>120035</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5">
       <c r="B39" s="2">
         <v>110035</v>
       </c>
@@ -11010,7 +11640,7 @@
         <v>120036</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5">
       <c r="B40" s="2">
         <v>110036</v>
       </c>
@@ -11024,7 +11654,7 @@
         <v>120037</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5">
       <c r="B41" s="2">
         <v>110037</v>
       </c>
@@ -11038,7 +11668,7 @@
         <v>120038</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:5">
       <c r="B42" s="2">
         <v>110038</v>
       </c>
@@ -11052,7 +11682,7 @@
         <v>120039</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:5">
       <c r="B43" s="2">
         <v>110039</v>
       </c>
@@ -11067,25 +11697,26 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L261"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="19.08203125" customWidth="1"/>
-    <col min="3" max="3" width="29.9140625" customWidth="1"/>
+    <col min="2" max="2" width="19.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="29.9166666666667" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="6" max="6" width="28.58203125" customWidth="1"/>
-    <col min="7" max="7" width="32.33203125" customWidth="1"/>
+    <col min="6" max="6" width="28.5833333333333" customWidth="1"/>
+    <col min="7" max="7" width="32.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" ht="16.5" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11106,7 +11737,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="2" ht="16.5" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -11127,7 +11758,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -11148,7 +11779,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" ht="16.5" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>110000</v>
@@ -11160,7 +11791,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>110001</v>
@@ -11172,7 +11803,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>110002</v>
@@ -11184,7 +11815,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>110003</v>
@@ -11196,7 +11827,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>110004</v>
@@ -11208,7 +11839,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>110005</v>
@@ -11220,7 +11851,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>110006</v>
@@ -11232,7 +11863,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>110007</v>
@@ -11244,7 +11875,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" ht="16.5" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>110008</v>
@@ -11256,7 +11887,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>110009</v>
@@ -11268,7 +11899,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>110010</v>
@@ -11280,7 +11911,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" ht="16.5" spans="1:12">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>110011</v>
@@ -11292,7 +11923,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>110012</v>
@@ -11304,7 +11935,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>110013</v>
@@ -11316,7 +11947,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>110014</v>
@@ -11328,7 +11959,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>110015</v>
@@ -11340,7 +11971,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>110016</v>
@@ -11352,7 +11983,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>110017</v>
@@ -11364,7 +11995,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>110018</v>
@@ -11376,7 +12007,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>110019</v>
@@ -11388,7 +12019,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>110020</v>
@@ -11400,7 +12031,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>110021</v>
@@ -11412,7 +12043,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>110022</v>
@@ -11424,7 +12055,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>110023</v>
@@ -11436,7 +12067,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" ht="16.5" spans="1:4">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>110024</v>
@@ -11448,7 +12079,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" ht="16.5" spans="1:4">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>110025</v>
@@ -11460,7 +12091,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" ht="16.5" spans="1:4">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>110026</v>
@@ -11472,7 +12103,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" ht="16.5" spans="1:4">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>110027</v>
@@ -11484,7 +12115,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" ht="16.5" spans="1:4">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>110028</v>
@@ -11496,7 +12127,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" ht="16.5" spans="1:4">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>110029</v>
@@ -11508,7 +12139,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" ht="16.5" spans="1:4">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>110030</v>
@@ -11520,7 +12151,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" ht="16.5" spans="1:4">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>110031</v>
@@ -11532,7 +12163,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" ht="16.5" spans="1:4">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>110032</v>
@@ -11544,7 +12175,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" ht="16.5" spans="1:4">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>110033</v>
@@ -11556,7 +12187,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" ht="16.5" spans="1:4">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>110034</v>
@@ -11568,7 +12199,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" ht="16.5" spans="1:4">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>110035</v>
@@ -11580,7 +12211,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" ht="16.5" spans="1:4">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>110036</v>
@@ -11592,7 +12223,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" ht="16.5" spans="1:4">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>110037</v>
@@ -11604,7 +12235,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="42" ht="16.5" spans="1:4">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>110038</v>
@@ -11616,7 +12247,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="43" ht="16.5" spans="1:4">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>110039</v>
@@ -11628,7 +12259,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" ht="16.5" spans="1:4">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>210000</v>
@@ -11640,7 +12271,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="45" ht="16.5" spans="1:4">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>210001</v>
@@ -11652,7 +12283,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" ht="16.5" spans="1:4">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>210002</v>
@@ -11664,7 +12295,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" ht="16.5" spans="1:4">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>210003</v>
@@ -11676,7 +12307,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" ht="16.5" spans="1:4">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>210004</v>
@@ -11688,7 +12319,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" ht="16.5" spans="1:4">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>210005</v>
@@ -11700,7 +12331,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>210006</v>
@@ -11712,7 +12343,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" ht="16.5" spans="1:4">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>210007</v>
@@ -11724,7 +12355,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" ht="16.5" spans="1:4">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>210008</v>
@@ -11736,7 +12367,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" ht="16.5" spans="1:4">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>210009</v>
@@ -11748,7 +12379,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" ht="16.5" spans="1:4">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>210010</v>
@@ -11760,7 +12391,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" ht="16.5" spans="1:4">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>210011</v>
@@ -11772,7 +12403,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" ht="16.5" spans="1:4">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>210012</v>
@@ -11784,7 +12415,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" ht="16.5" spans="1:4">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>210013</v>
@@ -11796,7 +12427,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" ht="16.5" spans="1:4">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>210014</v>
@@ -11808,7 +12439,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" ht="16.5" spans="1:4">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>210015</v>
@@ -11820,7 +12451,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" ht="16.5" spans="1:4">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>210016</v>
@@ -11832,7 +12463,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" ht="16.5" spans="1:4">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>210017</v>
@@ -11844,7 +12475,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" ht="16.5" spans="1:4">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>210018</v>
@@ -11856,7 +12487,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" ht="16.5" spans="1:4">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>210019</v>
@@ -11868,7 +12499,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" ht="16.5" spans="1:4">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>200000</v>
@@ -11880,7 +12511,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="65" ht="16.5" spans="1:4">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>200001</v>
@@ -11892,7 +12523,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="66" ht="16.5" spans="1:4">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>200002</v>
@@ -11904,7 +12535,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="67" ht="16.5" spans="1:4">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>200003</v>
@@ -11916,7 +12547,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" ht="16.5" spans="1:4">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>310000</v>
@@ -11928,7 +12559,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="69" ht="16.5" spans="1:4">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>310001</v>
@@ -11940,7 +12571,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="70" ht="16.5" spans="1:4">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>310002</v>
@@ -11952,7 +12583,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" ht="16.5" spans="1:4">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>310003</v>
@@ -11964,7 +12595,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="72" ht="16.5" spans="1:4">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>310004</v>
@@ -11976,7 +12607,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="73" ht="16.5" spans="1:4">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>310005</v>
@@ -11988,7 +12619,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="74" ht="16.5" spans="1:4">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>310006</v>
@@ -12000,7 +12631,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="75" ht="16.5" spans="1:4">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>310007</v>
@@ -12012,7 +12643,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="76" ht="16.5" spans="1:4">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>310008</v>
@@ -12024,7 +12655,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="77" ht="16.5" spans="1:4">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>310009</v>
@@ -12036,7 +12667,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="78" ht="16.5" spans="1:4">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>310010</v>
@@ -12048,7 +12679,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="79" ht="16.5" spans="1:4">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>310011</v>
@@ -12060,7 +12691,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="80" ht="16.5" spans="1:4">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>310012</v>
@@ -12072,7 +12703,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="81" ht="16.5" spans="1:4">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>310013</v>
@@ -12084,7 +12715,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="82" ht="16.5" spans="1:4">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>310014</v>
@@ -12096,7 +12727,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="83" ht="16.5" spans="1:4">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>310015</v>
@@ -12108,7 +12739,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="84" ht="16.5" spans="1:4">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>310016</v>
@@ -12120,7 +12751,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="85" ht="16.5" spans="1:4">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>310017</v>
@@ -12132,7 +12763,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="86" ht="16.5" spans="1:4">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>310018</v>
@@ -12144,7 +12775,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="87" ht="16.5" spans="1:4">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>310019</v>
@@ -12156,7 +12787,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="88" ht="16.5" spans="1:4">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>310020</v>
@@ -12168,7 +12799,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="89" ht="16.5" spans="1:4">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>310021</v>
@@ -12180,7 +12811,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="90" ht="16.5" spans="1:4">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>310022</v>
@@ -12192,7 +12823,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="91" ht="16.5" spans="1:4">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>310023</v>
@@ -12204,7 +12835,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="92" ht="16.5" spans="1:4">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>310024</v>
@@ -12216,7 +12847,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="93" ht="16.5" spans="1:4">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>310025</v>
@@ -12228,7 +12859,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="94" ht="16.5" spans="1:4">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>310026</v>
@@ -12240,7 +12871,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="95" ht="16.5" spans="1:4">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>310027</v>
@@ -12252,7 +12883,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="96" ht="16.5" spans="1:4">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>310028</v>
@@ -12264,7 +12895,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="97" ht="16.5" spans="1:4">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>310029</v>
@@ -12276,7 +12907,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="98" ht="16.5" spans="1:4">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>310030</v>
@@ -12288,7 +12919,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="99" ht="16.5" spans="1:4">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>310031</v>
@@ -12300,7 +12931,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="100" ht="16.5" spans="1:4">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>310032</v>
@@ -12312,7 +12943,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="101" ht="16.5" spans="1:4">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>310033</v>
@@ -12324,7 +12955,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="102" ht="16.5" spans="1:4">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>310034</v>
@@ -12336,7 +12967,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="103" ht="16.5" spans="1:4">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>310035</v>
@@ -12348,7 +12979,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="104" ht="16.5" spans="1:4">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>310036</v>
@@ -12360,7 +12991,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="105" ht="16.5" spans="1:4">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>310037</v>
@@ -12372,7 +13003,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="106" ht="16.5" spans="1:4">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>310038</v>
@@ -12384,7 +13015,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="107" ht="16.5" spans="1:4">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>310039</v>
@@ -12396,7 +13027,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="108" ht="16.5" spans="1:4">
       <c r="B108" s="1">
         <v>100000</v>
       </c>
@@ -12407,7 +13038,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="109" ht="16.5" spans="1:4">
       <c r="B109" s="1">
         <v>100001</v>
       </c>
@@ -12418,7 +13049,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="110" ht="16.5" spans="1:4">
       <c r="B110" s="1">
         <v>100002</v>
       </c>
@@ -12429,7 +13060,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="111" ht="16.5" spans="1:4">
       <c r="B111" s="1">
         <v>100003</v>
       </c>
@@ -12440,7 +13071,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="112" ht="16.5" spans="1:4">
       <c r="B112" s="1">
         <v>100004</v>
       </c>
@@ -12451,7 +13082,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="113" ht="16.5" spans="2:4">
       <c r="B113" s="1">
         <v>100005</v>
       </c>
@@ -12462,7 +13093,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="114" ht="16.5" spans="2:4">
       <c r="B114" s="1">
         <v>100006</v>
       </c>
@@ -12473,7 +13104,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="115" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="115" ht="16.5" spans="2:4">
       <c r="B115" s="1">
         <v>100007</v>
       </c>
@@ -12484,7 +13115,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="116" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="116" ht="16.5" spans="2:4">
       <c r="B116" s="1">
         <v>100008</v>
       </c>
@@ -12495,7 +13126,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="117" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="117" ht="16.5" spans="2:4">
       <c r="B117" s="1">
         <v>100009</v>
       </c>
@@ -12506,7 +13137,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="118" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="118" ht="16.5" spans="2:4">
       <c r="B118" s="1">
         <v>100010</v>
       </c>
@@ -12517,7 +13148,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="119" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="119" ht="16.5" spans="2:4">
       <c r="B119" s="1">
         <v>100011</v>
       </c>
@@ -12528,7 +13159,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="120" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="120" ht="16.5" spans="2:4">
       <c r="B120" s="1">
         <v>100012</v>
       </c>
@@ -12539,7 +13170,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="121" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="121" ht="16.5" spans="2:4">
       <c r="B121" s="1">
         <v>100013</v>
       </c>
@@ -12550,7 +13181,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="122" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="122" ht="16.5" spans="2:4">
       <c r="B122" s="1">
         <v>100014</v>
       </c>
@@ -12561,7 +13192,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="123" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="123" ht="16.5" spans="2:4">
       <c r="B123" s="1">
         <v>100015</v>
       </c>
@@ -12572,7 +13203,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="124" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="124" ht="16.5" spans="2:4">
       <c r="B124" s="1">
         <v>100016</v>
       </c>
@@ -12583,7 +13214,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="125" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="125" ht="16.5" spans="2:4">
       <c r="B125" s="1">
         <v>100017</v>
       </c>
@@ -12594,7 +13225,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="126" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="126" ht="16.5" spans="2:4">
       <c r="B126" s="1">
         <v>100018</v>
       </c>
@@ -12605,7 +13236,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="127" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="127" ht="16.5" spans="2:4">
       <c r="B127" s="1">
         <v>100019</v>
       </c>
@@ -12616,7 +13247,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="128" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="128" ht="16.5" spans="2:4">
       <c r="B128" s="1">
         <v>100020</v>
       </c>
@@ -12627,7 +13258,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="129" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="129" ht="16.5" spans="2:4">
       <c r="B129" s="1">
         <v>100021</v>
       </c>
@@ -12638,7 +13269,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="130" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="130" ht="16.5" spans="2:4">
       <c r="B130" s="1">
         <v>100022</v>
       </c>
@@ -12649,7 +13280,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="131" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="131" ht="16.5" spans="2:4">
       <c r="B131" s="1">
         <v>100023</v>
       </c>
@@ -12660,7 +13291,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="132" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" ht="16.5" spans="2:4">
       <c r="B132" s="1">
         <v>100024</v>
       </c>
@@ -12671,7 +13302,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="133" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" ht="16.5" spans="2:4">
       <c r="B133" s="1">
         <v>100025</v>
       </c>
@@ -12682,7 +13313,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="134" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="134" ht="16.5" spans="2:4">
       <c r="B134" s="1">
         <v>100026</v>
       </c>
@@ -12693,7 +13324,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="135" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" ht="16.5" spans="2:4">
       <c r="B135" s="1">
         <v>100027</v>
       </c>
@@ -12704,7 +13335,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="136" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" ht="16.5" spans="2:4">
       <c r="B136" s="1">
         <v>100028</v>
       </c>
@@ -12715,7 +13346,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="137" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" ht="16.5" spans="2:4">
       <c r="B137" s="1">
         <v>100029</v>
       </c>
@@ -12726,7 +13357,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="138" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="138" ht="16.5" spans="2:4">
       <c r="B138" s="1">
         <v>100030</v>
       </c>
@@ -12737,7 +13368,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="139" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" ht="16.5" spans="2:4">
       <c r="B139" s="1">
         <v>100031</v>
       </c>
@@ -12748,7 +13379,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="140" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" ht="16.5" spans="2:4">
       <c r="B140" s="1">
         <v>100032</v>
       </c>
@@ -12759,7 +13390,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="141" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="141" ht="16.5" spans="2:4">
       <c r="B141" s="1">
         <v>100033</v>
       </c>
@@ -12770,7 +13401,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="142" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="142" ht="16.5" spans="2:4">
       <c r="B142" s="1">
         <v>100034</v>
       </c>
@@ -12781,7 +13412,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="143" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="143" ht="16.5" spans="2:4">
       <c r="B143" s="1">
         <v>100035</v>
       </c>
@@ -12792,7 +13423,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="144" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="144" ht="16.5" spans="2:4">
       <c r="B144" s="1">
         <v>100036</v>
       </c>
@@ -12803,7 +13434,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="145" ht="16.5" spans="2:4">
       <c r="B145" s="1">
         <v>100037</v>
       </c>
@@ -12814,7 +13445,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="146" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="146" ht="16.5" spans="2:4">
       <c r="B146" s="1">
         <v>100038</v>
       </c>
@@ -12825,7 +13456,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="147" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="147" ht="16.5" spans="2:4">
       <c r="B147" s="1">
         <v>100039</v>
       </c>
@@ -12836,7 +13467,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="148" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="148" ht="16.5" spans="2:4">
       <c r="B148" s="1">
         <v>100040</v>
       </c>
@@ -12847,7 +13478,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="149" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="149" ht="16.5" spans="2:4">
       <c r="B149" s="1">
         <v>100041</v>
       </c>
@@ -12858,7 +13489,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="150" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="150" ht="16.5" spans="2:4">
       <c r="B150" s="1">
         <v>100042</v>
       </c>
@@ -12869,7 +13500,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="151" ht="16.5" spans="2:4">
       <c r="B151" s="1">
         <v>100043</v>
       </c>
@@ -12880,7 +13511,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="152" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="152" ht="16.5" spans="2:4">
       <c r="B152" s="1">
         <v>100044</v>
       </c>
@@ -12891,7 +13522,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="153" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="153" ht="16.5" spans="2:4">
       <c r="B153" s="1">
         <v>100045</v>
       </c>
@@ -12902,7 +13533,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="154" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="154" ht="16.5" spans="2:4">
       <c r="B154" s="1">
         <v>100046</v>
       </c>
@@ -12913,7 +13544,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="155" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="155" ht="16.5" spans="2:4">
       <c r="B155" s="1">
         <v>100047</v>
       </c>
@@ -12924,7 +13555,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="156" ht="16.5" spans="2:4">
       <c r="B156" s="1">
         <v>100048</v>
       </c>
@@ -12935,7 +13566,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="157" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="157" ht="16.5" spans="2:4">
       <c r="B157" s="1">
         <v>100049</v>
       </c>
@@ -12946,7 +13577,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="158" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="158" ht="16.5" spans="2:4">
       <c r="B158" s="1">
         <v>100051</v>
       </c>
@@ -12957,7 +13588,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="159" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="159" ht="16.5" spans="2:4">
       <c r="B159" s="1">
         <v>100052</v>
       </c>
@@ -12968,7 +13599,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="160" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="160" ht="16.5" spans="2:4">
       <c r="B160" s="1">
         <v>100053</v>
       </c>
@@ -12979,7 +13610,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="161" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="161" ht="16.5" spans="2:4">
       <c r="B161" s="1">
         <v>100054</v>
       </c>
@@ -12990,7 +13621,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="162" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="162" ht="16.5" spans="2:4">
       <c r="B162" s="1">
         <v>100055</v>
       </c>
@@ -13001,692 +13632,612 @@
         <v>355</v>
       </c>
     </row>
-    <row r="163" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="163" ht="16.5" spans="2:4">
       <c r="B163" s="1">
+        <v>220000</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="164" ht="16.5" spans="2:4">
+      <c r="B164" s="1">
+        <v>220001</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="165" ht="16.5" spans="2:4">
+      <c r="B165" s="1">
+        <v>220002</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="166" ht="16.5" spans="2:4">
+      <c r="B166" s="1">
+        <v>220003</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167" ht="16.5" spans="2:4">
+      <c r="B167" s="1">
+        <v>220004</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="168" ht="16.5" spans="2:4">
+      <c r="B168" s="1">
+        <v>220005</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="169" ht="16.5" spans="2:4">
+      <c r="B169" s="1">
         <v>220006</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C169" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="D169" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="164" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B164" s="1">
+    <row r="170" ht="16.5" spans="2:4">
+      <c r="B170" s="1">
         <v>220007</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="D170" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="165" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B165" s="1">
+    <row r="171" ht="16.5" spans="2:4">
+      <c r="B171" s="1">
         <v>220008</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D171" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="166" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B166" s="1">
+    <row r="172" ht="16.5" spans="2:4">
+      <c r="B172" s="1">
         <v>220009</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="D172" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="167" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B167" s="1">
-        <v>300000</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B168" s="1">
-        <v>300001</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B169" s="1">
-        <v>300002</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B170" s="1">
-        <v>300003</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B171" s="1">
-        <v>300004</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B172" s="1">
-        <v>300005</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="173" ht="16.5" spans="2:4">
       <c r="B173" s="1">
-        <v>300006</v>
+        <v>130000</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="174" ht="16.5" spans="2:4">
       <c r="B174" s="1">
-        <v>300007</v>
+        <v>130001</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="2:4">
       <c r="B175" s="1">
-        <v>300008</v>
+        <v>130002</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="2:4">
       <c r="B176" s="1">
-        <v>300009</v>
+        <v>140000</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="2:4">
       <c r="B177" s="1">
-        <v>130000</v>
+        <v>140001</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="2:4">
       <c r="B178" s="1">
-        <v>130001</v>
+        <v>140002</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="2:4">
       <c r="B179" s="1">
-        <v>130002</v>
+        <v>140003</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="2:4">
       <c r="B180" s="1">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181" ht="16.5" spans="2:4">
       <c r="B181" s="1">
-        <v>140001</v>
+        <v>150001</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="2:4">
       <c r="B182" s="1">
-        <v>140002</v>
+        <v>150002</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" spans="2:4">
       <c r="B183" s="1">
-        <v>140003</v>
+        <v>150003</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="184" ht="16.5" spans="2:4">
       <c r="B184" s="1">
-        <v>150000</v>
+        <v>150004</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="185" ht="16.5" spans="2:4">
       <c r="B185" s="1">
-        <v>150001</v>
+        <v>150005</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="186" ht="16.5" spans="2:4">
       <c r="B186" s="1">
-        <v>150002</v>
+        <v>150006</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="187" ht="16.5" spans="2:4">
       <c r="B187" s="1">
-        <v>150003</v>
+        <v>150007</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="188" ht="16.5" spans="2:4">
       <c r="B188" s="1">
-        <v>150004</v>
+        <v>150008</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="189" ht="16.5" spans="2:4">
       <c r="B189" s="1">
-        <v>150005</v>
+        <v>150009</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B190" s="1">
-        <v>150006</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B191" s="1">
-        <v>150007</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B192" s="1">
-        <v>150008</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="193" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B193" s="1">
-        <v>150009</v>
-      </c>
-      <c r="C193" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="194" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-    </row>
-    <row r="195" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-    </row>
-    <row r="196" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
-    </row>
-    <row r="197" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
-    </row>
-    <row r="198" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
-    </row>
-    <row r="199" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
-    </row>
-    <row r="200" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="D189" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="200" ht="16.5" spans="2:4">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
     </row>
-    <row r="201" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="201" ht="16.5" spans="2:4">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
     </row>
-    <row r="202" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="202" ht="16.5" spans="2:4">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
     </row>
-    <row r="203" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="203" ht="16.5" spans="2:4">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
     </row>
-    <row r="204" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="204" ht="16.5" spans="2:4">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
     </row>
-    <row r="205" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="205" ht="16.5" spans="2:4">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
     </row>
-    <row r="206" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="206" ht="16.5" spans="2:4">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
     </row>
-    <row r="207" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="207" ht="16.5" spans="2:4">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
     </row>
-    <row r="208" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="208" ht="16.5" spans="2:4">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
     </row>
-    <row r="209" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="209" ht="16.5" spans="2:4">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
     </row>
-    <row r="210" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="210" ht="16.5" spans="2:4">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
     </row>
-    <row r="211" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="211" ht="16.5" spans="2:4">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
     </row>
-    <row r="212" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="212" ht="16.5" spans="2:4">
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
     </row>
-    <row r="213" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="213" ht="16.5" spans="2:4">
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
     </row>
-    <row r="214" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="214" ht="16.5" spans="2:4">
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
     </row>
-    <row r="215" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="215" ht="16.5" spans="2:4">
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
     </row>
-    <row r="216" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="216" ht="16.5" spans="2:4">
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
     </row>
-    <row r="217" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="217" ht="16.5" spans="2:4">
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
     </row>
-    <row r="218" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="218" ht="16.5" spans="2:4">
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
     </row>
-    <row r="219" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="219" ht="16.5" spans="2:4">
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
     </row>
-    <row r="220" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="220" ht="16.5" spans="2:4">
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
     </row>
-    <row r="221" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="221" ht="16.5" spans="2:4">
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
     </row>
-    <row r="222" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="222" ht="16.5" spans="2:4">
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
     </row>
-    <row r="223" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="223" ht="16.5" spans="2:4">
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
     </row>
-    <row r="224" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="224" ht="16.5" spans="2:4">
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
     </row>
-    <row r="225" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="225" ht="16.5" spans="2:4">
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
     </row>
-    <row r="226" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="226" ht="16.5" spans="2:4">
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
     </row>
-    <row r="227" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="227" ht="16.5" spans="2:4">
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
     </row>
-    <row r="228" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="228" ht="16.5" spans="2:4">
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
     </row>
-    <row r="229" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="229" ht="16.5" spans="2:4">
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
     </row>
-    <row r="230" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="230" ht="16.5" spans="2:4">
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
     </row>
-    <row r="231" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="231" ht="16.5" spans="2:4">
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
     </row>
-    <row r="232" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="232" ht="16.5" spans="2:4">
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
     </row>
-    <row r="233" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="233" ht="16.5" spans="2:4">
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
     </row>
-    <row r="234" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="234" ht="16.5" spans="2:4">
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
     </row>
-    <row r="235" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="235" ht="16.5" spans="2:4">
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
     </row>
-    <row r="236" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="236" ht="16.5" spans="2:4">
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
     </row>
-    <row r="237" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="237" ht="16.5" spans="2:4">
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
     </row>
-    <row r="238" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="238" ht="16.5" spans="2:4">
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
     </row>
-    <row r="239" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="239" ht="16.5" spans="2:4">
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
     </row>
-    <row r="240" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="240" ht="16.5" spans="2:4">
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
     </row>
-    <row r="241" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="241" ht="16.5" spans="2:4">
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
     </row>
-    <row r="242" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="242" ht="16.5" spans="2:4">
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
     </row>
-    <row r="243" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="243" ht="16.5" spans="2:4">
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
     </row>
-    <row r="244" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="244" ht="16.5" spans="2:4">
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
     </row>
-    <row r="245" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="245" ht="16.5" spans="2:4">
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
     </row>
-    <row r="246" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="246" ht="16.5" spans="2:4">
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
     </row>
-    <row r="247" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="247" ht="16.5" spans="2:4">
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
     </row>
-    <row r="248" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="248" ht="16.5" spans="2:4">
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
     </row>
-    <row r="249" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="249" ht="16.5" spans="2:4">
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
     </row>
-    <row r="250" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="250" ht="16.5" spans="2:4">
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
     </row>
-    <row r="251" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="251" ht="16.5" spans="2:4">
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
     </row>
-    <row r="252" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="252" ht="16.5" spans="2:4">
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
     </row>
-    <row r="253" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="253" ht="16.5" spans="2:4">
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
     </row>
-    <row r="254" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="254" ht="16.5" spans="2:4">
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
     </row>
-    <row r="255" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="255" ht="16.5" spans="2:4">
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
     </row>
-    <row r="256" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="256" ht="16.5" spans="2:4">
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
     </row>
-    <row r="257" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="257" ht="16.5" spans="2:4">
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
     </row>
-    <row r="258" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="258" ht="16.5" spans="2:4">
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
     </row>
-    <row r="259" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B259" s="1">
-        <v>310039</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C260" s="9"/>
-    </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C261" s="9"/>
+    <row r="259" ht="16.5" spans="2:4">
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+    </row>
+    <row r="260" spans="2:4">
+      <c r="C260" s="5"/>
+    </row>
+    <row r="261" spans="2:4">
+      <c r="C261" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.78749999999999998" header="0.39374999999999999" footer="0.39374999999999999"/>
+  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.39375" footer="0.39375"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA54460-1A5E-4153-B1D1-E26872E84603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" activeTab="3"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="30580" windowHeight="18680" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -1084,7 +1090,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Item</t>
     </r>
@@ -1092,7 +1098,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>MaterialType</t>
     </r>
@@ -1131,14 +1137,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1149,178 +1149,37 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1333,194 +1192,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1543,253 +1216,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1799,9 +1230,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1825,61 +1253,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2132,25 +1516,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R240"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="29.0833333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="33.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="58.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="42.3333333333333" style="5" customWidth="1"/>
-    <col min="7" max="7" width="21.1666666666667" customWidth="1"/>
-    <col min="9" max="9" width="16.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="58.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" customWidth="1"/>
     <col min="10" max="10" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2182,7 +1566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2214,7 +1598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -2246,7 +1630,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>100000</v>
@@ -2279,7 +1663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>100001</v>
@@ -2312,7 +1696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>100002</v>
@@ -2345,7 +1729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>100003</v>
@@ -2378,7 +1762,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>100004</v>
@@ -2411,7 +1795,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>100005</v>
@@ -2444,7 +1828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>100006</v>
@@ -2477,7 +1861,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>100007</v>
@@ -2510,7 +1894,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>100008</v>
@@ -2543,7 +1927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>100009</v>
@@ -2576,7 +1960,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>100010</v>
@@ -2609,7 +1993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>100011</v>
@@ -2642,7 +2026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>100012</v>
@@ -2675,7 +2059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:18">
+    <row r="17" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>100013</v>
@@ -2708,7 +2092,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:18">
+    <row r="18" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>100014</v>
@@ -2741,7 +2125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:18">
+    <row r="19" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>100015</v>
@@ -2774,7 +2158,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:18">
+    <row r="20" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>100016</v>
@@ -2807,7 +2191,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:18">
+    <row r="21" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>100017</v>
@@ -2840,7 +2224,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:18">
+    <row r="22" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>100018</v>
@@ -2873,7 +2257,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:18">
+    <row r="23" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>100019</v>
@@ -2905,12 +2289,12 @@
       <c r="J23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:18">
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+    </row>
+    <row r="24" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>100020</v>
@@ -2943,7 +2327,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:18">
+    <row r="25" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>100021</v>
@@ -2976,7 +2360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:18">
+    <row r="26" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>100022</v>
@@ -3009,7 +2393,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:18">
+    <row r="27" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>100023</v>
@@ -3042,7 +2426,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:18">
+    <row r="28" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>100024</v>
@@ -3075,7 +2459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:18">
+    <row r="29" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>100025</v>
@@ -3108,7 +2492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:18">
+    <row r="30" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>100026</v>
@@ -3141,7 +2525,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:18">
+    <row r="31" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>100027</v>
@@ -3174,7 +2558,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:18">
+    <row r="32" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>100028</v>
@@ -3207,7 +2591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:10">
+    <row r="33" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>100029</v>
@@ -3240,7 +2624,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:10">
+    <row r="34" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>100030</v>
@@ -3273,7 +2657,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:10">
+    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>100031</v>
@@ -3306,7 +2690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:10">
+    <row r="36" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>100032</v>
@@ -3339,7 +2723,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="1:10">
+    <row r="37" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>100033</v>
@@ -3372,7 +2756,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" ht="16.5" spans="1:10">
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>100034</v>
@@ -3405,7 +2789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:10">
+    <row r="39" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>100035</v>
@@ -3438,7 +2822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" ht="16.5" spans="1:10">
+    <row r="40" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>100036</v>
@@ -3471,7 +2855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" ht="16.5" spans="1:10">
+    <row r="41" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>100037</v>
@@ -3504,7 +2888,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" ht="16.5" spans="1:10">
+    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>100038</v>
@@ -3537,7 +2921,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" ht="16.5" spans="1:10">
+    <row r="43" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>100039</v>
@@ -3570,7 +2954,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:10">
+    <row r="44" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>100040</v>
@@ -3603,7 +2987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:10">
+    <row r="45" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>100041</v>
@@ -3636,7 +3020,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:10">
+    <row r="46" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>100042</v>
@@ -3669,7 +3053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:10">
+    <row r="47" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>100043</v>
@@ -3702,7 +3086,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:10">
+    <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>100044</v>
@@ -3735,7 +3119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:10">
+    <row r="49" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>100045</v>
@@ -3768,7 +3152,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:10">
+    <row r="50" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>100046</v>
@@ -3801,7 +3185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:10">
+    <row r="51" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>100047</v>
@@ -3834,7 +3218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:10">
+    <row r="52" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>100048</v>
@@ -3867,7 +3251,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:10">
+    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>100049</v>
@@ -3900,7 +3284,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:10">
+    <row r="54" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>100051</v>
@@ -3933,7 +3317,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:10">
+    <row r="55" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>100052</v>
@@ -3966,7 +3350,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:10">
+    <row r="56" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>100053</v>
@@ -3999,7 +3383,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:10">
+    <row r="57" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>100054</v>
@@ -4032,7 +3416,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:10">
+    <row r="58" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>100055</v>
@@ -4065,7 +3449,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:10">
+    <row r="59" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>110000</v>
@@ -4098,7 +3482,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:10">
+    <row r="60" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>110001</v>
@@ -4131,7 +3515,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:10">
+    <row r="61" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>110002</v>
@@ -4164,7 +3548,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:10">
+    <row r="62" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>110003</v>
@@ -4197,7 +3581,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:10">
+    <row r="63" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>110004</v>
@@ -4230,7 +3614,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:10">
+    <row r="64" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>110005</v>
@@ -4263,7 +3647,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:10">
+    <row r="65" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>110006</v>
@@ -4296,7 +3680,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:10">
+    <row r="66" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>110007</v>
@@ -4329,7 +3713,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:10">
+    <row r="67" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>110008</v>
@@ -4362,7 +3746,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" ht="16.5" spans="1:10">
+    <row r="68" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>110009</v>
@@ -4395,7 +3779,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:10">
+    <row r="69" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>110010</v>
@@ -4428,7 +3812,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" ht="16.5" spans="1:10">
+    <row r="70" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>110011</v>
@@ -4461,7 +3845,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" ht="16.5" spans="1:10">
+    <row r="71" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>110012</v>
@@ -4494,7 +3878,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" ht="16.5" spans="1:10">
+    <row r="72" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>110013</v>
@@ -4527,7 +3911,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" ht="16.5" spans="1:10">
+    <row r="73" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>110014</v>
@@ -4560,7 +3944,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" ht="16.5" spans="1:10">
+    <row r="74" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>110015</v>
@@ -4593,7 +3977,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:10">
+    <row r="75" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>110016</v>
@@ -4626,7 +4010,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" ht="16.5" spans="1:10">
+    <row r="76" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>110017</v>
@@ -4659,7 +4043,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" ht="16.5" spans="1:10">
+    <row r="77" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>110018</v>
@@ -4692,7 +4076,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:10">
+    <row r="78" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>110019</v>
@@ -4725,7 +4109,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:10">
+    <row r="79" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>110020</v>
@@ -4758,7 +4142,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:10">
+    <row r="80" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>110021</v>
@@ -4791,7 +4175,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" ht="16.5" spans="1:10">
+    <row r="81" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>110022</v>
@@ -4824,7 +4208,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" ht="16.5" spans="1:10">
+    <row r="82" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>110023</v>
@@ -4857,7 +4241,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" ht="16.5" spans="1:10">
+    <row r="83" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>110024</v>
@@ -4890,7 +4274,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" ht="16.5" spans="1:10">
+    <row r="84" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>110025</v>
@@ -4923,7 +4307,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" ht="16.5" spans="1:10">
+    <row r="85" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>110026</v>
@@ -4956,7 +4340,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="86" ht="16.5" spans="1:10">
+    <row r="86" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>110027</v>
@@ -4989,7 +4373,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="87" ht="16.5" spans="1:10">
+    <row r="87" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>110028</v>
@@ -5022,7 +4406,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" ht="16.5" spans="1:10">
+    <row r="88" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>110029</v>
@@ -5055,7 +4439,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" ht="16.5" spans="1:10">
+    <row r="89" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>110030</v>
@@ -5088,7 +4472,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="90" ht="16.5" spans="1:10">
+    <row r="90" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>110031</v>
@@ -5121,7 +4505,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" ht="16.5" spans="1:10">
+    <row r="91" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>110032</v>
@@ -5154,7 +4538,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="92" ht="16.5" spans="1:10">
+    <row r="92" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>110033</v>
@@ -5187,7 +4571,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" ht="16.5" spans="1:10">
+    <row r="93" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>110034</v>
@@ -5220,7 +4604,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="94" ht="16.5" spans="1:10">
+    <row r="94" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>110035</v>
@@ -5253,7 +4637,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="95" ht="16.5" spans="1:10">
+    <row r="95" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>110036</v>
@@ -5286,7 +4670,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="96" ht="16.5" spans="1:10">
+    <row r="96" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>110037</v>
@@ -5319,7 +4703,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="97" ht="16.5" spans="1:10">
+    <row r="97" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>110038</v>
@@ -5352,7 +4736,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="98" ht="16.5" spans="1:10">
+    <row r="98" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>110039</v>
@@ -5385,7 +4769,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="99" ht="16.5" spans="1:10">
+    <row r="99" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>120000</v>
@@ -5418,7 +4802,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" ht="16.5" spans="1:10">
+    <row r="100" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>120001</v>
@@ -5451,7 +4835,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="101" ht="16.5" spans="1:10">
+    <row r="101" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>120002</v>
@@ -5484,7 +4868,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="102" ht="16.5" spans="1:10">
+    <row r="102" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>120003</v>
@@ -5517,7 +4901,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:10">
+    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>120004</v>
@@ -5550,7 +4934,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:10">
+    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>120005</v>
@@ -5583,7 +4967,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:10">
+    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>120006</v>
@@ -5616,7 +5000,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:10">
+    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>120007</v>
@@ -5649,7 +5033,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:10">
+    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>120008</v>
@@ -5682,7 +5066,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:10">
+    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
         <v>120009</v>
@@ -5715,7 +5099,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:10">
+    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
         <v>120010</v>
@@ -5748,7 +5132,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="110" ht="16.5" spans="1:10">
+    <row r="110" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
         <v>120011</v>
@@ -5781,7 +5165,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="111" ht="16.5" spans="1:10">
+    <row r="111" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
         <v>120012</v>
@@ -5814,7 +5198,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="112" ht="16.5" spans="1:10">
+    <row r="112" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
         <v>120013</v>
@@ -5847,7 +5231,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="113" ht="16.5" spans="1:10">
+    <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
         <v>120014</v>
@@ -5880,7 +5264,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="114" ht="16.5" spans="1:10">
+    <row r="114" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
         <v>120015</v>
@@ -5913,7 +5297,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" ht="16.5" spans="1:10">
+    <row r="115" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
         <v>120016</v>
@@ -5946,7 +5330,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="116" ht="16.5" spans="1:10">
+    <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
         <v>120017</v>
@@ -5979,7 +5363,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="117" ht="16.5" spans="1:10">
+    <row r="117" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
         <v>120018</v>
@@ -6012,7 +5396,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="118" ht="16.5" spans="1:10">
+    <row r="118" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
         <v>120019</v>
@@ -6045,7 +5429,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="119" ht="16.5" spans="1:10">
+    <row r="119" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
         <v>120020</v>
@@ -6078,7 +5462,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="120" ht="16.5" spans="1:10">
+    <row r="120" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
         <v>120021</v>
@@ -6111,7 +5495,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="121" ht="16.5" spans="1:10">
+    <row r="121" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
         <v>120022</v>
@@ -6144,7 +5528,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="122" ht="16.5" spans="1:10">
+    <row r="122" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
         <v>120023</v>
@@ -6177,7 +5561,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="123" ht="16.5" spans="1:10">
+    <row r="123" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
         <v>120024</v>
@@ -6210,7 +5594,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="124" ht="16.5" spans="1:10">
+    <row r="124" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
         <v>120025</v>
@@ -6243,7 +5627,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="125" ht="16.5" spans="1:10">
+    <row r="125" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
         <v>120026</v>
@@ -6276,7 +5660,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="126" ht="16.5" spans="1:10">
+    <row r="126" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
         <v>120027</v>
@@ -6309,7 +5693,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="127" ht="16.5" spans="1:10">
+    <row r="127" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
         <v>120028</v>
@@ -6342,7 +5726,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="128" ht="16.5" spans="1:10">
+    <row r="128" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
         <v>120029</v>
@@ -6375,7 +5759,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="129" ht="16.5" spans="1:10">
+    <row r="129" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
         <v>120030</v>
@@ -6408,7 +5792,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="130" ht="16.5" spans="1:10">
+    <row r="130" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
         <v>120031</v>
@@ -6441,7 +5825,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" ht="16.5" spans="1:10">
+    <row r="131" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
         <v>120032</v>
@@ -6474,7 +5858,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="132" ht="16.5" spans="1:10">
+    <row r="132" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
         <v>120033</v>
@@ -6507,7 +5891,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="133" ht="16.5" spans="1:10">
+    <row r="133" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
         <v>120034</v>
@@ -6540,7 +5924,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="134" ht="16.5" spans="1:10">
+    <row r="134" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
         <v>120035</v>
@@ -6573,7 +5957,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="135" ht="16.5" spans="1:10">
+    <row r="135" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
         <v>120036</v>
@@ -6606,7 +5990,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="136" ht="16.5" spans="1:10">
+    <row r="136" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
         <v>120037</v>
@@ -6639,7 +6023,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" ht="16.5" spans="1:10">
+    <row r="137" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
         <v>120038</v>
@@ -6672,7 +6056,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="138" ht="16.5" spans="1:10">
+    <row r="138" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
         <v>120039</v>
@@ -6705,7 +6089,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" ht="16.5" spans="1:10">
+    <row r="139" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
         <v>120040</v>
@@ -6738,7 +6122,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" ht="16.5" spans="1:10">
+    <row r="140" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
         <v>200000</v>
@@ -6771,7 +6155,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="141" ht="16.5" spans="1:10">
+    <row r="141" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
         <v>200001</v>
@@ -6804,7 +6188,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="142" ht="16.5" spans="1:10">
+    <row r="142" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
         <v>200002</v>
@@ -6837,7 +6221,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" ht="16.5" spans="1:10">
+    <row r="143" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
         <v>200003</v>
@@ -6870,7 +6254,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" ht="16.5" spans="1:10">
+    <row r="144" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
         <v>210000</v>
@@ -6903,7 +6287,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" ht="16.5" spans="1:10">
+    <row r="145" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
         <v>210001</v>
@@ -6936,7 +6320,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="146" ht="16.5" spans="1:10">
+    <row r="146" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
         <v>210002</v>
@@ -6969,7 +6353,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="147" ht="16.5" spans="1:10">
+    <row r="147" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
         <v>210003</v>
@@ -7002,7 +6386,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="148" ht="16.5" spans="1:10">
+    <row r="148" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
         <v>210004</v>
@@ -7035,7 +6419,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="149" ht="16.5" spans="1:10">
+    <row r="149" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
         <v>210005</v>
@@ -7068,7 +6452,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" ht="16.5" spans="1:10">
+    <row r="150" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
         <v>210006</v>
@@ -7101,7 +6485,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="151" ht="16.5" spans="1:10">
+    <row r="151" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
         <v>210007</v>
@@ -7134,7 +6518,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="152" ht="16.5" spans="1:10">
+    <row r="152" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
         <v>210008</v>
@@ -7167,7 +6551,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="153" ht="16.5" spans="1:10">
+    <row r="153" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
         <v>210009</v>
@@ -7200,7 +6584,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" ht="16.5" spans="1:10">
+    <row r="154" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
         <v>210010</v>
@@ -7233,7 +6617,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" ht="16.5" spans="1:10">
+    <row r="155" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
         <v>210011</v>
@@ -7266,7 +6650,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" ht="16.5" spans="1:10">
+    <row r="156" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
         <v>210012</v>
@@ -7299,7 +6683,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="157" ht="16.5" spans="1:10">
+    <row r="157" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
         <v>210013</v>
@@ -7332,7 +6716,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="158" ht="16.5" spans="1:10">
+    <row r="158" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
         <v>210014</v>
@@ -7365,7 +6749,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="159" ht="16.5" spans="1:10">
+    <row r="159" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
         <v>210015</v>
@@ -7398,7 +6782,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="160" ht="16.5" spans="1:10">
+    <row r="160" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
         <v>210016</v>
@@ -7431,7 +6815,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" ht="16.5" spans="1:10">
+    <row r="161" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
         <v>210017</v>
@@ -7464,7 +6848,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" ht="16.5" spans="1:10">
+    <row r="162" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
         <v>210018</v>
@@ -7497,7 +6881,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" ht="16.5" spans="1:10">
+    <row r="163" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
         <v>210019</v>
@@ -7530,7 +6914,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" ht="16.5" spans="1:10">
+    <row r="164" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
         <v>220000</v>
@@ -7563,7 +6947,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" ht="16.5" spans="1:10">
+    <row r="165" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
         <v>220001</v>
@@ -7596,7 +6980,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166" ht="16.5" spans="1:10">
+    <row r="166" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
         <v>220002</v>
@@ -7629,7 +7013,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="167" ht="16.5" spans="1:10">
+    <row r="167" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
         <v>220003</v>
@@ -7662,7 +7046,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="168" ht="16.5" spans="1:10">
+    <row r="168" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
         <v>220004</v>
@@ -7695,7 +7079,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="169" ht="16.5" spans="1:10">
+    <row r="169" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
         <v>220005</v>
@@ -7728,7 +7112,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" ht="16.5" spans="1:10">
+    <row r="170" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
         <v>220006</v>
@@ -7761,7 +7145,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="171" ht="16.5" spans="1:10">
+    <row r="171" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
         <v>220007</v>
@@ -7794,7 +7178,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="172" ht="16.5" spans="1:10">
+    <row r="172" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
         <v>220008</v>
@@ -7827,7 +7211,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="173" ht="16.5" spans="1:10">
+    <row r="173" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
         <v>220009</v>
@@ -7860,7 +7244,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="174" ht="16.5" spans="1:10">
+    <row r="174" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
         <v>300000</v>
@@ -7893,7 +7277,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175" ht="16.5" spans="1:10">
+    <row r="175" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
         <v>300001</v>
@@ -7926,7 +7310,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" ht="16.5" spans="1:10">
+    <row r="176" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
         <v>300002</v>
@@ -7959,7 +7343,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="177" ht="16.5" spans="1:10">
+    <row r="177" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
         <v>300003</v>
@@ -7992,7 +7376,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="178" ht="16.5" spans="1:10">
+    <row r="178" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
         <v>300004</v>
@@ -8025,7 +7409,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="179" ht="16.5" spans="1:10">
+    <row r="179" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
         <v>300005</v>
@@ -8058,7 +7442,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="180" ht="16.5" spans="1:10">
+    <row r="180" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
         <v>300006</v>
@@ -8091,7 +7475,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="181" ht="16.5" spans="1:10">
+    <row r="181" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
         <v>300007</v>
@@ -8124,7 +7508,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="182" ht="16.5" spans="1:10">
+    <row r="182" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
         <v>300008</v>
@@ -8157,7 +7541,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="183" ht="16.5" spans="1:10">
+    <row r="183" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
         <v>300009</v>
@@ -8190,7 +7574,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="184" ht="16.5" spans="1:10">
+    <row r="184" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
         <v>130000</v>
@@ -8223,7 +7607,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="185" ht="16.5" spans="1:10">
+    <row r="185" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
         <v>130001</v>
@@ -8256,7 +7640,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="186" ht="16.5" spans="1:10">
+    <row r="186" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
         <v>130002</v>
@@ -8289,7 +7673,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="187" ht="16.5" spans="1:10">
+    <row r="187" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
         <v>140000</v>
@@ -8322,7 +7706,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="188" ht="16.5" spans="1:10">
+    <row r="188" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
         <v>140001</v>
@@ -8355,7 +7739,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="189" ht="16.5" spans="1:10">
+    <row r="189" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
         <v>140002</v>
@@ -8388,7 +7772,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="190" ht="16.5" spans="1:10">
+    <row r="190" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
         <v>140003</v>
@@ -8421,7 +7805,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="191" ht="16.5" spans="1:10">
+    <row r="191" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
         <v>150000</v>
@@ -8454,7 +7838,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="192" ht="16.5" spans="1:10">
+    <row r="192" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
         <v>150001</v>
@@ -8487,7 +7871,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="193" ht="16.5" spans="1:10">
+    <row r="193" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
         <v>150002</v>
@@ -8520,7 +7904,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="194" ht="16.5" spans="1:10">
+    <row r="194" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
         <v>150003</v>
@@ -8553,7 +7937,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="195" ht="16.5" spans="1:10">
+    <row r="195" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
         <v>150004</v>
@@ -8586,7 +7970,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="196" ht="16.5" spans="1:10">
+    <row r="196" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
         <v>150005</v>
@@ -8619,7 +8003,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="197" ht="16.5" spans="1:10">
+    <row r="197" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
         <v>150006</v>
@@ -8652,7 +8036,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="198" ht="16.5" spans="1:10">
+    <row r="198" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
         <v>150007</v>
@@ -8685,7 +8069,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="199" ht="16.5" spans="1:10">
+    <row r="199" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
         <v>150008</v>
@@ -8718,7 +8102,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="200" ht="16.5" spans="1:10">
+    <row r="200" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
         <v>150009</v>
@@ -8751,7 +8135,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" ht="16.5" spans="1:10">
+    <row r="201" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
         <v>310000</v>
@@ -8784,7 +8168,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="202" ht="16.5" spans="1:10">
+    <row r="202" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
         <v>310001</v>
@@ -8817,7 +8201,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="203" ht="16.5" spans="1:10">
+    <row r="203" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
         <v>310002</v>
@@ -8850,7 +8234,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="204" ht="16.5" spans="1:10">
+    <row r="204" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
         <v>310003</v>
@@ -8883,7 +8267,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="205" ht="16.5" spans="1:10">
+    <row r="205" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
         <v>310004</v>
@@ -8916,7 +8300,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="206" ht="16.5" spans="1:10">
+    <row r="206" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
         <v>310005</v>
@@ -8949,7 +8333,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" ht="16.5" spans="1:10">
+    <row r="207" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
         <v>310006</v>
@@ -8982,7 +8366,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="208" ht="16.5" spans="1:10">
+    <row r="208" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
         <v>310007</v>
@@ -9015,7 +8399,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="209" ht="16.5" spans="1:10">
+    <row r="209" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
         <v>310008</v>
@@ -9048,7 +8432,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="210" ht="16.5" spans="1:10">
+    <row r="210" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
         <v>310009</v>
@@ -9081,7 +8465,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="211" ht="16.5" spans="1:10">
+    <row r="211" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
         <v>310010</v>
@@ -9114,7 +8498,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="212" ht="16.5" spans="1:10">
+    <row r="212" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
         <v>310011</v>
@@ -9147,7 +8531,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="213" ht="16.5" spans="1:10">
+    <row r="213" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
         <v>310012</v>
@@ -9180,7 +8564,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="214" ht="16.5" spans="1:10">
+    <row r="214" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
         <v>310013</v>
@@ -9213,7 +8597,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="215" ht="16.5" spans="1:10">
+    <row r="215" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
         <v>310014</v>
@@ -9246,7 +8630,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" ht="16.5" spans="1:10">
+    <row r="216" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
         <v>310015</v>
@@ -9279,7 +8663,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="217" ht="16.5" spans="1:10">
+    <row r="217" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
         <v>310016</v>
@@ -9312,7 +8696,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="218" ht="16.5" spans="1:10">
+    <row r="218" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
         <v>310017</v>
@@ -9345,7 +8729,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="219" ht="16.5" spans="1:10">
+    <row r="219" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
         <v>310018</v>
@@ -9378,7 +8762,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="220" ht="16.5" spans="1:10">
+    <row r="220" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
         <v>310019</v>
@@ -9411,7 +8795,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="221" ht="16.5" spans="1:10">
+    <row r="221" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
         <v>310020</v>
@@ -9444,7 +8828,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="222" ht="16.5" spans="1:10">
+    <row r="222" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
         <v>310021</v>
@@ -9477,7 +8861,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="223" ht="16.5" spans="1:10">
+    <row r="223" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
         <v>310022</v>
@@ -9510,7 +8894,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="224" ht="16.5" spans="1:10">
+    <row r="224" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
         <v>310023</v>
@@ -9543,7 +8927,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="225" ht="16.5" spans="1:10">
+    <row r="225" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
         <v>310024</v>
@@ -9576,7 +8960,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="226" ht="16.5" spans="1:10">
+    <row r="226" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
         <v>310025</v>
@@ -9609,7 +8993,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="227" ht="16.5" spans="1:10">
+    <row r="227" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
         <v>310026</v>
@@ -9642,7 +9026,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="228" ht="16.5" spans="1:10">
+    <row r="228" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
         <v>310027</v>
@@ -9675,7 +9059,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="229" ht="16.5" spans="1:10">
+    <row r="229" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
         <v>310028</v>
@@ -9708,7 +9092,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="230" ht="16.5" spans="1:10">
+    <row r="230" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
         <v>310029</v>
@@ -9741,7 +9125,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="231" ht="16.5" spans="1:10">
+    <row r="231" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
         <v>310030</v>
@@ -9774,7 +9158,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" ht="16.5" spans="1:10">
+    <row r="232" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
         <v>310031</v>
@@ -9807,7 +9191,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" ht="16.5" spans="1:10">
+    <row r="233" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
         <v>310032</v>
@@ -9840,7 +9224,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="234" ht="16.5" spans="1:10">
+    <row r="234" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
         <v>310033</v>
@@ -9873,7 +9257,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" ht="16.5" spans="1:10">
+    <row r="235" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
         <v>310034</v>
@@ -9906,7 +9290,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" ht="16.5" spans="1:10">
+    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
         <v>310035</v>
@@ -9939,7 +9323,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" ht="16.5" spans="1:10">
+    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
         <v>310036</v>
@@ -9972,7 +9356,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" ht="16.5" spans="1:10">
+    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
         <v>310037</v>
@@ -10005,7 +9389,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="239" ht="16.5" spans="1:10">
+    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
         <v>310038</v>
@@ -10038,7 +9422,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="240" ht="16.5" spans="1:10">
+    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
         <v>310039</v>
@@ -10072,30 +9456,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="12.5833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29.0833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.1666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.0833333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.5833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.08203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.08203125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10114,11 +9497,11 @@
       <c r="F1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -10141,7 +9524,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -10164,37 +9547,37 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="B4" s="7">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="B4" s="6">
         <v>120000</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
         <v>297</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B5" s="2">
         <v>120001</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -10203,13 +9586,13 @@
       <c r="G5" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B6" s="2">
         <v>120002</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -10218,13 +9601,13 @@
       <c r="G6" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B7" s="2">
         <v>120003</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -10233,13 +9616,13 @@
       <c r="G7" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B8" s="2">
         <v>120004</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -10248,13 +9631,13 @@
       <c r="G8" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B9" s="2">
         <v>120005</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -10263,13 +9646,13 @@
       <c r="G9" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>120006</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -10278,13 +9661,13 @@
       <c r="G10" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B11" s="2">
         <v>120007</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -10293,13 +9676,13 @@
       <c r="G11" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B12" s="2">
         <v>120008</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -10308,13 +9691,13 @@
       <c r="G12" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>120009</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -10323,13 +9706,13 @@
       <c r="G13" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <v>120010</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -10338,13 +9721,13 @@
       <c r="G14" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>120011</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -10353,13 +9736,13 @@
       <c r="G15" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>120012</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -10368,13 +9751,13 @@
       <c r="G16" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="2:8">
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <v>120013</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -10383,13 +9766,13 @@
       <c r="G17" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="2:8">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>120014</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -10398,13 +9781,13 @@
       <c r="G18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="2:8">
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <v>120015</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -10413,13 +9796,13 @@
       <c r="G19" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="2:8">
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <v>120016</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -10428,13 +9811,13 @@
       <c r="G20" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="2:8">
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="2">
         <v>120017</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -10443,13 +9826,13 @@
       <c r="G21" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="2:8">
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="2">
         <v>120018</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -10458,13 +9841,13 @@
       <c r="G22" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="2:8">
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="2">
         <v>120019</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -10473,13 +9856,13 @@
       <c r="G23" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="2">
         <v>120020</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -10488,13 +9871,13 @@
       <c r="G24" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="2">
         <v>120021</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -10503,13 +9886,13 @@
       <c r="G25" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="2">
         <v>120022</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -10518,13 +9901,13 @@
       <c r="G26" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="2:8">
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <v>120023</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -10533,13 +9916,13 @@
       <c r="G27" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="2:8">
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B28" s="2">
         <v>120024</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -10548,13 +9931,13 @@
       <c r="G28" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="2:8">
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2">
         <v>120025</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -10563,13 +9946,13 @@
       <c r="G29" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="2:8">
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B30" s="2">
         <v>120026</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -10578,13 +9961,13 @@
       <c r="G30" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B31" s="2">
         <v>120027</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -10593,13 +9976,13 @@
       <c r="G31" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="2:8">
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B32" s="2">
         <v>120028</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -10608,13 +9991,13 @@
       <c r="G32" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="2:8">
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B33" s="2">
         <v>120029</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -10623,13 +10006,13 @@
       <c r="G33" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" s="2">
         <v>120030</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -10638,13 +10021,13 @@
       <c r="G34" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="2">
         <v>120031</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -10653,13 +10036,13 @@
       <c r="G35" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B36" s="2">
         <v>120032</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -10668,13 +10051,13 @@
       <c r="G36" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="2:8">
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B37" s="2">
         <v>120033</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -10683,13 +10066,13 @@
       <c r="G37" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="2:8">
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B38" s="2">
         <v>120034</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -10698,13 +10081,13 @@
       <c r="G38" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" spans="2:8">
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B39" s="2">
         <v>120035</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -10713,13 +10096,13 @@
       <c r="G39" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40" spans="2:8">
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B40" s="2">
         <v>120036</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -10728,13 +10111,13 @@
       <c r="G40" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41" spans="2:8">
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B41" s="2">
         <v>120037</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -10743,13 +10126,13 @@
       <c r="G41" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B42" s="2">
         <v>120038</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -10758,13 +10141,13 @@
       <c r="G42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H42" s="7"/>
-    </row>
-    <row r="43" spans="2:8">
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B43" s="2">
         <v>120039</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -10773,13 +10156,13 @@
       <c r="G43" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" spans="2:8">
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B44" s="2">
         <v>120040</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -10788,304 +10171,303 @@
       <c r="G44" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="45" spans="2:8">
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B45"/>
       <c r="C45"/>
       <c r="G45"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B46"/>
       <c r="C46"/>
       <c r="G46"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B47"/>
       <c r="C47"/>
       <c r="G47"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B48"/>
       <c r="C48"/>
       <c r="G48"/>
     </row>
-    <row r="49" spans="2:7">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B49"/>
       <c r="C49"/>
       <c r="G49"/>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B50"/>
       <c r="C50"/>
       <c r="G50"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B51"/>
       <c r="C51"/>
       <c r="G51"/>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B52"/>
       <c r="C52"/>
       <c r="G52"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B53"/>
       <c r="C53"/>
       <c r="G53"/>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B54"/>
       <c r="C54"/>
       <c r="G54"/>
     </row>
-    <row r="55" spans="2:7">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B55"/>
       <c r="C55"/>
       <c r="G55"/>
     </row>
-    <row r="56" spans="2:7">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B56"/>
       <c r="C56"/>
       <c r="G56"/>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B57"/>
       <c r="C57"/>
       <c r="G57"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B58"/>
       <c r="C58"/>
       <c r="G58"/>
     </row>
-    <row r="59" spans="2:7">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B59"/>
       <c r="C59"/>
       <c r="G59"/>
     </row>
-    <row r="60" spans="2:7">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B60"/>
       <c r="C60"/>
       <c r="G60"/>
     </row>
-    <row r="61" spans="2:7">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B61"/>
       <c r="C61"/>
       <c r="G61"/>
     </row>
-    <row r="62" spans="2:7">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B62"/>
       <c r="C62"/>
       <c r="G62"/>
     </row>
-    <row r="63" spans="2:7">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B63"/>
       <c r="C63"/>
       <c r="G63"/>
     </row>
-    <row r="64" spans="2:7">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B64"/>
       <c r="C64"/>
       <c r="G64"/>
     </row>
-    <row r="65" spans="2:7">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B65"/>
       <c r="C65"/>
       <c r="G65"/>
     </row>
-    <row r="66" spans="2:7">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B66"/>
       <c r="C66"/>
       <c r="G66"/>
     </row>
-    <row r="67" spans="2:7">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B67"/>
       <c r="C67"/>
       <c r="G67"/>
     </row>
-    <row r="68" spans="2:7">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B68"/>
       <c r="C68"/>
       <c r="G68"/>
     </row>
-    <row r="69" spans="2:7">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B69"/>
       <c r="C69"/>
       <c r="G69"/>
     </row>
-    <row r="70" spans="2:7">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B70"/>
       <c r="C70"/>
       <c r="G70"/>
     </row>
-    <row r="71" spans="2:7">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B71"/>
       <c r="C71"/>
       <c r="G71"/>
     </row>
-    <row r="72" spans="2:7">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B72"/>
       <c r="C72"/>
       <c r="G72"/>
     </row>
-    <row r="73" spans="2:7">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B73"/>
       <c r="C73"/>
       <c r="G73"/>
     </row>
-    <row r="74" spans="2:7">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B74"/>
       <c r="C74"/>
       <c r="G74"/>
     </row>
-    <row r="75" spans="2:7">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B75"/>
       <c r="C75"/>
       <c r="G75"/>
     </row>
-    <row r="76" spans="2:7">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B76"/>
       <c r="C76"/>
       <c r="G76"/>
     </row>
-    <row r="77" spans="2:7">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B77"/>
       <c r="C77"/>
       <c r="G77"/>
     </row>
-    <row r="78" spans="2:7">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B78"/>
       <c r="C78"/>
       <c r="G78"/>
     </row>
-    <row r="79" spans="2:7">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B79"/>
       <c r="C79"/>
       <c r="G79"/>
     </row>
-    <row r="80" spans="2:7">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B80"/>
       <c r="C80"/>
       <c r="G80"/>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B81"/>
       <c r="C81"/>
       <c r="G81"/>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B82"/>
       <c r="C82"/>
       <c r="G82"/>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B83"/>
       <c r="C83"/>
       <c r="G83"/>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B84"/>
       <c r="C84"/>
       <c r="G84"/>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B85"/>
       <c r="C85"/>
       <c r="G85"/>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B86"/>
       <c r="C86"/>
       <c r="G86"/>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B87"/>
       <c r="C87"/>
       <c r="G87"/>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B88"/>
       <c r="C88"/>
       <c r="G88"/>
     </row>
-    <row r="89" spans="2:7">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B89"/>
       <c r="C89"/>
       <c r="G89"/>
     </row>
-    <row r="90" spans="2:7">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B90"/>
       <c r="C90"/>
       <c r="G90"/>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B91"/>
       <c r="C91"/>
       <c r="G91"/>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B92"/>
       <c r="C92"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="2:7">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B93"/>
       <c r="C93"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B94"/>
       <c r="C94"/>
       <c r="G94"/>
     </row>
-    <row r="95" spans="2:7">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B95"/>
       <c r="C95"/>
       <c r="G95"/>
     </row>
-    <row r="96" spans="2:7">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B96"/>
       <c r="C96"/>
       <c r="G96"/>
     </row>
-    <row r="97" spans="2:7">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B97"/>
       <c r="C97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="2:7">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B98"/>
       <c r="C98"/>
       <c r="G98"/>
     </row>
-    <row r="99" spans="2:7">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B99"/>
       <c r="C99"/>
       <c r="G99"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="29.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.9166666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.9140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11102,7 +10484,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -11119,7 +10501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -11136,7 +10518,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2">
         <v>110000</v>
       </c>
@@ -11150,7 +10532,7 @@
         <v>120001</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B5" s="2">
         <v>110001</v>
       </c>
@@ -11164,7 +10546,7 @@
         <v>120002</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2">
         <v>110002</v>
       </c>
@@ -11178,7 +10560,7 @@
         <v>120003</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B7" s="2">
         <v>110003</v>
       </c>
@@ -11192,7 +10574,7 @@
         <v>120004</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B8" s="2">
         <v>110004</v>
       </c>
@@ -11206,7 +10588,7 @@
         <v>120005</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B9" s="2">
         <v>110005</v>
       </c>
@@ -11220,7 +10602,7 @@
         <v>120006</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>110006</v>
       </c>
@@ -11234,7 +10616,7 @@
         <v>120007</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B11" s="2">
         <v>110007</v>
       </c>
@@ -11248,7 +10630,7 @@
         <v>120008</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B12" s="2">
         <v>110008</v>
       </c>
@@ -11262,7 +10644,7 @@
         <v>120009</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>110009</v>
       </c>
@@ -11276,7 +10658,7 @@
         <v>120010</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B14" s="2">
         <v>110010</v>
       </c>
@@ -11290,7 +10672,7 @@
         <v>120011</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>110011</v>
       </c>
@@ -11304,7 +10686,7 @@
         <v>120012</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>110012</v>
       </c>
@@ -11318,7 +10700,7 @@
         <v>120013</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="2">
         <v>110013</v>
       </c>
@@ -11332,7 +10714,7 @@
         <v>120014</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>110014</v>
       </c>
@@ -11346,7 +10728,7 @@
         <v>120015</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="2">
         <v>110015</v>
       </c>
@@ -11360,7 +10742,7 @@
         <v>120016</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="2">
         <v>110016</v>
       </c>
@@ -11374,7 +10756,7 @@
         <v>120017</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="2">
         <v>110017</v>
       </c>
@@ -11388,7 +10770,7 @@
         <v>120018</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="2">
         <v>110018</v>
       </c>
@@ -11402,7 +10784,7 @@
         <v>120019</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="2">
         <v>110019</v>
       </c>
@@ -11416,7 +10798,7 @@
         <v>120020</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="2">
         <v>110020</v>
       </c>
@@ -11430,7 +10812,7 @@
         <v>120021</v>
       </c>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="2">
         <v>110021</v>
       </c>
@@ -11444,7 +10826,7 @@
         <v>120022</v>
       </c>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="2">
         <v>110022</v>
       </c>
@@ -11458,7 +10840,7 @@
         <v>120023</v>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="2">
         <v>110023</v>
       </c>
@@ -11472,7 +10854,7 @@
         <v>120024</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="2">
         <v>110024</v>
       </c>
@@ -11486,7 +10868,7 @@
         <v>120025</v>
       </c>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="2">
         <v>110025</v>
       </c>
@@ -11500,7 +10882,7 @@
         <v>120026</v>
       </c>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="2">
         <v>110026</v>
       </c>
@@ -11514,7 +10896,7 @@
         <v>120027</v>
       </c>
     </row>
-    <row r="31" spans="2:5">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="2">
         <v>110027</v>
       </c>
@@ -11528,7 +10910,7 @@
         <v>120028</v>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="2">
         <v>110028</v>
       </c>
@@ -11542,7 +10924,7 @@
         <v>120029</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="2">
         <v>110029</v>
       </c>
@@ -11556,7 +10938,7 @@
         <v>120030</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B34" s="2">
         <v>110030</v>
       </c>
@@ -11570,7 +10952,7 @@
         <v>120031</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B35" s="2">
         <v>110031</v>
       </c>
@@ -11584,7 +10966,7 @@
         <v>120032</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B36" s="2">
         <v>110032</v>
       </c>
@@ -11598,7 +10980,7 @@
         <v>120033</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B37" s="2">
         <v>110033</v>
       </c>
@@ -11612,7 +10994,7 @@
         <v>120034</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B38" s="2">
         <v>110034</v>
       </c>
@@ -11626,7 +11008,7 @@
         <v>120035</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B39" s="2">
         <v>110035</v>
       </c>
@@ -11640,7 +11022,7 @@
         <v>120036</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B40" s="2">
         <v>110036</v>
       </c>
@@ -11654,7 +11036,7 @@
         <v>120037</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B41" s="2">
         <v>110037</v>
       </c>
@@ -11668,7 +11050,7 @@
         <v>120038</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B42" s="2">
         <v>110038</v>
       </c>
@@ -11682,7 +11064,7 @@
         <v>120039</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B43" s="2">
         <v>110039</v>
       </c>
@@ -11697,26 +11079,25 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L261"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.0833333333333" customWidth="1"/>
-    <col min="3" max="3" width="29.9166666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.08203125" customWidth="1"/>
+    <col min="3" max="3" width="29.9140625" customWidth="1"/>
     <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="6" max="6" width="28.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="32.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="28.58203125" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11737,7 +11118,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" ht="16.5" spans="1:12">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -11758,7 +11139,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:12">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -11779,7 +11160,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" ht="16.5" spans="1:12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>110000</v>
@@ -11791,7 +11172,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>110001</v>
@@ -11803,7 +11184,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>110002</v>
@@ -11815,7 +11196,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>110003</v>
@@ -11827,7 +11208,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>110004</v>
@@ -11839,7 +11220,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>110005</v>
@@ -11851,7 +11232,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>110006</v>
@@ -11863,7 +11244,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>110007</v>
@@ -11875,7 +11256,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>110008</v>
@@ -11887,7 +11268,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>110009</v>
@@ -11899,7 +11280,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:12">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>110010</v>
@@ -11911,7 +11292,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:12">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>110011</v>
@@ -11923,7 +11304,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:12">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>110012</v>
@@ -11935,7 +11316,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:4">
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>110013</v>
@@ -11947,7 +11328,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:4">
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>110014</v>
@@ -11959,7 +11340,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:4">
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>110015</v>
@@ -11971,7 +11352,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:4">
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>110016</v>
@@ -11983,7 +11364,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:4">
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>110017</v>
@@ -11995,7 +11376,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:4">
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>110018</v>
@@ -12007,7 +11388,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:4">
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>110019</v>
@@ -12019,7 +11400,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="24" ht="16.5" spans="1:4">
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>110020</v>
@@ -12031,7 +11412,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:4">
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>110021</v>
@@ -12043,7 +11424,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:4">
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>110022</v>
@@ -12055,7 +11436,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:4">
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>110023</v>
@@ -12067,7 +11448,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:4">
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>110024</v>
@@ -12079,7 +11460,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:4">
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>110025</v>
@@ -12091,7 +11472,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:4">
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>110026</v>
@@ -12103,7 +11484,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:4">
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>110027</v>
@@ -12115,7 +11496,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:4">
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>110028</v>
@@ -12127,7 +11508,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:4">
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>110029</v>
@@ -12139,7 +11520,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:4">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>110030</v>
@@ -12151,7 +11532,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:4">
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>110031</v>
@@ -12163,7 +11544,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:4">
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>110032</v>
@@ -12175,7 +11556,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="1:4">
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>110033</v>
@@ -12187,7 +11568,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="38" ht="16.5" spans="1:4">
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>110034</v>
@@ -12199,7 +11580,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:4">
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>110035</v>
@@ -12211,7 +11592,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="40" ht="16.5" spans="1:4">
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>110036</v>
@@ -12223,7 +11604,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="41" ht="16.5" spans="1:4">
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>110037</v>
@@ -12235,7 +11616,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="42" ht="16.5" spans="1:4">
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>110038</v>
@@ -12247,7 +11628,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="43" ht="16.5" spans="1:4">
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>110039</v>
@@ -12259,7 +11640,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:4">
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>210000</v>
@@ -12271,7 +11652,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:4">
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>210001</v>
@@ -12283,7 +11664,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:4">
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>210002</v>
@@ -12295,7 +11676,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:4">
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>210003</v>
@@ -12307,7 +11688,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:4">
+    <row r="48" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>210004</v>
@@ -12319,7 +11700,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:4">
+    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>210005</v>
@@ -12331,7 +11712,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:4">
+    <row r="50" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>210006</v>
@@ -12343,7 +11724,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:4">
+    <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>210007</v>
@@ -12355,7 +11736,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:4">
+    <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>210008</v>
@@ -12367,7 +11748,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:4">
+    <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>210009</v>
@@ -12379,7 +11760,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:4">
+    <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>210010</v>
@@ -12391,7 +11772,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:4">
+    <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>210011</v>
@@ -12403,7 +11784,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="56" ht="16.5" spans="1:4">
+    <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>210012</v>
@@ -12415,7 +11796,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:4">
+    <row r="57" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>210013</v>
@@ -12427,7 +11808,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:4">
+    <row r="58" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>210014</v>
@@ -12439,7 +11820,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:4">
+    <row r="59" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>210015</v>
@@ -12451,7 +11832,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:4">
+    <row r="60" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>210016</v>
@@ -12463,7 +11844,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:4">
+    <row r="61" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
         <v>210017</v>
@@ -12475,7 +11856,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:4">
+    <row r="62" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
         <v>210018</v>
@@ -12487,7 +11868,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:4">
+    <row r="63" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
         <v>210019</v>
@@ -12499,7 +11880,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:4">
+    <row r="64" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
         <v>200000</v>
@@ -12511,7 +11892,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:4">
+    <row r="65" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
         <v>200001</v>
@@ -12523,7 +11904,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:4">
+    <row r="66" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
         <v>200002</v>
@@ -12535,7 +11916,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:4">
+    <row r="67" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
         <v>200003</v>
@@ -12547,7 +11928,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" ht="16.5" spans="1:4">
+    <row r="68" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
         <v>310000</v>
@@ -12559,7 +11940,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:4">
+    <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
         <v>310001</v>
@@ -12571,7 +11952,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="70" ht="16.5" spans="1:4">
+    <row r="70" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
         <v>310002</v>
@@ -12583,7 +11964,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="71" ht="16.5" spans="1:4">
+    <row r="71" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
         <v>310003</v>
@@ -12595,7 +11976,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="72" ht="16.5" spans="1:4">
+    <row r="72" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
         <v>310004</v>
@@ -12607,7 +11988,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="73" ht="16.5" spans="1:4">
+    <row r="73" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
         <v>310005</v>
@@ -12619,7 +12000,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" ht="16.5" spans="1:4">
+    <row r="74" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
         <v>310006</v>
@@ -12631,7 +12012,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="75" ht="16.5" spans="1:4">
+    <row r="75" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
         <v>310007</v>
@@ -12643,7 +12024,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="76" ht="16.5" spans="1:4">
+    <row r="76" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
         <v>310008</v>
@@ -12655,7 +12036,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="77" ht="16.5" spans="1:4">
+    <row r="77" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
         <v>310009</v>
@@ -12667,7 +12048,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:4">
+    <row r="78" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
         <v>310010</v>
@@ -12679,7 +12060,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:4">
+    <row r="79" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
         <v>310011</v>
@@ -12691,7 +12072,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:4">
+    <row r="80" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
         <v>310012</v>
@@ -12703,7 +12084,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="81" ht="16.5" spans="1:4">
+    <row r="81" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
         <v>310013</v>
@@ -12715,7 +12096,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" ht="16.5" spans="1:4">
+    <row r="82" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
         <v>310014</v>
@@ -12727,7 +12108,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" ht="16.5" spans="1:4">
+    <row r="83" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
         <v>310015</v>
@@ -12739,7 +12120,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="84" ht="16.5" spans="1:4">
+    <row r="84" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
         <v>310016</v>
@@ -12751,7 +12132,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" ht="16.5" spans="1:4">
+    <row r="85" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
         <v>310017</v>
@@ -12763,7 +12144,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="86" ht="16.5" spans="1:4">
+    <row r="86" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
         <v>310018</v>
@@ -12775,7 +12156,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="87" ht="16.5" spans="1:4">
+    <row r="87" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
         <v>310019</v>
@@ -12787,7 +12168,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" ht="16.5" spans="1:4">
+    <row r="88" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
         <v>310020</v>
@@ -12799,7 +12180,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="89" ht="16.5" spans="1:4">
+    <row r="89" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
         <v>310021</v>
@@ -12811,7 +12192,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="90" ht="16.5" spans="1:4">
+    <row r="90" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
         <v>310022</v>
@@ -12823,7 +12204,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="91" ht="16.5" spans="1:4">
+    <row r="91" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
         <v>310023</v>
@@ -12835,7 +12216,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="92" ht="16.5" spans="1:4">
+    <row r="92" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
         <v>310024</v>
@@ -12847,7 +12228,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="93" ht="16.5" spans="1:4">
+    <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
         <v>310025</v>
@@ -12859,7 +12240,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="94" ht="16.5" spans="1:4">
+    <row r="94" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
         <v>310026</v>
@@ -12871,7 +12252,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="95" ht="16.5" spans="1:4">
+    <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
         <v>310027</v>
@@ -12883,7 +12264,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="96" ht="16.5" spans="1:4">
+    <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
         <v>310028</v>
@@ -12895,7 +12276,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="97" ht="16.5" spans="1:4">
+    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
         <v>310029</v>
@@ -12907,7 +12288,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="98" ht="16.5" spans="1:4">
+    <row r="98" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
         <v>310030</v>
@@ -12919,7 +12300,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="99" ht="16.5" spans="1:4">
+    <row r="99" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
         <v>310031</v>
@@ -12931,7 +12312,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="100" ht="16.5" spans="1:4">
+    <row r="100" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
         <v>310032</v>
@@ -12943,7 +12324,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="101" ht="16.5" spans="1:4">
+    <row r="101" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
         <v>310033</v>
@@ -12955,7 +12336,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" ht="16.5" spans="1:4">
+    <row r="102" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
         <v>310034</v>
@@ -12967,7 +12348,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:4">
+    <row r="103" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
         <v>310035</v>
@@ -12979,7 +12360,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:4">
+    <row r="104" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
         <v>310036</v>
@@ -12991,7 +12372,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:4">
+    <row r="105" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
         <v>310037</v>
@@ -13003,7 +12384,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:4">
+    <row r="106" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
         <v>310038</v>
@@ -13015,7 +12396,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:4">
+    <row r="107" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
         <v>310039</v>
@@ -13027,7 +12408,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:4">
+    <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B108" s="1">
         <v>100000</v>
       </c>
@@ -13038,7 +12419,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:4">
+    <row r="109" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B109" s="1">
         <v>100001</v>
       </c>
@@ -13049,7 +12430,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="110" ht="16.5" spans="1:4">
+    <row r="110" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B110" s="1">
         <v>100002</v>
       </c>
@@ -13060,7 +12441,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="111" ht="16.5" spans="1:4">
+    <row r="111" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B111" s="1">
         <v>100003</v>
       </c>
@@ -13071,7 +12452,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="112" ht="16.5" spans="1:4">
+    <row r="112" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B112" s="1">
         <v>100004</v>
       </c>
@@ -13082,7 +12463,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="113" ht="16.5" spans="2:4">
+    <row r="113" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B113" s="1">
         <v>100005</v>
       </c>
@@ -13093,7 +12474,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="114" ht="16.5" spans="2:4">
+    <row r="114" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B114" s="1">
         <v>100006</v>
       </c>
@@ -13104,7 +12485,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="115" ht="16.5" spans="2:4">
+    <row r="115" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B115" s="1">
         <v>100007</v>
       </c>
@@ -13115,7 +12496,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="116" ht="16.5" spans="2:4">
+    <row r="116" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B116" s="1">
         <v>100008</v>
       </c>
@@ -13126,7 +12507,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="117" ht="16.5" spans="2:4">
+    <row r="117" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B117" s="1">
         <v>100009</v>
       </c>
@@ -13137,7 +12518,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="118" ht="16.5" spans="2:4">
+    <row r="118" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B118" s="1">
         <v>100010</v>
       </c>
@@ -13148,7 +12529,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="119" ht="16.5" spans="2:4">
+    <row r="119" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B119" s="1">
         <v>100011</v>
       </c>
@@ -13159,7 +12540,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="120" ht="16.5" spans="2:4">
+    <row r="120" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B120" s="1">
         <v>100012</v>
       </c>
@@ -13170,7 +12551,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="121" ht="16.5" spans="2:4">
+    <row r="121" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B121" s="1">
         <v>100013</v>
       </c>
@@ -13181,7 +12562,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="122" ht="16.5" spans="2:4">
+    <row r="122" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B122" s="1">
         <v>100014</v>
       </c>
@@ -13192,7 +12573,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="123" ht="16.5" spans="2:4">
+    <row r="123" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B123" s="1">
         <v>100015</v>
       </c>
@@ -13203,7 +12584,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="124" ht="16.5" spans="2:4">
+    <row r="124" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B124" s="1">
         <v>100016</v>
       </c>
@@ -13214,7 +12595,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="125" ht="16.5" spans="2:4">
+    <row r="125" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B125" s="1">
         <v>100017</v>
       </c>
@@ -13225,7 +12606,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="126" ht="16.5" spans="2:4">
+    <row r="126" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B126" s="1">
         <v>100018</v>
       </c>
@@ -13236,7 +12617,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="127" ht="16.5" spans="2:4">
+    <row r="127" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B127" s="1">
         <v>100019</v>
       </c>
@@ -13247,7 +12628,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="128" ht="16.5" spans="2:4">
+    <row r="128" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B128" s="1">
         <v>100020</v>
       </c>
@@ -13258,7 +12639,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="129" ht="16.5" spans="2:4">
+    <row r="129" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>100021</v>
       </c>
@@ -13269,7 +12650,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="130" ht="16.5" spans="2:4">
+    <row r="130" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B130" s="1">
         <v>100022</v>
       </c>
@@ -13280,7 +12661,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="131" ht="16.5" spans="2:4">
+    <row r="131" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B131" s="1">
         <v>100023</v>
       </c>
@@ -13291,7 +12672,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="132" ht="16.5" spans="2:4">
+    <row r="132" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B132" s="1">
         <v>100024</v>
       </c>
@@ -13302,7 +12683,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="133" ht="16.5" spans="2:4">
+    <row r="133" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B133" s="1">
         <v>100025</v>
       </c>
@@ -13313,7 +12694,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="134" ht="16.5" spans="2:4">
+    <row r="134" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B134" s="1">
         <v>100026</v>
       </c>
@@ -13324,7 +12705,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="135" ht="16.5" spans="2:4">
+    <row r="135" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B135" s="1">
         <v>100027</v>
       </c>
@@ -13335,7 +12716,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="136" ht="16.5" spans="2:4">
+    <row r="136" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B136" s="1">
         <v>100028</v>
       </c>
@@ -13346,7 +12727,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="137" ht="16.5" spans="2:4">
+    <row r="137" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B137" s="1">
         <v>100029</v>
       </c>
@@ -13357,7 +12738,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="138" ht="16.5" spans="2:4">
+    <row r="138" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B138" s="1">
         <v>100030</v>
       </c>
@@ -13368,7 +12749,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="139" ht="16.5" spans="2:4">
+    <row r="139" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B139" s="1">
         <v>100031</v>
       </c>
@@ -13379,7 +12760,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="140" ht="16.5" spans="2:4">
+    <row r="140" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B140" s="1">
         <v>100032</v>
       </c>
@@ -13390,7 +12771,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="141" ht="16.5" spans="2:4">
+    <row r="141" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B141" s="1">
         <v>100033</v>
       </c>
@@ -13401,7 +12782,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="142" ht="16.5" spans="2:4">
+    <row r="142" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B142" s="1">
         <v>100034</v>
       </c>
@@ -13412,7 +12793,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="143" ht="16.5" spans="2:4">
+    <row r="143" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B143" s="1">
         <v>100035</v>
       </c>
@@ -13423,7 +12804,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="144" ht="16.5" spans="2:4">
+    <row r="144" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B144" s="1">
         <v>100036</v>
       </c>
@@ -13434,7 +12815,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="145" ht="16.5" spans="2:4">
+    <row r="145" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B145" s="1">
         <v>100037</v>
       </c>
@@ -13445,7 +12826,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="146" ht="16.5" spans="2:4">
+    <row r="146" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B146" s="1">
         <v>100038</v>
       </c>
@@ -13456,7 +12837,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="147" ht="16.5" spans="2:4">
+    <row r="147" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B147" s="1">
         <v>100039</v>
       </c>
@@ -13467,7 +12848,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="148" ht="16.5" spans="2:4">
+    <row r="148" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B148" s="1">
         <v>100040</v>
       </c>
@@ -13478,7 +12859,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="149" ht="16.5" spans="2:4">
+    <row r="149" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B149" s="1">
         <v>100041</v>
       </c>
@@ -13489,7 +12870,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="150" ht="16.5" spans="2:4">
+    <row r="150" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B150" s="1">
         <v>100042</v>
       </c>
@@ -13500,7 +12881,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="151" ht="16.5" spans="2:4">
+    <row r="151" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B151" s="1">
         <v>100043</v>
       </c>
@@ -13511,7 +12892,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="152" ht="16.5" spans="2:4">
+    <row r="152" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B152" s="1">
         <v>100044</v>
       </c>
@@ -13522,7 +12903,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="153" ht="16.5" spans="2:4">
+    <row r="153" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B153" s="1">
         <v>100045</v>
       </c>
@@ -13533,7 +12914,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="154" ht="16.5" spans="2:4">
+    <row r="154" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B154" s="1">
         <v>100046</v>
       </c>
@@ -13544,7 +12925,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="155" ht="16.5" spans="2:4">
+    <row r="155" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B155" s="1">
         <v>100047</v>
       </c>
@@ -13555,7 +12936,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" ht="16.5" spans="2:4">
+    <row r="156" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B156" s="1">
         <v>100048</v>
       </c>
@@ -13566,7 +12947,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="157" ht="16.5" spans="2:4">
+    <row r="157" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B157" s="1">
         <v>100049</v>
       </c>
@@ -13577,7 +12958,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="158" ht="16.5" spans="2:4">
+    <row r="158" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B158" s="1">
         <v>100051</v>
       </c>
@@ -13588,7 +12969,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="159" ht="16.5" spans="2:4">
+    <row r="159" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B159" s="1">
         <v>100052</v>
       </c>
@@ -13599,7 +12980,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="160" ht="16.5" spans="2:4">
+    <row r="160" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B160" s="1">
         <v>100053</v>
       </c>
@@ -13610,7 +12991,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="161" ht="16.5" spans="2:4">
+    <row r="161" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B161" s="1">
         <v>100054</v>
       </c>
@@ -13621,7 +13002,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="162" ht="16.5" spans="2:4">
+    <row r="162" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B162" s="1">
         <v>100055</v>
       </c>
@@ -13632,612 +13013,612 @@
         <v>355</v>
       </c>
     </row>
-    <row r="163" ht="16.5" spans="2:4">
+    <row r="163" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B163" s="1">
         <v>220000</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="D163" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="164" ht="16.5" spans="2:4">
+    <row r="164" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B164" s="1">
         <v>220001</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="D164" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="165" ht="16.5" spans="2:4">
+    <row r="165" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B165" s="1">
         <v>220002</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="166" ht="16.5" spans="2:4">
+    <row r="166" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B166" s="1">
         <v>220003</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="167" ht="16.5" spans="2:4">
+    <row r="167" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B167" s="1">
         <v>220004</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="D167" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="168" ht="16.5" spans="2:4">
+    <row r="168" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B168" s="1">
         <v>220005</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="D168" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="169" ht="16.5" spans="2:4">
+    <row r="169" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B169" s="1">
         <v>220006</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="D169" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="170" ht="16.5" spans="2:4">
+    <row r="170" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B170" s="1">
         <v>220007</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="D170" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="171" ht="16.5" spans="2:4">
+    <row r="171" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B171" s="1">
         <v>220008</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="D171" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="172" ht="16.5" spans="2:4">
+    <row r="172" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B172" s="1">
         <v>220009</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="D172" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="173" ht="16.5" spans="2:4">
+    <row r="173" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B173" s="1">
         <v>130000</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="D173" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="174" ht="16.5" spans="2:4">
+    <row r="174" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B174" s="1">
         <v>130001</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="D174" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="175" ht="16.5" spans="2:4">
+    <row r="175" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B175" s="1">
         <v>130002</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="176" ht="16.5" spans="2:4">
+    <row r="176" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B176" s="1">
         <v>140000</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="177" ht="16.5" spans="2:4">
+    <row r="177" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B177" s="1">
         <v>140001</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D177" s="4" t="s">
+      <c r="D177" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="178" ht="16.5" spans="2:4">
+    <row r="178" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B178" s="1">
         <v>140002</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D178" s="4" t="s">
+      <c r="D178" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="179" ht="16.5" spans="2:4">
+    <row r="179" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B179" s="1">
         <v>140003</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D179" s="4" t="s">
+      <c r="D179" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="180" ht="16.5" spans="2:4">
+    <row r="180" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B180" s="1">
         <v>150000</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D180" s="4" t="s">
+      <c r="D180" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="181" ht="16.5" spans="2:4">
+    <row r="181" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B181" s="1">
         <v>150001</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="182" ht="16.5" spans="2:4">
+    <row r="182" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B182" s="1">
         <v>150002</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D182" s="4" t="s">
+      <c r="D182" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="183" ht="16.5" spans="2:4">
+    <row r="183" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B183" s="1">
         <v>150003</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D183" s="4" t="s">
+      <c r="D183" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="184" ht="16.5" spans="2:4">
+    <row r="184" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B184" s="1">
         <v>150004</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D184" s="4" t="s">
+      <c r="D184" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="185" ht="16.5" spans="2:4">
+    <row r="185" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B185" s="1">
         <v>150005</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D185" s="4" t="s">
+      <c r="D185" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="186" ht="16.5" spans="2:4">
+    <row r="186" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B186" s="1">
         <v>150006</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D186" s="4" t="s">
+      <c r="D186" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="187" ht="16.5" spans="2:4">
+    <row r="187" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B187" s="1">
         <v>150007</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D187" s="4" t="s">
+      <c r="D187" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="188" ht="16.5" spans="2:4">
+    <row r="188" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B188" s="1">
         <v>150008</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D188" s="4" t="s">
+      <c r="D188" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="189" ht="16.5" spans="2:4">
+    <row r="189" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B189" s="1">
         <v>150009</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D189" s="4" t="s">
+      <c r="D189" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="200" ht="16.5" spans="2:4">
+    <row r="200" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
     </row>
-    <row r="201" ht="16.5" spans="2:4">
+    <row r="201" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
     </row>
-    <row r="202" ht="16.5" spans="2:4">
+    <row r="202" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
     </row>
-    <row r="203" ht="16.5" spans="2:4">
+    <row r="203" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
     </row>
-    <row r="204" ht="16.5" spans="2:4">
+    <row r="204" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
     </row>
-    <row r="205" ht="16.5" spans="2:4">
+    <row r="205" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
     </row>
-    <row r="206" ht="16.5" spans="2:4">
+    <row r="206" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
     </row>
-    <row r="207" ht="16.5" spans="2:4">
+    <row r="207" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
     </row>
-    <row r="208" ht="16.5" spans="2:4">
+    <row r="208" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
     </row>
-    <row r="209" ht="16.5" spans="2:4">
+    <row r="209" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
     </row>
-    <row r="210" ht="16.5" spans="2:4">
+    <row r="210" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
     </row>
-    <row r="211" ht="16.5" spans="2:4">
+    <row r="211" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
     </row>
-    <row r="212" ht="16.5" spans="2:4">
+    <row r="212" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
     </row>
-    <row r="213" ht="16.5" spans="2:4">
+    <row r="213" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
     </row>
-    <row r="214" ht="16.5" spans="2:4">
+    <row r="214" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
     </row>
-    <row r="215" ht="16.5" spans="2:4">
+    <row r="215" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
     </row>
-    <row r="216" ht="16.5" spans="2:4">
+    <row r="216" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
     </row>
-    <row r="217" ht="16.5" spans="2:4">
+    <row r="217" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
     </row>
-    <row r="218" ht="16.5" spans="2:4">
+    <row r="218" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
     </row>
-    <row r="219" ht="16.5" spans="2:4">
+    <row r="219" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
     </row>
-    <row r="220" ht="16.5" spans="2:4">
+    <row r="220" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
     </row>
-    <row r="221" ht="16.5" spans="2:4">
+    <row r="221" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
     </row>
-    <row r="222" ht="16.5" spans="2:4">
+    <row r="222" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
     </row>
-    <row r="223" ht="16.5" spans="2:4">
+    <row r="223" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
     </row>
-    <row r="224" ht="16.5" spans="2:4">
+    <row r="224" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
     </row>
-    <row r="225" ht="16.5" spans="2:4">
+    <row r="225" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
     </row>
-    <row r="226" ht="16.5" spans="2:4">
+    <row r="226" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
     </row>
-    <row r="227" ht="16.5" spans="2:4">
+    <row r="227" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
     </row>
-    <row r="228" ht="16.5" spans="2:4">
+    <row r="228" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
     </row>
-    <row r="229" ht="16.5" spans="2:4">
+    <row r="229" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
     </row>
-    <row r="230" ht="16.5" spans="2:4">
+    <row r="230" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
     </row>
-    <row r="231" ht="16.5" spans="2:4">
+    <row r="231" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
     </row>
-    <row r="232" ht="16.5" spans="2:4">
+    <row r="232" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
     </row>
-    <row r="233" ht="16.5" spans="2:4">
+    <row r="233" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
     </row>
-    <row r="234" ht="16.5" spans="2:4">
+    <row r="234" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
     </row>
-    <row r="235" ht="16.5" spans="2:4">
+    <row r="235" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
     </row>
-    <row r="236" ht="16.5" spans="2:4">
+    <row r="236" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
     </row>
-    <row r="237" ht="16.5" spans="2:4">
+    <row r="237" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
     </row>
-    <row r="238" ht="16.5" spans="2:4">
+    <row r="238" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
     </row>
-    <row r="239" ht="16.5" spans="2:4">
+    <row r="239" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
     </row>
-    <row r="240" ht="16.5" spans="2:4">
+    <row r="240" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
     </row>
-    <row r="241" ht="16.5" spans="2:4">
+    <row r="241" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
     </row>
-    <row r="242" ht="16.5" spans="2:4">
+    <row r="242" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
     </row>
-    <row r="243" ht="16.5" spans="2:4">
+    <row r="243" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
     </row>
-    <row r="244" ht="16.5" spans="2:4">
+    <row r="244" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
     </row>
-    <row r="245" ht="16.5" spans="2:4">
+    <row r="245" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
     </row>
-    <row r="246" ht="16.5" spans="2:4">
+    <row r="246" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
     </row>
-    <row r="247" ht="16.5" spans="2:4">
+    <row r="247" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
     </row>
-    <row r="248" ht="16.5" spans="2:4">
+    <row r="248" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
     </row>
-    <row r="249" ht="16.5" spans="2:4">
+    <row r="249" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
     </row>
-    <row r="250" ht="16.5" spans="2:4">
+    <row r="250" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
     </row>
-    <row r="251" ht="16.5" spans="2:4">
+    <row r="251" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
     </row>
-    <row r="252" ht="16.5" spans="2:4">
+    <row r="252" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
     </row>
-    <row r="253" ht="16.5" spans="2:4">
+    <row r="253" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
     </row>
-    <row r="254" ht="16.5" spans="2:4">
+    <row r="254" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
     </row>
-    <row r="255" ht="16.5" spans="2:4">
+    <row r="255" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
     </row>
-    <row r="256" ht="16.5" spans="2:4">
+    <row r="256" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
     </row>
-    <row r="257" ht="16.5" spans="2:4">
+    <row r="257" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
     </row>
-    <row r="258" ht="16.5" spans="2:4">
+    <row r="258" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
     </row>
-    <row r="259" ht="16.5" spans="2:4">
+    <row r="259" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
     </row>
-    <row r="260" spans="2:4">
-      <c r="C260" s="5"/>
-    </row>
-    <row r="261" spans="2:4">
-      <c r="C261" s="5"/>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C260" s="4"/>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C261" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.39375" footer="0.39375"/>
-  <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.78749999999999998" header="0.39374999999999999" footer="0.39374999999999999"/>
+  <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView windowHeight="17680" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="403">
   <si>
     <t>##var</t>
   </si>
@@ -1046,6 +1046,9 @@
     <t>3+30</t>
   </si>
   <si>
+    <t>1+10001+10/1+20001+10</t>
+  </si>
+  <si>
     <t>Food</t>
   </si>
   <si>
@@ -1055,10 +1058,16 @@
     <t>3+90</t>
   </si>
   <si>
+    <t>11+50</t>
+  </si>
+  <si>
     <t>3+120</t>
   </si>
   <si>
-    <t>3+150</t>
+    <t>11+100</t>
+  </si>
+  <si>
+    <t>12+20</t>
   </si>
   <si>
     <t>TypeNum</t>
@@ -8712,15 +8721,15 @@
         <v>234</v>
       </c>
       <c r="D196" s="1" t="str">
-        <f t="shared" ref="D196:D213" si="9">CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" ref="D196:D235" si="9">CONCATENATE(B:B,"Name.png")</f>
         <v>240002Name.png</v>
       </c>
       <c r="E196" s="1" t="str">
-        <f t="shared" ref="E196:E213" si="10">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" ref="E196:E235" si="10">CONCATENATE("InventoryItem+",B:B,"Name")</f>
         <v>InventoryItem+240002Name</v>
       </c>
       <c r="F196" s="1" t="str">
-        <f t="shared" ref="F196:F213" si="11">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" ref="F196:F235" si="11">CONCATENATE("InventoryItem+",B:B,"Text")</f>
         <v>InventoryItem+240002Text</v>
       </c>
       <c r="G196" s="1" t="s">
@@ -9306,15 +9315,15 @@
         <v>252</v>
       </c>
       <c r="D214" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300000Name.png</v>
       </c>
       <c r="E214" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300000Name</v>
       </c>
       <c r="F214" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300000Text</v>
       </c>
       <c r="G214" s="1" t="s">
@@ -9339,15 +9348,15 @@
         <v>253</v>
       </c>
       <c r="D215" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300001Name.png</v>
       </c>
       <c r="E215" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300001Name</v>
       </c>
       <c r="F215" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300001Text</v>
       </c>
       <c r="G215" s="1" t="s">
@@ -9372,15 +9381,15 @@
         <v>254</v>
       </c>
       <c r="D216" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300002Name.png</v>
       </c>
       <c r="E216" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300002Name</v>
       </c>
       <c r="F216" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300002Text</v>
       </c>
       <c r="G216" s="1" t="s">
@@ -9405,15 +9414,15 @@
         <v>255</v>
       </c>
       <c r="D217" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300003Name.png</v>
       </c>
       <c r="E217" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300003Name</v>
       </c>
       <c r="F217" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300003Text</v>
       </c>
       <c r="G217" s="1" t="s">
@@ -9438,15 +9447,15 @@
         <v>256</v>
       </c>
       <c r="D218" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300004Name.png</v>
       </c>
       <c r="E218" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300004Name</v>
       </c>
       <c r="F218" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300004Text</v>
       </c>
       <c r="G218" s="1" t="s">
@@ -9471,15 +9480,15 @@
         <v>257</v>
       </c>
       <c r="D219" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300005Name.png</v>
       </c>
       <c r="E219" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300005Name</v>
       </c>
       <c r="F219" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300005Text</v>
       </c>
       <c r="G219" s="1" t="s">
@@ -9504,15 +9513,15 @@
         <v>258</v>
       </c>
       <c r="D220" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300006Name.png</v>
       </c>
       <c r="E220" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300006Name</v>
       </c>
       <c r="F220" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300006Text</v>
       </c>
       <c r="G220" s="1" t="s">
@@ -9537,15 +9546,15 @@
         <v>259</v>
       </c>
       <c r="D221" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300007Name.png</v>
       </c>
       <c r="E221" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300007Name</v>
       </c>
       <c r="F221" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300007Text</v>
       </c>
       <c r="G221" s="1" t="s">
@@ -9570,15 +9579,15 @@
         <v>260</v>
       </c>
       <c r="D222" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300008Name.png</v>
       </c>
       <c r="E222" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300008Name</v>
       </c>
       <c r="F222" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300008Text</v>
       </c>
       <c r="G222" s="1" t="s">
@@ -9603,15 +9612,15 @@
         <v>261</v>
       </c>
       <c r="D223" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>300009Name.png</v>
       </c>
       <c r="E223" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+300009Name</v>
       </c>
       <c r="F223" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+300009Text</v>
       </c>
       <c r="G223" s="1" t="s">
@@ -9636,15 +9645,15 @@
         <v>262</v>
       </c>
       <c r="D224" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>130000Name.png</v>
       </c>
       <c r="E224" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+130000Name</v>
       </c>
       <c r="F224" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+130000Text</v>
       </c>
       <c r="G224" s="1" t="s">
@@ -9669,15 +9678,15 @@
         <v>263</v>
       </c>
       <c r="D225" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>130001Name.png</v>
       </c>
       <c r="E225" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+130001Name</v>
       </c>
       <c r="F225" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+130001Text</v>
       </c>
       <c r="G225" s="1" t="s">
@@ -9702,15 +9711,15 @@
         <v>264</v>
       </c>
       <c r="D226" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>130002Name.png</v>
       </c>
       <c r="E226" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+130002Name</v>
       </c>
       <c r="F226" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+130002Text</v>
       </c>
       <c r="G226" s="1" t="s">
@@ -9735,15 +9744,15 @@
         <v>265</v>
       </c>
       <c r="D227" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140000Name.png</v>
       </c>
       <c r="E227" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140000Name</v>
       </c>
       <c r="F227" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140000Text</v>
       </c>
       <c r="G227" s="1" t="s">
@@ -9768,15 +9777,15 @@
         <v>266</v>
       </c>
       <c r="D228" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140001Name.png</v>
       </c>
       <c r="E228" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140001Name</v>
       </c>
       <c r="F228" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140001Text</v>
       </c>
       <c r="G228" s="1" t="s">
@@ -9801,15 +9810,15 @@
         <v>267</v>
       </c>
       <c r="D229" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140002Name.png</v>
       </c>
       <c r="E229" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140002Name</v>
       </c>
       <c r="F229" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140002Text</v>
       </c>
       <c r="G229" s="1" t="s">
@@ -9834,15 +9843,15 @@
         <v>268</v>
       </c>
       <c r="D230" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140003Name.png</v>
       </c>
       <c r="E230" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140003Name</v>
       </c>
       <c r="F230" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140003Text</v>
       </c>
       <c r="G230" s="1" t="s">
@@ -9867,15 +9876,15 @@
         <v>269</v>
       </c>
       <c r="D231" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150000Name.png</v>
       </c>
       <c r="E231" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150000Name</v>
       </c>
       <c r="F231" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150000Text</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -9900,15 +9909,15 @@
         <v>270</v>
       </c>
       <c r="D232" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150001Name.png</v>
       </c>
       <c r="E232" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150001Name</v>
       </c>
       <c r="F232" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150001Text</v>
       </c>
       <c r="G232" s="1" t="s">
@@ -9933,15 +9942,15 @@
         <v>271</v>
       </c>
       <c r="D233" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150002Name.png</v>
       </c>
       <c r="E233" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150002Name</v>
       </c>
       <c r="F233" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150002Text</v>
       </c>
       <c r="G233" s="1" t="s">
@@ -9966,15 +9975,15 @@
         <v>272</v>
       </c>
       <c r="D234" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150003Name.png</v>
       </c>
       <c r="E234" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150003Name</v>
       </c>
       <c r="F234" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150003Text</v>
       </c>
       <c r="G234" s="1" t="s">
@@ -9999,15 +10008,15 @@
         <v>273</v>
       </c>
       <c r="D235" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150004Name.png</v>
       </c>
       <c r="E235" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150004Name</v>
       </c>
       <c r="F235" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150004Text</v>
       </c>
       <c r="G235" s="1" t="s">
@@ -11526,7 +11535,7 @@
     <col min="3" max="3" width="29.0833333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="40.1666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.0833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="61.0833333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5833333333333" style="2" customWidth="1"/>
     <col min="8" max="8" width="15.0833333333333" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
@@ -11612,8 +11621,11 @@
       <c r="E4" s="8" t="s">
         <v>337</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>338</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -11635,10 +11647,13 @@
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H5" s="6"/>
     </row>
@@ -11650,10 +11665,13 @@
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -11665,10 +11683,13 @@
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -11680,10 +11701,13 @@
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -11695,10 +11719,13 @@
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H9" s="6"/>
     </row>
@@ -11710,10 +11737,13 @@
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -11725,10 +11755,13 @@
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -11740,10 +11773,13 @@
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -11755,10 +11791,13 @@
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H13" s="6"/>
     </row>
@@ -11770,10 +11809,13 @@
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H14" s="6"/>
     </row>
@@ -11785,10 +11827,13 @@
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H15" s="6"/>
     </row>
@@ -11800,10 +11845,13 @@
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -11815,10 +11863,13 @@
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H17" s="6"/>
     </row>
@@ -11830,10 +11881,13 @@
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H18" s="6"/>
     </row>
@@ -11845,10 +11899,13 @@
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H19" s="6"/>
     </row>
@@ -11860,10 +11917,13 @@
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H20" s="6"/>
     </row>
@@ -11875,10 +11935,13 @@
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H21" s="6"/>
     </row>
@@ -11890,10 +11953,13 @@
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H22" s="6"/>
     </row>
@@ -11905,10 +11971,13 @@
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H23" s="6"/>
     </row>
@@ -11920,10 +11989,13 @@
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H24" s="6"/>
     </row>
@@ -11935,10 +12007,13 @@
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H25" s="6"/>
     </row>
@@ -11950,10 +12025,13 @@
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H26" s="6"/>
     </row>
@@ -11965,10 +12043,13 @@
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H27" s="6"/>
     </row>
@@ -11980,10 +12061,13 @@
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H28" s="6"/>
     </row>
@@ -11995,10 +12079,13 @@
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H29" s="6"/>
     </row>
@@ -12010,10 +12097,13 @@
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H30" s="6"/>
     </row>
@@ -12025,10 +12115,13 @@
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H31" s="6"/>
     </row>
@@ -12042,8 +12135,11 @@
       <c r="E32" s="2" t="s">
         <v>342</v>
       </c>
+      <c r="F32" s="2" t="s">
+        <v>338</v>
+      </c>
       <c r="G32" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H32" s="6"/>
     </row>
@@ -12055,10 +12151,13 @@
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H33" s="6"/>
     </row>
@@ -12070,10 +12169,13 @@
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H34" s="6"/>
     </row>
@@ -12085,10 +12187,13 @@
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H35" s="6"/>
     </row>
@@ -12100,10 +12205,13 @@
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H36" s="6"/>
     </row>
@@ -12115,10 +12223,13 @@
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H37" s="6"/>
     </row>
@@ -12130,10 +12241,13 @@
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H38" s="6"/>
     </row>
@@ -12145,10 +12259,13 @@
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H39" s="6"/>
     </row>
@@ -12160,10 +12277,13 @@
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H40" s="6"/>
     </row>
@@ -12175,10 +12295,13 @@
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H41" s="6"/>
     </row>
@@ -12190,10 +12313,13 @@
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H42" s="6"/>
     </row>
@@ -12205,10 +12331,13 @@
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H43" s="6"/>
     </row>
@@ -12220,10 +12349,13 @@
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H44" s="6"/>
     </row>
@@ -12533,10 +12665,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12550,7 +12682,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -12567,10 +12699,10 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -12581,7 +12713,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E4" s="2">
         <v>120001</v>
@@ -12595,7 +12727,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E5" s="2">
         <v>120002</v>
@@ -12609,7 +12741,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E6" s="2">
         <v>120003</v>
@@ -12623,7 +12755,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E7" s="2">
         <v>120004</v>
@@ -12637,7 +12769,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E8" s="2">
         <v>120005</v>
@@ -12651,7 +12783,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E9" s="2">
         <v>120006</v>
@@ -12665,7 +12797,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E10" s="2">
         <v>120007</v>
@@ -12679,7 +12811,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E11" s="2">
         <v>120008</v>
@@ -12693,7 +12825,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E12" s="2">
         <v>120009</v>
@@ -12707,7 +12839,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E13" s="2">
         <v>120010</v>
@@ -12721,7 +12853,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E14" s="2">
         <v>120011</v>
@@ -12735,7 +12867,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E15" s="2">
         <v>120012</v>
@@ -12749,7 +12881,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E16" s="2">
         <v>120013</v>
@@ -12763,7 +12895,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E17" s="2">
         <v>120014</v>
@@ -12777,7 +12909,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E18" s="2">
         <v>120015</v>
@@ -12791,7 +12923,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E19" s="2">
         <v>120016</v>
@@ -12805,7 +12937,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E20" s="2">
         <v>120017</v>
@@ -12819,7 +12951,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E21" s="2">
         <v>120018</v>
@@ -12833,7 +12965,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2">
         <v>120019</v>
@@ -12847,7 +12979,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E23" s="2">
         <v>120020</v>
@@ -12861,7 +12993,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E24" s="2">
         <v>120021</v>
@@ -12875,7 +13007,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2">
         <v>120022</v>
@@ -12889,7 +13021,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E26" s="2">
         <v>120023</v>
@@ -12903,7 +13035,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E27" s="2">
         <v>120024</v>
@@ -12917,7 +13049,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E28" s="2">
         <v>120025</v>
@@ -12931,7 +13063,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2">
         <v>120026</v>
@@ -12945,7 +13077,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E30" s="2">
         <v>120027</v>
@@ -12959,7 +13091,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E31" s="2">
         <v>120028</v>
@@ -12973,7 +13105,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E32" s="2">
         <v>120029</v>
@@ -12987,7 +13119,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E33" s="2">
         <v>120030</v>
@@ -13001,7 +13133,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E34" s="2">
         <v>120031</v>
@@ -13015,7 +13147,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E35" s="2">
         <v>120032</v>
@@ -13029,7 +13161,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E36" s="2">
         <v>120033</v>
@@ -13043,7 +13175,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E37" s="2">
         <v>120034</v>
@@ -13057,7 +13189,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E38" s="2">
         <v>120035</v>
@@ -13071,7 +13203,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E39" s="2">
         <v>120036</v>
@@ -13085,7 +13217,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E40" s="2">
         <v>120037</v>
@@ -13099,7 +13231,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E41" s="2">
         <v>120038</v>
@@ -13113,7 +13245,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E42" s="2">
         <v>120039</v>
@@ -13127,7 +13259,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E43" s="2">
         <v>120040</v>
@@ -13164,7 +13296,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -13185,7 +13317,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -13206,7 +13338,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -13225,7 +13357,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:12">
@@ -13237,7 +13369,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:12">
@@ -13249,7 +13381,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:12">
@@ -13261,7 +13393,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:12">
@@ -13273,7 +13405,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:12">
@@ -13285,7 +13417,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:12">
@@ -13297,7 +13429,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:12">
@@ -13309,7 +13441,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:12">
@@ -13321,7 +13453,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:12">
@@ -13333,7 +13465,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:12">
@@ -13345,7 +13477,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:12">
@@ -13357,7 +13489,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
@@ -13369,7 +13501,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -13381,7 +13513,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -13393,7 +13525,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -13405,7 +13537,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -13417,7 +13549,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -13429,7 +13561,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -13441,7 +13573,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -13453,7 +13585,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -13465,7 +13597,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -13477,7 +13609,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -13489,7 +13621,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -13501,7 +13633,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -13513,7 +13645,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -13525,7 +13657,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -13537,7 +13669,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -13549,7 +13681,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -13561,7 +13693,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -13573,7 +13705,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -13585,7 +13717,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -13597,7 +13729,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -13609,7 +13741,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -13621,7 +13753,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -13633,7 +13765,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
@@ -13645,7 +13777,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
@@ -13657,7 +13789,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -13669,7 +13801,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
@@ -13681,7 +13813,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:4">
@@ -13693,7 +13825,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
@@ -13705,7 +13837,7 @@
         <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
@@ -13717,7 +13849,7 @@
         <v>183</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
@@ -13729,7 +13861,7 @@
         <v>184</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
@@ -13741,7 +13873,7 @@
         <v>185</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
@@ -13753,7 +13885,7 @@
         <v>186</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
@@ -13765,7 +13897,7 @@
         <v>187</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
@@ -13777,7 +13909,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:4">
@@ -13789,7 +13921,7 @@
         <v>189</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:4">
@@ -13801,7 +13933,7 @@
         <v>190</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:4">
@@ -13813,7 +13945,7 @@
         <v>191</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:4">
@@ -13825,7 +13957,7 @@
         <v>192</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
@@ -13837,7 +13969,7 @@
         <v>193</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:4">
@@ -13849,7 +13981,7 @@
         <v>194</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
@@ -13861,7 +13993,7 @@
         <v>195</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:4">
@@ -13873,7 +14005,7 @@
         <v>196</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:4">
@@ -13885,7 +14017,7 @@
         <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:4">
@@ -13897,7 +14029,7 @@
         <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:4">
@@ -13909,7 +14041,7 @@
         <v>199</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:4">
@@ -13921,7 +14053,7 @@
         <v>200</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:4">
@@ -13933,7 +14065,7 @@
         <v>201</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:4">
@@ -13945,7 +14077,7 @@
         <v>178</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:4">
@@ -13957,7 +14089,7 @@
         <v>179</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:4">
@@ -13969,7 +14101,7 @@
         <v>180</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:4">
@@ -13981,7 +14113,7 @@
         <v>181</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:4">
@@ -13993,7 +14125,7 @@
         <v>279</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:4">
@@ -14005,7 +14137,7 @@
         <v>281</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:4">
@@ -14017,7 +14149,7 @@
         <v>282</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:4">
@@ -14029,7 +14161,7 @@
         <v>283</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:4">
@@ -14041,7 +14173,7 @@
         <v>284</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:4">
@@ -14053,7 +14185,7 @@
         <v>285</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:4">
@@ -14065,7 +14197,7 @@
         <v>286</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:4">
@@ -14077,7 +14209,7 @@
         <v>287</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:4">
@@ -14089,7 +14221,7 @@
         <v>288</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:4">
@@ -14101,7 +14233,7 @@
         <v>289</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:4">
@@ -14113,7 +14245,7 @@
         <v>290</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:4">
@@ -14125,7 +14257,7 @@
         <v>292</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:4">
@@ -14137,7 +14269,7 @@
         <v>293</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:4">
@@ -14149,7 +14281,7 @@
         <v>294</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:4">
@@ -14161,7 +14293,7 @@
         <v>295</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:4">
@@ -14173,7 +14305,7 @@
         <v>296</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:4">
@@ -14185,7 +14317,7 @@
         <v>297</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:4">
@@ -14197,7 +14329,7 @@
         <v>298</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:4">
@@ -14209,7 +14341,7 @@
         <v>299</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
@@ -14221,7 +14353,7 @@
         <v>300</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:4">
@@ -14233,7 +14365,7 @@
         <v>301</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:4">
@@ -14245,7 +14377,7 @@
         <v>303</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:4">
@@ -14257,7 +14389,7 @@
         <v>304</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:4">
@@ -14269,7 +14401,7 @@
         <v>305</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:4">
@@ -14281,7 +14413,7 @@
         <v>306</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:4">
@@ -14293,7 +14425,7 @@
         <v>307</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:4">
@@ -14305,7 +14437,7 @@
         <v>308</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:4">
@@ -14317,7 +14449,7 @@
         <v>309</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:4">
@@ -14329,7 +14461,7 @@
         <v>310</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:4">
@@ -14341,7 +14473,7 @@
         <v>311</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:4">
@@ -14353,7 +14485,7 @@
         <v>312</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:4">
@@ -14365,7 +14497,7 @@
         <v>314</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:4">
@@ -14377,7 +14509,7 @@
         <v>315</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:4">
@@ -14389,7 +14521,7 @@
         <v>316</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:4">
@@ -14401,7 +14533,7 @@
         <v>317</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:4">
@@ -14413,7 +14545,7 @@
         <v>318</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:4">
@@ -14425,7 +14557,7 @@
         <v>319</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:4">
@@ -14437,7 +14569,7 @@
         <v>320</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:4">
@@ -14449,7 +14581,7 @@
         <v>321</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:4">
@@ -14461,7 +14593,7 @@
         <v>322</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:4">
@@ -14472,7 +14604,7 @@
         <v>27</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:4">
@@ -14483,7 +14615,7 @@
         <v>30</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:4">
@@ -14494,7 +14626,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:4">
@@ -14505,7 +14637,7 @@
         <v>32</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:4">
@@ -14516,7 +14648,7 @@
         <v>33</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="2:4">
@@ -14527,7 +14659,7 @@
         <v>34</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="2:4">
@@ -14538,7 +14670,7 @@
         <v>35</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="2:4">
@@ -14549,7 +14681,7 @@
         <v>36</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="2:4">
@@ -14560,7 +14692,7 @@
         <v>37</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="2:4">
@@ -14571,7 +14703,7 @@
         <v>38</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="2:4">
@@ -14582,7 +14714,7 @@
         <v>39</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="2:4">
@@ -14593,7 +14725,7 @@
         <v>40</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="2:4">
@@ -14604,7 +14736,7 @@
         <v>41</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="2:4">
@@ -14615,7 +14747,7 @@
         <v>42</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="122" ht="16.5" spans="2:4">
@@ -14626,7 +14758,7 @@
         <v>43</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="2:4">
@@ -14637,7 +14769,7 @@
         <v>44</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="2:4">
@@ -14648,7 +14780,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="2:4">
@@ -14659,7 +14791,7 @@
         <v>46</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="2:4">
@@ -14670,7 +14802,7 @@
         <v>47</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="2:4">
@@ -14681,7 +14813,7 @@
         <v>48</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="2:4">
@@ -14692,7 +14824,7 @@
         <v>49</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="2:4">
@@ -14703,7 +14835,7 @@
         <v>50</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="2:4">
@@ -14714,7 +14846,7 @@
         <v>51</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="2:4">
@@ -14725,7 +14857,7 @@
         <v>52</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="2:4">
@@ -14736,7 +14868,7 @@
         <v>53</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="2:4">
@@ -14747,7 +14879,7 @@
         <v>54</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="2:4">
@@ -14758,7 +14890,7 @@
         <v>55</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="2:4">
@@ -14769,7 +14901,7 @@
         <v>56</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="2:4">
@@ -14780,7 +14912,7 @@
         <v>58</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="2:4">
@@ -14791,7 +14923,7 @@
         <v>59</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="2:4">
@@ -14802,7 +14934,7 @@
         <v>60</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="2:4">
@@ -14813,7 +14945,7 @@
         <v>61</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="2:4">
@@ -14824,7 +14956,7 @@
         <v>62</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="2:4">
@@ -14835,7 +14967,7 @@
         <v>63</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="2:4">
@@ -14846,7 +14978,7 @@
         <v>65</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="2:4">
@@ -14857,7 +14989,7 @@
         <v>66</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="2:4">
@@ -14868,7 +15000,7 @@
         <v>67</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="2:4">
@@ -14879,7 +15011,7 @@
         <v>68</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="2:4">
@@ -14890,7 +15022,7 @@
         <v>69</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="2:4">
@@ -14901,7 +15033,7 @@
         <v>71</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="2:4">
@@ -14912,7 +15044,7 @@
         <v>72</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="2:4">
@@ -14923,7 +15055,7 @@
         <v>73</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="2:4">
@@ -14934,7 +15066,7 @@
         <v>74</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="2:4">
@@ -14945,7 +15077,7 @@
         <v>75</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="2:4">
@@ -14956,7 +15088,7 @@
         <v>76</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="2:4">
@@ -14967,7 +15099,7 @@
         <v>77</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="2:4">
@@ -14978,7 +15110,7 @@
         <v>78</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="2:4">
@@ -14989,7 +15121,7 @@
         <v>79</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="2:4">
@@ -15000,7 +15132,7 @@
         <v>80</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="2:4">
@@ -15011,7 +15143,7 @@
         <v>81</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="2:4">
@@ -15022,7 +15154,7 @@
         <v>82</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="2:4">
@@ -15033,7 +15165,7 @@
         <v>84</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="2:4">
@@ -15044,7 +15176,7 @@
         <v>85</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="2:4">
@@ -15055,7 +15187,7 @@
         <v>86</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="2:4">
@@ -15066,7 +15198,7 @@
         <v>87</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="2:4">
@@ -15077,7 +15209,7 @@
         <v>202</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="2:4">
@@ -15088,7 +15220,7 @@
         <v>203</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="2:4">
@@ -15099,7 +15231,7 @@
         <v>204</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="2:4">
@@ -15110,7 +15242,7 @@
         <v>205</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="2:4">
@@ -15121,7 +15253,7 @@
         <v>206</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="2:4">
@@ -15132,7 +15264,7 @@
         <v>207</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="2:4">
@@ -15143,7 +15275,7 @@
         <v>208</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="2:4">
@@ -15154,7 +15286,7 @@
         <v>209</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="2:4">
@@ -15165,7 +15297,7 @@
         <v>210</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="2:4">
@@ -15176,7 +15308,7 @@
         <v>211</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="2:4">
@@ -15187,7 +15319,7 @@
         <v>262</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="2:4">
@@ -15198,7 +15330,7 @@
         <v>263</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="2:4">
@@ -15209,7 +15341,7 @@
         <v>264</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="2:4">
@@ -15220,7 +15352,7 @@
         <v>265</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="2:4">
@@ -15231,7 +15363,7 @@
         <v>266</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="2:4">
@@ -15242,7 +15374,7 @@
         <v>267</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="2:4">
@@ -15253,7 +15385,7 @@
         <v>268</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="2:4">
@@ -15264,7 +15396,7 @@
         <v>269</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="2:4">
@@ -15275,7 +15407,7 @@
         <v>270</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="2:4">
@@ -15286,7 +15418,7 @@
         <v>271</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="2:4">
@@ -15297,7 +15429,7 @@
         <v>272</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="2:4">
@@ -15308,7 +15440,7 @@
         <v>273</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="2:4">
@@ -15319,7 +15451,7 @@
         <v>274</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="2:4">
@@ -15330,7 +15462,7 @@
         <v>275</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="2:4">
@@ -15341,7 +15473,7 @@
         <v>276</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="2:4">
@@ -15352,7 +15484,7 @@
         <v>277</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="2:4">
@@ -15363,7 +15495,7 @@
         <v>278</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="2:4">

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500" activeTab="1"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="404">
   <si>
     <t>##var</t>
   </si>
@@ -819,6 +819,9 @@
   </si>
   <si>
     <t>初级鱼饵</t>
+  </si>
+  <si>
+    <t>1+5</t>
   </si>
   <si>
     <t>中级鱼饵</t>
@@ -9666,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>70</v>
+        <v>263</v>
       </c>
     </row>
     <row r="225" ht="16.5" spans="1:10">
@@ -9675,7 +9678,7 @@
         <v>130001</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D225" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9699,7 +9702,7 @@
         <v>2</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
     </row>
     <row r="226" ht="16.5" spans="1:10">
@@ -9708,7 +9711,7 @@
         <v>130002</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D226" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9732,7 +9735,7 @@
         <v>3</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>143</v>
+        <v>263</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:10">
@@ -9741,7 +9744,7 @@
         <v>140000</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D227" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9774,7 +9777,7 @@
         <v>140001</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9807,7 +9810,7 @@
         <v>140002</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D229" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9840,7 +9843,7 @@
         <v>140003</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D230" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9873,7 +9876,7 @@
         <v>150000</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D231" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9906,7 +9909,7 @@
         <v>150001</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D232" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9939,7 +9942,7 @@
         <v>150002</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D233" s="1" t="str">
         <f t="shared" si="9"/>
@@ -9972,7 +9975,7 @@
         <v>150003</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D234" s="1" t="str">
         <f t="shared" si="9"/>
@@ -10005,7 +10008,7 @@
         <v>150004</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D235" s="1" t="str">
         <f t="shared" si="9"/>
@@ -10038,7 +10041,7 @@
         <v>150005</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D236" s="1" t="str">
         <f t="shared" ref="D236:D280" si="12">CONCATENATE(B:B,"Name.png")</f>
@@ -10071,7 +10074,7 @@
         <v>150006</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D237" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10104,7 +10107,7 @@
         <v>150007</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D238" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10137,7 +10140,7 @@
         <v>150008</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D239" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10170,7 +10173,7 @@
         <v>150009</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D240" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10203,7 +10206,7 @@
         <v>310000</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D241" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10227,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:10">
@@ -10236,7 +10239,7 @@
         <v>310001</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D242" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10260,7 +10263,7 @@
         <v>1</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:10">
@@ -10269,7 +10272,7 @@
         <v>310002</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D243" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10293,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:10">
@@ -10302,7 +10305,7 @@
         <v>310003</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D244" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10326,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:10">
@@ -10335,7 +10338,7 @@
         <v>310004</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D245" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10359,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:10">
@@ -10368,7 +10371,7 @@
         <v>310005</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D246" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10392,7 +10395,7 @@
         <v>1</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:10">
@@ -10401,7 +10404,7 @@
         <v>310006</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D247" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10425,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:10">
@@ -10434,7 +10437,7 @@
         <v>310007</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D248" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10458,7 +10461,7 @@
         <v>1</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:10">
@@ -10467,7 +10470,7 @@
         <v>310008</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D249" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10491,7 +10494,7 @@
         <v>1</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:10">
@@ -10500,7 +10503,7 @@
         <v>310009</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D250" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10524,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:10">
@@ -10533,7 +10536,7 @@
         <v>310010</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D251" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10557,7 +10560,7 @@
         <v>2</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:10">
@@ -10566,7 +10569,7 @@
         <v>310011</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D252" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10590,7 +10593,7 @@
         <v>2</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:10">
@@ -10599,7 +10602,7 @@
         <v>310012</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D253" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10623,7 +10626,7 @@
         <v>2</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:10">
@@ -10632,7 +10635,7 @@
         <v>310013</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D254" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10656,7 +10659,7 @@
         <v>2</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:10">
@@ -10665,7 +10668,7 @@
         <v>310014</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D255" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10689,7 +10692,7 @@
         <v>2</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:10">
@@ -10698,7 +10701,7 @@
         <v>310015</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D256" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10722,7 +10725,7 @@
         <v>2</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:10">
@@ -10731,7 +10734,7 @@
         <v>310016</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D257" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10755,7 +10758,7 @@
         <v>2</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:10">
@@ -10764,7 +10767,7 @@
         <v>310017</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D258" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10788,7 +10791,7 @@
         <v>2</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:10">
@@ -10797,7 +10800,7 @@
         <v>310018</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D259" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10821,7 +10824,7 @@
         <v>2</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:10">
@@ -10830,7 +10833,7 @@
         <v>310019</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D260" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10854,7 +10857,7 @@
         <v>2</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:10">
@@ -10863,7 +10866,7 @@
         <v>310020</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D261" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10887,7 +10890,7 @@
         <v>3</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:10">
@@ -10896,7 +10899,7 @@
         <v>310021</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D262" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10920,7 +10923,7 @@
         <v>3</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:10">
@@ -10929,7 +10932,7 @@
         <v>310022</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D263" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10953,7 +10956,7 @@
         <v>3</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:10">
@@ -10962,7 +10965,7 @@
         <v>310023</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D264" s="1" t="str">
         <f t="shared" si="12"/>
@@ -10986,7 +10989,7 @@
         <v>3</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:10">
@@ -10995,7 +10998,7 @@
         <v>310024</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D265" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11019,7 +11022,7 @@
         <v>3</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:10">
@@ -11028,7 +11031,7 @@
         <v>310025</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D266" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11052,7 +11055,7 @@
         <v>3</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:10">
@@ -11061,7 +11064,7 @@
         <v>310026</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D267" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11085,7 +11088,7 @@
         <v>3</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:10">
@@ -11094,7 +11097,7 @@
         <v>310027</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D268" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11118,7 +11121,7 @@
         <v>3</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:10">
@@ -11127,7 +11130,7 @@
         <v>310028</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D269" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11151,7 +11154,7 @@
         <v>3</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:10">
@@ -11160,7 +11163,7 @@
         <v>310029</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D270" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11184,7 +11187,7 @@
         <v>3</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:10">
@@ -11193,7 +11196,7 @@
         <v>310030</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D271" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11217,7 +11220,7 @@
         <v>4</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:10">
@@ -11226,7 +11229,7 @@
         <v>310031</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D272" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11250,7 +11253,7 @@
         <v>4</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:10">
@@ -11259,7 +11262,7 @@
         <v>310032</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D273" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11283,7 +11286,7 @@
         <v>4</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:10">
@@ -11292,7 +11295,7 @@
         <v>310033</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D274" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11316,7 +11319,7 @@
         <v>4</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:10">
@@ -11325,7 +11328,7 @@
         <v>310034</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D275" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11349,7 +11352,7 @@
         <v>4</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:10">
@@ -11358,7 +11361,7 @@
         <v>310035</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D276" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11382,7 +11385,7 @@
         <v>4</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:10">
@@ -11391,7 +11394,7 @@
         <v>310036</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D277" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11415,7 +11418,7 @@
         <v>4</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:10">
@@ -11424,7 +11427,7 @@
         <v>310037</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D278" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11448,7 +11451,7 @@
         <v>4</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:10">
@@ -11457,7 +11460,7 @@
         <v>310038</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D279" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11481,7 +11484,7 @@
         <v>4</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:10">
@@ -11490,7 +11493,7 @@
         <v>310039</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D280" s="1" t="str">
         <f t="shared" si="12"/>
@@ -11514,7 +11517,7 @@
         <v>4</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -11546,22 +11549,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -11575,16 +11578,16 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11592,22 +11595,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11619,13 +11622,13 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -11647,13 +11650,13 @@
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H5" s="6"/>
     </row>
@@ -11665,13 +11668,13 @@
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -11683,13 +11686,13 @@
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -11701,13 +11704,13 @@
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -11719,13 +11722,13 @@
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H9" s="6"/>
     </row>
@@ -11737,13 +11740,13 @@
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -11755,13 +11758,13 @@
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -11773,13 +11776,13 @@
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -11791,13 +11794,13 @@
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H13" s="6"/>
     </row>
@@ -11809,13 +11812,13 @@
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H14" s="6"/>
     </row>
@@ -11827,13 +11830,13 @@
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H15" s="6"/>
     </row>
@@ -11845,13 +11848,13 @@
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -11863,13 +11866,13 @@
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H17" s="6"/>
     </row>
@@ -11881,13 +11884,13 @@
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H18" s="6"/>
     </row>
@@ -11899,13 +11902,13 @@
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H19" s="6"/>
     </row>
@@ -11917,13 +11920,13 @@
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H20" s="6"/>
     </row>
@@ -11935,13 +11938,13 @@
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H21" s="6"/>
     </row>
@@ -11953,13 +11956,13 @@
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H22" s="6"/>
     </row>
@@ -11971,13 +11974,13 @@
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H23" s="6"/>
     </row>
@@ -11989,13 +11992,13 @@
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H24" s="6"/>
     </row>
@@ -12007,13 +12010,13 @@
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H25" s="6"/>
     </row>
@@ -12025,13 +12028,13 @@
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H26" s="6"/>
     </row>
@@ -12043,13 +12046,13 @@
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H27" s="6"/>
     </row>
@@ -12061,13 +12064,13 @@
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H28" s="6"/>
     </row>
@@ -12079,13 +12082,13 @@
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H29" s="6"/>
     </row>
@@ -12097,13 +12100,13 @@
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H30" s="6"/>
     </row>
@@ -12115,13 +12118,13 @@
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H31" s="6"/>
     </row>
@@ -12133,13 +12136,13 @@
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H32" s="6"/>
     </row>
@@ -12151,13 +12154,13 @@
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H33" s="6"/>
     </row>
@@ -12169,13 +12172,13 @@
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H34" s="6"/>
     </row>
@@ -12187,13 +12190,13 @@
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H35" s="6"/>
     </row>
@@ -12205,13 +12208,13 @@
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H36" s="6"/>
     </row>
@@ -12223,13 +12226,13 @@
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H37" s="6"/>
     </row>
@@ -12241,13 +12244,13 @@
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H38" s="6"/>
     </row>
@@ -12259,13 +12262,13 @@
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H39" s="6"/>
     </row>
@@ -12277,13 +12280,13 @@
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H40" s="6"/>
     </row>
@@ -12295,13 +12298,13 @@
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H41" s="6"/>
     </row>
@@ -12313,13 +12316,13 @@
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H42" s="6"/>
     </row>
@@ -12331,13 +12334,13 @@
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H43" s="6"/>
     </row>
@@ -12349,13 +12352,13 @@
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H44" s="6"/>
     </row>
@@ -12659,16 +12662,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12682,7 +12685,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -12693,16 +12696,16 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -12713,7 +12716,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E4" s="2">
         <v>120001</v>
@@ -12727,7 +12730,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E5" s="2">
         <v>120002</v>
@@ -12741,7 +12744,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E6" s="2">
         <v>120003</v>
@@ -12755,7 +12758,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E7" s="2">
         <v>120004</v>
@@ -12769,7 +12772,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E8" s="2">
         <v>120005</v>
@@ -12783,7 +12786,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E9" s="2">
         <v>120006</v>
@@ -12797,7 +12800,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E10" s="2">
         <v>120007</v>
@@ -12811,7 +12814,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E11" s="2">
         <v>120008</v>
@@ -12825,7 +12828,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E12" s="2">
         <v>120009</v>
@@ -12839,7 +12842,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E13" s="2">
         <v>120010</v>
@@ -12853,7 +12856,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E14" s="2">
         <v>120011</v>
@@ -12867,7 +12870,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E15" s="2">
         <v>120012</v>
@@ -12881,7 +12884,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E16" s="2">
         <v>120013</v>
@@ -12895,7 +12898,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E17" s="2">
         <v>120014</v>
@@ -12909,7 +12912,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E18" s="2">
         <v>120015</v>
@@ -12923,7 +12926,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E19" s="2">
         <v>120016</v>
@@ -12937,7 +12940,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E20" s="2">
         <v>120017</v>
@@ -12951,7 +12954,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E21" s="2">
         <v>120018</v>
@@ -12965,7 +12968,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E22" s="2">
         <v>120019</v>
@@ -12979,7 +12982,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E23" s="2">
         <v>120020</v>
@@ -12993,7 +12996,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E24" s="2">
         <v>120021</v>
@@ -13007,7 +13010,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E25" s="2">
         <v>120022</v>
@@ -13021,7 +13024,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E26" s="2">
         <v>120023</v>
@@ -13035,7 +13038,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E27" s="2">
         <v>120024</v>
@@ -13049,7 +13052,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2">
         <v>120025</v>
@@ -13063,7 +13066,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E29" s="2">
         <v>120026</v>
@@ -13077,7 +13080,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2">
         <v>120027</v>
@@ -13091,7 +13094,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E31" s="2">
         <v>120028</v>
@@ -13105,7 +13108,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E32" s="2">
         <v>120029</v>
@@ -13119,7 +13122,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E33" s="2">
         <v>120030</v>
@@ -13133,7 +13136,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E34" s="2">
         <v>120031</v>
@@ -13147,7 +13150,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E35" s="2">
         <v>120032</v>
@@ -13161,7 +13164,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E36" s="2">
         <v>120033</v>
@@ -13175,7 +13178,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E37" s="2">
         <v>120034</v>
@@ -13189,7 +13192,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E38" s="2">
         <v>120035</v>
@@ -13203,7 +13206,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E39" s="2">
         <v>120036</v>
@@ -13217,7 +13220,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E40" s="2">
         <v>120037</v>
@@ -13231,7 +13234,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2">
         <v>120038</v>
@@ -13245,7 +13248,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E42" s="2">
         <v>120039</v>
@@ -13259,7 +13262,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E43" s="2">
         <v>120040</v>
@@ -13290,13 +13293,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -13317,7 +13320,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -13332,13 +13335,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -13357,7 +13360,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:12">
@@ -13369,7 +13372,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:12">
@@ -13381,7 +13384,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:12">
@@ -13393,7 +13396,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:12">
@@ -13405,7 +13408,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:12">
@@ -13417,7 +13420,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:12">
@@ -13429,7 +13432,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:12">
@@ -13441,7 +13444,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:12">
@@ -13453,7 +13456,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:12">
@@ -13465,7 +13468,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:12">
@@ -13477,7 +13480,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:12">
@@ -13489,7 +13492,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
@@ -13501,7 +13504,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -13513,7 +13516,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -13525,7 +13528,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -13537,7 +13540,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -13549,7 +13552,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -13561,7 +13564,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -13573,7 +13576,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -13585,7 +13588,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -13597,7 +13600,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -13609,7 +13612,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -13621,7 +13624,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -13633,7 +13636,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -13645,7 +13648,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -13657,7 +13660,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -13669,7 +13672,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -13681,7 +13684,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -13693,7 +13696,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -13705,7 +13708,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -13717,7 +13720,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -13729,7 +13732,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -13741,7 +13744,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -13753,7 +13756,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -13765,7 +13768,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
@@ -13777,7 +13780,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
@@ -13789,7 +13792,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -13801,7 +13804,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
@@ -13813,7 +13816,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:4">
@@ -13825,7 +13828,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
@@ -13837,7 +13840,7 @@
         <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
@@ -13849,7 +13852,7 @@
         <v>183</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
@@ -13861,7 +13864,7 @@
         <v>184</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
@@ -13873,7 +13876,7 @@
         <v>185</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
@@ -13885,7 +13888,7 @@
         <v>186</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
@@ -13897,7 +13900,7 @@
         <v>187</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
@@ -13909,7 +13912,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:4">
@@ -13921,7 +13924,7 @@
         <v>189</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:4">
@@ -13933,7 +13936,7 @@
         <v>190</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:4">
@@ -13945,7 +13948,7 @@
         <v>191</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:4">
@@ -13957,7 +13960,7 @@
         <v>192</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
@@ -13969,7 +13972,7 @@
         <v>193</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:4">
@@ -13981,7 +13984,7 @@
         <v>194</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
@@ -13993,7 +13996,7 @@
         <v>195</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:4">
@@ -14005,7 +14008,7 @@
         <v>196</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:4">
@@ -14017,7 +14020,7 @@
         <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:4">
@@ -14029,7 +14032,7 @@
         <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:4">
@@ -14041,7 +14044,7 @@
         <v>199</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:4">
@@ -14053,7 +14056,7 @@
         <v>200</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:4">
@@ -14065,7 +14068,7 @@
         <v>201</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:4">
@@ -14077,7 +14080,7 @@
         <v>178</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:4">
@@ -14089,7 +14092,7 @@
         <v>179</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:4">
@@ -14101,7 +14104,7 @@
         <v>180</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:4">
@@ -14113,7 +14116,7 @@
         <v>181</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:4">
@@ -14122,10 +14125,10 @@
         <v>310000</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:4">
@@ -14134,10 +14137,10 @@
         <v>310001</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:4">
@@ -14146,10 +14149,10 @@
         <v>310002</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:4">
@@ -14158,10 +14161,10 @@
         <v>310003</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:4">
@@ -14170,10 +14173,10 @@
         <v>310004</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:4">
@@ -14182,10 +14185,10 @@
         <v>310005</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:4">
@@ -14194,10 +14197,10 @@
         <v>310006</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:4">
@@ -14206,10 +14209,10 @@
         <v>310007</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:4">
@@ -14218,10 +14221,10 @@
         <v>310008</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:4">
@@ -14230,10 +14233,10 @@
         <v>310009</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:4">
@@ -14242,10 +14245,10 @@
         <v>310010</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:4">
@@ -14254,10 +14257,10 @@
         <v>310011</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:4">
@@ -14266,10 +14269,10 @@
         <v>310012</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:4">
@@ -14278,10 +14281,10 @@
         <v>310013</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:4">
@@ -14290,10 +14293,10 @@
         <v>310014</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:4">
@@ -14302,10 +14305,10 @@
         <v>310015</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:4">
@@ -14314,10 +14317,10 @@
         <v>310016</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:4">
@@ -14326,10 +14329,10 @@
         <v>310017</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:4">
@@ -14338,10 +14341,10 @@
         <v>310018</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
@@ -14350,10 +14353,10 @@
         <v>310019</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:4">
@@ -14362,10 +14365,10 @@
         <v>310020</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:4">
@@ -14374,10 +14377,10 @@
         <v>310021</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:4">
@@ -14386,10 +14389,10 @@
         <v>310022</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:4">
@@ -14398,10 +14401,10 @@
         <v>310023</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:4">
@@ -14410,10 +14413,10 @@
         <v>310024</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:4">
@@ -14422,10 +14425,10 @@
         <v>310025</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:4">
@@ -14434,10 +14437,10 @@
         <v>310026</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:4">
@@ -14446,10 +14449,10 @@
         <v>310027</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:4">
@@ -14458,10 +14461,10 @@
         <v>310028</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:4">
@@ -14470,10 +14473,10 @@
         <v>310029</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:4">
@@ -14482,10 +14485,10 @@
         <v>310030</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:4">
@@ -14494,10 +14497,10 @@
         <v>310031</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:4">
@@ -14506,10 +14509,10 @@
         <v>310032</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:4">
@@ -14518,10 +14521,10 @@
         <v>310033</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:4">
@@ -14530,10 +14533,10 @@
         <v>310034</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:4">
@@ -14542,10 +14545,10 @@
         <v>310035</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:4">
@@ -14554,10 +14557,10 @@
         <v>310036</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:4">
@@ -14566,10 +14569,10 @@
         <v>310037</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:4">
@@ -14578,10 +14581,10 @@
         <v>310038</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:4">
@@ -14590,10 +14593,10 @@
         <v>310039</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:4">
@@ -14604,7 +14607,7 @@
         <v>27</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:4">
@@ -14615,7 +14618,7 @@
         <v>30</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:4">
@@ -14626,7 +14629,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:4">
@@ -14637,7 +14640,7 @@
         <v>32</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:4">
@@ -14648,7 +14651,7 @@
         <v>33</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="2:4">
@@ -14659,7 +14662,7 @@
         <v>34</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="2:4">
@@ -14670,7 +14673,7 @@
         <v>35</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="2:4">
@@ -14681,7 +14684,7 @@
         <v>36</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="2:4">
@@ -14692,7 +14695,7 @@
         <v>37</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="2:4">
@@ -14703,7 +14706,7 @@
         <v>38</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="2:4">
@@ -14714,7 +14717,7 @@
         <v>39</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="2:4">
@@ -14725,7 +14728,7 @@
         <v>40</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="2:4">
@@ -14736,7 +14739,7 @@
         <v>41</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="2:4">
@@ -14747,7 +14750,7 @@
         <v>42</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" ht="16.5" spans="2:4">
@@ -14758,7 +14761,7 @@
         <v>43</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="2:4">
@@ -14769,7 +14772,7 @@
         <v>44</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="2:4">
@@ -14780,7 +14783,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="2:4">
@@ -14791,7 +14794,7 @@
         <v>46</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="2:4">
@@ -14802,7 +14805,7 @@
         <v>47</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="2:4">
@@ -14813,7 +14816,7 @@
         <v>48</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="2:4">
@@ -14824,7 +14827,7 @@
         <v>49</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="2:4">
@@ -14835,7 +14838,7 @@
         <v>50</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="2:4">
@@ -14846,7 +14849,7 @@
         <v>51</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="2:4">
@@ -14857,7 +14860,7 @@
         <v>52</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="2:4">
@@ -14868,7 +14871,7 @@
         <v>53</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="2:4">
@@ -14879,7 +14882,7 @@
         <v>54</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="2:4">
@@ -14890,7 +14893,7 @@
         <v>55</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="2:4">
@@ -14901,7 +14904,7 @@
         <v>56</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="2:4">
@@ -14912,7 +14915,7 @@
         <v>58</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="2:4">
@@ -14923,7 +14926,7 @@
         <v>59</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="2:4">
@@ -14934,7 +14937,7 @@
         <v>60</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="2:4">
@@ -14945,7 +14948,7 @@
         <v>61</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="2:4">
@@ -14956,7 +14959,7 @@
         <v>62</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="2:4">
@@ -14967,7 +14970,7 @@
         <v>63</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="2:4">
@@ -14978,7 +14981,7 @@
         <v>65</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="2:4">
@@ -14989,7 +14992,7 @@
         <v>66</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="2:4">
@@ -15000,7 +15003,7 @@
         <v>67</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="2:4">
@@ -15011,7 +15014,7 @@
         <v>68</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="2:4">
@@ -15022,7 +15025,7 @@
         <v>69</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="2:4">
@@ -15033,7 +15036,7 @@
         <v>71</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="2:4">
@@ -15044,7 +15047,7 @@
         <v>72</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="2:4">
@@ -15055,7 +15058,7 @@
         <v>73</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="2:4">
@@ -15066,7 +15069,7 @@
         <v>74</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="2:4">
@@ -15077,7 +15080,7 @@
         <v>75</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="2:4">
@@ -15088,7 +15091,7 @@
         <v>76</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="2:4">
@@ -15099,7 +15102,7 @@
         <v>77</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="2:4">
@@ -15110,7 +15113,7 @@
         <v>78</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="2:4">
@@ -15121,7 +15124,7 @@
         <v>79</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="2:4">
@@ -15132,7 +15135,7 @@
         <v>80</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="2:4">
@@ -15143,7 +15146,7 @@
         <v>81</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="2:4">
@@ -15154,7 +15157,7 @@
         <v>82</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="2:4">
@@ -15165,7 +15168,7 @@
         <v>84</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="2:4">
@@ -15176,7 +15179,7 @@
         <v>85</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="2:4">
@@ -15187,7 +15190,7 @@
         <v>86</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="2:4">
@@ -15198,7 +15201,7 @@
         <v>87</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="2:4">
@@ -15209,7 +15212,7 @@
         <v>202</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="2:4">
@@ -15220,7 +15223,7 @@
         <v>203</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="2:4">
@@ -15231,7 +15234,7 @@
         <v>204</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="2:4">
@@ -15242,7 +15245,7 @@
         <v>205</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="2:4">
@@ -15253,7 +15256,7 @@
         <v>206</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="2:4">
@@ -15264,7 +15267,7 @@
         <v>207</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="2:4">
@@ -15275,7 +15278,7 @@
         <v>208</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="2:4">
@@ -15286,7 +15289,7 @@
         <v>209</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="2:4">
@@ -15297,7 +15300,7 @@
         <v>210</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="2:4">
@@ -15308,7 +15311,7 @@
         <v>211</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="2:4">
@@ -15319,7 +15322,7 @@
         <v>262</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="2:4">
@@ -15327,10 +15330,10 @@
         <v>130001</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="2:4">
@@ -15338,10 +15341,10 @@
         <v>130002</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="2:4">
@@ -15349,10 +15352,10 @@
         <v>140000</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="2:4">
@@ -15360,10 +15363,10 @@
         <v>140001</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="2:4">
@@ -15371,10 +15374,10 @@
         <v>140002</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="2:4">
@@ -15382,10 +15385,10 @@
         <v>140003</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="2:4">
@@ -15393,10 +15396,10 @@
         <v>150000</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="2:4">
@@ -15404,10 +15407,10 @@
         <v>150001</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="2:4">
@@ -15415,10 +15418,10 @@
         <v>150002</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="2:4">
@@ -15426,10 +15429,10 @@
         <v>150003</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="2:4">
@@ -15437,10 +15440,10 @@
         <v>150004</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="2:4">
@@ -15448,10 +15451,10 @@
         <v>150005</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="2:4">
@@ -15459,10 +15462,10 @@
         <v>150006</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="2:4">
@@ -15470,10 +15473,10 @@
         <v>150007</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="2:4">
@@ -15481,10 +15484,10 @@
         <v>150008</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="2:4">
@@ -15492,10 +15495,10 @@
         <v>150009</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="2:4">

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView windowWidth="32390" windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="410">
   <si>
     <t>##var</t>
   </si>
@@ -828,6 +828,24 @@
   </si>
   <si>
     <t>高级鱼饵</t>
+  </si>
+  <si>
+    <t>易拉罐</t>
+  </si>
+  <si>
+    <t>1+1</t>
+  </si>
+  <si>
+    <t>拖鞋</t>
+  </si>
+  <si>
+    <t>避孕套</t>
+  </si>
+  <si>
+    <t>使用过的避孕套</t>
+  </si>
+  <si>
+    <t>一颗珠子</t>
   </si>
   <si>
     <t>竹鱼竿</t>
@@ -2267,7 +2285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R280"/>
+  <dimension ref="A1:R285"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="29.0833333333333" style="4" customWidth="1"/>
@@ -9409,7 +9427,7 @@
       </c>
     </row>
     <row r="217" ht="16.5" spans="1:10">
-      <c r="A217" s="1"/>
+      <c r="A217" s="4"/>
       <c r="B217" s="1">
         <v>300003</v>
       </c>
@@ -9442,7 +9460,7 @@
       </c>
     </row>
     <row r="218" ht="16.5" spans="1:10">
-      <c r="A218" s="1"/>
+      <c r="A218" s="4"/>
       <c r="B218" s="1">
         <v>300004</v>
       </c>
@@ -9475,7 +9493,7 @@
       </c>
     </row>
     <row r="219" ht="16.5" spans="1:10">
-      <c r="A219" s="1"/>
+      <c r="A219" s="4"/>
       <c r="B219" s="1">
         <v>300005</v>
       </c>
@@ -9508,7 +9526,7 @@
       </c>
     </row>
     <row r="220" ht="16.5" spans="1:10">
-      <c r="A220" s="1"/>
+      <c r="A220" s="4"/>
       <c r="B220" s="1">
         <v>300006</v>
       </c>
@@ -9541,7 +9559,7 @@
       </c>
     </row>
     <row r="221" ht="16.5" spans="1:10">
-      <c r="A221" s="1"/>
+      <c r="A221" s="4"/>
       <c r="B221" s="1">
         <v>300007</v>
       </c>
@@ -9741,22 +9759,22 @@
     <row r="227" ht="16.5" spans="1:10">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>140000</v>
+        <v>131000</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D227" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>140000Name.png</v>
+        <v>131000Name.png</v>
       </c>
       <c r="E227" s="1" t="str">
         <f t="shared" si="10"/>
-        <v>InventoryItem+140000Name</v>
+        <v>InventoryItem+131000Name</v>
       </c>
       <c r="F227" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>InventoryItem+140000Text</v>
+        <v>InventoryItem+131000Text</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>28</v>
@@ -9768,28 +9786,28 @@
         <v>1</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>70</v>
+        <v>267</v>
       </c>
     </row>
     <row r="228" ht="16.5" spans="1:10">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>140001</v>
+        <v>131001</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D228" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>140001Name.png</v>
+        <v>131001Name.png</v>
       </c>
       <c r="E228" s="1" t="str">
         <f t="shared" si="10"/>
-        <v>InventoryItem+140001Name</v>
+        <v>InventoryItem+131001Name</v>
       </c>
       <c r="F228" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>InventoryItem+140001Text</v>
+        <v>InventoryItem+131001Text</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>28</v>
@@ -9798,31 +9816,31 @@
         <v>999</v>
       </c>
       <c r="I228" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
     </row>
     <row r="229" ht="16.5" spans="1:10">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>140002</v>
+        <v>131002</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D229" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>140002Name.png</v>
+        <v>131002Name.png</v>
       </c>
       <c r="E229" s="1" t="str">
         <f t="shared" si="10"/>
-        <v>InventoryItem+140002Name</v>
+        <v>InventoryItem+131002Name</v>
       </c>
       <c r="F229" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>InventoryItem+140002Text</v>
+        <v>InventoryItem+131002Text</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>28</v>
@@ -9831,31 +9849,31 @@
         <v>999</v>
       </c>
       <c r="I229" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>143</v>
+        <v>267</v>
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:10">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>140003</v>
+        <v>131003</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D230" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>140003Name.png</v>
+        <v>131003Name.png</v>
       </c>
       <c r="E230" s="1" t="str">
         <f t="shared" si="10"/>
-        <v>InventoryItem+140003Name</v>
+        <v>InventoryItem+131003Name</v>
       </c>
       <c r="F230" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>InventoryItem+140003Text</v>
+        <v>InventoryItem+131003Text</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>28</v>
@@ -9864,31 +9882,31 @@
         <v>999</v>
       </c>
       <c r="I230" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
     </row>
     <row r="231" ht="16.5" spans="1:10">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>150000</v>
+        <v>131004</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D231" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>150000Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>131004Name.png</v>
       </c>
       <c r="E231" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>InventoryItem+150000Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+131004Name</v>
       </c>
       <c r="F231" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>InventoryItem+150000Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+131004Text</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>28</v>
@@ -9897,31 +9915,31 @@
         <v>999</v>
       </c>
       <c r="I231" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>70</v>
+        <v>263</v>
       </c>
     </row>
     <row r="232" ht="16.5" spans="1:10">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>150001</v>
+        <v>140000</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D232" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>150001Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>140000Name.png</v>
       </c>
       <c r="E232" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>InventoryItem+150001Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+140000Name</v>
       </c>
       <c r="F232" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>InventoryItem+150001Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+140000Text</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>28</v>
@@ -9939,22 +9957,22 @@
     <row r="233" ht="16.5" spans="1:10">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>150002</v>
+        <v>140001</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D233" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>150002Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>140001Name.png</v>
       </c>
       <c r="E233" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>InventoryItem+150002Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+140001Name</v>
       </c>
       <c r="F233" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>InventoryItem+150002Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+140001Text</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>28</v>
@@ -9972,22 +9990,22 @@
     <row r="234" ht="16.5" spans="1:10">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>150003</v>
+        <v>140002</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D234" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>150003Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>140002Name.png</v>
       </c>
       <c r="E234" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>InventoryItem+150003Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+140002Name</v>
       </c>
       <c r="F234" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>InventoryItem+150003Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+140002Text</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>28</v>
@@ -9996,31 +10014,31 @@
         <v>999</v>
       </c>
       <c r="I234" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="235" ht="16.5" spans="1:10">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>150004</v>
+        <v>140003</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D235" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>150004Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>140003Name.png</v>
       </c>
       <c r="E235" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>InventoryItem+150004Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+140003Name</v>
       </c>
       <c r="F235" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>InventoryItem+150004Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+140003Text</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>28</v>
@@ -10029,31 +10047,31 @@
         <v>999</v>
       </c>
       <c r="I235" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="236" ht="16.5" spans="1:10">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>150005</v>
+        <v>150000</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D236" s="1" t="str">
-        <f t="shared" ref="D236:D280" si="12">CONCATENATE(B:B,"Name.png")</f>
-        <v>150005Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>150000Name.png</v>
       </c>
       <c r="E236" s="1" t="str">
-        <f t="shared" ref="E236:E280" si="13">CONCATENATE("InventoryItem+",B:B,"Name")</f>
-        <v>InventoryItem+150005Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150000Name</v>
       </c>
       <c r="F236" s="1" t="str">
-        <f t="shared" ref="F236:F280" si="14">CONCATENATE("InventoryItem+",B:B,"Text")</f>
-        <v>InventoryItem+150005Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150000Text</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>28</v>
@@ -10062,31 +10080,31 @@
         <v>999</v>
       </c>
       <c r="I236" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:10">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>150006</v>
+        <v>150001</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D237" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>150006Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>150001Name.png</v>
       </c>
       <c r="E237" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>InventoryItem+150006Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150001Name</v>
       </c>
       <c r="F237" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>InventoryItem+150006Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150001Text</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>28</v>
@@ -10095,31 +10113,31 @@
         <v>999</v>
       </c>
       <c r="I237" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
     </row>
     <row r="238" ht="16.5" spans="1:10">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>150007</v>
+        <v>150002</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D238" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>150007Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>150002Name.png</v>
       </c>
       <c r="E238" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>InventoryItem+150007Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150002Name</v>
       </c>
       <c r="F238" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>InventoryItem+150007Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150002Text</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>28</v>
@@ -10128,31 +10146,31 @@
         <v>999</v>
       </c>
       <c r="I238" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="239" ht="16.5" spans="1:10">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>150008</v>
+        <v>150003</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D239" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>150008Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>150003Name.png</v>
       </c>
       <c r="E239" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>InventoryItem+150008Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150003Name</v>
       </c>
       <c r="F239" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>InventoryItem+150008Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150003Text</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>28</v>
@@ -10161,31 +10179,31 @@
         <v>999</v>
       </c>
       <c r="I239" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240" ht="16.5" spans="1:10">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>150009</v>
+        <v>150004</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D240" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>150009Name.png</v>
+        <f>CONCATENATE(B:B,"Name.png")</f>
+        <v>150004Name.png</v>
       </c>
       <c r="E240" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>InventoryItem+150009Name</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150004Name</v>
       </c>
       <c r="F240" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>InventoryItem+150009Text</v>
+        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150004Text</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>28</v>
@@ -10194,31 +10212,31 @@
         <v>999</v>
       </c>
       <c r="I240" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
     </row>
     <row r="241" ht="16.5" spans="1:10">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>310000</v>
+        <v>150005</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D241" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>310000Name.png</v>
+        <f t="shared" ref="D241:D285" si="12">CONCATENATE(B:B,"Name.png")</f>
+        <v>150005Name.png</v>
       </c>
       <c r="E241" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>InventoryItem+310000Name</v>
+        <f t="shared" ref="E241:E285" si="13">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <v>InventoryItem+150005Name</v>
       </c>
       <c r="F241" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>InventoryItem+310000Text</v>
+        <f t="shared" ref="F241:F285" si="14">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <v>InventoryItem+150005Text</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>28</v>
@@ -10227,31 +10245,31 @@
         <v>999</v>
       </c>
       <c r="I241" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
     </row>
     <row r="242" ht="16.5" spans="1:10">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>310001</v>
+        <v>150006</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D242" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310001Name.png</v>
+        <v>150006Name.png</v>
       </c>
       <c r="E242" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310001Name</v>
+        <v>InventoryItem+150006Name</v>
       </c>
       <c r="F242" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310001Text</v>
+        <v>InventoryItem+150006Text</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>28</v>
@@ -10260,31 +10278,31 @@
         <v>999</v>
       </c>
       <c r="I242" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>281</v>
+        <v>159</v>
       </c>
     </row>
     <row r="243" ht="16.5" spans="1:10">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>310002</v>
+        <v>150007</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>283</v>
       </c>
       <c r="D243" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310002Name.png</v>
+        <v>150007Name.png</v>
       </c>
       <c r="E243" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310002Name</v>
+        <v>InventoryItem+150007Name</v>
       </c>
       <c r="F243" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310002Text</v>
+        <v>InventoryItem+150007Text</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>28</v>
@@ -10293,31 +10311,31 @@
         <v>999</v>
       </c>
       <c r="I243" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>281</v>
+        <v>159</v>
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:10">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>310003</v>
+        <v>150008</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D244" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310003Name.png</v>
+        <v>150008Name.png</v>
       </c>
       <c r="E244" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310003Name</v>
+        <v>InventoryItem+150008Name</v>
       </c>
       <c r="F244" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310003Text</v>
+        <v>InventoryItem+150008Text</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>28</v>
@@ -10326,31 +10344,31 @@
         <v>999</v>
       </c>
       <c r="I244" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>281</v>
+        <v>89</v>
       </c>
     </row>
     <row r="245" ht="16.5" spans="1:10">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>310004</v>
+        <v>150009</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>285</v>
       </c>
       <c r="D245" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310004Name.png</v>
+        <v>150009Name.png</v>
       </c>
       <c r="E245" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310004Name</v>
+        <v>InventoryItem+150009Name</v>
       </c>
       <c r="F245" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310004Text</v>
+        <v>InventoryItem+150009Text</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>28</v>
@@ -10359,31 +10377,31 @@
         <v>999</v>
       </c>
       <c r="I245" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>281</v>
+        <v>89</v>
       </c>
     </row>
     <row r="246" ht="16.5" spans="1:10">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>310005</v>
+        <v>310000</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D246" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310005Name.png</v>
+        <v>310000Name.png</v>
       </c>
       <c r="E246" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310005Name</v>
+        <v>InventoryItem+310000Name</v>
       </c>
       <c r="F246" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310005Text</v>
+        <v>InventoryItem+310000Text</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>28</v>
@@ -10395,28 +10413,28 @@
         <v>1</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="247" ht="16.5" spans="1:10">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>310006</v>
+        <v>310001</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D247" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310006Name.png</v>
+        <v>310001Name.png</v>
       </c>
       <c r="E247" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310006Name</v>
+        <v>InventoryItem+310001Name</v>
       </c>
       <c r="F247" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310006Text</v>
+        <v>InventoryItem+310001Text</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>28</v>
@@ -10428,28 +10446,28 @@
         <v>1</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:10">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>310007</v>
+        <v>310002</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D248" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310007Name.png</v>
+        <v>310002Name.png</v>
       </c>
       <c r="E248" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310007Name</v>
+        <v>InventoryItem+310002Name</v>
       </c>
       <c r="F248" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310007Text</v>
+        <v>InventoryItem+310002Text</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>28</v>
@@ -10461,28 +10479,28 @@
         <v>1</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:10">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>310008</v>
+        <v>310003</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D249" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310008Name.png</v>
+        <v>310003Name.png</v>
       </c>
       <c r="E249" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310008Name</v>
+        <v>InventoryItem+310003Name</v>
       </c>
       <c r="F249" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310008Text</v>
+        <v>InventoryItem+310003Text</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>28</v>
@@ -10494,28 +10512,28 @@
         <v>1</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:10">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>310009</v>
+        <v>310004</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D250" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310009Name.png</v>
+        <v>310004Name.png</v>
       </c>
       <c r="E250" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310009Name</v>
+        <v>InventoryItem+310004Name</v>
       </c>
       <c r="F250" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310009Text</v>
+        <v>InventoryItem+310004Text</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>28</v>
@@ -10527,28 +10545,28 @@
         <v>1</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:10">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>310010</v>
+        <v>310005</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D251" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310010Name.png</v>
+        <v>310005Name.png</v>
       </c>
       <c r="E251" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310010Name</v>
+        <v>InventoryItem+310005Name</v>
       </c>
       <c r="F251" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310010Text</v>
+        <v>InventoryItem+310005Text</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>28</v>
@@ -10557,31 +10575,31 @@
         <v>999</v>
       </c>
       <c r="I251" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:10">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>310011</v>
+        <v>310006</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>293</v>
       </c>
       <c r="D252" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310011Name.png</v>
+        <v>310006Name.png</v>
       </c>
       <c r="E252" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310011Name</v>
+        <v>InventoryItem+310006Name</v>
       </c>
       <c r="F252" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310011Text</v>
+        <v>InventoryItem+310006Text</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>28</v>
@@ -10590,31 +10608,31 @@
         <v>999</v>
       </c>
       <c r="I252" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:10">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>310012</v>
+        <v>310007</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>294</v>
       </c>
       <c r="D253" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310012Name.png</v>
+        <v>310007Name.png</v>
       </c>
       <c r="E253" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310012Name</v>
+        <v>InventoryItem+310007Name</v>
       </c>
       <c r="F253" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310012Text</v>
+        <v>InventoryItem+310007Text</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>28</v>
@@ -10623,31 +10641,31 @@
         <v>999</v>
       </c>
       <c r="I253" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="254" ht="16.5" spans="1:10">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>310013</v>
+        <v>310008</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>295</v>
       </c>
       <c r="D254" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310013Name.png</v>
+        <v>310008Name.png</v>
       </c>
       <c r="E254" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310013Name</v>
+        <v>InventoryItem+310008Name</v>
       </c>
       <c r="F254" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310013Text</v>
+        <v>InventoryItem+310008Text</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>28</v>
@@ -10656,31 +10674,31 @@
         <v>999</v>
       </c>
       <c r="I254" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:10">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>310014</v>
+        <v>310009</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D255" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310014Name.png</v>
+        <v>310009Name.png</v>
       </c>
       <c r="E255" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310014Name</v>
+        <v>InventoryItem+310009Name</v>
       </c>
       <c r="F255" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310014Text</v>
+        <v>InventoryItem+310009Text</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>28</v>
@@ -10689,31 +10707,31 @@
         <v>999</v>
       </c>
       <c r="I255" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:10">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>310015</v>
+        <v>310010</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D256" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310015Name.png</v>
+        <v>310010Name.png</v>
       </c>
       <c r="E256" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310015Name</v>
+        <v>InventoryItem+310010Name</v>
       </c>
       <c r="F256" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310015Text</v>
+        <v>InventoryItem+310010Text</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>28</v>
@@ -10725,28 +10743,28 @@
         <v>2</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:10">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>310016</v>
+        <v>310011</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D257" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310016Name.png</v>
+        <v>310011Name.png</v>
       </c>
       <c r="E257" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310016Name</v>
+        <v>InventoryItem+310011Name</v>
       </c>
       <c r="F257" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310016Text</v>
+        <v>InventoryItem+310011Text</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>28</v>
@@ -10758,28 +10776,28 @@
         <v>2</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:10">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>310017</v>
+        <v>310012</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D258" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310017Name.png</v>
+        <v>310012Name.png</v>
       </c>
       <c r="E258" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310017Name</v>
+        <v>InventoryItem+310012Name</v>
       </c>
       <c r="F258" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310017Text</v>
+        <v>InventoryItem+310012Text</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>28</v>
@@ -10791,28 +10809,28 @@
         <v>2</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:10">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>310018</v>
+        <v>310013</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D259" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310018Name.png</v>
+        <v>310013Name.png</v>
       </c>
       <c r="E259" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310018Name</v>
+        <v>InventoryItem+310013Name</v>
       </c>
       <c r="F259" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310018Text</v>
+        <v>InventoryItem+310013Text</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>28</v>
@@ -10824,28 +10842,28 @@
         <v>2</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:10">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>310019</v>
+        <v>310014</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D260" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310019Name.png</v>
+        <v>310014Name.png</v>
       </c>
       <c r="E260" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310019Name</v>
+        <v>InventoryItem+310014Name</v>
       </c>
       <c r="F260" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310019Text</v>
+        <v>InventoryItem+310014Text</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>28</v>
@@ -10857,28 +10875,28 @@
         <v>2</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:10">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>310020</v>
+        <v>310015</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D261" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310020Name.png</v>
+        <v>310015Name.png</v>
       </c>
       <c r="E261" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310020Name</v>
+        <v>InventoryItem+310015Name</v>
       </c>
       <c r="F261" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310020Text</v>
+        <v>InventoryItem+310015Text</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>28</v>
@@ -10887,31 +10905,31 @@
         <v>999</v>
       </c>
       <c r="I261" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:10">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>310021</v>
+        <v>310016</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D262" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310021Name.png</v>
+        <v>310016Name.png</v>
       </c>
       <c r="E262" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310021Name</v>
+        <v>InventoryItem+310016Name</v>
       </c>
       <c r="F262" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310021Text</v>
+        <v>InventoryItem+310016Text</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>28</v>
@@ -10920,31 +10938,31 @@
         <v>999</v>
       </c>
       <c r="I262" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="263" ht="16.5" spans="1:10">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>310022</v>
+        <v>310017</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>305</v>
       </c>
       <c r="D263" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310022Name.png</v>
+        <v>310017Name.png</v>
       </c>
       <c r="E263" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310022Name</v>
+        <v>InventoryItem+310017Name</v>
       </c>
       <c r="F263" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310022Text</v>
+        <v>InventoryItem+310017Text</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>28</v>
@@ -10953,31 +10971,31 @@
         <v>999</v>
       </c>
       <c r="I263" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:10">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>310023</v>
+        <v>310018</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>306</v>
       </c>
       <c r="D264" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310023Name.png</v>
+        <v>310018Name.png</v>
       </c>
       <c r="E264" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310023Name</v>
+        <v>InventoryItem+310018Name</v>
       </c>
       <c r="F264" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310023Text</v>
+        <v>InventoryItem+310018Text</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>28</v>
@@ -10986,31 +11004,31 @@
         <v>999</v>
       </c>
       <c r="I264" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:10">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>310024</v>
+        <v>310019</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D265" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310024Name.png</v>
+        <v>310019Name.png</v>
       </c>
       <c r="E265" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310024Name</v>
+        <v>InventoryItem+310019Name</v>
       </c>
       <c r="F265" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310024Text</v>
+        <v>InventoryItem+310019Text</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>28</v>
@@ -11019,31 +11037,31 @@
         <v>999</v>
       </c>
       <c r="I265" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="266" ht="16.5" spans="1:10">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>310025</v>
+        <v>310020</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D266" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310025Name.png</v>
+        <v>310020Name.png</v>
       </c>
       <c r="E266" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310025Name</v>
+        <v>InventoryItem+310020Name</v>
       </c>
       <c r="F266" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310025Text</v>
+        <v>InventoryItem+310020Text</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>28</v>
@@ -11055,28 +11073,28 @@
         <v>3</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="267" ht="16.5" spans="1:10">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>310026</v>
+        <v>310021</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D267" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310026Name.png</v>
+        <v>310021Name.png</v>
       </c>
       <c r="E267" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310026Name</v>
+        <v>InventoryItem+310021Name</v>
       </c>
       <c r="F267" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310026Text</v>
+        <v>InventoryItem+310021Text</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>28</v>
@@ -11088,28 +11106,28 @@
         <v>3</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="268" ht="16.5" spans="1:10">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>310027</v>
+        <v>310022</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D268" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310027Name.png</v>
+        <v>310022Name.png</v>
       </c>
       <c r="E268" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310027Name</v>
+        <v>InventoryItem+310022Name</v>
       </c>
       <c r="F268" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310027Text</v>
+        <v>InventoryItem+310022Text</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>28</v>
@@ -11121,28 +11139,28 @@
         <v>3</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:10">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>310028</v>
+        <v>310023</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D269" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310028Name.png</v>
+        <v>310023Name.png</v>
       </c>
       <c r="E269" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310028Name</v>
+        <v>InventoryItem+310023Name</v>
       </c>
       <c r="F269" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310028Text</v>
+        <v>InventoryItem+310023Text</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>28</v>
@@ -11154,28 +11172,28 @@
         <v>3</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:10">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>310029</v>
+        <v>310024</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D270" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310029Name.png</v>
+        <v>310024Name.png</v>
       </c>
       <c r="E270" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310029Name</v>
+        <v>InventoryItem+310024Name</v>
       </c>
       <c r="F270" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310029Text</v>
+        <v>InventoryItem+310024Text</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>28</v>
@@ -11187,28 +11205,28 @@
         <v>3</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:10">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>310030</v>
+        <v>310025</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D271" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310030Name.png</v>
+        <v>310025Name.png</v>
       </c>
       <c r="E271" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310030Name</v>
+        <v>InventoryItem+310025Name</v>
       </c>
       <c r="F271" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310030Text</v>
+        <v>InventoryItem+310025Text</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>28</v>
@@ -11217,31 +11235,31 @@
         <v>999</v>
       </c>
       <c r="I271" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:10">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>310031</v>
+        <v>310026</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>315</v>
       </c>
       <c r="D272" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310031Name.png</v>
+        <v>310026Name.png</v>
       </c>
       <c r="E272" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310031Name</v>
+        <v>InventoryItem+310026Name</v>
       </c>
       <c r="F272" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310031Text</v>
+        <v>InventoryItem+310026Text</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>28</v>
@@ -11250,31 +11268,31 @@
         <v>999</v>
       </c>
       <c r="I272" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:10">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>310032</v>
+        <v>310027</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>316</v>
       </c>
       <c r="D273" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310032Name.png</v>
+        <v>310027Name.png</v>
       </c>
       <c r="E273" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310032Name</v>
+        <v>InventoryItem+310027Name</v>
       </c>
       <c r="F273" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310032Text</v>
+        <v>InventoryItem+310027Text</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>28</v>
@@ -11283,31 +11301,31 @@
         <v>999</v>
       </c>
       <c r="I273" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:10">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>310033</v>
+        <v>310028</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>317</v>
       </c>
       <c r="D274" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310033Name.png</v>
+        <v>310028Name.png</v>
       </c>
       <c r="E274" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310033Name</v>
+        <v>InventoryItem+310028Name</v>
       </c>
       <c r="F274" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310033Text</v>
+        <v>InventoryItem+310028Text</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>28</v>
@@ -11316,31 +11334,31 @@
         <v>999</v>
       </c>
       <c r="I274" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:10">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>310034</v>
+        <v>310029</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>318</v>
       </c>
       <c r="D275" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310034Name.png</v>
+        <v>310029Name.png</v>
       </c>
       <c r="E275" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310034Name</v>
+        <v>InventoryItem+310029Name</v>
       </c>
       <c r="F275" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310034Text</v>
+        <v>InventoryItem+310029Text</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>28</v>
@@ -11349,31 +11367,31 @@
         <v>999</v>
       </c>
       <c r="I275" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:10">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>310035</v>
+        <v>310030</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>319</v>
       </c>
       <c r="D276" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310035Name.png</v>
+        <v>310030Name.png</v>
       </c>
       <c r="E276" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310035Name</v>
+        <v>InventoryItem+310030Name</v>
       </c>
       <c r="F276" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310035Text</v>
+        <v>InventoryItem+310030Text</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>28</v>
@@ -11385,28 +11403,28 @@
         <v>4</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="277" ht="16.5" spans="1:10">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>310036</v>
+        <v>310031</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D277" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310036Name.png</v>
+        <v>310031Name.png</v>
       </c>
       <c r="E277" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310036Name</v>
+        <v>InventoryItem+310031Name</v>
       </c>
       <c r="F277" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310036Text</v>
+        <v>InventoryItem+310031Text</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>28</v>
@@ -11418,28 +11436,28 @@
         <v>4</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:10">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>310037</v>
+        <v>310032</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D278" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310037Name.png</v>
+        <v>310032Name.png</v>
       </c>
       <c r="E278" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310037Name</v>
+        <v>InventoryItem+310032Name</v>
       </c>
       <c r="F278" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310037Text</v>
+        <v>InventoryItem+310032Text</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>28</v>
@@ -11451,28 +11469,28 @@
         <v>4</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:10">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>310038</v>
+        <v>310033</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D279" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310038Name.png</v>
+        <v>310033Name.png</v>
       </c>
       <c r="E279" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310038Name</v>
+        <v>InventoryItem+310033Name</v>
       </c>
       <c r="F279" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310038Text</v>
+        <v>InventoryItem+310033Text</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>28</v>
@@ -11484,28 +11502,28 @@
         <v>4</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="280" ht="16.5" spans="1:10">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>310039</v>
+        <v>310034</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D280" s="1" t="str">
         <f t="shared" si="12"/>
-        <v>310039Name.png</v>
+        <v>310034Name.png</v>
       </c>
       <c r="E280" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>InventoryItem+310039Name</v>
+        <v>InventoryItem+310034Name</v>
       </c>
       <c r="F280" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>InventoryItem+310039Text</v>
+        <v>InventoryItem+310034Text</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>28</v>
@@ -11517,7 +11535,172 @@
         <v>4</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="281" ht="16.5" spans="1:10">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1">
+        <v>310035</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D281" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>310035Name.png</v>
+      </c>
+      <c r="E281" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>InventoryItem+310035Name</v>
+      </c>
+      <c r="F281" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>InventoryItem+310035Text</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H281" s="1">
+        <v>999</v>
+      </c>
+      <c r="I281" s="1">
+        <v>4</v>
+      </c>
+      <c r="J281" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="282" ht="16.5" spans="1:10">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1">
+        <v>310036</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D282" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>310036Name.png</v>
+      </c>
+      <c r="E282" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>InventoryItem+310036Name</v>
+      </c>
+      <c r="F282" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>InventoryItem+310036Text</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H282" s="1">
+        <v>999</v>
+      </c>
+      <c r="I282" s="1">
+        <v>4</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="283" ht="16.5" spans="1:10">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1">
+        <v>310037</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D283" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>310037Name.png</v>
+      </c>
+      <c r="E283" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>InventoryItem+310037Name</v>
+      </c>
+      <c r="F283" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>InventoryItem+310037Text</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H283" s="1">
+        <v>999</v>
+      </c>
+      <c r="I283" s="1">
+        <v>4</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="284" ht="16.5" spans="1:10">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1">
+        <v>310038</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D284" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>310038Name.png</v>
+      </c>
+      <c r="E284" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>InventoryItem+310038Name</v>
+      </c>
+      <c r="F284" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>InventoryItem+310038Text</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H284" s="1">
+        <v>999</v>
+      </c>
+      <c r="I284" s="1">
+        <v>4</v>
+      </c>
+      <c r="J284" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="285" ht="16.5" spans="1:10">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1">
+        <v>310039</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D285" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>310039Name.png</v>
+      </c>
+      <c r="E285" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>InventoryItem+310039Name</v>
+      </c>
+      <c r="F285" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>InventoryItem+310039Text</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H285" s="1">
+        <v>999</v>
+      </c>
+      <c r="I285" s="1">
+        <v>4</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -11549,22 +11732,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -11578,16 +11761,16 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11595,22 +11778,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11622,13 +11805,13 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -11650,13 +11833,13 @@
         <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H5" s="6"/>
     </row>
@@ -11668,13 +11851,13 @@
         <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -11686,13 +11869,13 @@
         <v>138</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -11704,13 +11887,13 @@
         <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H8" s="6"/>
     </row>
@@ -11722,13 +11905,13 @@
         <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H9" s="6"/>
     </row>
@@ -11740,13 +11923,13 @@
         <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -11758,13 +11941,13 @@
         <v>142</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -11776,13 +11959,13 @@
         <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -11794,13 +11977,13 @@
         <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H13" s="6"/>
     </row>
@@ -11812,13 +11995,13 @@
         <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H14" s="6"/>
     </row>
@@ -11830,13 +12013,13 @@
         <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H15" s="6"/>
     </row>
@@ -11848,13 +12031,13 @@
         <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H16" s="6"/>
     </row>
@@ -11866,13 +12049,13 @@
         <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H17" s="6"/>
     </row>
@@ -11884,13 +12067,13 @@
         <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H18" s="6"/>
     </row>
@@ -11902,13 +12085,13 @@
         <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H19" s="6"/>
     </row>
@@ -11920,13 +12103,13 @@
         <v>152</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H20" s="6"/>
     </row>
@@ -11938,13 +12121,13 @@
         <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H21" s="6"/>
     </row>
@@ -11956,13 +12139,13 @@
         <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H22" s="6"/>
     </row>
@@ -11974,13 +12157,13 @@
         <v>155</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H23" s="6"/>
     </row>
@@ -11992,13 +12175,13 @@
         <v>156</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H24" s="6"/>
     </row>
@@ -12010,13 +12193,13 @@
         <v>157</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H25" s="6"/>
     </row>
@@ -12028,13 +12211,13 @@
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H26" s="6"/>
     </row>
@@ -12046,13 +12229,13 @@
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H27" s="6"/>
     </row>
@@ -12064,13 +12247,13 @@
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H28" s="6"/>
     </row>
@@ -12082,13 +12265,13 @@
         <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H29" s="6"/>
     </row>
@@ -12100,13 +12283,13 @@
         <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H30" s="6"/>
     </row>
@@ -12118,13 +12301,13 @@
         <v>164</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H31" s="6"/>
     </row>
@@ -12136,13 +12319,13 @@
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H32" s="6"/>
     </row>
@@ -12154,13 +12337,13 @@
         <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H33" s="6"/>
     </row>
@@ -12172,13 +12355,13 @@
         <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H34" s="6"/>
     </row>
@@ -12190,13 +12373,13 @@
         <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H35" s="6"/>
     </row>
@@ -12208,13 +12391,13 @@
         <v>169</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H36" s="6"/>
     </row>
@@ -12226,13 +12409,13 @@
         <v>170</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H37" s="6"/>
     </row>
@@ -12244,13 +12427,13 @@
         <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H38" s="6"/>
     </row>
@@ -12262,13 +12445,13 @@
         <v>172</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H39" s="6"/>
     </row>
@@ -12280,13 +12463,13 @@
         <v>173</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="H40" s="6"/>
     </row>
@@ -12298,13 +12481,13 @@
         <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="H41" s="6"/>
     </row>
@@ -12316,13 +12499,13 @@
         <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="H42" s="6"/>
     </row>
@@ -12334,13 +12517,13 @@
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="H43" s="6"/>
     </row>
@@ -12352,13 +12535,13 @@
         <v>177</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="H44" s="6"/>
     </row>
@@ -12662,16 +12845,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12685,7 +12868,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -12696,16 +12879,16 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -12716,7 +12899,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E4" s="2">
         <v>120001</v>
@@ -12730,7 +12913,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E5" s="2">
         <v>120002</v>
@@ -12744,7 +12927,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E6" s="2">
         <v>120003</v>
@@ -12758,7 +12941,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E7" s="2">
         <v>120004</v>
@@ -12772,7 +12955,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E8" s="2">
         <v>120005</v>
@@ -12786,7 +12969,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E9" s="2">
         <v>120006</v>
@@ -12800,7 +12983,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E10" s="2">
         <v>120007</v>
@@ -12814,7 +12997,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E11" s="2">
         <v>120008</v>
@@ -12828,7 +13011,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E12" s="2">
         <v>120009</v>
@@ -12842,7 +13025,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E13" s="2">
         <v>120010</v>
@@ -12856,7 +13039,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E14" s="2">
         <v>120011</v>
@@ -12870,7 +13053,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E15" s="2">
         <v>120012</v>
@@ -12884,7 +13067,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E16" s="2">
         <v>120013</v>
@@ -12898,7 +13081,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E17" s="2">
         <v>120014</v>
@@ -12912,7 +13095,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E18" s="2">
         <v>120015</v>
@@ -12926,7 +13109,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E19" s="2">
         <v>120016</v>
@@ -12940,7 +13123,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E20" s="2">
         <v>120017</v>
@@ -12954,7 +13137,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E21" s="2">
         <v>120018</v>
@@ -12968,7 +13151,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E22" s="2">
         <v>120019</v>
@@ -12982,7 +13165,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E23" s="2">
         <v>120020</v>
@@ -12996,7 +13179,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E24" s="2">
         <v>120021</v>
@@ -13010,7 +13193,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E25" s="2">
         <v>120022</v>
@@ -13024,7 +13207,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E26" s="2">
         <v>120023</v>
@@ -13038,7 +13221,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E27" s="2">
         <v>120024</v>
@@ -13052,7 +13235,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E28" s="2">
         <v>120025</v>
@@ -13066,7 +13249,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E29" s="2">
         <v>120026</v>
@@ -13080,7 +13263,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E30" s="2">
         <v>120027</v>
@@ -13094,7 +13277,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E31" s="2">
         <v>120028</v>
@@ -13108,7 +13291,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E32" s="2">
         <v>120029</v>
@@ -13122,7 +13305,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E33" s="2">
         <v>120030</v>
@@ -13136,7 +13319,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E34" s="2">
         <v>120031</v>
@@ -13150,7 +13333,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E35" s="2">
         <v>120032</v>
@@ -13164,7 +13347,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E36" s="2">
         <v>120033</v>
@@ -13178,7 +13361,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E37" s="2">
         <v>120034</v>
@@ -13192,7 +13375,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E38" s="2">
         <v>120035</v>
@@ -13206,7 +13389,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E39" s="2">
         <v>120036</v>
@@ -13220,7 +13403,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E40" s="2">
         <v>120037</v>
@@ -13234,7 +13417,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E41" s="2">
         <v>120038</v>
@@ -13248,7 +13431,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E42" s="2">
         <v>120039</v>
@@ -13262,7 +13445,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E43" s="2">
         <v>120040</v>
@@ -13293,13 +13476,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -13320,7 +13503,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -13335,13 +13518,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -13360,7 +13543,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:12">
@@ -13372,7 +13555,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:12">
@@ -13384,7 +13567,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:12">
@@ -13396,7 +13579,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:12">
@@ -13408,7 +13591,7 @@
         <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:12">
@@ -13420,7 +13603,7 @@
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:12">
@@ -13432,7 +13615,7 @@
         <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:12">
@@ -13444,7 +13627,7 @@
         <v>97</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:12">
@@ -13456,7 +13639,7 @@
         <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:12">
@@ -13468,7 +13651,7 @@
         <v>99</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:12">
@@ -13480,7 +13663,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:12">
@@ -13492,7 +13675,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
@@ -13504,7 +13687,7 @@
         <v>102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -13516,7 +13699,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -13528,7 +13711,7 @@
         <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -13540,7 +13723,7 @@
         <v>105</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -13552,7 +13735,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -13564,7 +13747,7 @@
         <v>107</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -13576,7 +13759,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -13588,7 +13771,7 @@
         <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -13600,7 +13783,7 @@
         <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -13612,7 +13795,7 @@
         <v>111</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -13624,7 +13807,7 @@
         <v>113</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -13636,7 +13819,7 @@
         <v>114</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -13648,7 +13831,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -13660,7 +13843,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -13672,7 +13855,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -13684,7 +13867,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -13696,7 +13879,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -13708,7 +13891,7 @@
         <v>121</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -13720,7 +13903,7 @@
         <v>122</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -13732,7 +13915,7 @@
         <v>123</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -13744,7 +13927,7 @@
         <v>124</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -13756,7 +13939,7 @@
         <v>125</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -13768,7 +13951,7 @@
         <v>126</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
@@ -13780,7 +13963,7 @@
         <v>127</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
@@ -13792,7 +13975,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -13804,7 +13987,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
@@ -13816,7 +13999,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:4">
@@ -13828,7 +14011,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
@@ -13840,7 +14023,7 @@
         <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
@@ -13852,7 +14035,7 @@
         <v>183</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
@@ -13864,7 +14047,7 @@
         <v>184</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
@@ -13876,7 +14059,7 @@
         <v>185</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
@@ -13888,7 +14071,7 @@
         <v>186</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
@@ -13900,7 +14083,7 @@
         <v>187</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
@@ -13912,7 +14095,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:4">
@@ -13924,7 +14107,7 @@
         <v>189</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:4">
@@ -13936,7 +14119,7 @@
         <v>190</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:4">
@@ -13948,7 +14131,7 @@
         <v>191</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:4">
@@ -13960,7 +14143,7 @@
         <v>192</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
@@ -13972,7 +14155,7 @@
         <v>193</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:4">
@@ -13984,7 +14167,7 @@
         <v>194</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
@@ -13996,7 +14179,7 @@
         <v>195</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:4">
@@ -14008,7 +14191,7 @@
         <v>196</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:4">
@@ -14020,7 +14203,7 @@
         <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:4">
@@ -14032,7 +14215,7 @@
         <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:4">
@@ -14044,7 +14227,7 @@
         <v>199</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:4">
@@ -14056,7 +14239,7 @@
         <v>200</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:4">
@@ -14068,7 +14251,7 @@
         <v>201</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:4">
@@ -14080,7 +14263,7 @@
         <v>178</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:4">
@@ -14092,7 +14275,7 @@
         <v>179</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:4">
@@ -14104,7 +14287,7 @@
         <v>180</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:4">
@@ -14116,7 +14299,7 @@
         <v>181</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:4">
@@ -14125,10 +14308,10 @@
         <v>310000</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:4">
@@ -14137,10 +14320,10 @@
         <v>310001</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:4">
@@ -14149,10 +14332,10 @@
         <v>310002</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:4">
@@ -14161,10 +14344,10 @@
         <v>310003</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:4">
@@ -14173,10 +14356,10 @@
         <v>310004</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:4">
@@ -14185,10 +14368,10 @@
         <v>310005</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:4">
@@ -14197,10 +14380,10 @@
         <v>310006</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:4">
@@ -14209,10 +14392,10 @@
         <v>310007</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:4">
@@ -14221,10 +14404,10 @@
         <v>310008</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:4">
@@ -14233,10 +14416,10 @@
         <v>310009</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:4">
@@ -14245,10 +14428,10 @@
         <v>310010</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:4">
@@ -14257,10 +14440,10 @@
         <v>310011</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:4">
@@ -14269,10 +14452,10 @@
         <v>310012</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:4">
@@ -14281,10 +14464,10 @@
         <v>310013</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:4">
@@ -14293,10 +14476,10 @@
         <v>310014</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:4">
@@ -14305,10 +14488,10 @@
         <v>310015</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:4">
@@ -14317,10 +14500,10 @@
         <v>310016</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:4">
@@ -14329,10 +14512,10 @@
         <v>310017</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:4">
@@ -14341,10 +14524,10 @@
         <v>310018</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
@@ -14353,10 +14536,10 @@
         <v>310019</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:4">
@@ -14365,10 +14548,10 @@
         <v>310020</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:4">
@@ -14377,10 +14560,10 @@
         <v>310021</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:4">
@@ -14389,10 +14572,10 @@
         <v>310022</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:4">
@@ -14401,10 +14584,10 @@
         <v>310023</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:4">
@@ -14413,10 +14596,10 @@
         <v>310024</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:4">
@@ -14425,10 +14608,10 @@
         <v>310025</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:4">
@@ -14437,10 +14620,10 @@
         <v>310026</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:4">
@@ -14449,10 +14632,10 @@
         <v>310027</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:4">
@@ -14461,10 +14644,10 @@
         <v>310028</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:4">
@@ -14473,10 +14656,10 @@
         <v>310029</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:4">
@@ -14485,10 +14668,10 @@
         <v>310030</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:4">
@@ -14497,10 +14680,10 @@
         <v>310031</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:4">
@@ -14509,10 +14692,10 @@
         <v>310032</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:4">
@@ -14521,10 +14704,10 @@
         <v>310033</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:4">
@@ -14533,10 +14716,10 @@
         <v>310034</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:4">
@@ -14545,10 +14728,10 @@
         <v>310035</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:4">
@@ -14557,10 +14740,10 @@
         <v>310036</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:4">
@@ -14569,10 +14752,10 @@
         <v>310037</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:4">
@@ -14581,10 +14764,10 @@
         <v>310038</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:4">
@@ -14593,10 +14776,10 @@
         <v>310039</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:4">
@@ -14607,7 +14790,7 @@
         <v>27</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:4">
@@ -14618,7 +14801,7 @@
         <v>30</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:4">
@@ -14629,7 +14812,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:4">
@@ -14640,7 +14823,7 @@
         <v>32</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:4">
@@ -14651,7 +14834,7 @@
         <v>33</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="2:4">
@@ -14662,7 +14845,7 @@
         <v>34</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="2:4">
@@ -14673,7 +14856,7 @@
         <v>35</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="2:4">
@@ -14684,7 +14867,7 @@
         <v>36</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="2:4">
@@ -14695,7 +14878,7 @@
         <v>37</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="2:4">
@@ -14706,7 +14889,7 @@
         <v>38</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="2:4">
@@ -14717,7 +14900,7 @@
         <v>39</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="2:4">
@@ -14728,7 +14911,7 @@
         <v>40</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="2:4">
@@ -14739,7 +14922,7 @@
         <v>41</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="2:4">
@@ -14750,7 +14933,7 @@
         <v>42</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="122" ht="16.5" spans="2:4">
@@ -14761,7 +14944,7 @@
         <v>43</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="2:4">
@@ -14772,7 +14955,7 @@
         <v>44</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="2:4">
@@ -14783,7 +14966,7 @@
         <v>45</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="2:4">
@@ -14794,7 +14977,7 @@
         <v>46</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="2:4">
@@ -14805,7 +14988,7 @@
         <v>47</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="2:4">
@@ -14816,7 +14999,7 @@
         <v>48</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="2:4">
@@ -14827,7 +15010,7 @@
         <v>49</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="2:4">
@@ -14838,7 +15021,7 @@
         <v>50</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="2:4">
@@ -14849,7 +15032,7 @@
         <v>51</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="2:4">
@@ -14860,7 +15043,7 @@
         <v>52</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="2:4">
@@ -14871,7 +15054,7 @@
         <v>53</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="2:4">
@@ -14882,7 +15065,7 @@
         <v>54</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="2:4">
@@ -14893,7 +15076,7 @@
         <v>55</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="2:4">
@@ -14904,7 +15087,7 @@
         <v>56</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="2:4">
@@ -14915,7 +15098,7 @@
         <v>58</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="2:4">
@@ -14926,7 +15109,7 @@
         <v>59</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="2:4">
@@ -14937,7 +15120,7 @@
         <v>60</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="2:4">
@@ -14948,7 +15131,7 @@
         <v>61</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="2:4">
@@ -14959,7 +15142,7 @@
         <v>62</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="2:4">
@@ -14970,7 +15153,7 @@
         <v>63</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="2:4">
@@ -14981,7 +15164,7 @@
         <v>65</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="2:4">
@@ -14992,7 +15175,7 @@
         <v>66</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="2:4">
@@ -15003,7 +15186,7 @@
         <v>67</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="2:4">
@@ -15014,7 +15197,7 @@
         <v>68</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="2:4">
@@ -15025,7 +15208,7 @@
         <v>69</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="2:4">
@@ -15036,7 +15219,7 @@
         <v>71</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="2:4">
@@ -15047,7 +15230,7 @@
         <v>72</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="2:4">
@@ -15058,7 +15241,7 @@
         <v>73</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="2:4">
@@ -15069,7 +15252,7 @@
         <v>74</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="2:4">
@@ -15080,7 +15263,7 @@
         <v>75</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="2:4">
@@ -15091,7 +15274,7 @@
         <v>76</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="2:4">
@@ -15102,7 +15285,7 @@
         <v>77</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="2:4">
@@ -15113,7 +15296,7 @@
         <v>78</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="2:4">
@@ -15124,7 +15307,7 @@
         <v>79</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="2:4">
@@ -15135,7 +15318,7 @@
         <v>80</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="2:4">
@@ -15146,7 +15329,7 @@
         <v>81</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="2:4">
@@ -15157,7 +15340,7 @@
         <v>82</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="2:4">
@@ -15168,7 +15351,7 @@
         <v>84</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="2:4">
@@ -15179,7 +15362,7 @@
         <v>85</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="2:4">
@@ -15190,7 +15373,7 @@
         <v>86</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="2:4">
@@ -15201,7 +15384,7 @@
         <v>87</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="2:4">
@@ -15212,7 +15395,7 @@
         <v>202</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="2:4">
@@ -15223,7 +15406,7 @@
         <v>203</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="2:4">
@@ -15234,7 +15417,7 @@
         <v>204</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="2:4">
@@ -15245,7 +15428,7 @@
         <v>205</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="2:4">
@@ -15256,7 +15439,7 @@
         <v>206</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="2:4">
@@ -15267,7 +15450,7 @@
         <v>207</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="2:4">
@@ -15278,7 +15461,7 @@
         <v>208</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="2:4">
@@ -15289,7 +15472,7 @@
         <v>209</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="2:4">
@@ -15300,7 +15483,7 @@
         <v>210</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="2:4">
@@ -15311,7 +15494,7 @@
         <v>211</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="2:4">
@@ -15322,7 +15505,7 @@
         <v>262</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="2:4">
@@ -15333,7 +15516,7 @@
         <v>264</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="2:4">
@@ -15344,7 +15527,7 @@
         <v>265</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="2:4">
@@ -15352,10 +15535,10 @@
         <v>140000</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="2:4">
@@ -15363,10 +15546,10 @@
         <v>140001</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="2:4">
@@ -15374,10 +15557,10 @@
         <v>140002</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="2:4">
@@ -15385,10 +15568,10 @@
         <v>140003</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="2:4">
@@ -15396,10 +15579,10 @@
         <v>150000</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="2:4">
@@ -15407,10 +15590,10 @@
         <v>150001</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="2:4">
@@ -15418,10 +15601,10 @@
         <v>150002</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="2:4">
@@ -15429,10 +15612,10 @@
         <v>150003</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="2:4">
@@ -15440,10 +15623,10 @@
         <v>150004</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="2:4">
@@ -15451,10 +15634,10 @@
         <v>150005</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="2:4">
@@ -15462,10 +15645,10 @@
         <v>150006</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="2:4">
@@ -15473,10 +15656,10 @@
         <v>150007</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="2:4">
@@ -15484,10 +15667,10 @@
         <v>150008</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="2:4">
@@ -15495,10 +15678,10 @@
         <v>150009</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="2:4">

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32390" windowHeight="17680" tabRatio="500"/>
+    <workbookView windowHeight="17680" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="411">
   <si>
     <t>##var</t>
   </si>
@@ -1276,6 +1276,9 @@
   </si>
   <si>
     <t>AdultProduct</t>
+  </si>
+  <si>
+    <t>FishingProduct</t>
   </si>
 </sst>
 </file>
@@ -8742,15 +8745,15 @@
         <v>234</v>
       </c>
       <c r="D196" s="1" t="str">
-        <f t="shared" ref="D196:D235" si="9">CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" ref="D196:D240" si="9">CONCATENATE(B:B,"Name.png")</f>
         <v>240002Name.png</v>
       </c>
       <c r="E196" s="1" t="str">
-        <f t="shared" ref="E196:E235" si="10">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" ref="E196:E240" si="10">CONCATENATE("InventoryItem+",B:B,"Name")</f>
         <v>InventoryItem+240002Name</v>
       </c>
       <c r="F196" s="1" t="str">
-        <f t="shared" ref="F196:F235" si="11">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" ref="F196:F240" si="11">CONCATENATE("InventoryItem+",B:B,"Text")</f>
         <v>InventoryItem+240002Text</v>
       </c>
       <c r="G196" s="1" t="s">
@@ -9897,15 +9900,15 @@
         <v>271</v>
       </c>
       <c r="D231" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>131004Name.png</v>
       </c>
       <c r="E231" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+131004Name</v>
       </c>
       <c r="F231" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+131004Text</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -9930,15 +9933,15 @@
         <v>272</v>
       </c>
       <c r="D232" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140000Name.png</v>
       </c>
       <c r="E232" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140000Name</v>
       </c>
       <c r="F232" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140000Text</v>
       </c>
       <c r="G232" s="1" t="s">
@@ -9963,15 +9966,15 @@
         <v>273</v>
       </c>
       <c r="D233" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140001Name.png</v>
       </c>
       <c r="E233" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140001Name</v>
       </c>
       <c r="F233" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140001Text</v>
       </c>
       <c r="G233" s="1" t="s">
@@ -9996,15 +9999,15 @@
         <v>274</v>
       </c>
       <c r="D234" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140002Name.png</v>
       </c>
       <c r="E234" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140002Name</v>
       </c>
       <c r="F234" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140002Text</v>
       </c>
       <c r="G234" s="1" t="s">
@@ -10029,15 +10032,15 @@
         <v>275</v>
       </c>
       <c r="D235" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>140003Name.png</v>
       </c>
       <c r="E235" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+140003Name</v>
       </c>
       <c r="F235" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+140003Text</v>
       </c>
       <c r="G235" s="1" t="s">
@@ -10062,15 +10065,15 @@
         <v>276</v>
       </c>
       <c r="D236" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150000Name.png</v>
       </c>
       <c r="E236" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150000Name</v>
       </c>
       <c r="F236" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150000Text</v>
       </c>
       <c r="G236" s="1" t="s">
@@ -10095,15 +10098,15 @@
         <v>277</v>
       </c>
       <c r="D237" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150001Name.png</v>
       </c>
       <c r="E237" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150001Name</v>
       </c>
       <c r="F237" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150001Text</v>
       </c>
       <c r="G237" s="1" t="s">
@@ -10128,15 +10131,15 @@
         <v>278</v>
       </c>
       <c r="D238" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150002Name.png</v>
       </c>
       <c r="E238" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150002Name</v>
       </c>
       <c r="F238" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150002Text</v>
       </c>
       <c r="G238" s="1" t="s">
@@ -10161,15 +10164,15 @@
         <v>279</v>
       </c>
       <c r="D239" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150003Name.png</v>
       </c>
       <c r="E239" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150003Name</v>
       </c>
       <c r="F239" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150003Text</v>
       </c>
       <c r="G239" s="1" t="s">
@@ -10194,15 +10197,15 @@
         <v>280</v>
       </c>
       <c r="D240" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="9"/>
         <v>150004Name.png</v>
       </c>
       <c r="E240" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="10"/>
         <v>InventoryItem+150004Name</v>
       </c>
       <c r="F240" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="11"/>
         <v>InventoryItem+150004Text</v>
       </c>
       <c r="G240" s="1" t="s">
@@ -15541,7 +15544,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="177" ht="16.5" spans="2:4">
+    <row r="177" ht="16.5" spans="1:10">
       <c r="B177" s="1">
         <v>140001</v>
       </c>
@@ -15552,7 +15555,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="178" ht="16.5" spans="2:4">
+    <row r="178" ht="16.5" spans="1:10">
       <c r="B178" s="1">
         <v>140002</v>
       </c>
@@ -15563,7 +15566,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="179" ht="16.5" spans="2:4">
+    <row r="179" ht="16.5" spans="1:10">
       <c r="B179" s="1">
         <v>140003</v>
       </c>
@@ -15574,7 +15577,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="180" ht="16.5" spans="2:4">
+    <row r="180" ht="16.5" spans="1:10">
       <c r="B180" s="1">
         <v>150000</v>
       </c>
@@ -15585,7 +15588,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="181" ht="16.5" spans="2:4">
+    <row r="181" ht="16.5" spans="1:10">
       <c r="B181" s="1">
         <v>150001</v>
       </c>
@@ -15596,7 +15599,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="182" ht="16.5" spans="2:4">
+    <row r="182" ht="16.5" spans="1:10">
       <c r="B182" s="1">
         <v>150002</v>
       </c>
@@ -15607,7 +15610,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="183" ht="16.5" spans="2:4">
+    <row r="183" ht="16.5" spans="1:10">
       <c r="B183" s="1">
         <v>150003</v>
       </c>
@@ -15618,7 +15621,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="184" ht="16.5" spans="2:4">
+    <row r="184" ht="16.5" spans="1:10">
       <c r="B184" s="1">
         <v>150004</v>
       </c>
@@ -15629,7 +15632,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="185" ht="16.5" spans="2:4">
+    <row r="185" ht="16.5" spans="1:10">
       <c r="B185" s="1">
         <v>150005</v>
       </c>
@@ -15640,7 +15643,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="186" ht="16.5" spans="2:4">
+    <row r="186" ht="16.5" spans="1:10">
       <c r="B186" s="1">
         <v>150006</v>
       </c>
@@ -15651,7 +15654,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="187" ht="16.5" spans="2:4">
+    <row r="187" ht="16.5" spans="1:10">
       <c r="B187" s="1">
         <v>150007</v>
       </c>
@@ -15662,7 +15665,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="188" ht="16.5" spans="2:4">
+    <row r="188" ht="16.5" spans="1:10">
       <c r="B188" s="1">
         <v>150008</v>
       </c>
@@ -15673,7 +15676,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="189" ht="16.5" spans="2:4">
+    <row r="189" ht="16.5" spans="1:10">
       <c r="B189" s="1">
         <v>150009</v>
       </c>
@@ -15684,47 +15687,137 @@
         <v>409</v>
       </c>
     </row>
-    <row r="200" ht="16.5" spans="2:4">
+    <row r="190" ht="16.5" spans="1:10">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1">
+        <v>131000</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+    </row>
+    <row r="191" ht="16.5" spans="1:10">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1">
+        <v>131001</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+    </row>
+    <row r="192" ht="16.5" spans="1:10">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1">
+        <v>131002</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+    </row>
+    <row r="193" ht="16.5" spans="1:10">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1">
+        <v>131003</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+    </row>
+    <row r="194" ht="16.5" spans="1:10">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1">
+        <v>131004</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+    </row>
+    <row r="200" ht="16.5" spans="1:10">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
     </row>
-    <row r="201" ht="16.5" spans="2:4">
+    <row r="201" ht="16.5" spans="1:10">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
     </row>
-    <row r="202" ht="16.5" spans="2:4">
+    <row r="202" ht="16.5" spans="1:10">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
     </row>
-    <row r="203" ht="16.5" spans="2:4">
+    <row r="203" ht="16.5" spans="1:10">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
     </row>
-    <row r="204" ht="16.5" spans="2:4">
+    <row r="204" ht="16.5" spans="1:10">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
     </row>
-    <row r="205" ht="16.5" spans="2:4">
+    <row r="205" ht="16.5" spans="1:10">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
     </row>
-    <row r="206" ht="16.5" spans="2:4">
+    <row r="206" ht="16.5" spans="1:10">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
     </row>
-    <row r="207" ht="16.5" spans="2:4">
+    <row r="207" ht="16.5" spans="1:10">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
     </row>
-    <row r="208" ht="16.5" spans="2:4">
+    <row r="208" ht="16.5" spans="1:10">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView windowHeight="17680" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="440">
   <si>
     <t>##var</t>
   </si>
@@ -1378,7 +1378,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1393,6 +1393,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1884,31 +1890,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1917,119 +1920,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2039,6 +2045,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2052,17 +2061,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2119,6 +2122,18 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2384,16 +2399,16 @@
   <dimension ref="A1:R314"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="10"/>
-    <col min="3" max="3" width="29.0833333333333" style="11" customWidth="1"/>
-    <col min="4" max="4" width="33.5" style="11" customWidth="1"/>
-    <col min="5" max="5" width="58.75" style="11" customWidth="1"/>
-    <col min="6" max="6" width="42.3333333333333" style="11" customWidth="1"/>
-    <col min="7" max="7" width="21.1666666666667" style="10" customWidth="1"/>
-    <col min="8" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="16.0833333333333" style="10" customWidth="1"/>
-    <col min="10" max="10" width="22.75" style="10" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="10"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="29.0833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="58.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="16.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.75" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2493,7 +2508,6 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>100000</v>
       </c>
@@ -2526,7 +2540,6 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>100001</v>
       </c>
@@ -2559,7 +2572,6 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>100002</v>
       </c>
@@ -2592,7 +2604,6 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>100003</v>
       </c>
@@ -2625,7 +2636,6 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>100004</v>
       </c>
@@ -2658,7 +2668,6 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>100005</v>
       </c>
@@ -2691,7 +2700,6 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>100006</v>
       </c>
@@ -2724,7 +2732,6 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>100007</v>
       </c>
@@ -2757,7 +2764,6 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>100008</v>
       </c>
@@ -2790,7 +2796,6 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>100009</v>
       </c>
@@ -2823,7 +2828,6 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>100010</v>
       </c>
@@ -2856,7 +2860,6 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>100011</v>
       </c>
@@ -2889,7 +2892,6 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>100012</v>
       </c>
@@ -2921,8 +2923,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1"/>
+    <row r="17" spans="2:18">
       <c r="B17" s="1">
         <v>100013</v>
       </c>
@@ -2954,8 +2955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1"/>
+    <row r="18" spans="2:18">
       <c r="B18" s="1">
         <v>100014</v>
       </c>
@@ -2987,8 +2987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1"/>
+    <row r="19" spans="2:18">
       <c r="B19" s="1">
         <v>100015</v>
       </c>
@@ -3020,8 +3019,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1"/>
+    <row r="20" spans="2:18">
       <c r="B20" s="1">
         <v>100016</v>
       </c>
@@ -3053,8 +3051,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1"/>
+    <row r="21" spans="2:18">
       <c r="B21" s="1">
         <v>100017</v>
       </c>
@@ -3086,8 +3083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1"/>
+    <row r="22" spans="2:18">
       <c r="B22" s="1">
         <v>100018</v>
       </c>
@@ -3119,8 +3115,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1"/>
+    <row r="23" spans="2:18">
       <c r="B23" s="1">
         <v>100019</v>
       </c>
@@ -3151,13 +3146,12 @@
       <c r="J23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" s="1">
         <v>100020</v>
       </c>
@@ -3189,8 +3183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1"/>
+    <row r="25" spans="2:18">
       <c r="B25" s="1">
         <v>100021</v>
       </c>
@@ -3222,8 +3215,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1"/>
+    <row r="26" spans="2:18">
       <c r="B26" s="1">
         <v>100022</v>
       </c>
@@ -3255,8 +3247,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1"/>
+    <row r="27" spans="2:18">
       <c r="B27" s="1">
         <v>100023</v>
       </c>
@@ -3288,8 +3279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="1"/>
+    <row r="28" spans="2:18">
       <c r="B28" s="1">
         <v>100024</v>
       </c>
@@ -3321,8 +3311,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="1"/>
+    <row r="29" spans="2:18">
       <c r="B29" s="1">
         <v>100025</v>
       </c>
@@ -3354,8 +3343,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="1"/>
+    <row r="30" spans="2:18">
       <c r="B30" s="1">
         <v>100026</v>
       </c>
@@ -3387,8 +3375,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="1"/>
+    <row r="31" spans="2:18">
       <c r="B31" s="1">
         <v>100027</v>
       </c>
@@ -3420,8 +3407,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="1"/>
+    <row r="32" spans="2:18">
       <c r="B32" s="1">
         <v>100028</v>
       </c>
@@ -3453,8 +3439,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="1"/>
+    <row r="33" spans="2:10">
       <c r="B33" s="1">
         <v>100029</v>
       </c>
@@ -3486,8 +3471,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="1"/>
+    <row r="34" spans="2:10">
       <c r="B34" s="1">
         <v>100030</v>
       </c>
@@ -3519,8 +3503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="1"/>
+    <row r="35" spans="2:10">
       <c r="B35" s="1">
         <v>100031</v>
       </c>
@@ -3552,8 +3535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="1"/>
+    <row r="36" spans="2:10">
       <c r="B36" s="1">
         <v>100032</v>
       </c>
@@ -3585,8 +3567,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="1"/>
+    <row r="37" spans="2:10">
       <c r="B37" s="1">
         <v>100033</v>
       </c>
@@ -3618,8 +3599,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="1"/>
+    <row r="38" spans="2:10">
       <c r="B38" s="1">
         <v>100034</v>
       </c>
@@ -3651,8 +3631,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="1"/>
+    <row r="39" spans="2:10">
       <c r="B39" s="1">
         <v>100035</v>
       </c>
@@ -3684,8 +3663,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="1"/>
+    <row r="40" spans="2:10">
       <c r="B40" s="1">
         <v>100036</v>
       </c>
@@ -3717,8 +3695,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="1"/>
+    <row r="41" spans="2:10">
       <c r="B41" s="1">
         <v>100037</v>
       </c>
@@ -3750,8 +3727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="1"/>
+    <row r="42" spans="2:10">
       <c r="B42" s="1">
         <v>100038</v>
       </c>
@@ -3783,8 +3759,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="1"/>
+    <row r="43" spans="2:10">
       <c r="B43" s="1">
         <v>100039</v>
       </c>
@@ -3816,8 +3791,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="1"/>
+    <row r="44" spans="2:10">
       <c r="B44" s="1">
         <v>100040</v>
       </c>
@@ -3849,8 +3823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="1"/>
+    <row r="45" spans="2:10">
       <c r="B45" s="1">
         <v>100041</v>
       </c>
@@ -3882,8 +3855,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="1"/>
+    <row r="46" spans="2:10">
       <c r="B46" s="1">
         <v>100042</v>
       </c>
@@ -3915,8 +3887,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="1"/>
+    <row r="47" spans="2:10">
       <c r="B47" s="1">
         <v>100043</v>
       </c>
@@ -3948,8 +3919,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="1"/>
+    <row r="48" spans="2:10">
       <c r="B48" s="1">
         <v>100044</v>
       </c>
@@ -3981,8 +3951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="1"/>
+    <row r="49" spans="2:10">
       <c r="B49" s="1">
         <v>100045</v>
       </c>
@@ -4014,8 +3983,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="1"/>
+    <row r="50" spans="2:10">
       <c r="B50" s="1">
         <v>100046</v>
       </c>
@@ -4047,8 +4015,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="1"/>
+    <row r="51" spans="2:10">
       <c r="B51" s="1">
         <v>100047</v>
       </c>
@@ -4080,8 +4047,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="1"/>
+    <row r="52" spans="2:10">
       <c r="B52" s="1">
         <v>100048</v>
       </c>
@@ -4113,8 +4079,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="1"/>
+    <row r="53" spans="2:10">
       <c r="B53" s="1">
         <v>100049</v>
       </c>
@@ -4146,8 +4111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="1"/>
+    <row r="54" spans="2:10">
       <c r="B54" s="1">
         <v>100051</v>
       </c>
@@ -4179,8 +4143,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="1"/>
+    <row r="55" spans="2:10">
       <c r="B55" s="1">
         <v>100052</v>
       </c>
@@ -4212,8 +4175,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="1"/>
+    <row r="56" spans="2:10">
       <c r="B56" s="1">
         <v>100053</v>
       </c>
@@ -4245,8 +4207,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="1"/>
+    <row r="57" spans="2:10">
       <c r="B57" s="1">
         <v>100054</v>
       </c>
@@ -4278,8 +4239,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="1"/>
+    <row r="58" spans="2:10">
       <c r="B58" s="1">
         <v>100055</v>
       </c>
@@ -4311,8 +4271,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="1"/>
+    <row r="59" spans="2:10">
       <c r="B59" s="1">
         <v>100056</v>
       </c>
@@ -4344,8 +4303,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="1"/>
+    <row r="60" spans="2:10">
       <c r="B60" s="1">
         <v>100057</v>
       </c>
@@ -4377,8 +4335,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="1"/>
+    <row r="61" spans="2:10">
       <c r="B61" s="1">
         <v>100058</v>
       </c>
@@ -4410,8 +4367,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="1"/>
+    <row r="62" spans="2:10">
       <c r="B62" s="1">
         <v>100059</v>
       </c>
@@ -4443,8 +4399,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="1"/>
+    <row r="63" spans="2:10">
       <c r="B63" s="1">
         <v>100060</v>
       </c>
@@ -4476,8 +4431,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="1"/>
+    <row r="64" spans="2:10">
       <c r="B64" s="1">
         <v>100061</v>
       </c>
@@ -4509,8 +4463,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="1"/>
+    <row r="65" spans="2:10">
       <c r="B65" s="1">
         <v>100062</v>
       </c>
@@ -4542,8 +4495,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="1"/>
+    <row r="66" spans="2:10">
       <c r="B66" s="1">
         <v>100063</v>
       </c>
@@ -4575,8 +4527,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="1"/>
+    <row r="67" spans="2:10">
       <c r="B67" s="1">
         <v>100064</v>
       </c>
@@ -4608,8 +4559,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="1"/>
+    <row r="68" spans="2:10">
       <c r="B68" s="1">
         <v>100065</v>
       </c>
@@ -4617,15 +4567,15 @@
         <v>97</v>
       </c>
       <c r="D68" s="1" t="str">
-        <f t="shared" ref="D68:D87" si="3">CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" ref="D68:D96" si="3">CONCATENATE(B:B,"Name.png")</f>
         <v>100065Name.png</v>
       </c>
       <c r="E68" s="1" t="str">
-        <f t="shared" ref="E68:E87" si="4">CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" ref="E68:E96" si="4">CONCATENATE("InventoryItem+",B:B,"Name")</f>
         <v>InventoryItem+100065Name</v>
       </c>
       <c r="F68" s="1" t="str">
-        <f t="shared" ref="F68:F87" si="5">CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" ref="F68:F96" si="5">CONCATENATE("InventoryItem+",B:B,"Text")</f>
         <v>InventoryItem+100065Text</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -4641,8 +4591,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="1"/>
+    <row r="69" spans="2:10">
       <c r="B69" s="1">
         <v>100066</v>
       </c>
@@ -4674,8 +4623,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
-      <c r="A70" s="1"/>
+    <row r="70" spans="2:10">
       <c r="B70" s="1">
         <v>100067</v>
       </c>
@@ -4707,8 +4655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="1"/>
+    <row r="71" spans="2:10">
       <c r="B71" s="1">
         <v>100068</v>
       </c>
@@ -4740,8 +4687,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
-      <c r="A72" s="1"/>
+    <row r="72" spans="2:10">
       <c r="B72" s="1">
         <v>100069</v>
       </c>
@@ -4773,8 +4719,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="1"/>
+    <row r="73" spans="2:10">
       <c r="B73" s="1">
         <v>100070</v>
       </c>
@@ -4806,8 +4751,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="1"/>
+    <row r="74" spans="2:10">
       <c r="B74" s="1">
         <v>100071</v>
       </c>
@@ -4839,8 +4783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="1"/>
+    <row r="75" spans="2:10">
       <c r="B75" s="1">
         <v>100072</v>
       </c>
@@ -4872,8 +4815,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="1"/>
+    <row r="76" spans="2:10">
       <c r="B76" s="1">
         <v>100073</v>
       </c>
@@ -4905,8 +4847,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
-      <c r="A77" s="1"/>
+    <row r="77" spans="2:10">
       <c r="B77" s="1">
         <v>100074</v>
       </c>
@@ -4938,8 +4879,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="1"/>
+    <row r="78" spans="2:10">
       <c r="B78" s="1">
         <v>100075</v>
       </c>
@@ -4971,8 +4911,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="1"/>
+    <row r="79" spans="2:10">
       <c r="B79" s="1">
         <v>100076</v>
       </c>
@@ -5004,8 +4943,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="1"/>
+    <row r="80" spans="2:10">
       <c r="B80" s="1">
         <v>100077</v>
       </c>
@@ -5037,8 +4975,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="1"/>
+    <row r="81" spans="2:10">
       <c r="B81" s="1">
         <v>100078</v>
       </c>
@@ -5070,8 +5007,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="1"/>
+    <row r="82" spans="2:10">
       <c r="B82" s="1">
         <v>100079</v>
       </c>
@@ -5103,8 +5039,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="1"/>
+    <row r="83" spans="2:10">
       <c r="B83" s="1">
         <v>100080</v>
       </c>
@@ -5136,8 +5071,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="1"/>
+    <row r="84" spans="2:10">
       <c r="B84" s="1">
         <v>100081</v>
       </c>
@@ -5169,8 +5103,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="1"/>
+    <row r="85" spans="2:10">
       <c r="B85" s="1">
         <v>100082</v>
       </c>
@@ -5202,8 +5135,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="1"/>
+    <row r="86" spans="2:10">
       <c r="B86" s="1">
         <v>100083</v>
       </c>
@@ -5235,8 +5167,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
-      <c r="A87" s="1"/>
+    <row r="87" spans="2:10">
       <c r="B87" s="1">
         <v>100084</v>
       </c>
@@ -5268,8 +5199,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
-      <c r="A88" s="1"/>
+    <row r="88" spans="2:10">
       <c r="B88" s="1">
         <v>110000</v>
       </c>
@@ -5277,15 +5207,15 @@
         <v>117</v>
       </c>
       <c r="D88" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110000Name.png</v>
       </c>
       <c r="E88" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110000Name</v>
       </c>
       <c r="F88" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110000Text</v>
       </c>
       <c r="G88" s="1" t="s">
@@ -5301,8 +5231,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="1"/>
+    <row r="89" spans="2:10">
       <c r="B89" s="1">
         <v>110001</v>
       </c>
@@ -5310,15 +5239,15 @@
         <v>119</v>
       </c>
       <c r="D89" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110001Name.png</v>
       </c>
       <c r="E89" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110001Name</v>
       </c>
       <c r="F89" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110001Text</v>
       </c>
       <c r="G89" s="1" t="s">
@@ -5334,8 +5263,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="1"/>
+    <row r="90" spans="2:10">
       <c r="B90" s="1">
         <v>110002</v>
       </c>
@@ -5343,15 +5271,15 @@
         <v>120</v>
       </c>
       <c r="D90" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110002Name.png</v>
       </c>
       <c r="E90" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110002Name</v>
       </c>
       <c r="F90" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110002Text</v>
       </c>
       <c r="G90" s="1" t="s">
@@ -5367,8 +5295,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
-      <c r="A91" s="1"/>
+    <row r="91" spans="2:10">
       <c r="B91" s="1">
         <v>110003</v>
       </c>
@@ -5376,15 +5303,15 @@
         <v>121</v>
       </c>
       <c r="D91" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110003Name.png</v>
       </c>
       <c r="E91" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110003Name</v>
       </c>
       <c r="F91" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110003Text</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -5400,8 +5327,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="1"/>
+    <row r="92" spans="2:10">
       <c r="B92" s="1">
         <v>110004</v>
       </c>
@@ -5409,15 +5335,15 @@
         <v>122</v>
       </c>
       <c r="D92" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110004Name.png</v>
       </c>
       <c r="E92" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110004Name</v>
       </c>
       <c r="F92" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110004Text</v>
       </c>
       <c r="G92" s="1" t="s">
@@ -5433,8 +5359,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
-      <c r="A93" s="1"/>
+    <row r="93" spans="2:10">
       <c r="B93" s="1">
         <v>110005</v>
       </c>
@@ -5442,15 +5367,15 @@
         <v>123</v>
       </c>
       <c r="D93" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110005Name.png</v>
       </c>
       <c r="E93" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110005Name</v>
       </c>
       <c r="F93" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110005Text</v>
       </c>
       <c r="G93" s="1" t="s">
@@ -5466,8 +5391,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
-      <c r="A94" s="1"/>
+    <row r="94" spans="2:10">
       <c r="B94" s="1">
         <v>110006</v>
       </c>
@@ -5475,15 +5399,15 @@
         <v>124</v>
       </c>
       <c r="D94" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110006Name.png</v>
       </c>
       <c r="E94" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110006Name</v>
       </c>
       <c r="F94" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110006Text</v>
       </c>
       <c r="G94" s="1" t="s">
@@ -5499,8 +5423,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
-      <c r="A95" s="1"/>
+    <row r="95" spans="2:10">
       <c r="B95" s="1">
         <v>110007</v>
       </c>
@@ -5508,15 +5431,15 @@
         <v>126</v>
       </c>
       <c r="D95" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110007Name.png</v>
       </c>
       <c r="E95" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110007Name</v>
       </c>
       <c r="F95" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110007Text</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -5532,8 +5455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="1"/>
+    <row r="96" spans="2:10">
       <c r="B96" s="1">
         <v>110008</v>
       </c>
@@ -5541,15 +5463,15 @@
         <v>127</v>
       </c>
       <c r="D96" s="1" t="str">
-        <f>CONCATENATE(B:B,"Name.png")</f>
+        <f t="shared" si="3"/>
         <v>110008Name.png</v>
       </c>
       <c r="E96" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Name")</f>
+        <f t="shared" si="4"/>
         <v>InventoryItem+110008Name</v>
       </c>
       <c r="F96" s="1" t="str">
-        <f>CONCATENATE("InventoryItem+",B:B,"Text")</f>
+        <f t="shared" si="5"/>
         <v>InventoryItem+110008Text</v>
       </c>
       <c r="G96" s="1" t="s">
@@ -5565,8 +5487,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
-      <c r="A97" s="1"/>
+    <row r="97" spans="2:10">
       <c r="B97" s="1">
         <v>110009</v>
       </c>
@@ -5598,8 +5519,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="1"/>
+    <row r="98" spans="2:10">
       <c r="B98" s="1">
         <v>110010</v>
       </c>
@@ -5631,8 +5551,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="1"/>
+    <row r="99" spans="2:10">
       <c r="B99" s="1">
         <v>110011</v>
       </c>
@@ -5664,8 +5583,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="1"/>
+    <row r="100" spans="2:10">
       <c r="B100" s="1">
         <v>110012</v>
       </c>
@@ -5697,8 +5615,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
-      <c r="A101" s="1"/>
+    <row r="101" spans="2:10">
       <c r="B101" s="1">
         <v>110013</v>
       </c>
@@ -5730,8 +5647,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="1"/>
+    <row r="102" spans="2:10">
       <c r="B102" s="1">
         <v>110014</v>
       </c>
@@ -5763,8 +5679,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="1"/>
+    <row r="103" spans="2:10">
       <c r="B103" s="1">
         <v>110015</v>
       </c>
@@ -5796,8 +5711,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="1"/>
+    <row r="104" spans="2:10">
       <c r="B104" s="1">
         <v>110016</v>
       </c>
@@ -5829,8 +5743,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="1"/>
+    <row r="105" spans="2:10">
       <c r="B105" s="1">
         <v>110017</v>
       </c>
@@ -5862,8 +5775,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="1"/>
+    <row r="106" spans="2:10">
       <c r="B106" s="1">
         <v>110018</v>
       </c>
@@ -5895,8 +5807,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="1"/>
+    <row r="107" spans="2:10">
       <c r="B107" s="1">
         <v>110019</v>
       </c>
@@ -5928,8 +5839,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="1"/>
+    <row r="108" spans="2:10">
       <c r="B108" s="1">
         <v>110020</v>
       </c>
@@ -5961,8 +5871,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="1"/>
+    <row r="109" spans="2:10">
       <c r="B109" s="1">
         <v>110021</v>
       </c>
@@ -5994,8 +5903,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="1"/>
+    <row r="110" spans="2:10">
       <c r="B110" s="1">
         <v>110022</v>
       </c>
@@ -6027,8 +5935,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
-      <c r="A111" s="1"/>
+    <row r="111" spans="2:10">
       <c r="B111" s="1">
         <v>110023</v>
       </c>
@@ -6060,8 +5967,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="1"/>
+    <row r="112" spans="2:10">
       <c r="B112" s="1">
         <v>110024</v>
       </c>
@@ -6093,8 +5999,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="1"/>
+    <row r="113" spans="2:10">
       <c r="B113" s="1">
         <v>110025</v>
       </c>
@@ -6126,8 +6031,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="1"/>
+    <row r="114" spans="2:10">
       <c r="B114" s="1">
         <v>110026</v>
       </c>
@@ -6159,8 +6063,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="1"/>
+    <row r="115" spans="2:10">
       <c r="B115" s="1">
         <v>110027</v>
       </c>
@@ -6192,8 +6095,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="1"/>
+    <row r="116" spans="2:10">
       <c r="B116" s="1">
         <v>110028</v>
       </c>
@@ -6225,8 +6127,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="1"/>
+    <row r="117" spans="2:10">
       <c r="B117" s="1">
         <v>110029</v>
       </c>
@@ -6258,8 +6159,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="1"/>
+    <row r="118" spans="2:10">
       <c r="B118" s="1">
         <v>110030</v>
       </c>
@@ -6291,8 +6191,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="1"/>
+    <row r="119" spans="2:10">
       <c r="B119" s="1">
         <v>110031</v>
       </c>
@@ -6324,8 +6223,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
-      <c r="A120" s="1"/>
+    <row r="120" spans="2:10">
       <c r="B120" s="1">
         <v>110032</v>
       </c>
@@ -6357,8 +6255,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
-      <c r="A121" s="1"/>
+    <row r="121" spans="2:10">
       <c r="B121" s="1">
         <v>110033</v>
       </c>
@@ -6390,8 +6287,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
-      <c r="A122" s="1"/>
+    <row r="122" spans="2:10">
       <c r="B122" s="1">
         <v>110034</v>
       </c>
@@ -6423,8 +6319,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="1"/>
+    <row r="123" spans="2:10">
       <c r="B123" s="1">
         <v>110035</v>
       </c>
@@ -6456,8 +6351,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="1"/>
+    <row r="124" spans="2:10">
       <c r="B124" s="1">
         <v>110036</v>
       </c>
@@ -6489,8 +6383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="1"/>
+    <row r="125" spans="2:10">
       <c r="B125" s="1">
         <v>110037</v>
       </c>
@@ -6522,8 +6415,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="1"/>
+    <row r="126" spans="2:10">
       <c r="B126" s="1">
         <v>110038</v>
       </c>
@@ -6555,8 +6447,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
-      <c r="A127" s="1"/>
+    <row r="127" spans="2:10">
       <c r="B127" s="1">
         <v>110039</v>
       </c>
@@ -6588,8 +6479,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
-      <c r="A128" s="1"/>
+    <row r="128" spans="2:10">
       <c r="B128" s="1">
         <v>120000</v>
       </c>
@@ -6621,8 +6511,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
-      <c r="A129" s="1"/>
+    <row r="129" spans="2:10">
       <c r="B129" s="1">
         <v>120001</v>
       </c>
@@ -6654,8 +6543,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
-      <c r="A130" s="1"/>
+    <row r="130" spans="2:10">
       <c r="B130" s="1">
         <v>120002</v>
       </c>
@@ -6687,8 +6575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
-      <c r="A131" s="1"/>
+    <row r="131" spans="2:10">
       <c r="B131" s="1">
         <v>120003</v>
       </c>
@@ -6720,8 +6607,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
-      <c r="A132" s="1"/>
+    <row r="132" spans="2:10">
       <c r="B132" s="1">
         <v>120004</v>
       </c>
@@ -6753,8 +6639,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
-      <c r="A133" s="1"/>
+    <row r="133" spans="2:10">
       <c r="B133" s="1">
         <v>120005</v>
       </c>
@@ -6786,8 +6671,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
-      <c r="A134" s="1"/>
+    <row r="134" spans="2:10">
       <c r="B134" s="1">
         <v>120006</v>
       </c>
@@ -6819,8 +6703,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
-      <c r="A135" s="1"/>
+    <row r="135" spans="2:10">
       <c r="B135" s="1">
         <v>120007</v>
       </c>
@@ -6852,8 +6735,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
-      <c r="A136" s="1"/>
+    <row r="136" spans="2:10">
       <c r="B136" s="1">
         <v>120008</v>
       </c>
@@ -6885,8 +6767,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
-      <c r="A137" s="1"/>
+    <row r="137" spans="2:10">
       <c r="B137" s="1">
         <v>120009</v>
       </c>
@@ -6918,8 +6799,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
-      <c r="A138" s="1"/>
+    <row r="138" spans="2:10">
       <c r="B138" s="1">
         <v>120010</v>
       </c>
@@ -6951,8 +6831,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
-      <c r="A139" s="1"/>
+    <row r="139" spans="2:10">
       <c r="B139" s="1">
         <v>120011</v>
       </c>
@@ -6984,8 +6863,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
-      <c r="A140" s="1"/>
+    <row r="140" spans="2:10">
       <c r="B140" s="1">
         <v>120012</v>
       </c>
@@ -7017,8 +6895,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
-      <c r="A141" s="1"/>
+    <row r="141" spans="2:10">
       <c r="B141" s="1">
         <v>120013</v>
       </c>
@@ -7050,8 +6927,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
-      <c r="A142" s="1"/>
+    <row r="142" spans="2:10">
       <c r="B142" s="1">
         <v>120014</v>
       </c>
@@ -7083,8 +6959,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
-      <c r="A143" s="1"/>
+    <row r="143" spans="2:10">
       <c r="B143" s="1">
         <v>120015</v>
       </c>
@@ -7116,8 +6991,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
-      <c r="A144" s="1"/>
+    <row r="144" spans="2:10">
       <c r="B144" s="1">
         <v>120016</v>
       </c>
@@ -7149,8 +7023,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
-      <c r="A145" s="1"/>
+    <row r="145" spans="2:10">
       <c r="B145" s="1">
         <v>120017</v>
       </c>
@@ -7182,8 +7055,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
-      <c r="A146" s="1"/>
+    <row r="146" spans="2:10">
       <c r="B146" s="1">
         <v>120018</v>
       </c>
@@ -7215,8 +7087,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
-      <c r="A147" s="1"/>
+    <row r="147" spans="2:10">
       <c r="B147" s="1">
         <v>120019</v>
       </c>
@@ -7248,8 +7119,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
-      <c r="A148" s="1"/>
+    <row r="148" spans="2:10">
       <c r="B148" s="1">
         <v>120020</v>
       </c>
@@ -7281,8 +7151,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
-      <c r="A149" s="1"/>
+    <row r="149" spans="2:10">
       <c r="B149" s="1">
         <v>120021</v>
       </c>
@@ -7314,8 +7183,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
-      <c r="A150" s="1"/>
+    <row r="150" spans="2:10">
       <c r="B150" s="1">
         <v>120022</v>
       </c>
@@ -7347,8 +7215,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
-      <c r="A151" s="1"/>
+    <row r="151" spans="2:10">
       <c r="B151" s="1">
         <v>120023</v>
       </c>
@@ -7380,8 +7247,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
-      <c r="A152" s="1"/>
+    <row r="152" spans="2:10">
       <c r="B152" s="1">
         <v>120024</v>
       </c>
@@ -7413,8 +7279,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
-      <c r="A153" s="1"/>
+    <row r="153" spans="2:10">
       <c r="B153" s="1">
         <v>120025</v>
       </c>
@@ -7446,8 +7311,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
-      <c r="A154" s="1"/>
+    <row r="154" spans="2:10">
       <c r="B154" s="1">
         <v>120026</v>
       </c>
@@ -7479,8 +7343,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
-      <c r="A155" s="1"/>
+    <row r="155" spans="2:10">
       <c r="B155" s="1">
         <v>120027</v>
       </c>
@@ -7512,8 +7375,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
-      <c r="A156" s="1"/>
+    <row r="156" spans="2:10">
       <c r="B156" s="1">
         <v>120028</v>
       </c>
@@ -7545,8 +7407,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
-      <c r="A157" s="1"/>
+    <row r="157" spans="2:10">
       <c r="B157" s="1">
         <v>120029</v>
       </c>
@@ -7578,8 +7439,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
-      <c r="A158" s="1"/>
+    <row r="158" spans="2:10">
       <c r="B158" s="1">
         <v>120030</v>
       </c>
@@ -7611,8 +7471,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
-      <c r="A159" s="1"/>
+    <row r="159" spans="2:10">
       <c r="B159" s="1">
         <v>120031</v>
       </c>
@@ -7644,8 +7503,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
-      <c r="A160" s="1"/>
+    <row r="160" spans="2:10">
       <c r="B160" s="1">
         <v>120032</v>
       </c>
@@ -7677,8 +7535,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
-      <c r="A161" s="1"/>
+    <row r="161" spans="2:10">
       <c r="B161" s="1">
         <v>120033</v>
       </c>
@@ -7710,8 +7567,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
-      <c r="A162" s="1"/>
+    <row r="162" spans="2:10">
       <c r="B162" s="1">
         <v>120034</v>
       </c>
@@ -7743,8 +7599,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
-      <c r="A163" s="1"/>
+    <row r="163" spans="2:10">
       <c r="B163" s="1">
         <v>120035</v>
       </c>
@@ -7776,8 +7631,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
-      <c r="A164" s="1"/>
+    <row r="164" spans="2:10">
       <c r="B164" s="1">
         <v>120036</v>
       </c>
@@ -7809,8 +7663,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
-      <c r="A165" s="1"/>
+    <row r="165" spans="2:10">
       <c r="B165" s="1">
         <v>120037</v>
       </c>
@@ -7842,8 +7695,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
-      <c r="A166" s="1"/>
+    <row r="166" spans="2:10">
       <c r="B166" s="1">
         <v>120038</v>
       </c>
@@ -7875,8 +7727,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
-      <c r="A167" s="1"/>
+    <row r="167" spans="2:10">
       <c r="B167" s="1">
         <v>120039</v>
       </c>
@@ -7908,8 +7759,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
-      <c r="A168" s="1"/>
+    <row r="168" spans="2:10">
       <c r="B168" s="1">
         <v>120040</v>
       </c>
@@ -7941,8 +7791,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
-      <c r="A169" s="1"/>
+    <row r="169" spans="2:10">
       <c r="B169" s="1">
         <v>200000</v>
       </c>
@@ -7974,8 +7823,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
-      <c r="A170" s="1"/>
+    <row r="170" spans="2:10">
       <c r="B170" s="1">
         <v>200001</v>
       </c>
@@ -8007,8 +7855,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
-      <c r="A171" s="1"/>
+    <row r="171" spans="2:10">
       <c r="B171" s="1">
         <v>200002</v>
       </c>
@@ -8040,8 +7887,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
-      <c r="A172" s="1"/>
+    <row r="172" spans="2:10">
       <c r="B172" s="1">
         <v>200003</v>
       </c>
@@ -8073,8 +7919,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
-      <c r="A173" s="1"/>
+    <row r="173" spans="2:10">
       <c r="B173" s="1">
         <v>210000</v>
       </c>
@@ -8106,8 +7951,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
-      <c r="A174" s="1"/>
+    <row r="174" spans="2:10">
       <c r="B174" s="1">
         <v>210001</v>
       </c>
@@ -8139,8 +7983,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
-      <c r="A175" s="1"/>
+    <row r="175" spans="2:10">
       <c r="B175" s="1">
         <v>210002</v>
       </c>
@@ -8172,8 +8015,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
-      <c r="A176" s="1"/>
+    <row r="176" spans="2:10">
       <c r="B176" s="1">
         <v>210003</v>
       </c>
@@ -8205,8 +8047,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
-      <c r="A177" s="1"/>
+    <row r="177" spans="2:10">
       <c r="B177" s="1">
         <v>210004</v>
       </c>
@@ -8238,8 +8079,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
-      <c r="A178" s="1"/>
+    <row r="178" spans="2:10">
       <c r="B178" s="1">
         <v>210005</v>
       </c>
@@ -8271,8 +8111,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
-      <c r="A179" s="1"/>
+    <row r="179" spans="2:10">
       <c r="B179" s="1">
         <v>210006</v>
       </c>
@@ -8304,8 +8143,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
-      <c r="A180" s="1"/>
+    <row r="180" spans="2:10">
       <c r="B180" s="1">
         <v>210007</v>
       </c>
@@ -8337,8 +8175,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
-      <c r="A181" s="1"/>
+    <row r="181" spans="2:10">
       <c r="B181" s="1">
         <v>210008</v>
       </c>
@@ -8370,8 +8207,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
-      <c r="A182" s="1"/>
+    <row r="182" spans="2:10">
       <c r="B182" s="1">
         <v>210009</v>
       </c>
@@ -8403,8 +8239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
-      <c r="A183" s="1"/>
+    <row r="183" spans="2:10">
       <c r="B183" s="1">
         <v>210010</v>
       </c>
@@ -8436,8 +8271,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
-      <c r="A184" s="1"/>
+    <row r="184" spans="2:10">
       <c r="B184" s="1">
         <v>210011</v>
       </c>
@@ -8469,8 +8303,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
-      <c r="A185" s="1"/>
+    <row r="185" spans="2:10">
       <c r="B185" s="1">
         <v>210012</v>
       </c>
@@ -8502,8 +8335,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
-      <c r="A186" s="1"/>
+    <row r="186" spans="2:10">
       <c r="B186" s="1">
         <v>210013</v>
       </c>
@@ -8535,8 +8367,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
-      <c r="A187" s="1"/>
+    <row r="187" spans="2:10">
       <c r="B187" s="1">
         <v>210014</v>
       </c>
@@ -8568,8 +8399,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
-      <c r="A188" s="1"/>
+    <row r="188" spans="2:10">
       <c r="B188" s="1">
         <v>210015</v>
       </c>
@@ -8601,8 +8431,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
-      <c r="A189" s="1"/>
+    <row r="189" spans="2:10">
       <c r="B189" s="1">
         <v>210016</v>
       </c>
@@ -8634,8 +8463,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
-      <c r="A190" s="1"/>
+    <row r="190" spans="2:10">
       <c r="B190" s="1">
         <v>210017</v>
       </c>
@@ -8667,8 +8495,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
-      <c r="A191" s="1"/>
+    <row r="191" spans="2:10">
       <c r="B191" s="1">
         <v>210018</v>
       </c>
@@ -8700,8 +8527,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
-      <c r="A192" s="1"/>
+    <row r="192" spans="2:10">
       <c r="B192" s="1">
         <v>210019</v>
       </c>
@@ -8733,8 +8559,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
-      <c r="A193" s="1"/>
+    <row r="193" spans="2:10">
       <c r="B193" s="1">
         <v>220000</v>
       </c>
@@ -8766,8 +8591,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
-      <c r="A194" s="1"/>
+    <row r="194" spans="2:10">
       <c r="B194" s="1">
         <v>220001</v>
       </c>
@@ -8799,8 +8623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
-      <c r="A195" s="1"/>
+    <row r="195" spans="2:10">
       <c r="B195" s="1">
         <v>220002</v>
       </c>
@@ -8832,8 +8655,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
-      <c r="A196" s="1"/>
+    <row r="196" spans="2:10">
       <c r="B196" s="1">
         <v>220003</v>
       </c>
@@ -8865,8 +8687,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
-      <c r="A197" s="1"/>
+    <row r="197" spans="2:10">
       <c r="B197" s="1">
         <v>220004</v>
       </c>
@@ -8898,8 +8719,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
-      <c r="A198" s="1"/>
+    <row r="198" spans="2:10">
       <c r="B198" s="1">
         <v>220005</v>
       </c>
@@ -8931,8 +8751,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
-      <c r="A199" s="1"/>
+    <row r="199" spans="2:10">
       <c r="B199" s="1">
         <v>220006</v>
       </c>
@@ -8964,8 +8783,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
-      <c r="A200" s="1"/>
+    <row r="200" spans="2:10">
       <c r="B200" s="1">
         <v>220007</v>
       </c>
@@ -8997,8 +8815,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
-      <c r="A201" s="1"/>
+    <row r="201" spans="2:10">
       <c r="B201" s="1">
         <v>220008</v>
       </c>
@@ -9030,8 +8847,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
-      <c r="A202" s="1"/>
+    <row r="202" spans="2:10">
       <c r="B202" s="1">
         <v>220009</v>
       </c>
@@ -9063,8 +8879,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
-      <c r="A203" s="1"/>
+    <row r="203" spans="2:10">
       <c r="B203" s="1">
         <v>230000</v>
       </c>
@@ -9096,8 +8911,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
-      <c r="A204" s="1"/>
+    <row r="204" spans="2:10">
       <c r="B204" s="1">
         <v>230001</v>
       </c>
@@ -9129,8 +8943,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
-      <c r="A205" s="1"/>
+    <row r="205" spans="2:10">
       <c r="B205" s="1">
         <v>230002</v>
       </c>
@@ -9162,8 +8975,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
-      <c r="A206" s="1"/>
+    <row r="206" spans="2:10">
       <c r="B206" s="1">
         <v>230003</v>
       </c>
@@ -9195,8 +9007,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
-      <c r="A207" s="1"/>
+    <row r="207" spans="2:10">
       <c r="B207" s="1">
         <v>230004</v>
       </c>
@@ -9228,8 +9039,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
-      <c r="A208" s="1"/>
+    <row r="208" spans="2:10">
       <c r="B208" s="1">
         <v>230005</v>
       </c>
@@ -9261,8 +9071,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
-      <c r="A209" s="1"/>
+    <row r="209" spans="2:10">
       <c r="B209" s="1">
         <v>230006</v>
       </c>
@@ -9294,8 +9103,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
-      <c r="A210" s="1"/>
+    <row r="210" spans="2:10">
       <c r="B210" s="1">
         <v>230007</v>
       </c>
@@ -9327,8 +9135,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
-      <c r="A211" s="1"/>
+    <row r="211" spans="2:10">
       <c r="B211" s="1">
         <v>230008</v>
       </c>
@@ -9360,8 +9167,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
-      <c r="A212" s="1"/>
+    <row r="212" spans="2:10">
       <c r="B212" s="1">
         <v>230009</v>
       </c>
@@ -9393,8 +9199,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
-      <c r="A213" s="1"/>
+    <row r="213" spans="2:10">
       <c r="B213" s="1">
         <v>230010</v>
       </c>
@@ -9426,8 +9231,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
-      <c r="A214" s="1"/>
+    <row r="214" spans="2:10">
       <c r="B214" s="1">
         <v>230011</v>
       </c>
@@ -9459,8 +9263,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
-      <c r="A215" s="1"/>
+    <row r="215" spans="2:10">
       <c r="B215" s="1">
         <v>230012</v>
       </c>
@@ -9492,8 +9295,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
-      <c r="A216" s="1"/>
+    <row r="216" spans="2:10">
       <c r="B216" s="1">
         <v>230013</v>
       </c>
@@ -9525,8 +9327,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
-      <c r="A217" s="1"/>
+    <row r="217" spans="2:10">
       <c r="B217" s="1">
         <v>230014</v>
       </c>
@@ -9558,8 +9359,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
-      <c r="A218" s="1"/>
+    <row r="218" spans="2:10">
       <c r="B218" s="1">
         <v>230015</v>
       </c>
@@ -9591,8 +9391,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
-      <c r="A219" s="1"/>
+    <row r="219" spans="2:10">
       <c r="B219" s="1">
         <v>230016</v>
       </c>
@@ -9624,8 +9423,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
-      <c r="A220" s="1"/>
+    <row r="220" spans="2:10">
       <c r="B220" s="1">
         <v>230017</v>
       </c>
@@ -9657,8 +9455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
-      <c r="A221" s="1"/>
+    <row r="221" spans="2:10">
       <c r="B221" s="1">
         <v>230018</v>
       </c>
@@ -9690,8 +9487,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
-      <c r="A222" s="1"/>
+    <row r="222" spans="2:10">
       <c r="B222" s="1">
         <v>230019</v>
       </c>
@@ -9723,8 +9519,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
-      <c r="A223" s="1"/>
+    <row r="223" spans="2:10">
       <c r="B223" s="1">
         <v>240000</v>
       </c>
@@ -9756,8 +9551,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
-      <c r="A224" s="1"/>
+    <row r="224" spans="2:10">
       <c r="B224" s="1">
         <v>240001</v>
       </c>
@@ -9789,8 +9583,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
-      <c r="A225" s="1"/>
+    <row r="225" spans="2:10">
       <c r="B225" s="1">
         <v>240002</v>
       </c>
@@ -9822,8 +9615,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
-      <c r="A226" s="1"/>
+    <row r="226" spans="2:10">
       <c r="B226" s="1">
         <v>240003</v>
       </c>
@@ -9855,8 +9647,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
-      <c r="A227" s="1"/>
+    <row r="227" spans="2:10">
       <c r="B227" s="1">
         <v>240004</v>
       </c>
@@ -9888,8 +9679,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
-      <c r="A228" s="1"/>
+    <row r="228" spans="2:10">
       <c r="B228" s="1">
         <v>240005</v>
       </c>
@@ -9921,8 +9711,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
-      <c r="A229" s="1"/>
+    <row r="229" spans="2:10">
       <c r="B229" s="1">
         <v>240006</v>
       </c>
@@ -9954,8 +9743,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
-      <c r="A230" s="1"/>
+    <row r="230" spans="2:10">
       <c r="B230" s="1">
         <v>240007</v>
       </c>
@@ -9987,8 +9775,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
-      <c r="A231" s="1"/>
+    <row r="231" spans="2:10">
       <c r="B231" s="1">
         <v>240008</v>
       </c>
@@ -10020,8 +9807,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
-      <c r="A232" s="1"/>
+    <row r="232" spans="2:10">
       <c r="B232" s="1">
         <v>240009</v>
       </c>
@@ -10053,8 +9839,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
-      <c r="A233" s="1"/>
+    <row r="233" spans="2:10">
       <c r="B233" s="1">
         <v>240010</v>
       </c>
@@ -10086,8 +9871,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
-      <c r="A234" s="1"/>
+    <row r="234" spans="2:10">
       <c r="B234" s="1">
         <v>240011</v>
       </c>
@@ -10119,8 +9903,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
-      <c r="A235" s="1"/>
+    <row r="235" spans="2:10">
       <c r="B235" s="1">
         <v>240012</v>
       </c>
@@ -10152,8 +9935,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
-      <c r="A236" s="1"/>
+    <row r="236" spans="2:10">
       <c r="B236" s="1">
         <v>240013</v>
       </c>
@@ -10185,8 +9967,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
-      <c r="A237" s="1"/>
+    <row r="237" spans="2:10">
       <c r="B237" s="1">
         <v>240014</v>
       </c>
@@ -10218,8 +9999,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
-      <c r="A238" s="1"/>
+    <row r="238" spans="2:10">
       <c r="B238" s="1">
         <v>240015</v>
       </c>
@@ -10251,8 +10031,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
-      <c r="A239" s="1"/>
+    <row r="239" spans="2:10">
       <c r="B239" s="1">
         <v>240016</v>
       </c>
@@ -10284,8 +10063,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
-      <c r="A240" s="1"/>
+    <row r="240" spans="2:10">
       <c r="B240" s="1">
         <v>240017</v>
       </c>
@@ -10317,8 +10095,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
-      <c r="A241" s="1"/>
+    <row r="241" spans="2:10">
       <c r="B241" s="1">
         <v>240018</v>
       </c>
@@ -10350,8 +10127,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
-      <c r="A242" s="1"/>
+    <row r="242" spans="2:10">
       <c r="B242" s="1">
         <v>240019</v>
       </c>
@@ -10383,8 +10159,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
-      <c r="A243" s="1"/>
+    <row r="243" spans="2:10">
       <c r="B243" s="1">
         <v>300000</v>
       </c>
@@ -10416,8 +10191,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
-      <c r="A244" s="1"/>
+    <row r="244" spans="2:10">
       <c r="B244" s="1">
         <v>300001</v>
       </c>
@@ -10449,8 +10223,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
-      <c r="A245" s="1"/>
+    <row r="245" spans="2:10">
       <c r="B245" s="1">
         <v>300002</v>
       </c>
@@ -10482,8 +10255,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
-      <c r="A246" s="11"/>
+    <row r="246" spans="2:10">
       <c r="B246" s="1">
         <v>300003</v>
       </c>
@@ -10515,8 +10287,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
-      <c r="A247" s="11"/>
+    <row r="247" spans="2:10">
       <c r="B247" s="1">
         <v>300004</v>
       </c>
@@ -10548,8 +10319,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
-      <c r="A248" s="11"/>
+    <row r="248" spans="2:10">
       <c r="B248" s="1">
         <v>300005</v>
       </c>
@@ -10581,8 +10351,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
-      <c r="A249" s="11"/>
+    <row r="249" spans="2:10">
       <c r="B249" s="1">
         <v>300006</v>
       </c>
@@ -10614,8 +10383,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
-      <c r="A250" s="11"/>
+    <row r="250" spans="2:10">
       <c r="B250" s="1">
         <v>300007</v>
       </c>
@@ -10647,8 +10415,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
-      <c r="A251" s="1"/>
+    <row r="251" spans="2:10">
       <c r="B251" s="1">
         <v>300008</v>
       </c>
@@ -10680,8 +10447,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
-      <c r="A252" s="1"/>
+    <row r="252" spans="2:10">
       <c r="B252" s="1">
         <v>300009</v>
       </c>
@@ -10713,8 +10479,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
-      <c r="A253" s="1"/>
+    <row r="253" spans="2:10">
       <c r="B253" s="1">
         <v>130000</v>
       </c>
@@ -10746,8 +10511,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
-      <c r="A254" s="1"/>
+    <row r="254" spans="2:10">
       <c r="B254" s="1">
         <v>130001</v>
       </c>
@@ -10779,8 +10543,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
-      <c r="A255" s="1"/>
+    <row r="255" spans="2:10">
       <c r="B255" s="1">
         <v>130002</v>
       </c>
@@ -10812,8 +10575,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
-      <c r="A256" s="1"/>
+    <row r="256" spans="2:10">
       <c r="B256" s="1">
         <v>131000</v>
       </c>
@@ -10845,8 +10607,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
-      <c r="A257" s="1"/>
+    <row r="257" spans="2:10">
       <c r="B257" s="1">
         <v>131001</v>
       </c>
@@ -10878,8 +10639,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
-      <c r="A258" s="1"/>
+    <row r="258" spans="2:10">
       <c r="B258" s="1">
         <v>131002</v>
       </c>
@@ -10911,8 +10671,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
-      <c r="A259" s="1"/>
+    <row r="259" spans="2:10">
       <c r="B259" s="1">
         <v>131003</v>
       </c>
@@ -10944,8 +10703,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
-      <c r="A260" s="1"/>
+    <row r="260" spans="2:10">
       <c r="B260" s="1">
         <v>131004</v>
       </c>
@@ -10977,8 +10735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
-      <c r="A261" s="1"/>
+    <row r="261" spans="2:10">
       <c r="B261" s="1">
         <v>140000</v>
       </c>
@@ -11010,8 +10767,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
-      <c r="A262" s="1"/>
+    <row r="262" spans="2:10">
       <c r="B262" s="1">
         <v>140001</v>
       </c>
@@ -11043,8 +10799,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
-      <c r="A263" s="1"/>
+    <row r="263" spans="2:10">
       <c r="B263" s="1">
         <v>140002</v>
       </c>
@@ -11076,8 +10831,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
-      <c r="A264" s="1"/>
+    <row r="264" spans="2:10">
       <c r="B264" s="1">
         <v>140003</v>
       </c>
@@ -11109,8 +10863,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
-      <c r="A265" s="1"/>
+    <row r="265" spans="2:10">
       <c r="B265" s="1">
         <v>150000</v>
       </c>
@@ -11142,8 +10895,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
-      <c r="A266" s="1"/>
+    <row r="266" spans="2:10">
       <c r="B266" s="1">
         <v>150001</v>
       </c>
@@ -11175,8 +10927,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
-      <c r="A267" s="1"/>
+    <row r="267" spans="2:10">
       <c r="B267" s="1">
         <v>150002</v>
       </c>
@@ -11208,8 +10959,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
-      <c r="A268" s="1"/>
+    <row r="268" spans="2:10">
       <c r="B268" s="1">
         <v>150003</v>
       </c>
@@ -11241,8 +10991,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
-      <c r="A269" s="1"/>
+    <row r="269" spans="2:10">
       <c r="B269" s="1">
         <v>150004</v>
       </c>
@@ -11274,8 +11023,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
-      <c r="A270" s="1"/>
+    <row r="270" spans="2:10">
       <c r="B270" s="1">
         <v>150005</v>
       </c>
@@ -11307,8 +11055,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
-      <c r="A271" s="1"/>
+    <row r="271" spans="2:10">
       <c r="B271" s="1">
         <v>150006</v>
       </c>
@@ -11340,8 +11087,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
-      <c r="A272" s="1"/>
+    <row r="272" spans="2:10">
       <c r="B272" s="1">
         <v>150007</v>
       </c>
@@ -11373,8 +11119,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
-      <c r="A273" s="1"/>
+    <row r="273" spans="2:10">
       <c r="B273" s="1">
         <v>150008</v>
       </c>
@@ -11406,8 +11151,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
-      <c r="A274" s="1"/>
+    <row r="274" spans="2:10">
       <c r="B274" s="1">
         <v>150009</v>
       </c>
@@ -11439,8 +11183,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
-      <c r="A275" s="1"/>
+    <row r="275" spans="2:10">
       <c r="B275" s="1">
         <v>310000</v>
       </c>
@@ -11472,8 +11215,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
-      <c r="A276" s="1"/>
+    <row r="276" spans="2:10">
       <c r="B276" s="1">
         <v>310001</v>
       </c>
@@ -11505,8 +11247,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
-      <c r="A277" s="1"/>
+    <row r="277" spans="2:10">
       <c r="B277" s="1">
         <v>310002</v>
       </c>
@@ -11538,8 +11279,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
-      <c r="A278" s="1"/>
+    <row r="278" spans="2:10">
       <c r="B278" s="1">
         <v>310003</v>
       </c>
@@ -11571,8 +11311,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
-      <c r="A279" s="1"/>
+    <row r="279" spans="2:10">
       <c r="B279" s="1">
         <v>310004</v>
       </c>
@@ -11604,8 +11343,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
-      <c r="A280" s="1"/>
+    <row r="280" spans="2:10">
       <c r="B280" s="1">
         <v>310005</v>
       </c>
@@ -11637,8 +11375,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
-      <c r="A281" s="1"/>
+    <row r="281" spans="2:10">
       <c r="B281" s="1">
         <v>310006</v>
       </c>
@@ -11670,8 +11407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
-      <c r="A282" s="1"/>
+    <row r="282" spans="2:10">
       <c r="B282" s="1">
         <v>310007</v>
       </c>
@@ -11703,8 +11439,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
-      <c r="A283" s="1"/>
+    <row r="283" spans="2:10">
       <c r="B283" s="1">
         <v>310008</v>
       </c>
@@ -11736,8 +11471,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
-      <c r="A284" s="1"/>
+    <row r="284" spans="2:10">
       <c r="B284" s="1">
         <v>310009</v>
       </c>
@@ -11769,8 +11503,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
-      <c r="A285" s="1"/>
+    <row r="285" spans="2:10">
       <c r="B285" s="1">
         <v>310010</v>
       </c>
@@ -11802,8 +11535,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
-      <c r="A286" s="1"/>
+    <row r="286" spans="2:10">
       <c r="B286" s="1">
         <v>310011</v>
       </c>
@@ -11835,8 +11567,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
-      <c r="A287" s="1"/>
+    <row r="287" spans="2:10">
       <c r="B287" s="1">
         <v>310012</v>
       </c>
@@ -11868,8 +11599,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
-      <c r="A288" s="1"/>
+    <row r="288" spans="2:10">
       <c r="B288" s="1">
         <v>310013</v>
       </c>
@@ -11901,8 +11631,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
-      <c r="A289" s="1"/>
+    <row r="289" spans="2:10">
       <c r="B289" s="1">
         <v>310014</v>
       </c>
@@ -11934,8 +11663,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
-      <c r="A290" s="1"/>
+    <row r="290" spans="2:10">
       <c r="B290" s="1">
         <v>310015</v>
       </c>
@@ -11967,8 +11695,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
-      <c r="A291" s="1"/>
+    <row r="291" spans="2:10">
       <c r="B291" s="1">
         <v>310016</v>
       </c>
@@ -12000,8 +11727,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
-      <c r="A292" s="1"/>
+    <row r="292" spans="2:10">
       <c r="B292" s="1">
         <v>310017</v>
       </c>
@@ -12033,8 +11759,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
-      <c r="A293" s="1"/>
+    <row r="293" spans="2:10">
       <c r="B293" s="1">
         <v>310018</v>
       </c>
@@ -12066,8 +11791,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
-      <c r="A294" s="1"/>
+    <row r="294" spans="2:10">
       <c r="B294" s="1">
         <v>310019</v>
       </c>
@@ -12099,8 +11823,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
-      <c r="A295" s="1"/>
+    <row r="295" spans="2:10">
       <c r="B295" s="1">
         <v>310020</v>
       </c>
@@ -12132,8 +11855,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
-      <c r="A296" s="1"/>
+    <row r="296" spans="2:10">
       <c r="B296" s="1">
         <v>310021</v>
       </c>
@@ -12165,8 +11887,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
-      <c r="A297" s="1"/>
+    <row r="297" spans="2:10">
       <c r="B297" s="1">
         <v>310022</v>
       </c>
@@ -12198,8 +11919,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
-      <c r="A298" s="1"/>
+    <row r="298" spans="2:10">
       <c r="B298" s="1">
         <v>310023</v>
       </c>
@@ -12231,8 +11951,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
-      <c r="A299" s="1"/>
+    <row r="299" spans="2:10">
       <c r="B299" s="1">
         <v>310024</v>
       </c>
@@ -12264,8 +11983,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
-      <c r="A300" s="1"/>
+    <row r="300" spans="2:10">
       <c r="B300" s="1">
         <v>310025</v>
       </c>
@@ -12297,8 +12015,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
-      <c r="A301" s="1"/>
+    <row r="301" spans="2:10">
       <c r="B301" s="1">
         <v>310026</v>
       </c>
@@ -12330,8 +12047,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
-      <c r="A302" s="1"/>
+    <row r="302" spans="2:10">
       <c r="B302" s="1">
         <v>310027</v>
       </c>
@@ -12363,8 +12079,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
-      <c r="A303" s="1"/>
+    <row r="303" spans="2:10">
       <c r="B303" s="1">
         <v>310028</v>
       </c>
@@ -12396,8 +12111,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
-      <c r="A304" s="1"/>
+    <row r="304" spans="2:10">
       <c r="B304" s="1">
         <v>310029</v>
       </c>
@@ -12429,8 +12143,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
-      <c r="A305" s="1"/>
+    <row r="305" spans="2:10">
       <c r="B305" s="1">
         <v>310030</v>
       </c>
@@ -12462,8 +12175,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
-      <c r="A306" s="1"/>
+    <row r="306" spans="2:10">
       <c r="B306" s="1">
         <v>310031</v>
       </c>
@@ -12495,8 +12207,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
-      <c r="A307" s="1"/>
+    <row r="307" spans="2:10">
       <c r="B307" s="1">
         <v>310032</v>
       </c>
@@ -12528,8 +12239,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
-      <c r="A308" s="1"/>
+    <row r="308" spans="2:10">
       <c r="B308" s="1">
         <v>310033</v>
       </c>
@@ -12561,8 +12271,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
-      <c r="A309" s="1"/>
+    <row r="309" spans="2:10">
       <c r="B309" s="1">
         <v>310034</v>
       </c>
@@ -12594,8 +12303,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
-      <c r="A310" s="1"/>
+    <row r="310" spans="2:10">
       <c r="B310" s="1">
         <v>310035</v>
       </c>
@@ -12627,8 +12335,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
-      <c r="A311" s="1"/>
+    <row r="311" spans="2:10">
       <c r="B311" s="1">
         <v>310036</v>
       </c>
@@ -12660,8 +12367,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
-      <c r="A312" s="1"/>
+    <row r="312" spans="2:10">
       <c r="B312" s="1">
         <v>310037</v>
       </c>
@@ -12693,8 +12399,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
-      <c r="A313" s="1"/>
+    <row r="313" spans="2:10">
       <c r="B313" s="1">
         <v>310038</v>
       </c>
@@ -12726,8 +12431,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
-      <c r="A314" s="1"/>
+    <row r="314" spans="2:10">
       <c r="B314" s="1">
         <v>310039</v>
       </c>
@@ -12802,7 +12506,7 @@
       <c r="F1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>363</v>
       </c>
     </row>
@@ -12853,14 +12557,14 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>120000</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
         <v>373</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -12869,23 +12573,23 @@
       <c r="G4" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
     </row>
     <row r="5" spans="1:18">
       <c r="B5" s="2">
         <v>120001</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -12897,13 +12601,13 @@
       <c r="G5" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:18">
       <c r="B6" s="2">
         <v>120002</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>166</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -12915,13 +12619,13 @@
       <c r="G6" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:18">
       <c r="B7" s="2">
         <v>120003</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>167</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -12933,13 +12637,13 @@
       <c r="G7" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:18">
       <c r="B8" s="2">
         <v>120004</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -12951,13 +12655,13 @@
       <c r="G8" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:18">
       <c r="B9" s="2">
         <v>120005</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>169</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -12969,13 +12673,13 @@
       <c r="G9" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:18">
       <c r="B10" s="2">
         <v>120006</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -12987,13 +12691,13 @@
       <c r="G10" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:18">
       <c r="B11" s="2">
         <v>120007</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>171</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -13005,13 +12709,13 @@
       <c r="G11" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:18">
       <c r="B12" s="2">
         <v>120008</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>173</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -13023,13 +12727,13 @@
       <c r="G12" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:18">
       <c r="B13" s="2">
         <v>120009</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>174</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -13041,13 +12745,13 @@
       <c r="G13" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:18">
       <c r="B14" s="2">
         <v>120010</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>175</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -13059,13 +12763,13 @@
       <c r="G14" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:18">
       <c r="B15" s="2">
         <v>120011</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>176</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -13077,13 +12781,13 @@
       <c r="G15" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:18">
       <c r="B16" s="2">
         <v>120012</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>177</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -13095,13 +12799,13 @@
       <c r="G16" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="2">
         <v>120013</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>178</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -13113,13 +12817,13 @@
       <c r="G17" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="2">
         <v>120014</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>179</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -13131,13 +12835,13 @@
       <c r="G18" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="2">
         <v>120015</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>180</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -13149,13 +12853,13 @@
       <c r="G19" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="2">
         <v>120016</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>181</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -13167,13 +12871,13 @@
       <c r="G20" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="2">
         <v>120017</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>182</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -13185,13 +12889,13 @@
       <c r="G21" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="2">
         <v>120018</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -13203,13 +12907,13 @@
       <c r="G22" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="2">
         <v>120019</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -13221,13 +12925,13 @@
       <c r="G23" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="2">
         <v>120020</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>185</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -13239,13 +12943,13 @@
       <c r="G24" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="2">
         <v>120021</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>186</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -13257,13 +12961,13 @@
       <c r="G25" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="2">
         <v>120022</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>187</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -13275,13 +12979,13 @@
       <c r="G26" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="2">
         <v>120023</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>189</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -13293,13 +12997,13 @@
       <c r="G27" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H27" s="6"/>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="2">
         <v>120024</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>190</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -13311,13 +13015,13 @@
       <c r="G28" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H28" s="6"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="2">
         <v>120025</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>191</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -13329,13 +13033,13 @@
       <c r="G29" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H29" s="6"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="2">
         <v>120026</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -13347,13 +13051,13 @@
       <c r="G30" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H30" s="6"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="2">
         <v>120027</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>193</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -13365,13 +13069,13 @@
       <c r="G31" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="2">
         <v>120028</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>194</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -13383,13 +13087,13 @@
       <c r="G32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H32" s="6"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="2">
         <v>120029</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>195</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -13401,13 +13105,13 @@
       <c r="G33" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H33" s="6"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="2">
         <v>120030</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>196</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -13419,13 +13123,13 @@
       <c r="G34" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H34" s="6"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" s="2">
         <v>120031</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -13437,13 +13141,13 @@
       <c r="G35" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="2">
         <v>120032</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -13455,13 +13159,13 @@
       <c r="G36" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="2">
         <v>120033</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>199</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -13473,13 +13177,13 @@
       <c r="G37" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H37" s="6"/>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="2">
         <v>120034</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>200</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -13491,13 +13195,13 @@
       <c r="G38" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H38" s="6"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="2">
         <v>120035</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>201</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -13509,13 +13213,13 @@
       <c r="G39" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H39" s="6"/>
+      <c r="H39" s="7"/>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="2">
         <v>120036</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>202</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -13527,13 +13231,13 @@
       <c r="G40" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H40" s="6"/>
+      <c r="H40" s="7"/>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="2">
         <v>120037</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>203</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -13545,13 +13249,13 @@
       <c r="G41" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H41" s="6"/>
+      <c r="H41" s="7"/>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="2">
         <v>120038</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>204</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -13563,13 +13267,13 @@
       <c r="G42" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H42" s="6"/>
+      <c r="H42" s="7"/>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="2">
         <v>120039</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>205</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -13581,13 +13285,13 @@
       <c r="G43" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H43" s="6"/>
+      <c r="H43" s="7"/>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="2">
         <v>120040</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>206</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -13599,7 +13303,7 @@
       <c r="G44" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H44" s="6"/>
+      <c r="H44" s="7"/>
     </row>
     <row r="45" spans="2:8">
       <c r="B45"/>
@@ -14517,7 +14221,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19.0833333333333" customWidth="1"/>
@@ -16060,10 +15764,10 @@
     </row>
     <row r="128" ht="16.5" spans="2:4">
       <c r="B128" s="1">
-        <v>100020</v>
+        <v>100040</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>434</v>
@@ -16071,10 +15775,10 @@
     </row>
     <row r="129" ht="16.5" spans="2:4">
       <c r="B129" s="1">
-        <v>100021</v>
+        <v>100041</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>434</v>
@@ -16082,10 +15786,10 @@
     </row>
     <row r="130" ht="16.5" spans="2:4">
       <c r="B130" s="1">
-        <v>100022</v>
+        <v>100042</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>434</v>
@@ -16093,10 +15797,10 @@
     </row>
     <row r="131" ht="16.5" spans="2:4">
       <c r="B131" s="1">
-        <v>100023</v>
+        <v>100043</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>434</v>
@@ -16104,10 +15808,10 @@
     </row>
     <row r="132" ht="16.5" spans="2:4">
       <c r="B132" s="1">
-        <v>100024</v>
+        <v>100044</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>434</v>
@@ -16115,10 +15819,10 @@
     </row>
     <row r="133" ht="16.5" spans="2:4">
       <c r="B133" s="1">
-        <v>100025</v>
+        <v>100045</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>434</v>
@@ -16126,10 +15830,10 @@
     </row>
     <row r="134" ht="16.5" spans="2:4">
       <c r="B134" s="1">
-        <v>100026</v>
+        <v>100046</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>434</v>
@@ -16137,10 +15841,10 @@
     </row>
     <row r="135" ht="16.5" spans="2:4">
       <c r="B135" s="1">
-        <v>100027</v>
+        <v>100047</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>434</v>
@@ -16148,10 +15852,10 @@
     </row>
     <row r="136" ht="16.5" spans="2:4">
       <c r="B136" s="1">
-        <v>100028</v>
+        <v>100048</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>434</v>
@@ -16159,10 +15863,10 @@
     </row>
     <row r="137" ht="16.5" spans="2:4">
       <c r="B137" s="1">
-        <v>100029</v>
+        <v>100049</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>434</v>
@@ -16170,10 +15874,10 @@
     </row>
     <row r="138" ht="16.5" spans="2:4">
       <c r="B138" s="1">
-        <v>100030</v>
+        <v>100052</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>434</v>
@@ -16181,10 +15885,10 @@
     </row>
     <row r="139" ht="16.5" spans="2:4">
       <c r="B139" s="1">
-        <v>100031</v>
+        <v>100053</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>434</v>
@@ -16192,10 +15896,10 @@
     </row>
     <row r="140" ht="16.5" spans="2:4">
       <c r="B140" s="1">
-        <v>100032</v>
+        <v>100054</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>434</v>
@@ -16203,10 +15907,10 @@
     </row>
     <row r="141" ht="16.5" spans="2:4">
       <c r="B141" s="1">
-        <v>100033</v>
+        <v>100055</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>434</v>
@@ -16214,741 +15918,940 @@
     </row>
     <row r="142" ht="16.5" spans="2:4">
       <c r="B142" s="1">
-        <v>100034</v>
+        <v>220000</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="2:4">
       <c r="B143" s="1">
-        <v>100035</v>
+        <v>220001</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>66</v>
+        <v>232</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="2:4">
       <c r="B144" s="1">
-        <v>100036</v>
+        <v>220002</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="2:4">
       <c r="B145" s="1">
-        <v>100037</v>
+        <v>220003</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="2:4">
       <c r="B146" s="1">
-        <v>100038</v>
+        <v>220004</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="2:4">
       <c r="B147" s="1">
-        <v>100039</v>
+        <v>220005</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="2:4">
       <c r="B148" s="1">
-        <v>100040</v>
+        <v>220006</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>72</v>
+        <v>237</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="2:4">
       <c r="B149" s="1">
-        <v>100041</v>
+        <v>220007</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="2:4">
       <c r="B150" s="1">
-        <v>100042</v>
+        <v>220008</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="2:4">
       <c r="B151" s="1">
-        <v>100043</v>
+        <v>220009</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="2:4">
       <c r="B152" s="1">
-        <v>100044</v>
+        <v>130000</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>76</v>
+        <v>291</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="2:4">
       <c r="B153" s="1">
-        <v>100045</v>
+        <v>130001</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="2:4">
       <c r="B154" s="1">
-        <v>100046</v>
+        <v>130002</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="2:4">
       <c r="B155" s="1">
-        <v>100047</v>
+        <v>140000</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="2:4">
       <c r="B156" s="1">
-        <v>100048</v>
+        <v>140001</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="2:4">
       <c r="B157" s="1">
-        <v>100049</v>
+        <v>140002</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>81</v>
+        <v>303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="2:4">
       <c r="B158" s="1">
-        <v>100051</v>
+        <v>140003</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="2:4">
       <c r="B159" s="1">
-        <v>100052</v>
+        <v>150000</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="2:4">
       <c r="B160" s="1">
-        <v>100053</v>
+        <v>150001</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>85</v>
+        <v>306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="161" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="161" ht="16.5" spans="1:10">
       <c r="B161" s="1">
-        <v>100054</v>
+        <v>150002</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>86</v>
+        <v>307</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="162" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="162" ht="16.5" spans="1:10">
       <c r="B162" s="1">
-        <v>100055</v>
+        <v>150003</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>87</v>
+        <v>308</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="163" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="163" ht="16.5" spans="1:10">
       <c r="B163" s="1">
-        <v>220000</v>
+        <v>150004</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>231</v>
+        <v>309</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="164" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="164" ht="16.5" spans="1:10">
       <c r="B164" s="1">
-        <v>220001</v>
+        <v>150005</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="165" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="165" ht="16.5" spans="1:10">
       <c r="B165" s="1">
-        <v>220002</v>
+        <v>150006</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="166" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="166" ht="16.5" spans="1:10">
       <c r="B166" s="1">
-        <v>220003</v>
+        <v>150007</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="167" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="167" ht="16.5" spans="1:10">
       <c r="B167" s="1">
-        <v>220004</v>
+        <v>150008</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="168" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="168" ht="16.5" spans="1:10">
       <c r="B168" s="1">
-        <v>220005</v>
+        <v>150009</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="169" ht="16.5" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="169" ht="16.5" spans="1:10">
+      <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>220006</v>
+        <v>131000</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="170" ht="16.5" spans="2:4">
+        <v>439</v>
+      </c>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+    </row>
+    <row r="170" ht="16.5" spans="1:10">
+      <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>220007</v>
+        <v>131001</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="171" ht="16.5" spans="2:4">
+        <v>439</v>
+      </c>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+    </row>
+    <row r="171" ht="16.5" spans="1:10">
+      <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>220008</v>
+        <v>131002</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="172" ht="16.5" spans="2:4">
+        <v>439</v>
+      </c>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+    </row>
+    <row r="172" ht="16.5" spans="1:10">
+      <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>220009</v>
+        <v>131003</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="173" ht="16.5" spans="2:4">
+        <v>439</v>
+      </c>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+    </row>
+    <row r="173" ht="16.5" spans="1:10">
+      <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>130000</v>
+        <v>131004</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="174" ht="16.5" spans="2:4">
+        <v>439</v>
+      </c>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+    </row>
+    <row r="174" ht="16.5" spans="1:10">
       <c r="B174" s="1">
-        <v>130001</v>
+        <v>100020</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="175" ht="16.5" spans="2:4">
+        <v>49</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="1:10">
       <c r="B175" s="1">
-        <v>130002</v>
+        <v>100021</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="176" ht="16.5" spans="2:4">
+        <v>50</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:10">
       <c r="B176" s="1">
-        <v>140000</v>
+        <v>100022</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="177" ht="16.5" spans="1:10">
+        <v>51</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="2:4">
       <c r="B177" s="1">
-        <v>140001</v>
+        <v>100023</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="178" ht="16.5" spans="1:10">
+        <v>52</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="2:4">
       <c r="B178" s="1">
-        <v>140002</v>
+        <v>100024</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="179" ht="16.5" spans="1:10">
+        <v>53</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="2:4">
       <c r="B179" s="1">
-        <v>140003</v>
+        <v>100025</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="180" ht="16.5" spans="1:10">
+        <v>54</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="2:4">
       <c r="B180" s="1">
-        <v>150000</v>
+        <v>100026</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="181" ht="16.5" spans="1:10">
+        <v>55</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="181" ht="16.5" spans="2:4">
       <c r="B181" s="1">
-        <v>150001</v>
+        <v>100027</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="182" ht="16.5" spans="1:10">
+        <v>56</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="2:4">
       <c r="B182" s="1">
-        <v>150002</v>
+        <v>100028</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="183" ht="16.5" spans="1:10">
+        <v>58</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" spans="2:4">
       <c r="B183" s="1">
-        <v>150003</v>
+        <v>100029</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="184" ht="16.5" spans="1:10">
+        <v>59</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="184" ht="16.5" spans="2:4">
       <c r="B184" s="1">
-        <v>150004</v>
+        <v>100030</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="185" ht="16.5" spans="1:10">
+        <v>60</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="185" ht="16.5" spans="2:4">
       <c r="B185" s="1">
-        <v>150005</v>
+        <v>100031</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="186" ht="16.5" spans="1:10">
+        <v>61</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="186" ht="16.5" spans="2:4">
       <c r="B186" s="1">
-        <v>150006</v>
+        <v>100032</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="187" ht="16.5" spans="1:10">
+        <v>62</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="187" ht="16.5" spans="2:4">
       <c r="B187" s="1">
-        <v>150007</v>
+        <v>100033</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="188" ht="16.5" spans="1:10">
+        <v>63</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="188" ht="16.5" spans="2:4">
       <c r="B188" s="1">
-        <v>150008</v>
+        <v>100034</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="189" ht="16.5" spans="1:10">
+        <v>65</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="189" ht="16.5" spans="2:4">
       <c r="B189" s="1">
-        <v>150009</v>
+        <v>100035</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="190" ht="16.5" spans="1:10">
-      <c r="A190" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="190" ht="16.5" spans="2:4">
       <c r="B190" s="1">
-        <v>131000</v>
+        <v>100036</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D190" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E190" s="1"/>
-      <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
-      <c r="H190" s="1"/>
-      <c r="I190" s="1"/>
-      <c r="J190" s="1"/>
-    </row>
-    <row r="191" ht="16.5" spans="1:10">
-      <c r="A191" s="1"/>
+    </row>
+    <row r="191" ht="16.5" spans="2:4">
       <c r="B191" s="1">
-        <v>131001</v>
+        <v>100037</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D191" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-    </row>
-    <row r="192" ht="16.5" spans="1:10">
-      <c r="A192" s="1"/>
+    </row>
+    <row r="192" ht="16.5" spans="2:4">
       <c r="B192" s="1">
-        <v>131002</v>
+        <v>100038</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D192" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D192" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
-      <c r="I192" s="1"/>
-      <c r="J192" s="1"/>
-    </row>
-    <row r="193" ht="16.5" spans="1:10">
-      <c r="A193" s="1"/>
+    </row>
+    <row r="193" ht="16.5" spans="2:4">
       <c r="B193" s="1">
-        <v>131003</v>
+        <v>100039</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D193" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D193" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-      <c r="H193" s="1"/>
-      <c r="I193" s="1"/>
-      <c r="J193" s="1"/>
-    </row>
-    <row r="194" ht="16.5" spans="1:10">
-      <c r="A194" s="1"/>
+    </row>
+    <row r="194" ht="16.5" spans="2:4">
       <c r="B194" s="1">
-        <v>131004</v>
+        <v>100051</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D194" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D194" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
-      <c r="I194" s="1"/>
-      <c r="J194" s="1"/>
-    </row>
-    <row r="200" ht="16.5" spans="1:10">
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
-    </row>
-    <row r="201" ht="16.5" spans="1:10">
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
-    </row>
-    <row r="202" ht="16.5" spans="1:10">
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
-    </row>
-    <row r="203" ht="16.5" spans="1:10">
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
-    </row>
-    <row r="204" ht="16.5" spans="1:10">
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
-    </row>
-    <row r="205" ht="16.5" spans="1:10">
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
-    </row>
-    <row r="206" ht="16.5" spans="1:10">
-      <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
-    </row>
-    <row r="207" ht="16.5" spans="1:10">
-      <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
-    </row>
-    <row r="208" ht="16.5" spans="1:10">
-      <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+    </row>
+    <row r="195" ht="16.5" spans="2:4">
+      <c r="B195" s="1">
+        <v>100056</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="196" ht="16.5" spans="2:4">
+      <c r="B196" s="1">
+        <v>100057</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="197" ht="16.5" spans="2:4">
+      <c r="B197" s="1">
+        <v>100058</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="198" ht="16.5" spans="2:4">
+      <c r="B198" s="1">
+        <v>100059</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="199" ht="16.5" spans="2:4">
+      <c r="B199" s="1">
+        <v>100060</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="200" ht="16.5" spans="2:4">
+      <c r="B200" s="1">
+        <v>100061</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="201" ht="16.5" spans="2:4">
+      <c r="B201" s="1">
+        <v>100062</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="202" ht="16.5" spans="2:4">
+      <c r="B202" s="1">
+        <v>100063</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="203" ht="16.5" spans="2:4">
+      <c r="B203" s="1">
+        <v>100064</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="204" ht="16.5" spans="2:4">
+      <c r="B204" s="1">
+        <v>100065</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="205" ht="16.5" spans="2:4">
+      <c r="B205" s="1">
+        <v>100066</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="206" ht="16.5" spans="2:4">
+      <c r="B206" s="1">
+        <v>100067</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="207" ht="16.5" spans="2:4">
+      <c r="B207" s="1">
+        <v>100068</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="208" ht="16.5" spans="2:4">
+      <c r="B208" s="1">
+        <v>100069</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="209" ht="16.5" spans="2:4">
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="B209" s="1">
+        <v>100070</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="210" ht="16.5" spans="2:4">
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="B210" s="1">
+        <v>100071</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="211" ht="16.5" spans="2:4">
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="B211" s="1">
+        <v>100072</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="212" ht="16.5" spans="2:4">
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="B212" s="1">
+        <v>100073</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="213" ht="16.5" spans="2:4">
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="B213" s="1">
+        <v>100074</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="214" ht="16.5" spans="2:4">
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="B214" s="1">
+        <v>100075</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="215" ht="16.5" spans="2:4">
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="B215" s="1">
+        <v>100076</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="216" ht="16.5" spans="2:4">
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="B216" s="1">
+        <v>100077</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="217" ht="16.5" spans="2:4">
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="B217" s="1">
+        <v>100078</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="218" ht="16.5" spans="2:4">
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="B218" s="1">
+        <v>100079</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="219" ht="16.5" spans="2:4">
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="B219" s="1">
+        <v>100080</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="220" ht="16.5" spans="2:4">
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="B220" s="1">
+        <v>100081</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="221" ht="16.5" spans="2:4">
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="B221" s="1">
+        <v>100082</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="222" ht="16.5" spans="2:4">
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="B222" s="1">
+        <v>100083</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="223" ht="16.5" spans="2:4">
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="B223" s="1">
+        <v>100084</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="224" ht="16.5" spans="2:4">
       <c r="B224" s="1"/>
@@ -17005,138 +16908,16 @@
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
     </row>
-    <row r="235" ht="16.5" spans="2:4">
-      <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
-    </row>
-    <row r="236" ht="16.5" spans="2:4">
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
-    </row>
-    <row r="237" ht="16.5" spans="2:4">
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
-    </row>
-    <row r="238" ht="16.5" spans="2:4">
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
-    </row>
-    <row r="239" ht="16.5" spans="2:4">
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
-    </row>
-    <row r="240" ht="16.5" spans="2:4">
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
-    </row>
-    <row r="241" ht="16.5" spans="2:4">
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
-    </row>
-    <row r="242" ht="16.5" spans="2:4">
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
-    </row>
-    <row r="243" ht="16.5" spans="2:4">
-      <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
-    </row>
-    <row r="244" ht="16.5" spans="2:4">
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
-    </row>
-    <row r="245" ht="16.5" spans="2:4">
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
-    </row>
-    <row r="246" ht="16.5" spans="2:4">
-      <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
-    </row>
-    <row r="247" ht="16.5" spans="2:4">
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
-    </row>
-    <row r="248" ht="16.5" spans="2:4">
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
-    </row>
-    <row r="249" ht="16.5" spans="2:4">
-      <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
-    </row>
-    <row r="250" ht="16.5" spans="2:4">
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
-    </row>
-    <row r="251" ht="16.5" spans="2:4">
-      <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
-    </row>
-    <row r="252" ht="16.5" spans="2:4">
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
-    </row>
-    <row r="253" ht="16.5" spans="2:4">
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
-    </row>
-    <row r="254" ht="16.5" spans="2:4">
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
-    </row>
-    <row r="255" ht="16.5" spans="2:4">
-      <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
-    </row>
-    <row r="256" ht="16.5" spans="2:4">
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
-    </row>
-    <row r="257" ht="16.5" spans="2:4">
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
-    </row>
-    <row r="258" ht="16.5" spans="2:4">
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
-    </row>
-    <row r="259" ht="16.5" spans="2:4">
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
-    </row>
-    <row r="260" spans="2:4">
-      <c r="C260" s="4"/>
-    </row>
-    <row r="261" spans="2:4">
-      <c r="C261" s="4"/>
+    <row r="235" spans="2:4">
+      <c r="C235" s="5"/>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="C236" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B$1:B$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.39375" footer="0.39375"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
   <headerFooter/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="441">
   <si>
     <t>##var</t>
   </si>
@@ -1366,6 +1366,9 @@
   </si>
   <si>
     <t>FishingProduct</t>
+  </si>
+  <si>
+    <t>Fishing</t>
   </si>
 </sst>
 </file>
@@ -16311,7 +16314,7 @@
         <v>49</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:10">
@@ -16322,7 +16325,7 @@
         <v>50</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:10">
@@ -16333,7 +16336,7 @@
         <v>51</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="2:4">
@@ -16344,7 +16347,7 @@
         <v>52</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="2:4">
@@ -16355,7 +16358,7 @@
         <v>53</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="2:4">
@@ -16366,7 +16369,7 @@
         <v>54</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="2:4">
@@ -16377,7 +16380,7 @@
         <v>55</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="181" ht="16.5" spans="2:4">
@@ -16388,7 +16391,7 @@
         <v>56</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="182" ht="16.5" spans="2:4">
@@ -16399,7 +16402,7 @@
         <v>58</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="183" ht="16.5" spans="2:4">
@@ -16410,7 +16413,7 @@
         <v>59</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="184" ht="16.5" spans="2:4">
@@ -16421,7 +16424,7 @@
         <v>60</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" ht="16.5" spans="2:4">
@@ -16432,7 +16435,7 @@
         <v>61</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="186" ht="16.5" spans="2:4">
@@ -16443,7 +16446,7 @@
         <v>62</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" ht="16.5" spans="2:4">
@@ -16454,7 +16457,7 @@
         <v>63</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" ht="16.5" spans="2:4">
@@ -16465,7 +16468,7 @@
         <v>65</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="189" ht="16.5" spans="2:4">
@@ -16476,7 +16479,7 @@
         <v>66</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" ht="16.5" spans="2:4">
@@ -16487,7 +16490,7 @@
         <v>67</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" ht="16.5" spans="2:4">
@@ -16498,7 +16501,7 @@
         <v>68</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="2:4">
@@ -16509,7 +16512,7 @@
         <v>69</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="2:4">
@@ -16520,7 +16523,7 @@
         <v>71</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" ht="16.5" spans="2:4">
@@ -16531,7 +16534,7 @@
         <v>82</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" ht="16.5" spans="2:4">
@@ -16542,7 +16545,7 @@
         <v>88</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" ht="16.5" spans="2:4">
@@ -16553,7 +16556,7 @@
         <v>89</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" ht="16.5" spans="2:4">
@@ -16564,7 +16567,7 @@
         <v>90</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" ht="16.5" spans="2:4">
@@ -16575,7 +16578,7 @@
         <v>91</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" ht="16.5" spans="2:4">
@@ -16586,7 +16589,7 @@
         <v>92</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" ht="16.5" spans="2:4">
@@ -16597,7 +16600,7 @@
         <v>93</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" ht="16.5" spans="2:4">
@@ -16608,7 +16611,7 @@
         <v>94</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" ht="16.5" spans="2:4">
@@ -16619,7 +16622,7 @@
         <v>95</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="203" ht="16.5" spans="2:4">
@@ -16630,7 +16633,7 @@
         <v>96</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="204" ht="16.5" spans="2:4">
@@ -16641,7 +16644,7 @@
         <v>97</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" ht="16.5" spans="2:4">
@@ -16652,7 +16655,7 @@
         <v>98</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="206" ht="16.5" spans="2:4">
@@ -16663,7 +16666,7 @@
         <v>99</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" ht="16.5" spans="2:4">
@@ -16674,7 +16677,7 @@
         <v>100</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="208" ht="16.5" spans="2:4">
@@ -16685,7 +16688,7 @@
         <v>101</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="209" ht="16.5" spans="2:4">
@@ -16696,7 +16699,7 @@
         <v>102</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="210" ht="16.5" spans="2:4">
@@ -16707,7 +16710,7 @@
         <v>103</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" ht="16.5" spans="2:4">
@@ -16718,7 +16721,7 @@
         <v>104</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="212" ht="16.5" spans="2:4">
@@ -16729,7 +16732,7 @@
         <v>105</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="213" ht="16.5" spans="2:4">
@@ -16740,7 +16743,7 @@
         <v>106</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="214" ht="16.5" spans="2:4">
@@ -16751,7 +16754,7 @@
         <v>107</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" ht="16.5" spans="2:4">
@@ -16762,7 +16765,7 @@
         <v>108</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="216" ht="16.5" spans="2:4">
@@ -16773,7 +16776,7 @@
         <v>109</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="217" ht="16.5" spans="2:4">
@@ -16784,7 +16787,7 @@
         <v>110</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="218" ht="16.5" spans="2:4">
@@ -16795,7 +16798,7 @@
         <v>111</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="219" ht="16.5" spans="2:4">
@@ -16806,7 +16809,7 @@
         <v>112</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="220" ht="16.5" spans="2:4">
@@ -16817,7 +16820,7 @@
         <v>113</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="221" ht="16.5" spans="2:4">
@@ -16828,7 +16831,7 @@
         <v>114</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="222" ht="16.5" spans="2:4">
@@ -16839,7 +16842,7 @@
         <v>115</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="223" ht="16.5" spans="2:4">
@@ -16850,7 +16853,7 @@
         <v>116</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="224" ht="16.5" spans="2:4">

--- a/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ItemData.xlsx
@@ -17,17 +17,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784876544" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784876544" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784876544" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784876544"/>
+      <pm:revision xmlns:pm="smNativeData" day="1785130485" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785130485" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785130485" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785130485"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="612">
   <si>
     <t>##var</t>
   </si>
@@ -1727,7 +1727,7 @@
     <t>Fish</t>
   </si>
   <si>
-    <t>IconName</t>
+    <t>DraftImageName</t>
   </si>
   <si>
     <t>BaseScore</t>
@@ -1745,13 +1745,16 @@
     <t xml:space="preserve">IsSpecial </t>
   </si>
   <si>
+    <t>FinalImageName</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
-    <t>图标名</t>
+    <t>草稿图</t>
   </si>
   <si>
     <t>线稿基础评分</t>
@@ -1767,6 +1770,9 @@
   </si>
   <si>
     <t>是否是特殊稿件</t>
+  </si>
+  <si>
+    <t>成品图</t>
   </si>
   <si>
     <t>320000.png</t>
@@ -1887,7 +1893,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -1902,7 +1908,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1918,7 +1924,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="微软雅黑" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -1934,7 +1940,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="微软雅黑" sz="240" lang="default"/>
             <pm:cs face="Times New Roman" sz="240" lang="default"/>
             <pm:ea face="SimSun" sz="240" lang="default"/>
@@ -1950,7 +1956,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="微软雅黑" sz="240" lang="default"/>
             <pm:cs face="Times New Roman" sz="240" lang="default"/>
             <pm:ea face="SimSun" sz="240" lang="default"/>
@@ -1964,7 +1970,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -1979,7 +1985,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -1994,7 +2000,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="800080" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="800080" ulstyle="single" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2008,7 +2014,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="FF0000" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="FF0000" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2023,7 +2029,7 @@
       <sz val="18"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="EEECE1" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="EEECE1" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="360" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="360" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="360" lang="default" weight="bold"/>
@@ -2038,7 +2044,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="7F7F7F" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="7F7F7F" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
@@ -2053,7 +2059,7 @@
       <sz val="15"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="EEECE1" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="EEECE1" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="300" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="300" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="300" lang="default" weight="bold"/>
@@ -2068,7 +2074,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="EEECE1" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="EEECE1" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
@@ -2083,7 +2089,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="EEECE1" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="EEECE1" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -2097,7 +2103,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="3F3F76" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="3F3F76" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2112,7 +2118,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="3F3F3F" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="3F3F3F" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -2127,7 +2133,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="FA7D00" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="FA7D00" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -2142,7 +2148,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -2156,7 +2162,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="FA7D00" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="FA7D00" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2171,7 +2177,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -2185,7 +2191,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="006100" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="006100" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2199,7 +2205,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="9C0006" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="9C0006" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2213,7 +2219,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="9C6500" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="9C6500" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2227,7 +2233,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="SimSun" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -2249,7 +2255,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2266,7 +2272,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFCC99" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFCC99" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2277,7 +2283,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2288,7 +2294,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2299,7 +2305,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2316,7 +2322,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2327,7 +2333,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2338,7 +2344,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2349,7 +2355,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="004F81BD" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="004F81BD" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2360,7 +2366,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2371,7 +2377,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00B8CCE4" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00B8CCE4" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2382,7 +2388,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="0095B3D7" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="0095B3D7" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2393,7 +2399,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00C0504D" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00C0504D" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2404,7 +2410,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00F2DCDB" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00F2DCDB" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2415,7 +2421,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00E6B8B7" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00E6B8B7" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2426,7 +2432,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00DA9694" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00DA9694" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2437,7 +2443,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="009BBB59" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="009BBB59" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2448,7 +2454,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00EBF1DC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00EBF1DC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2459,7 +2465,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00D7E3BB" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00D7E3BB" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2470,7 +2476,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00C2D69A" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00C2D69A" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2481,7 +2487,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="008064A2" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="008064A2" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2492,7 +2498,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00E4DFEC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00E4DFEC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2503,7 +2509,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00CCC0DA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00CCC0DA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2514,7 +2520,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00B1A0C7" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00B1A0C7" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2525,7 +2531,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="004BACC6" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="004BACC6" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2536,7 +2542,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00DAEEF3" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00DAEEF3" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2547,7 +2553,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00B7DEE8" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00B7DEE8" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2558,7 +2564,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="0092CDDC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="0092CDDC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2569,7 +2575,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00F79646" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00F79646" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2580,7 +2586,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FDE9D9" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FDE9D9" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2591,7 +2597,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FCD5B4" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FCD5B4" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2602,7 +2608,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FABF8F" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FABF8F" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2616,7 +2622,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2627,7 +2633,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -2649,7 +2655,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2668,7 +2674,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
@@ -2692,7 +2698,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="4F81BD"/>
           </pm:border>
         </ext>
@@ -2713,7 +2719,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="A6BEDD"/>
           </pm:border>
         </ext>
@@ -2734,7 +2740,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
@@ -2758,7 +2764,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
@@ -2782,7 +2788,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
@@ -2806,7 +2812,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
             <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
             <pm:line position="left" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
@@ -2830,7 +2836,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="FF8001"/>
           </pm:border>
         </ext>
@@ -2851,7 +2857,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="4F81BD"/>
             <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="4F81BD"/>
           </pm:border>
@@ -2873,7 +2879,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2892,7 +2898,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2911,7 +2917,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2930,7 +2936,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2949,7 +2955,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2968,7 +2974,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -2987,7 +2993,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3006,7 +3012,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3025,7 +3031,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3044,7 +3050,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3063,7 +3069,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3082,7 +3088,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3101,7 +3107,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3120,7 +3126,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3139,7 +3145,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3158,7 +3164,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3177,7 +3183,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3196,7 +3202,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3215,7 +3221,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3234,7 +3240,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3253,7 +3259,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3272,7 +3278,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3291,7 +3297,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3310,7 +3316,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3329,7 +3335,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3348,7 +3354,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3367,7 +3373,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3386,7 +3392,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -3410,7 +3416,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544">
+          <pm:border xmlns:pm="smNativeData" id="1785130485">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -3434,7 +3440,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784876544"/>
+          <pm:border xmlns:pm="smNativeData" id="1785130485"/>
         </ext>
       </extLst>
     </border>
@@ -3824,7 +3830,7 @@
         <color rgb="FF9C0006"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1784876544" fgClr="9C0006">
+            <pm:charSpec xmlns:pm="smNativeData" id="1785130485" fgClr="9C0006">
               <pm:latin/>
               <pm:cs/>
               <pm:ea/>
@@ -3837,7 +3843,7 @@
           <bgColor rgb="FFFFC7CE"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1784876544" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+              <pm:shade xmlns:pm="smNativeData" id="1785130485" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
             </ext>
           </extLst>
         </patternFill>
@@ -3847,10 +3853,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784876544" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785130485" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784876544" count="44">
+      <pm:colors xmlns:pm="smNativeData" id="1785130485" count="44">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="800080"/>
         <pm:color name="颜色 26" rgb="EEECE1"/>
@@ -15098,7 +15104,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784876544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785130485" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -15107,16 +15113,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784876544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785130485" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -16238,7 +16244,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784876544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785130485" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -16247,16 +16253,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784876544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785130485" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -16892,7 +16898,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784876544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785130485" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -16901,16 +16907,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784876544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785130485" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -19621,7 +19627,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784876544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785130485" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -19630,16 +19636,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784876544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785130485" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -19650,16 +19656,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="4" max="4" width="12.310345" customWidth="1"/>
+    <col min="3" max="3" width="14.379310" customWidth="1"/>
+    <col min="4" max="4" width="17.051724" customWidth="1"/>
     <col min="5" max="5" width="18.000000" customWidth="1"/>
     <col min="9" max="9" width="14.896552" customWidth="1"/>
     <col min="10" max="10" width="15.327586" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
@@ -19687,8 +19694,11 @@
       <c r="I1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="59" t="s">
         <v>10</v>
       </c>
@@ -19705,19 +19715,22 @@
         <v>14</v>
       </c>
       <c r="F2" s="59" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2" s="59" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>574</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="59" t="s">
         <v>17</v>
       </c>
@@ -19728,25 +19741,28 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H3" s="59" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>580</v>
+      </c>
+      <c r="J3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
       <c r="B4" t="n">
         <v>320000</v>
       </c>
@@ -19754,7 +19770,7 @@
         <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E4" t="n">
         <v>50</v>
@@ -19771,8 +19787,11 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:9">
+      <c r="J4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" t="n">
         <v>320001</v>
       </c>
@@ -19780,7 +19799,7 @@
         <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -19797,8 +19816,11 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:9">
+      <c r="J5" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" t="n">
         <v>320002</v>
       </c>
@@ -19806,7 +19828,7 @@
         <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E6" t="n">
         <v>50</v>
@@ -19823,8 +19845,11 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:9">
+      <c r="J6" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" t="n">
         <v>320003</v>
       </c>
@@ -19832,7 +19857,7 @@
         <v>372</v>
       </c>
       <c r="D7" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
@@ -19849,8 +19874,11 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:9">
+      <c r="J7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="B8" t="n">
         <v>320004</v>
       </c>
@@ -19858,7 +19886,7 @@
         <v>376</v>
       </c>
       <c r="D8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E8" t="n">
         <v>50</v>
@@ -19875,8 +19903,11 @@
       <c r="I8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:9">
+      <c r="J8" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" t="n">
         <v>320005</v>
       </c>
@@ -19884,7 +19915,7 @@
         <v>380</v>
       </c>
       <c r="D9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -19901,8 +19932,11 @@
       <c r="I9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="2:9">
+      <c r="J9" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" t="n">
         <v>320006</v>
       </c>
@@ -19910,7 +19944,7 @@
         <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E10" t="n">
         <v>50</v>
@@ -19927,8 +19961,11 @@
       <c r="I10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:9">
+      <c r="J10" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" t="n">
         <v>320007</v>
       </c>
@@ -19936,7 +19973,7 @@
         <v>388</v>
       </c>
       <c r="D11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E11" t="n">
         <v>50</v>
@@ -19953,8 +19990,11 @@
       <c r="I11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:9">
+      <c r="J11" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
       <c r="B12" t="n">
         <v>320008</v>
       </c>
@@ -19962,7 +20002,7 @@
         <v>392</v>
       </c>
       <c r="D12" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E12" t="n">
         <v>50</v>
@@ -19979,8 +20019,11 @@
       <c r="I12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:9">
+      <c r="J12" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" t="n">
         <v>320009</v>
       </c>
@@ -19988,7 +20031,7 @@
         <v>396</v>
       </c>
       <c r="D13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E13" t="n">
         <v>50</v>
@@ -20005,8 +20048,11 @@
       <c r="I13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:9">
+      <c r="J13" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
       <c r="B14" t="n">
         <v>320010</v>
       </c>
@@ -20014,7 +20060,7 @@
         <v>400</v>
       </c>
       <c r="D14" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E14" t="n">
         <v>50</v>
@@ -20031,8 +20077,11 @@
       <c r="I14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:9">
+      <c r="J14" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="B15" t="n">
         <v>320011</v>
       </c>
@@ -20040,7 +20089,7 @@
         <v>404</v>
       </c>
       <c r="D15" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E15" t="n">
         <v>50</v>
@@ -20057,8 +20106,11 @@
       <c r="I15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:9">
+      <c r="J15" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
       <c r="B16" t="n">
         <v>320012</v>
       </c>
@@ -20066,7 +20118,7 @@
         <v>408</v>
       </c>
       <c r="D16" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E16" t="n">
         <v>60</v>
@@ -20083,8 +20135,11 @@
       <c r="I16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="J16" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" t="n">
         <v>320013</v>
       </c>
@@ -20092,7 +20147,7 @@
         <v>413</v>
       </c>
       <c r="D17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E17" t="n">
         <v>60</v>
@@ -20109,8 +20164,11 @@
       <c r="I17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:9">
+      <c r="J17" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="n">
         <v>320014</v>
       </c>
@@ -20118,7 +20176,7 @@
         <v>417</v>
       </c>
       <c r="D18" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E18" t="n">
         <v>60</v>
@@ -20135,8 +20193,11 @@
       <c r="I18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="J18" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="n">
         <v>320015</v>
       </c>
@@ -20144,7 +20205,7 @@
         <v>421</v>
       </c>
       <c r="D19" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E19" t="n">
         <v>60</v>
@@ -20161,8 +20222,11 @@
       <c r="I19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:9">
+      <c r="J19" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" t="n">
         <v>320016</v>
       </c>
@@ -20170,7 +20234,7 @@
         <v>425</v>
       </c>
       <c r="D20" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E20" t="n">
         <v>60</v>
@@ -20187,8 +20251,11 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:9">
+      <c r="J20" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" t="n">
         <v>320017</v>
       </c>
@@ -20196,7 +20263,7 @@
         <v>429</v>
       </c>
       <c r="D21" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E21" t="n">
         <v>60</v>
@@ -20213,8 +20280,11 @@
       <c r="I21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:9">
+      <c r="J21" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" t="n">
         <v>320018</v>
       </c>
@@ -20222,7 +20292,7 @@
         <v>433</v>
       </c>
       <c r="D22" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E22" t="n">
         <v>60</v>
@@ -20239,8 +20309,11 @@
       <c r="I22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="J22" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" t="n">
         <v>320019</v>
       </c>
@@ -20248,7 +20321,7 @@
         <v>437</v>
       </c>
       <c r="D23" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E23" t="n">
         <v>60</v>
@@ -20265,8 +20338,11 @@
       <c r="I23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:9">
+      <c r="J23" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" t="n">
         <v>320020</v>
       </c>
@@ -20274,7 +20350,7 @@
         <v>441</v>
       </c>
       <c r="D24" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E24" t="n">
         <v>70</v>
@@ -20291,8 +20367,11 @@
       <c r="I24" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:9">
+      <c r="J24" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" t="n">
         <v>320021</v>
       </c>
@@ -20300,7 +20379,7 @@
         <v>446</v>
       </c>
       <c r="D25" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E25" t="n">
         <v>70</v>
@@ -20317,8 +20396,11 @@
       <c r="I25" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:9">
+      <c r="J25" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
       <c r="B26" t="n">
         <v>320022</v>
       </c>
@@ -20326,7 +20408,7 @@
         <v>450</v>
       </c>
       <c r="D26" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E26" t="n">
         <v>70</v>
@@ -20343,8 +20425,11 @@
       <c r="I26" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:9">
+      <c r="J26" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" t="n">
         <v>320023</v>
       </c>
@@ -20352,7 +20437,7 @@
         <v>454</v>
       </c>
       <c r="D27" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E27" t="n">
         <v>70</v>
@@ -20369,8 +20454,11 @@
       <c r="I27" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:9">
+      <c r="J27" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" t="n">
         <v>320024</v>
       </c>
@@ -20378,7 +20466,7 @@
         <v>458</v>
       </c>
       <c r="D28" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E28" t="n">
         <v>70</v>
@@ -20395,8 +20483,11 @@
       <c r="I28" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:9">
+      <c r="J28" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" t="n">
         <v>320025</v>
       </c>
@@ -20404,7 +20495,7 @@
         <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E29" t="n">
         <v>70</v>
@@ -20421,8 +20512,11 @@
       <c r="I29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:9">
+      <c r="J29" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" t="n">
         <v>320026</v>
       </c>
@@ -20430,7 +20524,7 @@
         <v>466</v>
       </c>
       <c r="D30" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E30" t="n">
         <v>80</v>
@@ -20447,8 +20541,11 @@
       <c r="I30" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:9">
+      <c r="J30" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" t="n">
         <v>320027</v>
       </c>
@@ -20456,7 +20553,7 @@
         <v>471</v>
       </c>
       <c r="D31" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E31" t="n">
         <v>80</v>
@@ -20473,8 +20570,11 @@
       <c r="I31" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:9">
+      <c r="J31" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" t="n">
         <v>320028</v>
       </c>
@@ -20482,7 +20582,7 @@
         <v>475</v>
       </c>
       <c r="D32" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E32" t="n">
         <v>80</v>
@@ -20499,8 +20599,11 @@
       <c r="I32" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="J32" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" t="n">
         <v>320029</v>
       </c>
@@ -20508,7 +20611,7 @@
         <v>479</v>
       </c>
       <c r="D33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E33" t="n">
         <v>90</v>
@@ -20524,13 +20627,16 @@
       </c>
       <c r="I33" t="b">
         <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784876544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785130485" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -20539,16 +20645,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784876544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784876544" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785130485" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785130485" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784876544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785130485" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
